--- a/gcc-x64/Scattered unsuccessful looukp.xlsx
+++ b/gcc-x64/Scattered unsuccessful looukp.xlsx
@@ -5079,19 +5079,19 @@
         <v>10000</v>
       </c>
       <c r="B2" t="n">
-        <v>3.15631</v>
+        <v>3.52341</v>
       </c>
       <c r="C2" t="n">
-        <v>3.42922</v>
+        <v>2.26914</v>
       </c>
       <c r="D2" t="n">
-        <v>13.17</v>
+        <v>13.477</v>
       </c>
       <c r="E2" t="n">
-        <v>2.5774</v>
+        <v>2.57438</v>
       </c>
       <c r="F2" t="n">
-        <v>2.74288</v>
+        <v>2.88443</v>
       </c>
     </row>
     <row r="3">
@@ -5099,19 +5099,19 @@
         <v>10500</v>
       </c>
       <c r="B3" t="n">
-        <v>3.30184</v>
+        <v>3.57743</v>
       </c>
       <c r="C3" t="n">
-        <v>3.59273</v>
+        <v>2.29064</v>
       </c>
       <c r="D3" t="n">
-        <v>13.5672</v>
+        <v>13.7907</v>
       </c>
       <c r="E3" t="n">
-        <v>2.54056</v>
+        <v>2.61687</v>
       </c>
       <c r="F3" t="n">
-        <v>2.7595</v>
+        <v>2.86336</v>
       </c>
     </row>
     <row r="4">
@@ -5119,19 +5119,19 @@
         <v>11025</v>
       </c>
       <c r="B4" t="n">
-        <v>3.38591</v>
+        <v>3.86468</v>
       </c>
       <c r="C4" t="n">
-        <v>3.83653</v>
+        <v>2.31755</v>
       </c>
       <c r="D4" t="n">
-        <v>14.0457</v>
+        <v>14.5114</v>
       </c>
       <c r="E4" t="n">
-        <v>2.58214</v>
+        <v>2.60123</v>
       </c>
       <c r="F4" t="n">
-        <v>2.80495</v>
+        <v>2.78421</v>
       </c>
     </row>
     <row r="5">
@@ -5139,19 +5139,19 @@
         <v>11576</v>
       </c>
       <c r="B5" t="n">
-        <v>4.00517</v>
+        <v>4.13328</v>
       </c>
       <c r="C5" t="n">
-        <v>4.30181</v>
+        <v>2.58705</v>
       </c>
       <c r="D5" t="n">
-        <v>14.4806</v>
+        <v>15.2216</v>
       </c>
       <c r="E5" t="n">
-        <v>2.56503</v>
+        <v>2.56175</v>
       </c>
       <c r="F5" t="n">
-        <v>2.60256</v>
+        <v>2.77187</v>
       </c>
     </row>
     <row r="6">
@@ -5159,19 +5159,19 @@
         <v>12154</v>
       </c>
       <c r="B6" t="n">
-        <v>5.42597</v>
+        <v>5.19673</v>
       </c>
       <c r="C6" t="n">
-        <v>5.67812</v>
+        <v>3.64762</v>
       </c>
       <c r="D6" t="n">
-        <v>15.2105</v>
+        <v>15.7325</v>
       </c>
       <c r="E6" t="n">
-        <v>2.57031</v>
+        <v>2.5485</v>
       </c>
       <c r="F6" t="n">
-        <v>2.87285</v>
+        <v>2.87095</v>
       </c>
     </row>
     <row r="7">
@@ -5179,19 +5179,19 @@
         <v>12760</v>
       </c>
       <c r="B7" t="n">
-        <v>7.02754</v>
+        <v>7.26818</v>
       </c>
       <c r="C7" t="n">
-        <v>7.73813</v>
+        <v>6.02216</v>
       </c>
       <c r="D7" t="n">
-        <v>10.2546</v>
+        <v>10.9824</v>
       </c>
       <c r="E7" t="n">
-        <v>2.94692</v>
+        <v>2.92088</v>
       </c>
       <c r="F7" t="n">
-        <v>3.48502</v>
+        <v>3.25776</v>
       </c>
     </row>
     <row r="8">
@@ -5199,19 +5199,19 @@
         <v>13396</v>
       </c>
       <c r="B8" t="n">
-        <v>10.6448</v>
+        <v>10.3193</v>
       </c>
       <c r="C8" t="n">
-        <v>10.9905</v>
+        <v>2.04433</v>
       </c>
       <c r="D8" t="n">
-        <v>10.8248</v>
+        <v>11.5523</v>
       </c>
       <c r="E8" t="n">
-        <v>4.81245</v>
+        <v>4.85496</v>
       </c>
       <c r="F8" t="n">
-        <v>5.33091</v>
+        <v>5.15047</v>
       </c>
     </row>
     <row r="9">
@@ -5219,19 +5219,19 @@
         <v>14063</v>
       </c>
       <c r="B9" t="n">
-        <v>15.6091</v>
+        <v>14.6827</v>
       </c>
       <c r="C9" t="n">
-        <v>15.3938</v>
+        <v>2.0654</v>
       </c>
       <c r="D9" t="n">
-        <v>11.4778</v>
+        <v>12.2144</v>
       </c>
       <c r="E9" t="n">
-        <v>2.55696</v>
+        <v>2.59173</v>
       </c>
       <c r="F9" t="n">
-        <v>2.7312</v>
+        <v>2.72773</v>
       </c>
     </row>
     <row r="10">
@@ -5239,19 +5239,19 @@
         <v>14763</v>
       </c>
       <c r="B10" t="n">
-        <v>3.02714</v>
+        <v>3.19442</v>
       </c>
       <c r="C10" t="n">
-        <v>3.30632</v>
+        <v>2.08943</v>
       </c>
       <c r="D10" t="n">
-        <v>11.8129</v>
+        <v>12.8079</v>
       </c>
       <c r="E10" t="n">
-        <v>2.60624</v>
+        <v>2.60932</v>
       </c>
       <c r="F10" t="n">
-        <v>2.74117</v>
+        <v>2.74182</v>
       </c>
     </row>
     <row r="11">
@@ -5259,19 +5259,19 @@
         <v>15498</v>
       </c>
       <c r="B11" t="n">
-        <v>3.07118</v>
+        <v>3.23282</v>
       </c>
       <c r="C11" t="n">
-        <v>3.36856</v>
+        <v>2.09641</v>
       </c>
       <c r="D11" t="n">
-        <v>12.3885</v>
+        <v>13.3346</v>
       </c>
       <c r="E11" t="n">
-        <v>2.62822</v>
+        <v>2.63828</v>
       </c>
       <c r="F11" t="n">
-        <v>2.772</v>
+        <v>2.78005</v>
       </c>
     </row>
     <row r="12">
@@ -5279,19 +5279,19 @@
         <v>16269</v>
       </c>
       <c r="B12" t="n">
-        <v>3.14981</v>
+        <v>3.28637</v>
       </c>
       <c r="C12" t="n">
-        <v>3.43464</v>
+        <v>2.16797</v>
       </c>
       <c r="D12" t="n">
-        <v>12.8516</v>
+        <v>13.8148</v>
       </c>
       <c r="E12" t="n">
-        <v>2.62925</v>
+        <v>2.64039</v>
       </c>
       <c r="F12" t="n">
-        <v>2.79335</v>
+        <v>2.80169</v>
       </c>
     </row>
     <row r="13">
@@ -5299,19 +5299,19 @@
         <v>17078</v>
       </c>
       <c r="B13" t="n">
-        <v>3.22354</v>
+        <v>3.34401</v>
       </c>
       <c r="C13" t="n">
-        <v>3.47967</v>
+        <v>2.20496</v>
       </c>
       <c r="D13" t="n">
-        <v>13.325</v>
+        <v>14.2878</v>
       </c>
       <c r="E13" t="n">
-        <v>2.6415</v>
+        <v>2.66176</v>
       </c>
       <c r="F13" t="n">
-        <v>2.81638</v>
+        <v>2.82413</v>
       </c>
     </row>
     <row r="14">
@@ -5319,19 +5319,19 @@
         <v>17927</v>
       </c>
       <c r="B14" t="n">
-        <v>3.31745</v>
+        <v>3.46761</v>
       </c>
       <c r="C14" t="n">
-        <v>3.57932</v>
+        <v>2.26771</v>
       </c>
       <c r="D14" t="n">
-        <v>13.8141</v>
+        <v>14.781</v>
       </c>
       <c r="E14" t="n">
-        <v>2.67325</v>
+        <v>2.66176</v>
       </c>
       <c r="F14" t="n">
-        <v>2.82896</v>
+        <v>2.84786</v>
       </c>
     </row>
     <row r="15">
@@ -5339,19 +5339,19 @@
         <v>18818</v>
       </c>
       <c r="B15" t="n">
-        <v>3.35654</v>
+        <v>3.5267</v>
       </c>
       <c r="C15" t="n">
-        <v>3.66151</v>
+        <v>2.33581</v>
       </c>
       <c r="D15" t="n">
-        <v>14.2299</v>
+        <v>15.2013</v>
       </c>
       <c r="E15" t="n">
-        <v>2.66408</v>
+        <v>2.68524</v>
       </c>
       <c r="F15" t="n">
-        <v>2.86923</v>
+        <v>2.88405</v>
       </c>
     </row>
     <row r="16">
@@ -5359,19 +5359,19 @@
         <v>19753</v>
       </c>
       <c r="B16" t="n">
-        <v>3.47483</v>
+        <v>3.68715</v>
       </c>
       <c r="C16" t="n">
-        <v>3.82698</v>
+        <v>2.39985</v>
       </c>
       <c r="D16" t="n">
-        <v>14.746</v>
+        <v>15.5416</v>
       </c>
       <c r="E16" t="n">
-        <v>2.70756</v>
+        <v>2.70858</v>
       </c>
       <c r="F16" t="n">
-        <v>2.9223</v>
+        <v>2.92648</v>
       </c>
     </row>
     <row r="17">
@@ -5379,19 +5379,19 @@
         <v>20734</v>
       </c>
       <c r="B17" t="n">
-        <v>3.64004</v>
+        <v>3.88296</v>
       </c>
       <c r="C17" t="n">
-        <v>4.03059</v>
+        <v>2.53108</v>
       </c>
       <c r="D17" t="n">
-        <v>15.0589</v>
+        <v>16.0473</v>
       </c>
       <c r="E17" t="n">
-        <v>2.73662</v>
+        <v>2.72336</v>
       </c>
       <c r="F17" t="n">
-        <v>2.94673</v>
+        <v>2.97822</v>
       </c>
     </row>
     <row r="18">
@@ -5399,19 +5399,19 @@
         <v>21764</v>
       </c>
       <c r="B18" t="n">
-        <v>4.18777</v>
+        <v>4.14155</v>
       </c>
       <c r="C18" t="n">
-        <v>4.43516</v>
+        <v>2.79268</v>
       </c>
       <c r="D18" t="n">
-        <v>15.5695</v>
+        <v>16.4357</v>
       </c>
       <c r="E18" t="n">
-        <v>2.60497</v>
+        <v>2.74665</v>
       </c>
       <c r="F18" t="n">
-        <v>2.92003</v>
+        <v>2.98112</v>
       </c>
     </row>
     <row r="19">
@@ -5419,19 +5419,19 @@
         <v>22845</v>
       </c>
       <c r="B19" t="n">
-        <v>4.89499</v>
+        <v>4.68738</v>
       </c>
       <c r="C19" t="n">
-        <v>5.23268</v>
+        <v>3.29823</v>
       </c>
       <c r="D19" t="n">
-        <v>16.0255</v>
+        <v>16.9274</v>
       </c>
       <c r="E19" t="n">
-        <v>2.72834</v>
+        <v>2.74949</v>
       </c>
       <c r="F19" t="n">
-        <v>3.01902</v>
+        <v>3.01833</v>
       </c>
     </row>
     <row r="20">
@@ -5439,19 +5439,19 @@
         <v>23980</v>
       </c>
       <c r="B20" t="n">
-        <v>6.25394</v>
+        <v>5.43337</v>
       </c>
       <c r="C20" t="n">
-        <v>6.352</v>
+        <v>4.44666</v>
       </c>
       <c r="D20" t="n">
-        <v>16.4696</v>
+        <v>17.2481</v>
       </c>
       <c r="E20" t="n">
-        <v>3.06867</v>
+        <v>3.09395</v>
       </c>
       <c r="F20" t="n">
-        <v>3.38662</v>
+        <v>3.42193</v>
       </c>
     </row>
     <row r="21">
@@ -5459,19 +5459,19 @@
         <v>25171</v>
       </c>
       <c r="B21" t="n">
-        <v>7.96232</v>
+        <v>7.14319</v>
       </c>
       <c r="C21" t="n">
-        <v>8.057090000000001</v>
+        <v>6.35117</v>
       </c>
       <c r="D21" t="n">
-        <v>11.7427</v>
+        <v>12.1733</v>
       </c>
       <c r="E21" t="n">
-        <v>3.99202</v>
+        <v>4.08928</v>
       </c>
       <c r="F21" t="n">
-        <v>4.34904</v>
+        <v>4.34871</v>
       </c>
     </row>
     <row r="22">
@@ -5479,19 +5479,19 @@
         <v>26421</v>
       </c>
       <c r="B22" t="n">
-        <v>11.014</v>
+        <v>10.0274</v>
       </c>
       <c r="C22" t="n">
-        <v>11.2538</v>
+        <v>2.10188</v>
       </c>
       <c r="D22" t="n">
-        <v>12.2044</v>
+        <v>12.6375</v>
       </c>
       <c r="E22" t="n">
-        <v>5.96133</v>
+        <v>5.96108</v>
       </c>
       <c r="F22" t="n">
-        <v>6.17919</v>
+        <v>6.21624</v>
       </c>
     </row>
     <row r="23">
@@ -5499,19 +5499,19 @@
         <v>27733</v>
       </c>
       <c r="B23" t="n">
-        <v>14.1111</v>
+        <v>13.8082</v>
       </c>
       <c r="C23" t="n">
-        <v>14.4672</v>
+        <v>2.17084</v>
       </c>
       <c r="D23" t="n">
-        <v>12.6985</v>
+        <v>13.1758</v>
       </c>
       <c r="E23" t="n">
-        <v>2.6705</v>
+        <v>2.68286</v>
       </c>
       <c r="F23" t="n">
-        <v>2.85196</v>
+        <v>2.88796</v>
       </c>
     </row>
     <row r="24">
@@ -5519,19 +5519,19 @@
         <v>29110</v>
       </c>
       <c r="B24" t="n">
-        <v>3.20718</v>
+        <v>3.35072</v>
       </c>
       <c r="C24" t="n">
-        <v>3.53007</v>
+        <v>2.19587</v>
       </c>
       <c r="D24" t="n">
-        <v>13.2002</v>
+        <v>13.7104</v>
       </c>
       <c r="E24" t="n">
-        <v>2.68566</v>
+        <v>2.69618</v>
       </c>
       <c r="F24" t="n">
-        <v>2.88648</v>
+        <v>2.92115</v>
       </c>
     </row>
     <row r="25">
@@ -5539,19 +5539,19 @@
         <v>30555</v>
       </c>
       <c r="B25" t="n">
-        <v>3.26451</v>
+        <v>3.41035</v>
       </c>
       <c r="C25" t="n">
-        <v>3.61485</v>
+        <v>2.20066</v>
       </c>
       <c r="D25" t="n">
-        <v>13.683</v>
+        <v>14.1952</v>
       </c>
       <c r="E25" t="n">
-        <v>2.69679</v>
+        <v>2.73155</v>
       </c>
       <c r="F25" t="n">
-        <v>2.91401</v>
+        <v>2.95658</v>
       </c>
     </row>
     <row r="26">
@@ -5559,19 +5559,19 @@
         <v>32072</v>
       </c>
       <c r="B26" t="n">
-        <v>3.31223</v>
+        <v>3.49789</v>
       </c>
       <c r="C26" t="n">
-        <v>3.69677</v>
+        <v>2.22737</v>
       </c>
       <c r="D26" t="n">
-        <v>14.1313</v>
+        <v>14.6111</v>
       </c>
       <c r="E26" t="n">
-        <v>2.7334</v>
+        <v>2.74304</v>
       </c>
       <c r="F26" t="n">
-        <v>2.95474</v>
+        <v>3.00811</v>
       </c>
     </row>
     <row r="27">
@@ -5579,19 +5579,19 @@
         <v>33664</v>
       </c>
       <c r="B27" t="n">
-        <v>3.38875</v>
+        <v>3.58104</v>
       </c>
       <c r="C27" t="n">
-        <v>3.80109</v>
+        <v>2.29376</v>
       </c>
       <c r="D27" t="n">
-        <v>14.6088</v>
+        <v>15.1413</v>
       </c>
       <c r="E27" t="n">
-        <v>2.76314</v>
+        <v>2.77362</v>
       </c>
       <c r="F27" t="n">
-        <v>3.02013</v>
+        <v>3.04671</v>
       </c>
     </row>
     <row r="28">
@@ -5599,19 +5599,19 @@
         <v>35335</v>
       </c>
       <c r="B28" t="n">
-        <v>3.50823</v>
+        <v>3.63675</v>
       </c>
       <c r="C28" t="n">
-        <v>3.95092</v>
+        <v>2.36584</v>
       </c>
       <c r="D28" t="n">
-        <v>15.0055</v>
+        <v>15.5996</v>
       </c>
       <c r="E28" t="n">
-        <v>2.78457</v>
+        <v>2.81077</v>
       </c>
       <c r="F28" t="n">
-        <v>3.07837</v>
+        <v>3.10016</v>
       </c>
     </row>
     <row r="29">
@@ -5619,19 +5619,19 @@
         <v>37089</v>
       </c>
       <c r="B29" t="n">
-        <v>3.60166</v>
+        <v>3.76412</v>
       </c>
       <c r="C29" t="n">
-        <v>4.07283</v>
+        <v>2.44347</v>
       </c>
       <c r="D29" t="n">
-        <v>15.5109</v>
+        <v>16.0987</v>
       </c>
       <c r="E29" t="n">
-        <v>2.84176</v>
+        <v>2.8509</v>
       </c>
       <c r="F29" t="n">
-        <v>3.14999</v>
+        <v>3.16359</v>
       </c>
     </row>
     <row r="30">
@@ -5639,19 +5639,19 @@
         <v>38930</v>
       </c>
       <c r="B30" t="n">
-        <v>3.78731</v>
+        <v>3.92218</v>
       </c>
       <c r="C30" t="n">
-        <v>4.28846</v>
+        <v>2.571</v>
       </c>
       <c r="D30" t="n">
-        <v>15.9656</v>
+        <v>16.5611</v>
       </c>
       <c r="E30" t="n">
-        <v>2.86308</v>
+        <v>2.90341</v>
       </c>
       <c r="F30" t="n">
-        <v>3.21068</v>
+        <v>3.21124</v>
       </c>
     </row>
     <row r="31">
@@ -5659,19 +5659,19 @@
         <v>40863</v>
       </c>
       <c r="B31" t="n">
-        <v>4.03903</v>
+        <v>4.21782</v>
       </c>
       <c r="C31" t="n">
-        <v>4.54483</v>
+        <v>2.7307</v>
       </c>
       <c r="D31" t="n">
-        <v>16.3721</v>
+        <v>17.0278</v>
       </c>
       <c r="E31" t="n">
-        <v>2.94742</v>
+        <v>2.95638</v>
       </c>
       <c r="F31" t="n">
-        <v>3.30956</v>
+        <v>3.30651</v>
       </c>
     </row>
     <row r="32">
@@ -5679,19 +5679,19 @@
         <v>42892</v>
       </c>
       <c r="B32" t="n">
-        <v>4.51092</v>
+        <v>4.64101</v>
       </c>
       <c r="C32" t="n">
-        <v>4.99615</v>
+        <v>3.04028</v>
       </c>
       <c r="D32" t="n">
-        <v>16.7968</v>
+        <v>17.4349</v>
       </c>
       <c r="E32" t="n">
-        <v>2.99619</v>
+        <v>3.02553</v>
       </c>
       <c r="F32" t="n">
-        <v>3.38445</v>
+        <v>3.39808</v>
       </c>
     </row>
     <row r="33">
@@ -5699,19 +5699,19 @@
         <v>45022</v>
       </c>
       <c r="B33" t="n">
-        <v>5.17786</v>
+        <v>5.30542</v>
       </c>
       <c r="C33" t="n">
-        <v>5.51006</v>
+        <v>3.59433</v>
       </c>
       <c r="D33" t="n">
-        <v>17.1024</v>
+        <v>17.8794</v>
       </c>
       <c r="E33" t="n">
-        <v>3.13392</v>
+        <v>3.15883</v>
       </c>
       <c r="F33" t="n">
-        <v>3.5384</v>
+        <v>3.52918</v>
       </c>
     </row>
     <row r="34">
@@ -5719,19 +5719,19 @@
         <v>47258</v>
       </c>
       <c r="B34" t="n">
-        <v>6.26833</v>
+        <v>6.22424</v>
       </c>
       <c r="C34" t="n">
-        <v>6.48888</v>
+        <v>4.62483</v>
       </c>
       <c r="D34" t="n">
-        <v>17.6221</v>
+        <v>18.3264</v>
       </c>
       <c r="E34" t="n">
-        <v>3.61421</v>
+        <v>3.63888</v>
       </c>
       <c r="F34" t="n">
-        <v>3.98861</v>
+        <v>4.00706</v>
       </c>
     </row>
     <row r="35">
@@ -5739,19 +5739,19 @@
         <v>49605</v>
       </c>
       <c r="B35" t="n">
-        <v>7.6662</v>
+        <v>7.73692</v>
       </c>
       <c r="C35" t="n">
-        <v>7.82742</v>
+        <v>6.05465</v>
       </c>
       <c r="D35" t="n">
-        <v>12.2292</v>
+        <v>12.7184</v>
       </c>
       <c r="E35" t="n">
-        <v>4.47195</v>
+        <v>4.49826</v>
       </c>
       <c r="F35" t="n">
-        <v>4.79998</v>
+        <v>4.83719</v>
       </c>
     </row>
     <row r="36">
@@ -5759,19 +5759,19 @@
         <v>52069</v>
       </c>
       <c r="B36" t="n">
-        <v>9.82155</v>
+        <v>9.706429999999999</v>
       </c>
       <c r="C36" t="n">
-        <v>9.967689999999999</v>
+        <v>8.251950000000001</v>
       </c>
       <c r="D36" t="n">
-        <v>12.6587</v>
+        <v>13.1726</v>
       </c>
       <c r="E36" t="n">
-        <v>5.61529</v>
+        <v>5.64227</v>
       </c>
       <c r="F36" t="n">
-        <v>5.93739</v>
+        <v>5.93946</v>
       </c>
     </row>
     <row r="37">
@@ -5779,19 +5779,19 @@
         <v>54656</v>
       </c>
       <c r="B37" t="n">
-        <v>13.3794</v>
+        <v>13.0183</v>
       </c>
       <c r="C37" t="n">
-        <v>14.0718</v>
+        <v>2.14569</v>
       </c>
       <c r="D37" t="n">
-        <v>13.1006</v>
+        <v>13.6492</v>
       </c>
       <c r="E37" t="n">
-        <v>2.74663</v>
+        <v>2.74764</v>
       </c>
       <c r="F37" t="n">
-        <v>3.03041</v>
+        <v>3.04121</v>
       </c>
     </row>
     <row r="38">
@@ -5799,19 +5799,19 @@
         <v>57372</v>
       </c>
       <c r="B38" t="n">
-        <v>3.22622</v>
+        <v>3.43755</v>
       </c>
       <c r="C38" t="n">
-        <v>3.75546</v>
+        <v>2.18926</v>
       </c>
       <c r="D38" t="n">
-        <v>13.6402</v>
+        <v>14.1727</v>
       </c>
       <c r="E38" t="n">
-        <v>2.77718</v>
+        <v>2.78575</v>
       </c>
       <c r="F38" t="n">
-        <v>3.07949</v>
+        <v>3.09778</v>
       </c>
     </row>
     <row r="39">
@@ -5819,19 +5819,19 @@
         <v>60223</v>
       </c>
       <c r="B39" t="n">
-        <v>3.26149</v>
+        <v>3.49327</v>
       </c>
       <c r="C39" t="n">
-        <v>3.839</v>
+        <v>2.22221</v>
       </c>
       <c r="D39" t="n">
-        <v>14.1325</v>
+        <v>14.6988</v>
       </c>
       <c r="E39" t="n">
-        <v>2.82044</v>
+        <v>2.81359</v>
       </c>
       <c r="F39" t="n">
-        <v>3.14013</v>
+        <v>3.14529</v>
       </c>
     </row>
     <row r="40">
@@ -5839,19 +5839,19 @@
         <v>63216</v>
       </c>
       <c r="B40" t="n">
-        <v>3.36959</v>
+        <v>3.52752</v>
       </c>
       <c r="C40" t="n">
-        <v>3.93677</v>
+        <v>2.25451</v>
       </c>
       <c r="D40" t="n">
-        <v>14.5933</v>
+        <v>15.1941</v>
       </c>
       <c r="E40" t="n">
-        <v>2.83534</v>
+        <v>2.84712</v>
       </c>
       <c r="F40" t="n">
-        <v>3.18282</v>
+        <v>3.21434</v>
       </c>
     </row>
     <row r="41">
@@ -5859,19 +5859,19 @@
         <v>66358</v>
       </c>
       <c r="B41" t="n">
-        <v>3.4488</v>
+        <v>3.64828</v>
       </c>
       <c r="C41" t="n">
-        <v>4.02536</v>
+        <v>2.34992</v>
       </c>
       <c r="D41" t="n">
-        <v>15.0673</v>
+        <v>15.6641</v>
       </c>
       <c r="E41" t="n">
-        <v>2.8625</v>
+        <v>2.88238</v>
       </c>
       <c r="F41" t="n">
-        <v>3.24311</v>
+        <v>3.26828</v>
       </c>
     </row>
     <row r="42">
@@ -5879,19 +5879,19 @@
         <v>69657</v>
       </c>
       <c r="B42" t="n">
-        <v>3.54501</v>
+        <v>3.74254</v>
       </c>
       <c r="C42" t="n">
-        <v>4.13258</v>
+        <v>2.37975</v>
       </c>
       <c r="D42" t="n">
-        <v>15.538</v>
+        <v>16.1353</v>
       </c>
       <c r="E42" t="n">
-        <v>2.90911</v>
+        <v>2.91644</v>
       </c>
       <c r="F42" t="n">
-        <v>3.30703</v>
+        <v>3.33996</v>
       </c>
     </row>
     <row r="43">
@@ -5899,19 +5899,19 @@
         <v>73120</v>
       </c>
       <c r="B43" t="n">
-        <v>3.71841</v>
+        <v>3.86996</v>
       </c>
       <c r="C43" t="n">
-        <v>4.27752</v>
+        <v>2.49256</v>
       </c>
       <c r="D43" t="n">
-        <v>15.9607</v>
+        <v>16.5866</v>
       </c>
       <c r="E43" t="n">
-        <v>2.97258</v>
+        <v>2.98923</v>
       </c>
       <c r="F43" t="n">
-        <v>3.39037</v>
+        <v>3.42413</v>
       </c>
     </row>
     <row r="44">
@@ -5919,19 +5919,19 @@
         <v>76756</v>
       </c>
       <c r="B44" t="n">
-        <v>3.92705</v>
+        <v>4.15237</v>
       </c>
       <c r="C44" t="n">
-        <v>4.46928</v>
+        <v>2.64852</v>
       </c>
       <c r="D44" t="n">
-        <v>16.3895</v>
+        <v>17.0184</v>
       </c>
       <c r="E44" t="n">
-        <v>3.03966</v>
+        <v>3.05996</v>
       </c>
       <c r="F44" t="n">
-        <v>3.4986</v>
+        <v>3.50739</v>
       </c>
     </row>
     <row r="45">
@@ -5939,19 +5939,19 @@
         <v>80573</v>
       </c>
       <c r="B45" t="n">
-        <v>4.23675</v>
+        <v>4.38111</v>
       </c>
       <c r="C45" t="n">
-        <v>4.75965</v>
+        <v>2.87834</v>
       </c>
       <c r="D45" t="n">
-        <v>16.7451</v>
+        <v>17.3913</v>
       </c>
       <c r="E45" t="n">
-        <v>3.12286</v>
+        <v>3.39977</v>
       </c>
       <c r="F45" t="n">
-        <v>3.64227</v>
+        <v>3.63271</v>
       </c>
     </row>
     <row r="46">
@@ -5959,19 +5959,19 @@
         <v>84580</v>
       </c>
       <c r="B46" t="n">
-        <v>4.68797</v>
+        <v>4.81213</v>
       </c>
       <c r="C46" t="n">
-        <v>5.16664</v>
+        <v>3.21277</v>
       </c>
       <c r="D46" t="n">
-        <v>17.1027</v>
+        <v>17.8345</v>
       </c>
       <c r="E46" t="n">
-        <v>3.27874</v>
+        <v>3.55579</v>
       </c>
       <c r="F46" t="n">
-        <v>3.80677</v>
+        <v>3.79187</v>
       </c>
     </row>
     <row r="47">
@@ -5979,19 +5979,19 @@
         <v>88787</v>
       </c>
       <c r="B47" t="n">
-        <v>5.28479</v>
+        <v>5.438</v>
       </c>
       <c r="C47" t="n">
-        <v>5.69973</v>
+        <v>3.71946</v>
       </c>
       <c r="D47" t="n">
-        <v>17.5648</v>
+        <v>18.2794</v>
       </c>
       <c r="E47" t="n">
-        <v>3.52639</v>
+        <v>3.55146</v>
       </c>
       <c r="F47" t="n">
-        <v>3.9799</v>
+        <v>4.05399</v>
       </c>
     </row>
     <row r="48">
@@ -5999,19 +5999,19 @@
         <v>93204</v>
       </c>
       <c r="B48" t="n">
-        <v>6.14009</v>
+        <v>6.14801</v>
       </c>
       <c r="C48" t="n">
-        <v>6.47116</v>
+        <v>4.52096</v>
       </c>
       <c r="D48" t="n">
-        <v>17.9962</v>
+        <v>18.7167</v>
       </c>
       <c r="E48" t="n">
-        <v>3.94243</v>
+        <v>3.9706</v>
       </c>
       <c r="F48" t="n">
-        <v>4.3729</v>
+        <v>4.41347</v>
       </c>
     </row>
     <row r="49">
@@ -6019,19 +6019,19 @@
         <v>97841</v>
       </c>
       <c r="B49" t="n">
-        <v>7.47989</v>
+        <v>7.47889</v>
       </c>
       <c r="C49" t="n">
-        <v>7.69733</v>
+        <v>5.61487</v>
       </c>
       <c r="D49" t="n">
-        <v>18.4968</v>
+        <v>19.2263</v>
       </c>
       <c r="E49" t="n">
-        <v>4.49586</v>
+        <v>4.5114</v>
       </c>
       <c r="F49" t="n">
-        <v>4.90609</v>
+        <v>4.94877</v>
       </c>
     </row>
     <row r="50">
@@ -6039,19 +6039,19 @@
         <v>102709</v>
       </c>
       <c r="B50" t="n">
-        <v>9.71823</v>
+        <v>9.158709999999999</v>
       </c>
       <c r="C50" t="n">
-        <v>9.60957</v>
+        <v>7.31021</v>
       </c>
       <c r="D50" t="n">
-        <v>12.9524</v>
+        <v>13.4936</v>
       </c>
       <c r="E50" t="n">
-        <v>5.38068</v>
+        <v>5.34926</v>
       </c>
       <c r="F50" t="n">
-        <v>5.72043</v>
+        <v>5.73359</v>
       </c>
     </row>
     <row r="51">
@@ -6059,19 +6059,19 @@
         <v>107820</v>
       </c>
       <c r="B51" t="n">
-        <v>12.7525</v>
+        <v>12.2908</v>
       </c>
       <c r="C51" t="n">
-        <v>12.8388</v>
+        <v>2.25409</v>
       </c>
       <c r="D51" t="n">
-        <v>13.4402</v>
+        <v>13.9634</v>
       </c>
       <c r="E51" t="n">
-        <v>3.08475</v>
+        <v>2.92572</v>
       </c>
       <c r="F51" t="n">
-        <v>3.42002</v>
+        <v>3.41678</v>
       </c>
     </row>
     <row r="52">
@@ -6079,19 +6079,19 @@
         <v>113186</v>
       </c>
       <c r="B52" t="n">
-        <v>17.1997</v>
+        <v>16.8272</v>
       </c>
       <c r="C52" t="n">
-        <v>17.5065</v>
+        <v>2.34762</v>
       </c>
       <c r="D52" t="n">
-        <v>13.8837</v>
+        <v>14.4243</v>
       </c>
       <c r="E52" t="n">
-        <v>3.05853</v>
+        <v>2.95816</v>
       </c>
       <c r="F52" t="n">
-        <v>3.42965</v>
+        <v>3.47266</v>
       </c>
     </row>
     <row r="53">
@@ -6099,19 +6099,19 @@
         <v>118820</v>
       </c>
       <c r="B53" t="n">
-        <v>3.49564</v>
+        <v>3.73622</v>
       </c>
       <c r="C53" t="n">
-        <v>4.13033</v>
+        <v>2.38998</v>
       </c>
       <c r="D53" t="n">
-        <v>14.3387</v>
+        <v>14.9137</v>
       </c>
       <c r="E53" t="n">
-        <v>3.13824</v>
+        <v>3.10107</v>
       </c>
       <c r="F53" t="n">
-        <v>3.52147</v>
+        <v>3.59933</v>
       </c>
     </row>
     <row r="54">
@@ -6119,19 +6119,19 @@
         <v>124735</v>
       </c>
       <c r="B54" t="n">
-        <v>3.52253</v>
+        <v>3.7826</v>
       </c>
       <c r="C54" t="n">
-        <v>4.19786</v>
+        <v>2.41566</v>
       </c>
       <c r="D54" t="n">
-        <v>14.812</v>
+        <v>15.3956</v>
       </c>
       <c r="E54" t="n">
-        <v>3.04307</v>
+        <v>3.03158</v>
       </c>
       <c r="F54" t="n">
-        <v>3.59182</v>
+        <v>3.5903</v>
       </c>
     </row>
     <row r="55">
@@ -6139,19 +6139,19 @@
         <v>130945</v>
       </c>
       <c r="B55" t="n">
-        <v>3.61973</v>
+        <v>3.88708</v>
       </c>
       <c r="C55" t="n">
-        <v>4.31073</v>
+        <v>2.49693</v>
       </c>
       <c r="D55" t="n">
-        <v>15.3105</v>
+        <v>15.8861</v>
       </c>
       <c r="E55" t="n">
-        <v>3.22289</v>
+        <v>3.07718</v>
       </c>
       <c r="F55" t="n">
-        <v>3.64163</v>
+        <v>3.63989</v>
       </c>
     </row>
     <row r="56">
@@ -6159,19 +6159,19 @@
         <v>137465</v>
       </c>
       <c r="B56" t="n">
-        <v>3.72145</v>
+        <v>3.98048</v>
       </c>
       <c r="C56" t="n">
-        <v>4.4136</v>
+        <v>2.56745</v>
       </c>
       <c r="D56" t="n">
-        <v>15.7269</v>
+        <v>16.3417</v>
       </c>
       <c r="E56" t="n">
-        <v>3.354</v>
+        <v>3.18524</v>
       </c>
       <c r="F56" t="n">
-        <v>3.71746</v>
+        <v>3.72971</v>
       </c>
     </row>
     <row r="57">
@@ -6179,19 +6179,19 @@
         <v>144311</v>
       </c>
       <c r="B57" t="n">
-        <v>3.88726</v>
+        <v>4.0677</v>
       </c>
       <c r="C57" t="n">
-        <v>4.56132</v>
+        <v>2.63634</v>
       </c>
       <c r="D57" t="n">
-        <v>16.1623</v>
+        <v>16.7899</v>
       </c>
       <c r="E57" t="n">
-        <v>3.42264</v>
+        <v>3.19782</v>
       </c>
       <c r="F57" t="n">
-        <v>3.79388</v>
+        <v>3.81555</v>
       </c>
     </row>
     <row r="58">
@@ -6199,19 +6199,19 @@
         <v>151499</v>
       </c>
       <c r="B58" t="n">
-        <v>4.11895</v>
+        <v>4.25186</v>
       </c>
       <c r="C58" t="n">
-        <v>4.75643</v>
+        <v>2.82011</v>
       </c>
       <c r="D58" t="n">
-        <v>16.5824</v>
+        <v>17.2474</v>
       </c>
       <c r="E58" t="n">
-        <v>3.40535</v>
+        <v>3.34961</v>
       </c>
       <c r="F58" t="n">
-        <v>3.90725</v>
+        <v>3.91343</v>
       </c>
     </row>
     <row r="59">
@@ -6219,19 +6219,19 @@
         <v>159046</v>
       </c>
       <c r="B59" t="n">
-        <v>4.40929</v>
+        <v>4.5906</v>
       </c>
       <c r="C59" t="n">
-        <v>5.08765</v>
+        <v>3.02459</v>
       </c>
       <c r="D59" t="n">
-        <v>16.9729</v>
+        <v>17.6475</v>
       </c>
       <c r="E59" t="n">
-        <v>3.43148</v>
+        <v>3.46016</v>
       </c>
       <c r="F59" t="n">
-        <v>4.06268</v>
+        <v>4.08532</v>
       </c>
     </row>
     <row r="60">
@@ -6239,19 +6239,19 @@
         <v>166970</v>
       </c>
       <c r="B60" t="n">
-        <v>4.79322</v>
+        <v>4.82392</v>
       </c>
       <c r="C60" t="n">
-        <v>5.33355</v>
+        <v>3.36019</v>
       </c>
       <c r="D60" t="n">
-        <v>17.3899</v>
+        <v>18.0844</v>
       </c>
       <c r="E60" t="n">
-        <v>3.61321</v>
+        <v>3.60306</v>
       </c>
       <c r="F60" t="n">
-        <v>4.23446</v>
+        <v>4.25043</v>
       </c>
     </row>
     <row r="61">
@@ -6259,19 +6259,19 @@
         <v>175290</v>
       </c>
       <c r="B61" t="n">
-        <v>5.24399</v>
+        <v>5.48798</v>
       </c>
       <c r="C61" t="n">
-        <v>5.8254</v>
+        <v>3.85074</v>
       </c>
       <c r="D61" t="n">
-        <v>17.86</v>
+        <v>18.4886</v>
       </c>
       <c r="E61" t="n">
-        <v>3.77634</v>
+        <v>3.82908</v>
       </c>
       <c r="F61" t="n">
-        <v>4.32106</v>
+        <v>4.50657</v>
       </c>
     </row>
     <row r="62">
@@ -6279,19 +6279,19 @@
         <v>184026</v>
       </c>
       <c r="B62" t="n">
-        <v>6.09251</v>
+        <v>6.1021</v>
       </c>
       <c r="C62" t="n">
-        <v>6.59706</v>
+        <v>4.82356</v>
       </c>
       <c r="D62" t="n">
-        <v>18.1838</v>
+        <v>18.927</v>
       </c>
       <c r="E62" t="n">
-        <v>4.08243</v>
+        <v>4.15007</v>
       </c>
       <c r="F62" t="n">
-        <v>4.64746</v>
+        <v>4.70207</v>
       </c>
     </row>
     <row r="63">
@@ -6299,19 +6299,19 @@
         <v>193198</v>
       </c>
       <c r="B63" t="n">
-        <v>7.19629</v>
+        <v>7.25357</v>
       </c>
       <c r="C63" t="n">
-        <v>7.69566</v>
+        <v>5.79128</v>
       </c>
       <c r="D63" t="n">
-        <v>18.7172</v>
+        <v>19.4377</v>
       </c>
       <c r="E63" t="n">
-        <v>4.66281</v>
+        <v>4.64919</v>
       </c>
       <c r="F63" t="n">
-        <v>5.14067</v>
+        <v>5.2273</v>
       </c>
     </row>
     <row r="64">
@@ -6319,19 +6319,19 @@
         <v>202828</v>
       </c>
       <c r="B64" t="n">
-        <v>9.02087</v>
+        <v>9.132720000000001</v>
       </c>
       <c r="C64" t="n">
-        <v>9.374090000000001</v>
+        <v>7.06429</v>
       </c>
       <c r="D64" t="n">
-        <v>13.5855</v>
+        <v>14.0991</v>
       </c>
       <c r="E64" t="n">
-        <v>5.43122</v>
+        <v>5.4518</v>
       </c>
       <c r="F64" t="n">
-        <v>5.83287</v>
+        <v>5.96706</v>
       </c>
     </row>
     <row r="65">
@@ -6339,19 +6339,19 @@
         <v>212939</v>
       </c>
       <c r="B65" t="n">
-        <v>11.7387</v>
+        <v>11.6719</v>
       </c>
       <c r="C65" t="n">
-        <v>11.7938</v>
+        <v>2.78519</v>
       </c>
       <c r="D65" t="n">
-        <v>14.0361</v>
+        <v>14.479</v>
       </c>
       <c r="E65" t="n">
-        <v>6.7862</v>
+        <v>6.77929</v>
       </c>
       <c r="F65" t="n">
-        <v>7.23903</v>
+        <v>7.34217</v>
       </c>
     </row>
     <row r="66">
@@ -6359,19 +6359,19 @@
         <v>223555</v>
       </c>
       <c r="B66" t="n">
-        <v>16.0301</v>
+        <v>16.13</v>
       </c>
       <c r="C66" t="n">
-        <v>16.3967</v>
+        <v>2.8263</v>
       </c>
       <c r="D66" t="n">
-        <v>14.6458</v>
+        <v>15.2595</v>
       </c>
       <c r="E66" t="n">
-        <v>3.53242</v>
+        <v>3.53555</v>
       </c>
       <c r="F66" t="n">
-        <v>4.04282</v>
+        <v>4.17598</v>
       </c>
     </row>
     <row r="67">
@@ -6379,19 +6379,19 @@
         <v>234701</v>
       </c>
       <c r="B67" t="n">
-        <v>4.03316</v>
+        <v>4.17466</v>
       </c>
       <c r="C67" t="n">
-        <v>4.87725</v>
+        <v>2.87455</v>
       </c>
       <c r="D67" t="n">
-        <v>15.3266</v>
+        <v>15.9335</v>
       </c>
       <c r="E67" t="n">
-        <v>3.57441</v>
+        <v>3.54284</v>
       </c>
       <c r="F67" t="n">
-        <v>4.11524</v>
+        <v>4.26086</v>
       </c>
     </row>
     <row r="68">
@@ -6399,19 +6399,19 @@
         <v>246404</v>
       </c>
       <c r="B68" t="n">
-        <v>4.1173</v>
+        <v>4.21675</v>
       </c>
       <c r="C68" t="n">
-        <v>4.97904</v>
+        <v>2.85109</v>
       </c>
       <c r="D68" t="n">
-        <v>16.0533</v>
+        <v>16.6925</v>
       </c>
       <c r="E68" t="n">
-        <v>3.56893</v>
+        <v>3.60358</v>
       </c>
       <c r="F68" t="n">
-        <v>4.18152</v>
+        <v>4.30574</v>
       </c>
     </row>
     <row r="69">
@@ -6419,19 +6419,19 @@
         <v>258692</v>
       </c>
       <c r="B69" t="n">
-        <v>4.20302</v>
+        <v>4.38641</v>
       </c>
       <c r="C69" t="n">
-        <v>5.11206</v>
+        <v>2.96593</v>
       </c>
       <c r="D69" t="n">
-        <v>16.8752</v>
+        <v>17.5798</v>
       </c>
       <c r="E69" t="n">
-        <v>3.62765</v>
+        <v>3.63472</v>
       </c>
       <c r="F69" t="n">
-        <v>4.2494</v>
+        <v>4.37952</v>
       </c>
     </row>
     <row r="70">
@@ -6439,19 +6439,19 @@
         <v>271594</v>
       </c>
       <c r="B70" t="n">
-        <v>4.28909</v>
+        <v>4.35198</v>
       </c>
       <c r="C70" t="n">
-        <v>5.24294</v>
+        <v>2.96269</v>
       </c>
       <c r="D70" t="n">
-        <v>17.7606</v>
+        <v>18.4043</v>
       </c>
       <c r="E70" t="n">
-        <v>3.69274</v>
+        <v>3.68196</v>
       </c>
       <c r="F70" t="n">
-        <v>4.32945</v>
+        <v>4.46572</v>
       </c>
     </row>
     <row r="71">
@@ -6459,19 +6459,19 @@
         <v>285141</v>
       </c>
       <c r="B71" t="n">
-        <v>4.40523</v>
+        <v>4.60853</v>
       </c>
       <c r="C71" t="n">
-        <v>5.4049</v>
+        <v>3.12173</v>
       </c>
       <c r="D71" t="n">
-        <v>18.6648</v>
+        <v>19.2633</v>
       </c>
       <c r="E71" t="n">
-        <v>3.70704</v>
+        <v>3.81203</v>
       </c>
       <c r="F71" t="n">
-        <v>4.46354</v>
+        <v>4.60936</v>
       </c>
     </row>
     <row r="72">
@@ -6479,19 +6479,19 @@
         <v>299365</v>
       </c>
       <c r="B72" t="n">
-        <v>4.57202</v>
+        <v>4.64904</v>
       </c>
       <c r="C72" t="n">
-        <v>5.62147</v>
+        <v>3.1893</v>
       </c>
       <c r="D72" t="n">
-        <v>19.597</v>
+        <v>20.3541</v>
       </c>
       <c r="E72" t="n">
-        <v>3.78143</v>
+        <v>3.89181</v>
       </c>
       <c r="F72" t="n">
-        <v>4.56129</v>
+        <v>4.73959</v>
       </c>
     </row>
     <row r="73">
@@ -6499,19 +6499,19 @@
         <v>314300</v>
       </c>
       <c r="B73" t="n">
-        <v>4.79715</v>
+        <v>4.94946</v>
       </c>
       <c r="C73" t="n">
-        <v>5.89296</v>
+        <v>3.38466</v>
       </c>
       <c r="D73" t="n">
-        <v>20.7159</v>
+        <v>21.4134</v>
       </c>
       <c r="E73" t="n">
-        <v>3.91095</v>
+        <v>3.99607</v>
       </c>
       <c r="F73" t="n">
-        <v>4.6695</v>
+        <v>4.86</v>
       </c>
     </row>
     <row r="74">
@@ -6519,19 +6519,19 @@
         <v>329981</v>
       </c>
       <c r="B74" t="n">
-        <v>5.17386</v>
+        <v>5.25221</v>
       </c>
       <c r="C74" t="n">
-        <v>6.40156</v>
+        <v>3.64773</v>
       </c>
       <c r="D74" t="n">
-        <v>21.8468</v>
+        <v>22.4902</v>
       </c>
       <c r="E74" t="n">
-        <v>4.06468</v>
+        <v>4.06837</v>
       </c>
       <c r="F74" t="n">
-        <v>4.84928</v>
+        <v>4.9643</v>
       </c>
     </row>
     <row r="75">
@@ -6539,19 +6539,19 @@
         <v>346446</v>
       </c>
       <c r="B75" t="n">
-        <v>5.63586</v>
+        <v>5.74897</v>
       </c>
       <c r="C75" t="n">
-        <v>6.95352</v>
+        <v>4.05284</v>
       </c>
       <c r="D75" t="n">
-        <v>23.2163</v>
+        <v>23.5335</v>
       </c>
       <c r="E75" t="n">
-        <v>4.21547</v>
+        <v>4.25095</v>
       </c>
       <c r="F75" t="n">
-        <v>5.13253</v>
+        <v>5.21084</v>
       </c>
     </row>
     <row r="76">
@@ -6559,19 +6559,19 @@
         <v>363734</v>
       </c>
       <c r="B76" t="n">
-        <v>6.33258</v>
+        <v>6.47975</v>
       </c>
       <c r="C76" t="n">
-        <v>7.86745</v>
+        <v>4.65952</v>
       </c>
       <c r="D76" t="n">
-        <v>24.8346</v>
+        <v>25.0464</v>
       </c>
       <c r="E76" t="n">
-        <v>4.50381</v>
+        <v>4.54505</v>
       </c>
       <c r="F76" t="n">
-        <v>5.4441</v>
+        <v>5.49863</v>
       </c>
     </row>
     <row r="77">
@@ -6579,19 +6579,19 @@
         <v>381886</v>
       </c>
       <c r="B77" t="n">
-        <v>7.36024</v>
+        <v>7.55087</v>
       </c>
       <c r="C77" t="n">
-        <v>9.13941</v>
+        <v>5.62181</v>
       </c>
       <c r="D77" t="n">
-        <v>26.3696</v>
+        <v>26.5178</v>
       </c>
       <c r="E77" t="n">
-        <v>4.95803</v>
+        <v>4.9887</v>
       </c>
       <c r="F77" t="n">
-        <v>5.93338</v>
+        <v>5.96984</v>
       </c>
     </row>
     <row r="78">
@@ -6599,19 +6599,19 @@
         <v>400945</v>
       </c>
       <c r="B78" t="n">
-        <v>9.023960000000001</v>
+        <v>9.17723</v>
       </c>
       <c r="C78" t="n">
-        <v>11.0041</v>
+        <v>7.04844</v>
       </c>
       <c r="D78" t="n">
-        <v>22.8221</v>
+        <v>23.8246</v>
       </c>
       <c r="E78" t="n">
-        <v>5.66033</v>
+        <v>5.6501</v>
       </c>
       <c r="F78" t="n">
-        <v>6.69299</v>
+        <v>6.68491</v>
       </c>
     </row>
     <row r="79">
@@ -6619,19 +6619,19 @@
         <v>420956</v>
       </c>
       <c r="B79" t="n">
-        <v>11.6083</v>
+        <v>11.96</v>
       </c>
       <c r="C79" t="n">
-        <v>13.8747</v>
+        <v>3.1398</v>
       </c>
       <c r="D79" t="n">
-        <v>24.0583</v>
+        <v>25.0067</v>
       </c>
       <c r="E79" t="n">
-        <v>6.90805</v>
+        <v>6.87306</v>
       </c>
       <c r="F79" t="n">
-        <v>8.024330000000001</v>
+        <v>8.03158</v>
       </c>
     </row>
     <row r="80">
@@ -6639,19 +6639,19 @@
         <v>441967</v>
       </c>
       <c r="B80" t="n">
-        <v>16.0649</v>
+        <v>15.8202</v>
       </c>
       <c r="C80" t="n">
-        <v>18.7452</v>
+        <v>3.19237</v>
       </c>
       <c r="D80" t="n">
-        <v>25.4394</v>
+        <v>26.346</v>
       </c>
       <c r="E80" t="n">
-        <v>3.98159</v>
+        <v>4.0059</v>
       </c>
       <c r="F80" t="n">
-        <v>4.82674</v>
+        <v>5.06947</v>
       </c>
     </row>
     <row r="81">
@@ -6659,19 +6659,19 @@
         <v>464028</v>
       </c>
       <c r="B81" t="n">
-        <v>4.79834</v>
+        <v>4.99096</v>
       </c>
       <c r="C81" t="n">
-        <v>6.37025</v>
+        <v>3.39133</v>
       </c>
       <c r="D81" t="n">
-        <v>26.6745</v>
+        <v>27.7013</v>
       </c>
       <c r="E81" t="n">
-        <v>4.05996</v>
+        <v>4.16597</v>
       </c>
       <c r="F81" t="n">
-        <v>4.99627</v>
+        <v>5.16578</v>
       </c>
     </row>
     <row r="82">
@@ -6679,19 +6679,19 @@
         <v>487192</v>
       </c>
       <c r="B82" t="n">
-        <v>4.90328</v>
+        <v>5.18873</v>
       </c>
       <c r="C82" t="n">
-        <v>6.78849</v>
+        <v>3.40753</v>
       </c>
       <c r="D82" t="n">
-        <v>28.1036</v>
+        <v>29.1136</v>
       </c>
       <c r="E82" t="n">
-        <v>4.12028</v>
+        <v>4.30532</v>
       </c>
       <c r="F82" t="n">
-        <v>5.12215</v>
+        <v>5.38275</v>
       </c>
     </row>
     <row r="83">
@@ -6699,19 +6699,19 @@
         <v>511514</v>
       </c>
       <c r="B83" t="n">
-        <v>5.03596</v>
+        <v>5.3543</v>
       </c>
       <c r="C83" t="n">
-        <v>7.21922</v>
+        <v>3.58278</v>
       </c>
       <c r="D83" t="n">
-        <v>29.4397</v>
+        <v>30.5644</v>
       </c>
       <c r="E83" t="n">
-        <v>4.1881</v>
+        <v>4.39693</v>
       </c>
       <c r="F83" t="n">
-        <v>5.30678</v>
+        <v>5.52468</v>
       </c>
     </row>
     <row r="84">
@@ -6719,19 +6719,19 @@
         <v>537052</v>
       </c>
       <c r="B84" t="n">
-        <v>5.32593</v>
+        <v>5.63326</v>
       </c>
       <c r="C84" t="n">
-        <v>7.7618</v>
+        <v>3.7438</v>
       </c>
       <c r="D84" t="n">
-        <v>30.9282</v>
+        <v>32.0388</v>
       </c>
       <c r="E84" t="n">
-        <v>4.29385</v>
+        <v>4.51056</v>
       </c>
       <c r="F84" t="n">
-        <v>5.51871</v>
+        <v>5.73693</v>
       </c>
     </row>
     <row r="85">
@@ -6739,19 +6739,19 @@
         <v>563866</v>
       </c>
       <c r="B85" t="n">
-        <v>5.59067</v>
+        <v>6.00333</v>
       </c>
       <c r="C85" t="n">
-        <v>8.41737</v>
+        <v>3.9588</v>
       </c>
       <c r="D85" t="n">
-        <v>32.3831</v>
+        <v>33.6401</v>
       </c>
       <c r="E85" t="n">
-        <v>4.46238</v>
+        <v>4.59999</v>
       </c>
       <c r="F85" t="n">
-        <v>5.76283</v>
+        <v>6.38312</v>
       </c>
     </row>
     <row r="86">
@@ -6759,19 +6759,19 @@
         <v>592020</v>
       </c>
       <c r="B86" t="n">
-        <v>5.91921</v>
+        <v>6.4964</v>
       </c>
       <c r="C86" t="n">
-        <v>9.049099999999999</v>
+        <v>4.23545</v>
       </c>
       <c r="D86" t="n">
-        <v>33.9163</v>
+        <v>35.2231</v>
       </c>
       <c r="E86" t="n">
-        <v>4.64791</v>
+        <v>4.86632</v>
       </c>
       <c r="F86" t="n">
-        <v>6.1511</v>
+        <v>6.85511</v>
       </c>
     </row>
     <row r="87">
@@ -6779,19 +6779,19 @@
         <v>621581</v>
       </c>
       <c r="B87" t="n">
-        <v>6.29808</v>
+        <v>6.9299</v>
       </c>
       <c r="C87" t="n">
-        <v>9.954079999999999</v>
+        <v>4.53022</v>
       </c>
       <c r="D87" t="n">
-        <v>35.5297</v>
+        <v>36.8879</v>
       </c>
       <c r="E87" t="n">
-        <v>4.88409</v>
+        <v>5.0689</v>
       </c>
       <c r="F87" t="n">
-        <v>6.54123</v>
+        <v>7.31738</v>
       </c>
     </row>
     <row r="88">
@@ -6799,19 +6799,19 @@
         <v>652620</v>
       </c>
       <c r="B88" t="n">
-        <v>6.90225</v>
+        <v>7.56413</v>
       </c>
       <c r="C88" t="n">
-        <v>10.6903</v>
+        <v>4.8992</v>
       </c>
       <c r="D88" t="n">
-        <v>37.1793</v>
+        <v>38.5921</v>
       </c>
       <c r="E88" t="n">
-        <v>5.12008</v>
+        <v>5.22077</v>
       </c>
       <c r="F88" t="n">
-        <v>7.15233</v>
+        <v>7.21671</v>
       </c>
     </row>
     <row r="89">
@@ -6819,19 +6819,19 @@
         <v>685210</v>
       </c>
       <c r="B89" t="n">
-        <v>7.60888</v>
+        <v>8.306139999999999</v>
       </c>
       <c r="C89" t="n">
-        <v>11.8796</v>
+        <v>5.45644</v>
       </c>
       <c r="D89" t="n">
-        <v>38.9627</v>
+        <v>40.4295</v>
       </c>
       <c r="E89" t="n">
-        <v>5.42878</v>
+        <v>5.66347</v>
       </c>
       <c r="F89" t="n">
-        <v>7.67022</v>
+        <v>7.90322</v>
       </c>
     </row>
     <row r="90">
@@ -6839,19 +6839,19 @@
         <v>719429</v>
       </c>
       <c r="B90" t="n">
-        <v>8.567629999999999</v>
+        <v>9.43966</v>
       </c>
       <c r="C90" t="n">
-        <v>13.3597</v>
+        <v>6.12044</v>
       </c>
       <c r="D90" t="n">
-        <v>40.7544</v>
+        <v>42.2913</v>
       </c>
       <c r="E90" t="n">
-        <v>5.91095</v>
+        <v>6.18293</v>
       </c>
       <c r="F90" t="n">
-        <v>8.45241</v>
+        <v>8.686310000000001</v>
       </c>
     </row>
     <row r="91">
@@ -6859,19 +6859,19 @@
         <v>755358</v>
       </c>
       <c r="B91" t="n">
-        <v>9.78825</v>
+        <v>10.0804</v>
       </c>
       <c r="C91" t="n">
-        <v>14.8338</v>
+        <v>6.8229</v>
       </c>
       <c r="D91" t="n">
-        <v>42.5831</v>
+        <v>44.3331</v>
       </c>
       <c r="E91" t="n">
-        <v>6.59109</v>
+        <v>7.06282</v>
       </c>
       <c r="F91" t="n">
-        <v>9.44322</v>
+        <v>10.1444</v>
       </c>
     </row>
     <row r="92">
@@ -6879,19 +6879,19 @@
         <v>793083</v>
       </c>
       <c r="B92" t="n">
-        <v>11.3819</v>
+        <v>11.7282</v>
       </c>
       <c r="C92" t="n">
-        <v>17.0621</v>
+        <v>8.362550000000001</v>
       </c>
       <c r="D92" t="n">
-        <v>35.0954</v>
+        <v>36.1547</v>
       </c>
       <c r="E92" t="n">
-        <v>7.4188</v>
+        <v>7.4194</v>
       </c>
       <c r="F92" t="n">
-        <v>10.5533</v>
+        <v>10.7594</v>
       </c>
     </row>
     <row r="93">
@@ -6899,19 +6899,19 @@
         <v>832694</v>
       </c>
       <c r="B93" t="n">
-        <v>13.855</v>
+        <v>14.2778</v>
       </c>
       <c r="C93" t="n">
-        <v>20.1044</v>
+        <v>10.652</v>
       </c>
       <c r="D93" t="n">
-        <v>36.2552</v>
+        <v>37.3797</v>
       </c>
       <c r="E93" t="n">
-        <v>8.734059999999999</v>
+        <v>9.368449999999999</v>
       </c>
       <c r="F93" t="n">
-        <v>12.2339</v>
+        <v>13.1773</v>
       </c>
     </row>
     <row r="94">
@@ -6919,19 +6919,19 @@
         <v>874285</v>
       </c>
       <c r="B94" t="n">
-        <v>17.3096</v>
+        <v>18.0886</v>
       </c>
       <c r="C94" t="n">
-        <v>24.6337</v>
+        <v>4.32068</v>
       </c>
       <c r="D94" t="n">
-        <v>37.4608</v>
+        <v>38.6382</v>
       </c>
       <c r="E94" t="n">
-        <v>5.09114</v>
+        <v>5.21049</v>
       </c>
       <c r="F94" t="n">
-        <v>7.13061</v>
+        <v>7.26488</v>
       </c>
     </row>
     <row r="95">
@@ -6939,19 +6939,19 @@
         <v>917955</v>
       </c>
       <c r="B95" t="n">
-        <v>6.8564</v>
+        <v>6.91312</v>
       </c>
       <c r="C95" t="n">
-        <v>10.5473</v>
+        <v>4.41715</v>
       </c>
       <c r="D95" t="n">
-        <v>38.6567</v>
+        <v>39.9102</v>
       </c>
       <c r="E95" t="n">
-        <v>5.24818</v>
+        <v>5.39652</v>
       </c>
       <c r="F95" t="n">
-        <v>7.46807</v>
+        <v>7.70017</v>
       </c>
     </row>
     <row r="96">
@@ -6959,19 +6959,19 @@
         <v>963808</v>
       </c>
       <c r="B96" t="n">
-        <v>7.16353</v>
+        <v>7.27676</v>
       </c>
       <c r="C96" t="n">
-        <v>11.0832</v>
+        <v>4.61615</v>
       </c>
       <c r="D96" t="n">
-        <v>39.9399</v>
+        <v>41.2563</v>
       </c>
       <c r="E96" t="n">
-        <v>5.4735</v>
+        <v>5.55737</v>
       </c>
       <c r="F96" t="n">
-        <v>7.80817</v>
+        <v>7.99523</v>
       </c>
     </row>
     <row r="97">
@@ -6979,19 +6979,19 @@
         <v>1011953</v>
       </c>
       <c r="B97" t="n">
-        <v>7.49873</v>
+        <v>7.59403</v>
       </c>
       <c r="C97" t="n">
-        <v>11.5418</v>
+        <v>4.73453</v>
       </c>
       <c r="D97" t="n">
-        <v>41.2649</v>
+        <v>42.6223</v>
       </c>
       <c r="E97" t="n">
-        <v>5.67125</v>
+        <v>5.71749</v>
       </c>
       <c r="F97" t="n">
-        <v>8.17947</v>
+        <v>8.341749999999999</v>
       </c>
     </row>
     <row r="98">
@@ -6999,19 +6999,19 @@
         <v>1062505</v>
       </c>
       <c r="B98" t="n">
-        <v>7.79068</v>
+        <v>7.87553</v>
       </c>
       <c r="C98" t="n">
-        <v>12.2753</v>
+        <v>4.9426</v>
       </c>
       <c r="D98" t="n">
-        <v>42.5613</v>
+        <v>43.9545</v>
       </c>
       <c r="E98" t="n">
-        <v>5.86982</v>
+        <v>5.94982</v>
       </c>
       <c r="F98" t="n">
-        <v>8.47137</v>
+        <v>8.66253</v>
       </c>
     </row>
     <row r="99">
@@ -7019,19 +7019,19 @@
         <v>1115584</v>
       </c>
       <c r="B99" t="n">
-        <v>8.13313</v>
+        <v>8.25601</v>
       </c>
       <c r="C99" t="n">
-        <v>13.0485</v>
+        <v>5.16635</v>
       </c>
       <c r="D99" t="n">
-        <v>43.9996</v>
+        <v>45.4396</v>
       </c>
       <c r="E99" t="n">
-        <v>6.08061</v>
+        <v>6.21394</v>
       </c>
       <c r="F99" t="n">
-        <v>8.85561</v>
+        <v>9.08564</v>
       </c>
     </row>
     <row r="100">
@@ -7039,19 +7039,19 @@
         <v>1171316</v>
       </c>
       <c r="B100" t="n">
-        <v>8.43149</v>
+        <v>8.585610000000001</v>
       </c>
       <c r="C100" t="n">
-        <v>13.9059</v>
+        <v>5.40662</v>
       </c>
       <c r="D100" t="n">
-        <v>45.4107</v>
+        <v>47</v>
       </c>
       <c r="E100" t="n">
-        <v>6.37109</v>
+        <v>6.42913</v>
       </c>
       <c r="F100" t="n">
-        <v>9.184139999999999</v>
+        <v>9.43127</v>
       </c>
     </row>
     <row r="101">
@@ -7059,19 +7059,19 @@
         <v>1229834</v>
       </c>
       <c r="B101" t="n">
-        <v>8.89701</v>
+        <v>8.96245</v>
       </c>
       <c r="C101" t="n">
-        <v>14.8631</v>
+        <v>5.68821</v>
       </c>
       <c r="D101" t="n">
-        <v>46.9211</v>
+        <v>48.5697</v>
       </c>
       <c r="E101" t="n">
-        <v>6.55902</v>
+        <v>6.63754</v>
       </c>
       <c r="F101" t="n">
-        <v>9.64189</v>
+        <v>9.85145</v>
       </c>
     </row>
     <row r="102">
@@ -7079,19 +7079,19 @@
         <v>1291277</v>
       </c>
       <c r="B102" t="n">
-        <v>9.37904</v>
+        <v>9.52022</v>
       </c>
       <c r="C102" t="n">
-        <v>15.9837</v>
+        <v>6.00966</v>
       </c>
       <c r="D102" t="n">
-        <v>48.5772</v>
+        <v>50.2719</v>
       </c>
       <c r="E102" t="n">
-        <v>6.78759</v>
+        <v>6.88673</v>
       </c>
       <c r="F102" t="n">
-        <v>10.101</v>
+        <v>10.3018</v>
       </c>
     </row>
     <row r="103">
@@ -7099,19 +7099,19 @@
         <v>1355792</v>
       </c>
       <c r="B103" t="n">
-        <v>9.904920000000001</v>
+        <v>10.1338</v>
       </c>
       <c r="C103" t="n">
-        <v>17.2097</v>
+        <v>6.44717</v>
       </c>
       <c r="D103" t="n">
-        <v>50.2424</v>
+        <v>51.9808</v>
       </c>
       <c r="E103" t="n">
-        <v>7.16443</v>
+        <v>7.18788</v>
       </c>
       <c r="F103" t="n">
-        <v>10.7691</v>
+        <v>10.9922</v>
       </c>
     </row>
     <row r="104">
@@ -7119,19 +7119,19 @@
         <v>1423532</v>
       </c>
       <c r="B104" t="n">
-        <v>10.7413</v>
+        <v>11.0454</v>
       </c>
       <c r="C104" t="n">
-        <v>18.7086</v>
+        <v>7.16416</v>
       </c>
       <c r="D104" t="n">
-        <v>51.953</v>
+        <v>53.7546</v>
       </c>
       <c r="E104" t="n">
-        <v>7.50196</v>
+        <v>7.65509</v>
       </c>
       <c r="F104" t="n">
-        <v>11.5651</v>
+        <v>11.8779</v>
       </c>
     </row>
     <row r="105">
@@ -7139,19 +7139,19 @@
         <v>1494659</v>
       </c>
       <c r="B105" t="n">
-        <v>11.9008</v>
+        <v>12.3414</v>
       </c>
       <c r="C105" t="n">
-        <v>20.4346</v>
+        <v>8.0596</v>
       </c>
       <c r="D105" t="n">
-        <v>53.7783</v>
+        <v>55.9064</v>
       </c>
       <c r="E105" t="n">
-        <v>8.07179</v>
+        <v>8.17327</v>
       </c>
       <c r="F105" t="n">
-        <v>12.6558</v>
+        <v>12.9176</v>
       </c>
     </row>
     <row r="106">
@@ -7159,19 +7159,19 @@
         <v>1569342</v>
       </c>
       <c r="B106" t="n">
-        <v>13.5674</v>
+        <v>13.9346</v>
       </c>
       <c r="C106" t="n">
-        <v>22.5663</v>
+        <v>9.36835</v>
       </c>
       <c r="D106" t="n">
-        <v>55.5076</v>
+        <v>57.6897</v>
       </c>
       <c r="E106" t="n">
-        <v>8.937469999999999</v>
+        <v>8.976610000000001</v>
       </c>
       <c r="F106" t="n">
-        <v>14.1627</v>
+        <v>14.3177</v>
       </c>
     </row>
     <row r="107">
@@ -7179,19 +7179,19 @@
         <v>1647759</v>
       </c>
       <c r="B107" t="n">
-        <v>15.6771</v>
+        <v>16.2622</v>
       </c>
       <c r="C107" t="n">
-        <v>25.3214</v>
+        <v>11.3698</v>
       </c>
       <c r="D107" t="n">
-        <v>42.4983</v>
+        <v>44.1223</v>
       </c>
       <c r="E107" t="n">
-        <v>10.1457</v>
+        <v>10.2994</v>
       </c>
       <c r="F107" t="n">
-        <v>16.1973</v>
+        <v>16.4226</v>
       </c>
     </row>
     <row r="108">
@@ -7199,19 +7199,19 @@
         <v>1730096</v>
       </c>
       <c r="B108" t="n">
-        <v>19.0119</v>
+        <v>19.8295</v>
       </c>
       <c r="C108" t="n">
-        <v>29.4887</v>
+        <v>4.97127</v>
       </c>
       <c r="D108" t="n">
-        <v>43.6952</v>
+        <v>45.3595</v>
       </c>
       <c r="E108" t="n">
-        <v>6.05409</v>
+        <v>6.06194</v>
       </c>
       <c r="F108" t="n">
-        <v>8.8581</v>
+        <v>8.849740000000001</v>
       </c>
     </row>
     <row r="109">
@@ -7219,19 +7219,19 @@
         <v>1816549</v>
       </c>
       <c r="B109" t="n">
-        <v>24.0478</v>
+        <v>24.9768</v>
       </c>
       <c r="C109" t="n">
-        <v>36.4032</v>
+        <v>5.18423</v>
       </c>
       <c r="D109" t="n">
-        <v>44.8476</v>
+        <v>46.5355</v>
       </c>
       <c r="E109" t="n">
-        <v>6.20366</v>
+        <v>6.18743</v>
       </c>
       <c r="F109" t="n">
-        <v>9.25447</v>
+        <v>9.300409999999999</v>
       </c>
     </row>
     <row r="110">
@@ -7239,19 +7239,19 @@
         <v>1907324</v>
       </c>
       <c r="B110" t="n">
-        <v>8.4354</v>
+        <v>8.470050000000001</v>
       </c>
       <c r="C110" t="n">
-        <v>15.0619</v>
+        <v>5.2596</v>
       </c>
       <c r="D110" t="n">
-        <v>46.0931</v>
+        <v>47.8386</v>
       </c>
       <c r="E110" t="n">
-        <v>6.29206</v>
+        <v>6.34832</v>
       </c>
       <c r="F110" t="n">
-        <v>9.64907</v>
+        <v>9.80706</v>
       </c>
     </row>
     <row r="111">
@@ -7259,19 +7259,19 @@
         <v>2002637</v>
       </c>
       <c r="B111" t="n">
-        <v>8.781470000000001</v>
+        <v>8.85577</v>
       </c>
       <c r="C111" t="n">
-        <v>15.6353</v>
+        <v>5.45079</v>
       </c>
       <c r="D111" t="n">
-        <v>47.3214</v>
+        <v>49.129</v>
       </c>
       <c r="E111" t="n">
-        <v>6.48094</v>
+        <v>6.52432</v>
       </c>
       <c r="F111" t="n">
-        <v>10.1098</v>
+        <v>10.2358</v>
       </c>
     </row>
     <row r="112">
@@ -7279,19 +7279,19 @@
         <v>2102715</v>
       </c>
       <c r="B112" t="n">
-        <v>9.144130000000001</v>
+        <v>9.19984</v>
       </c>
       <c r="C112" t="n">
-        <v>16.2035</v>
+        <v>5.64065</v>
       </c>
       <c r="D112" t="n">
-        <v>48.5962</v>
+        <v>50.4937</v>
       </c>
       <c r="E112" t="n">
-        <v>6.62004</v>
+        <v>6.68552</v>
       </c>
       <c r="F112" t="n">
-        <v>10.6627</v>
+        <v>10.7263</v>
       </c>
     </row>
     <row r="113">
@@ -7299,19 +7299,19 @@
         <v>2207796</v>
       </c>
       <c r="B113" t="n">
-        <v>9.55364</v>
+        <v>9.700939999999999</v>
       </c>
       <c r="C113" t="n">
-        <v>16.8182</v>
+        <v>5.9434</v>
       </c>
       <c r="D113" t="n">
-        <v>50.0063</v>
+        <v>51.863</v>
       </c>
       <c r="E113" t="n">
-        <v>6.90616</v>
+        <v>6.91862</v>
       </c>
       <c r="F113" t="n">
-        <v>11.2408</v>
+        <v>11.3287</v>
       </c>
     </row>
     <row r="114">
@@ -7319,19 +7319,19 @@
         <v>2318131</v>
       </c>
       <c r="B114" t="n">
-        <v>10.0569</v>
+        <v>10.1798</v>
       </c>
       <c r="C114" t="n">
-        <v>17.4547</v>
+        <v>6.23798</v>
       </c>
       <c r="D114" t="n">
-        <v>51.3057</v>
+        <v>53.3025</v>
       </c>
       <c r="E114" t="n">
-        <v>7.14113</v>
+        <v>7.20527</v>
       </c>
       <c r="F114" t="n">
-        <v>11.8675</v>
+        <v>11.9758</v>
       </c>
     </row>
     <row r="115">
@@ -7339,19 +7339,19 @@
         <v>2433982</v>
       </c>
       <c r="B115" t="n">
-        <v>10.6177</v>
+        <v>10.823</v>
       </c>
       <c r="C115" t="n">
-        <v>18.1613</v>
+        <v>6.67794</v>
       </c>
       <c r="D115" t="n">
-        <v>52.8711</v>
+        <v>54.8462</v>
       </c>
       <c r="E115" t="n">
-        <v>7.5061</v>
+        <v>7.61844</v>
       </c>
       <c r="F115" t="n">
-        <v>12.4574</v>
+        <v>12.5848</v>
       </c>
     </row>
     <row r="116">
@@ -7359,19 +7359,19 @@
         <v>2555625</v>
       </c>
       <c r="B116" t="n">
-        <v>11.1941</v>
+        <v>11.5386</v>
       </c>
       <c r="C116" t="n">
-        <v>18.9237</v>
+        <v>7.22039</v>
       </c>
       <c r="D116" t="n">
-        <v>54.3596</v>
+        <v>56.4692</v>
       </c>
       <c r="E116" t="n">
-        <v>7.88144</v>
+        <v>8.08356</v>
       </c>
       <c r="F116" t="n">
-        <v>13.0621</v>
+        <v>13.2407</v>
       </c>
     </row>
     <row r="117">
@@ -7379,19 +7379,19 @@
         <v>2683350</v>
       </c>
       <c r="B117" t="n">
-        <v>11.9111</v>
+        <v>12.3254</v>
       </c>
       <c r="C117" t="n">
-        <v>19.9095</v>
+        <v>7.77691</v>
       </c>
       <c r="D117" t="n">
-        <v>55.9868</v>
+        <v>58.1333</v>
       </c>
       <c r="E117" t="n">
-        <v>8.30245</v>
+        <v>8.52528</v>
       </c>
       <c r="F117" t="n">
-        <v>13.7425</v>
+        <v>13.9231</v>
       </c>
     </row>
     <row r="118">
@@ -7399,19 +7399,19 @@
         <v>2817461</v>
       </c>
       <c r="B118" t="n">
-        <v>12.754</v>
+        <v>13.1681</v>
       </c>
       <c r="C118" t="n">
-        <v>20.9916</v>
+        <v>8.468159999999999</v>
       </c>
       <c r="D118" t="n">
-        <v>57.7118</v>
+        <v>59.8814</v>
       </c>
       <c r="E118" t="n">
-        <v>8.858470000000001</v>
+        <v>9.09122</v>
       </c>
       <c r="F118" t="n">
-        <v>14.4795</v>
+        <v>14.6844</v>
       </c>
     </row>
     <row r="119">
@@ -7419,19 +7419,19 @@
         <v>2958277</v>
       </c>
       <c r="B119" t="n">
-        <v>13.8046</v>
+        <v>14.2235</v>
       </c>
       <c r="C119" t="n">
-        <v>22.4555</v>
+        <v>9.40249</v>
       </c>
       <c r="D119" t="n">
-        <v>59.4816</v>
+        <v>61.7775</v>
       </c>
       <c r="E119" t="n">
-        <v>9.523680000000001</v>
+        <v>9.714320000000001</v>
       </c>
       <c r="F119" t="n">
-        <v>15.3527</v>
+        <v>15.4819</v>
       </c>
     </row>
     <row r="120">
@@ -7439,19 +7439,19 @@
         <v>3106133</v>
       </c>
       <c r="B120" t="n">
-        <v>15.1864</v>
+        <v>15.6738</v>
       </c>
       <c r="C120" t="n">
-        <v>24.4135</v>
+        <v>10.634</v>
       </c>
       <c r="D120" t="n">
-        <v>61.4264</v>
+        <v>63.8089</v>
       </c>
       <c r="E120" t="n">
-        <v>10.3418</v>
+        <v>10.6252</v>
       </c>
       <c r="F120" t="n">
-        <v>16.5195</v>
+        <v>16.7557</v>
       </c>
     </row>
     <row r="121">
@@ -7459,19 +7459,19 @@
         <v>3261381</v>
       </c>
       <c r="B121" t="n">
-        <v>17.0719</v>
+        <v>17.5943</v>
       </c>
       <c r="C121" t="n">
-        <v>27.2046</v>
+        <v>12.4201</v>
       </c>
       <c r="D121" t="n">
-        <v>45.6613</v>
+        <v>47.48</v>
       </c>
       <c r="E121" t="n">
-        <v>11.5666</v>
+        <v>11.8594</v>
       </c>
       <c r="F121" t="n">
-        <v>18.2197</v>
+        <v>18.5168</v>
       </c>
     </row>
     <row r="122">
@@ -7479,19 +7479,19 @@
         <v>3424391</v>
       </c>
       <c r="B122" t="n">
-        <v>19.9035</v>
+        <v>20.5112</v>
       </c>
       <c r="C122" t="n">
-        <v>31.3512</v>
+        <v>6.88994</v>
       </c>
       <c r="D122" t="n">
-        <v>46.9327</v>
+        <v>48.3084</v>
       </c>
       <c r="E122" t="n">
-        <v>13.4346</v>
+        <v>14.0093</v>
       </c>
       <c r="F122" t="n">
-        <v>20.7893</v>
+        <v>21.2421</v>
       </c>
     </row>
     <row r="123">
@@ -7499,19 +7499,19 @@
         <v>3595551</v>
       </c>
       <c r="B123" t="n">
-        <v>24.2494</v>
+        <v>24.8619</v>
       </c>
       <c r="C123" t="n">
-        <v>37.8113</v>
+        <v>6.78703</v>
       </c>
       <c r="D123" t="n">
-        <v>48.1103</v>
+        <v>49.8941</v>
       </c>
       <c r="E123" t="n">
-        <v>7.83583</v>
+        <v>8.628500000000001</v>
       </c>
       <c r="F123" t="n">
-        <v>12.1975</v>
+        <v>12.1641</v>
       </c>
     </row>
     <row r="124">
@@ -7519,19 +7519,19 @@
         <v>3775269</v>
       </c>
       <c r="B124" t="n">
-        <v>10.9843</v>
+        <v>11.7929</v>
       </c>
       <c r="C124" t="n">
-        <v>17.2658</v>
+        <v>7.39403</v>
       </c>
       <c r="D124" t="n">
-        <v>49.0893</v>
+        <v>51.2215</v>
       </c>
       <c r="E124" t="n">
-        <v>8.4232</v>
+        <v>8.50746</v>
       </c>
       <c r="F124" t="n">
-        <v>12.8606</v>
+        <v>13.5121</v>
       </c>
     </row>
     <row r="125">
@@ -7539,19 +7539,19 @@
         <v>3963972</v>
       </c>
       <c r="B125" t="n">
-        <v>11.2461</v>
+        <v>11.1608</v>
       </c>
       <c r="C125" t="n">
-        <v>17.9087</v>
+        <v>7.29532</v>
       </c>
       <c r="D125" t="n">
-        <v>50.5972</v>
+        <v>52.5135</v>
       </c>
       <c r="E125" t="n">
-        <v>8.76876</v>
+        <v>8.81629</v>
       </c>
       <c r="F125" t="n">
-        <v>13.1188</v>
+        <v>12.8709</v>
       </c>
     </row>
     <row r="126">
@@ -7559,19 +7559,19 @@
         <v>4162110</v>
       </c>
       <c r="B126" t="n">
-        <v>11.427</v>
+        <v>11.7553</v>
       </c>
       <c r="C126" t="n">
-        <v>18.2507</v>
+        <v>7.77253</v>
       </c>
       <c r="D126" t="n">
-        <v>51.6546</v>
+        <v>53.8118</v>
       </c>
       <c r="E126" t="n">
-        <v>8.70823</v>
+        <v>9.09294</v>
       </c>
       <c r="F126" t="n">
-        <v>13.5277</v>
+        <v>13.7971</v>
       </c>
     </row>
     <row r="127">
@@ -7579,19 +7579,19 @@
         <v>4370154</v>
       </c>
       <c r="B127" t="n">
-        <v>11.8357</v>
+        <v>12.1207</v>
       </c>
       <c r="C127" t="n">
-        <v>18.7791</v>
+        <v>7.67259</v>
       </c>
       <c r="D127" t="n">
-        <v>53.2124</v>
+        <v>55.2761</v>
       </c>
       <c r="E127" t="n">
-        <v>9.157080000000001</v>
+        <v>9.482060000000001</v>
       </c>
       <c r="F127" t="n">
-        <v>14.0201</v>
+        <v>14.1615</v>
       </c>
     </row>
     <row r="128">
@@ -7599,19 +7599,19 @@
         <v>4588600</v>
       </c>
       <c r="B128" t="n">
-        <v>12.0863</v>
+        <v>12.1662</v>
       </c>
       <c r="C128" t="n">
-        <v>19.551</v>
+        <v>8.765790000000001</v>
       </c>
       <c r="D128" t="n">
-        <v>54.3109</v>
+        <v>56.7278</v>
       </c>
       <c r="E128" t="n">
-        <v>9.265269999999999</v>
+        <v>9.48283</v>
       </c>
       <c r="F128" t="n">
-        <v>14.1027</v>
+        <v>14.4418</v>
       </c>
     </row>
     <row r="129">
@@ -7619,19 +7619,19 @@
         <v>4817968</v>
       </c>
       <c r="B129" t="n">
-        <v>11.9409</v>
+        <v>12.7213</v>
       </c>
       <c r="C129" t="n">
-        <v>20.0381</v>
+        <v>8.28218</v>
       </c>
       <c r="D129" t="n">
-        <v>56.0592</v>
+        <v>58.386</v>
       </c>
       <c r="E129" t="n">
-        <v>9.80363</v>
+        <v>10.0016</v>
       </c>
       <c r="F129" t="n">
-        <v>14.7287</v>
+        <v>15.098</v>
       </c>
     </row>
     <row r="130">
@@ -7639,19 +7639,19 @@
         <v>5058804</v>
       </c>
       <c r="B130" t="n">
-        <v>12.903</v>
+        <v>13.0346</v>
       </c>
       <c r="C130" t="n">
-        <v>20.896</v>
+        <v>8.75244</v>
       </c>
       <c r="D130" t="n">
-        <v>57.3097</v>
+        <v>59.4759</v>
       </c>
       <c r="E130" t="n">
-        <v>9.83259</v>
+        <v>10.57</v>
       </c>
       <c r="F130" t="n">
-        <v>15.3059</v>
+        <v>15.9633</v>
       </c>
     </row>
     <row r="131">
@@ -7659,19 +7659,19 @@
         <v>5311681</v>
       </c>
       <c r="B131" t="n">
-        <v>13.2571</v>
+        <v>13.8189</v>
       </c>
       <c r="C131" t="n">
-        <v>21.8698</v>
+        <v>9.00539</v>
       </c>
       <c r="D131" t="n">
-        <v>58.8043</v>
+        <v>61.0993</v>
       </c>
       <c r="E131" t="n">
-        <v>10.0764</v>
+        <v>10.5092</v>
       </c>
       <c r="F131" t="n">
-        <v>15.6907</v>
+        <v>16.1119</v>
       </c>
     </row>
     <row r="132">
@@ -7679,19 +7679,19 @@
         <v>5577201</v>
       </c>
       <c r="B132" t="n">
-        <v>14.1784</v>
+        <v>14.3089</v>
       </c>
       <c r="C132" t="n">
-        <v>22.8227</v>
+        <v>9.732200000000001</v>
       </c>
       <c r="D132" t="n">
-        <v>60.8364</v>
+        <v>62.8517</v>
       </c>
       <c r="E132" t="n">
-        <v>10.7115</v>
+        <v>10.7824</v>
       </c>
       <c r="F132" t="n">
-        <v>16.4103</v>
+        <v>16.6423</v>
       </c>
     </row>
     <row r="133">
@@ -7699,19 +7699,19 @@
         <v>5855997</v>
       </c>
       <c r="B133" t="n">
-        <v>15.0528</v>
+        <v>15.4093</v>
       </c>
       <c r="C133" t="n">
-        <v>24.4304</v>
+        <v>10.4183</v>
       </c>
       <c r="D133" t="n">
-        <v>62.657</v>
+        <v>64.57080000000001</v>
       </c>
       <c r="E133" t="n">
-        <v>10.5123</v>
+        <v>11.4757</v>
       </c>
       <c r="F133" t="n">
-        <v>17.0919</v>
+        <v>17.8552</v>
       </c>
     </row>
     <row r="134">
@@ -7719,19 +7719,19 @@
         <v>6148732</v>
       </c>
       <c r="B134" t="n">
-        <v>16.3369</v>
+        <v>16.8441</v>
       </c>
       <c r="C134" t="n">
-        <v>26.1324</v>
+        <v>11.4562</v>
       </c>
       <c r="D134" t="n">
-        <v>64.54049999999999</v>
+        <v>66.5779</v>
       </c>
       <c r="E134" t="n">
-        <v>11.6844</v>
+        <v>11.9683</v>
       </c>
       <c r="F134" t="n">
-        <v>18.1938</v>
+        <v>18.6973</v>
       </c>
     </row>
     <row r="135">
@@ -7739,19 +7739,19 @@
         <v>6456103</v>
       </c>
       <c r="B135" t="n">
-        <v>17.4125</v>
+        <v>18.5277</v>
       </c>
       <c r="C135" t="n">
-        <v>28.7874</v>
+        <v>13.0455</v>
       </c>
       <c r="D135" t="n">
-        <v>47.6959</v>
+        <v>48.9506</v>
       </c>
       <c r="E135" t="n">
-        <v>12.5391</v>
+        <v>12.9954</v>
       </c>
       <c r="F135" t="n">
-        <v>19.6937</v>
+        <v>20.1375</v>
       </c>
     </row>
     <row r="136">
@@ -7759,19 +7759,19 @@
         <v>6778842</v>
       </c>
       <c r="B136" t="n">
-        <v>20.4747</v>
+        <v>21.2659</v>
       </c>
       <c r="C136" t="n">
-        <v>32.6804</v>
+        <v>14.1647</v>
       </c>
       <c r="D136" t="n">
-        <v>48.6262</v>
+        <v>50.1521</v>
       </c>
       <c r="E136" t="n">
-        <v>13.7086</v>
+        <v>14.9875</v>
       </c>
       <c r="F136" t="n">
-        <v>22.1411</v>
+        <v>22.461</v>
       </c>
     </row>
     <row r="137">
@@ -7779,19 +7779,19 @@
         <v>7117717</v>
       </c>
       <c r="B137" t="n">
-        <v>24.6247</v>
+        <v>25.7063</v>
       </c>
       <c r="C137" t="n">
-        <v>38.6507</v>
+        <v>14.386</v>
       </c>
       <c r="D137" t="n">
-        <v>49.9863</v>
+        <v>51.5644</v>
       </c>
       <c r="E137" t="n">
-        <v>16.1923</v>
+        <v>16.5645</v>
       </c>
       <c r="F137" t="n">
-        <v>20.6402</v>
+        <v>21.0437</v>
       </c>
     </row>
     <row r="138">
@@ -7799,19 +7799,19 @@
         <v>7473535</v>
       </c>
       <c r="B138" t="n">
-        <v>17.9852</v>
+        <v>18.991</v>
       </c>
       <c r="C138" t="n">
-        <v>23.9131</v>
+        <v>14.1371</v>
       </c>
       <c r="D138" t="n">
-        <v>51.2278</v>
+        <v>52.5836</v>
       </c>
       <c r="E138" t="n">
-        <v>16.3027</v>
+        <v>16.958</v>
       </c>
       <c r="F138" t="n">
-        <v>20.8569</v>
+        <v>20.4608</v>
       </c>
     </row>
     <row r="139">
@@ -7819,19 +7819,19 @@
         <v>7847143</v>
       </c>
       <c r="B139" t="n">
-        <v>18.4713</v>
+        <v>19.12</v>
       </c>
       <c r="C139" t="n">
-        <v>25.189</v>
+        <v>14.3825</v>
       </c>
       <c r="D139" t="n">
-        <v>52.239</v>
+        <v>54.1142</v>
       </c>
       <c r="E139" t="n">
-        <v>16.8075</v>
+        <v>17.1163</v>
       </c>
       <c r="F139" t="n">
-        <v>20.5688</v>
+        <v>21.7438</v>
       </c>
     </row>
     <row r="140">
@@ -7839,19 +7839,19 @@
         <v>8239431</v>
       </c>
       <c r="B140" t="n">
-        <v>17.9774</v>
+        <v>19.3641</v>
       </c>
       <c r="C140" t="n">
-        <v>25.5769</v>
+        <v>14.6655</v>
       </c>
       <c r="D140" t="n">
-        <v>53.7378</v>
+        <v>55.3416</v>
       </c>
       <c r="E140" t="n">
-        <v>16.8214</v>
+        <v>17.1348</v>
       </c>
       <c r="F140" t="n">
-        <v>20.9686</v>
+        <v>21.2902</v>
       </c>
     </row>
     <row r="141">
@@ -7859,19 +7859,19 @@
         <v>8651333</v>
       </c>
       <c r="B141" t="n">
-        <v>18.7299</v>
+        <v>19.4152</v>
       </c>
       <c r="C141" t="n">
-        <v>25.582</v>
+        <v>14.6379</v>
       </c>
       <c r="D141" t="n">
-        <v>54.9049</v>
+        <v>56.8237</v>
       </c>
       <c r="E141" t="n">
-        <v>16.8717</v>
+        <v>17.4359</v>
       </c>
       <c r="F141" t="n">
-        <v>21.1705</v>
+        <v>22.2699</v>
       </c>
     </row>
     <row r="142">
@@ -7879,19 +7879,19 @@
         <v>9083830</v>
       </c>
       <c r="B142" t="n">
-        <v>18.9262</v>
+        <v>19.7235</v>
       </c>
       <c r="C142" t="n">
-        <v>26.6825</v>
+        <v>15.0083</v>
       </c>
       <c r="D142" t="n">
-        <v>56.5169</v>
+        <v>58.3189</v>
       </c>
       <c r="E142" t="n">
-        <v>17.1959</v>
+        <v>17.5784</v>
       </c>
       <c r="F142" t="n">
-        <v>21.5532</v>
+        <v>22.6924</v>
       </c>
     </row>
     <row r="143">
@@ -7899,19 +7899,19 @@
         <v>9537951</v>
       </c>
       <c r="B143" t="n">
-        <v>18.5493</v>
+        <v>20.1629</v>
       </c>
       <c r="C143" t="n">
-        <v>26.3986</v>
+        <v>14.9889</v>
       </c>
       <c r="D143" t="n">
-        <v>57.9351</v>
+        <v>59.8339</v>
       </c>
       <c r="E143" t="n">
-        <v>16.6662</v>
+        <v>17.787</v>
       </c>
       <c r="F143" t="n">
-        <v>22.6285</v>
+        <v>23.2661</v>
       </c>
     </row>
   </sheetData>

--- a/gcc-x64/Scattered unsuccessful looukp.xlsx
+++ b/gcc-x64/Scattered unsuccessful looukp.xlsx
@@ -5079,19 +5079,19 @@
         <v>10000</v>
       </c>
       <c r="B2" t="n">
-        <v>2.88572</v>
+        <v>2.86993</v>
       </c>
       <c r="C2" t="n">
-        <v>1.91271</v>
+        <v>1.91221</v>
       </c>
       <c r="D2" t="n">
-        <v>13.5896</v>
+        <v>13.4041</v>
       </c>
       <c r="E2" t="n">
-        <v>2.00044</v>
+        <v>1.98911</v>
       </c>
       <c r="F2" t="n">
-        <v>2.26249</v>
+        <v>2.28775</v>
       </c>
     </row>
     <row r="3">
@@ -5099,19 +5099,19 @@
         <v>10500</v>
       </c>
       <c r="B3" t="n">
-        <v>2.95857</v>
+        <v>2.94868</v>
       </c>
       <c r="C3" t="n">
-        <v>2.05126</v>
+        <v>1.98392</v>
       </c>
       <c r="D3" t="n">
-        <v>14.2891</v>
+        <v>14.2215</v>
       </c>
       <c r="E3" t="n">
-        <v>1.93833</v>
+        <v>1.92597</v>
       </c>
       <c r="F3" t="n">
-        <v>2.29297</v>
+        <v>2.14245</v>
       </c>
     </row>
     <row r="4">
@@ -5119,19 +5119,19 @@
         <v>11025</v>
       </c>
       <c r="B4" t="n">
-        <v>3.1046</v>
+        <v>3.05945</v>
       </c>
       <c r="C4" t="n">
-        <v>2.09485</v>
+        <v>2.11661</v>
       </c>
       <c r="D4" t="n">
-        <v>15.0719</v>
+        <v>14.7941</v>
       </c>
       <c r="E4" t="n">
-        <v>1.7781</v>
+        <v>1.76087</v>
       </c>
       <c r="F4" t="n">
-        <v>2.04914</v>
+        <v>1.95443</v>
       </c>
     </row>
     <row r="5">
@@ -5139,19 +5139,19 @@
         <v>11576</v>
       </c>
       <c r="B5" t="n">
-        <v>3.48038</v>
+        <v>3.41599</v>
       </c>
       <c r="C5" t="n">
-        <v>2.27078</v>
+        <v>2.25337</v>
       </c>
       <c r="D5" t="n">
-        <v>15.4101</v>
+        <v>15.332</v>
       </c>
       <c r="E5" t="n">
-        <v>1.76554</v>
+        <v>1.77106</v>
       </c>
       <c r="F5" t="n">
-        <v>1.97707</v>
+        <v>2.06225</v>
       </c>
     </row>
     <row r="6">
@@ -5159,19 +5159,19 @@
         <v>12154</v>
       </c>
       <c r="B6" t="n">
-        <v>4.25318</v>
+        <v>4.28394</v>
       </c>
       <c r="C6" t="n">
-        <v>2.91152</v>
+        <v>2.89986</v>
       </c>
       <c r="D6" t="n">
-        <v>15.9704</v>
+        <v>15.9533</v>
       </c>
       <c r="E6" t="n">
-        <v>1.86763</v>
+        <v>1.84047</v>
       </c>
       <c r="F6" t="n">
-        <v>2.16766</v>
+        <v>2.16583</v>
       </c>
     </row>
     <row r="7">
@@ -5179,19 +5179,19 @@
         <v>12760</v>
       </c>
       <c r="B7" t="n">
-        <v>6.62966</v>
+        <v>6.55447</v>
       </c>
       <c r="C7" t="n">
-        <v>5.01657</v>
+        <v>5.03874</v>
       </c>
       <c r="D7" t="n">
-        <v>11.1823</v>
+        <v>10.9289</v>
       </c>
       <c r="E7" t="n">
-        <v>2.19697</v>
+        <v>1.94683</v>
       </c>
       <c r="F7" t="n">
-        <v>2.71177</v>
+        <v>2.06793</v>
       </c>
     </row>
     <row r="8">
@@ -5199,19 +5199,19 @@
         <v>13396</v>
       </c>
       <c r="B8" t="n">
-        <v>9.20097</v>
+        <v>9.38894</v>
       </c>
       <c r="C8" t="n">
-        <v>1.8262</v>
+        <v>1.91746</v>
       </c>
       <c r="D8" t="n">
-        <v>11.501</v>
+        <v>11.5214</v>
       </c>
       <c r="E8" t="n">
-        <v>3.87427</v>
+        <v>1.95855</v>
       </c>
       <c r="F8" t="n">
-        <v>4.12485</v>
+        <v>2.09427</v>
       </c>
     </row>
     <row r="9">
@@ -5219,19 +5219,19 @@
         <v>14063</v>
       </c>
       <c r="B9" t="n">
-        <v>13.657</v>
+        <v>14.0402</v>
       </c>
       <c r="C9" t="n">
-        <v>1.74549</v>
+        <v>1.79742</v>
       </c>
       <c r="D9" t="n">
-        <v>12.205</v>
+        <v>12.0787</v>
       </c>
       <c r="E9" t="n">
-        <v>1.97837</v>
+        <v>1.96186</v>
       </c>
       <c r="F9" t="n">
-        <v>2.11651</v>
+        <v>2.10523</v>
       </c>
     </row>
     <row r="10">
@@ -5239,19 +5239,19 @@
         <v>14763</v>
       </c>
       <c r="B10" t="n">
-        <v>2.78797</v>
+        <v>2.79144</v>
       </c>
       <c r="C10" t="n">
-        <v>1.78657</v>
+        <v>1.96677</v>
       </c>
       <c r="D10" t="n">
-        <v>12.8904</v>
+        <v>12.8566</v>
       </c>
       <c r="E10" t="n">
-        <v>1.99688</v>
+        <v>1.98879</v>
       </c>
       <c r="F10" t="n">
-        <v>2.13727</v>
+        <v>2.10664</v>
       </c>
     </row>
     <row r="11">
@@ -5259,19 +5259,19 @@
         <v>15498</v>
       </c>
       <c r="B11" t="n">
-        <v>2.85086</v>
+        <v>2.84318</v>
       </c>
       <c r="C11" t="n">
-        <v>1.86586</v>
+        <v>1.93019</v>
       </c>
       <c r="D11" t="n">
-        <v>13.2866</v>
+        <v>13.3633</v>
       </c>
       <c r="E11" t="n">
-        <v>1.99153</v>
+        <v>1.9929</v>
       </c>
       <c r="F11" t="n">
-        <v>2.16461</v>
+        <v>2.14956</v>
       </c>
     </row>
     <row r="12">
@@ -5279,19 +5279,19 @@
         <v>16269</v>
       </c>
       <c r="B12" t="n">
-        <v>2.89046</v>
+        <v>2.87194</v>
       </c>
       <c r="C12" t="n">
-        <v>1.85772</v>
+        <v>1.87461</v>
       </c>
       <c r="D12" t="n">
-        <v>13.7907</v>
+        <v>13.8522</v>
       </c>
       <c r="E12" t="n">
-        <v>2.01961</v>
+        <v>2.01317</v>
       </c>
       <c r="F12" t="n">
-        <v>2.21093</v>
+        <v>2.21572</v>
       </c>
     </row>
     <row r="13">
@@ -5299,19 +5299,19 @@
         <v>17078</v>
       </c>
       <c r="B13" t="n">
-        <v>2.95441</v>
+        <v>2.87498</v>
       </c>
       <c r="C13" t="n">
-        <v>1.88526</v>
+        <v>1.90184</v>
       </c>
       <c r="D13" t="n">
-        <v>14.2878</v>
+        <v>14.3866</v>
       </c>
       <c r="E13" t="n">
-        <v>2.02606</v>
+        <v>2.02796</v>
       </c>
       <c r="F13" t="n">
-        <v>2.22693</v>
+        <v>2.2001</v>
       </c>
     </row>
     <row r="14">
@@ -5319,19 +5319,19 @@
         <v>17927</v>
       </c>
       <c r="B14" t="n">
-        <v>2.99985</v>
+        <v>2.95736</v>
       </c>
       <c r="C14" t="n">
-        <v>1.9664</v>
+        <v>1.97726</v>
       </c>
       <c r="D14" t="n">
-        <v>14.802</v>
+        <v>14.7972</v>
       </c>
       <c r="E14" t="n">
-        <v>2.05524</v>
+        <v>2.05052</v>
       </c>
       <c r="F14" t="n">
-        <v>2.24921</v>
+        <v>2.23283</v>
       </c>
     </row>
     <row r="15">
@@ -5339,19 +5339,19 @@
         <v>18818</v>
       </c>
       <c r="B15" t="n">
-        <v>3.04485</v>
+        <v>3.05583</v>
       </c>
       <c r="C15" t="n">
-        <v>2.01147</v>
+        <v>2.00136</v>
       </c>
       <c r="D15" t="n">
-        <v>15.1829</v>
+        <v>15.2089</v>
       </c>
       <c r="E15" t="n">
-        <v>2.07793</v>
+        <v>2.06897</v>
       </c>
       <c r="F15" t="n">
-        <v>2.26002</v>
+        <v>2.27739</v>
       </c>
     </row>
     <row r="16">
@@ -5359,19 +5359,19 @@
         <v>19753</v>
       </c>
       <c r="B16" t="n">
-        <v>3.09644</v>
+        <v>3.0964</v>
       </c>
       <c r="C16" t="n">
-        <v>2.14246</v>
+        <v>2.11706</v>
       </c>
       <c r="D16" t="n">
-        <v>15.6112</v>
+        <v>15.5479</v>
       </c>
       <c r="E16" t="n">
-        <v>2.09833</v>
+        <v>2.10968</v>
       </c>
       <c r="F16" t="n">
-        <v>2.33019</v>
+        <v>2.28261</v>
       </c>
     </row>
     <row r="17">
@@ -5379,19 +5379,19 @@
         <v>20734</v>
       </c>
       <c r="B17" t="n">
-        <v>3.33696</v>
+        <v>3.29122</v>
       </c>
       <c r="C17" t="n">
-        <v>2.26146</v>
+        <v>2.31409</v>
       </c>
       <c r="D17" t="n">
-        <v>16.0464</v>
+        <v>16.1127</v>
       </c>
       <c r="E17" t="n">
-        <v>2.15174</v>
+        <v>2.13968</v>
       </c>
       <c r="F17" t="n">
-        <v>2.37621</v>
+        <v>2.35641</v>
       </c>
     </row>
     <row r="18">
@@ -5399,19 +5399,19 @@
         <v>21764</v>
       </c>
       <c r="B18" t="n">
-        <v>3.59217</v>
+        <v>3.66781</v>
       </c>
       <c r="C18" t="n">
-        <v>2.49301</v>
+        <v>2.51657</v>
       </c>
       <c r="D18" t="n">
-        <v>16.4539</v>
+        <v>16.5091</v>
       </c>
       <c r="E18" t="n">
-        <v>2.1882</v>
+        <v>2.14668</v>
       </c>
       <c r="F18" t="n">
-        <v>2.41724</v>
+        <v>2.42623</v>
       </c>
     </row>
     <row r="19">
@@ -5419,19 +5419,19 @@
         <v>22845</v>
       </c>
       <c r="B19" t="n">
-        <v>4.08104</v>
+        <v>4.21634</v>
       </c>
       <c r="C19" t="n">
-        <v>3.12401</v>
+        <v>3.1316</v>
       </c>
       <c r="D19" t="n">
-        <v>16.9058</v>
+        <v>16.9761</v>
       </c>
       <c r="E19" t="n">
-        <v>2.18071</v>
+        <v>2.1773</v>
       </c>
       <c r="F19" t="n">
-        <v>2.46118</v>
+        <v>2.43475</v>
       </c>
     </row>
     <row r="20">
@@ -5439,19 +5439,19 @@
         <v>23980</v>
       </c>
       <c r="B20" t="n">
-        <v>5.28015</v>
+        <v>5.20072</v>
       </c>
       <c r="C20" t="n">
-        <v>4.25562</v>
+        <v>4.23828</v>
       </c>
       <c r="D20" t="n">
-        <v>17.1905</v>
+        <v>17.3384</v>
       </c>
       <c r="E20" t="n">
-        <v>2.59654</v>
+        <v>2.60138</v>
       </c>
       <c r="F20" t="n">
-        <v>2.83317</v>
+        <v>2.84298</v>
       </c>
     </row>
     <row r="21">
@@ -5459,19 +5459,19 @@
         <v>25171</v>
       </c>
       <c r="B21" t="n">
-        <v>6.84445</v>
+        <v>6.80223</v>
       </c>
       <c r="C21" t="n">
-        <v>5.53407</v>
+        <v>5.53148</v>
       </c>
       <c r="D21" t="n">
-        <v>12.1411</v>
+        <v>12.2414</v>
       </c>
       <c r="E21" t="n">
-        <v>3.50906</v>
+        <v>2.03143</v>
       </c>
       <c r="F21" t="n">
-        <v>3.64628</v>
+        <v>2.21373</v>
       </c>
     </row>
     <row r="22">
@@ -5479,19 +5479,19 @@
         <v>26421</v>
       </c>
       <c r="B22" t="n">
-        <v>9.244870000000001</v>
+        <v>9.066839999999999</v>
       </c>
       <c r="C22" t="n">
-        <v>1.79872</v>
+        <v>1.82336</v>
       </c>
       <c r="D22" t="n">
-        <v>12.6011</v>
+        <v>12.6751</v>
       </c>
       <c r="E22" t="n">
-        <v>4.97426</v>
+        <v>2.07152</v>
       </c>
       <c r="F22" t="n">
-        <v>4.95499</v>
+        <v>2.25743</v>
       </c>
     </row>
     <row r="23">
@@ -5499,19 +5499,19 @@
         <v>27733</v>
       </c>
       <c r="B23" t="n">
-        <v>12.4616</v>
+        <v>12.3841</v>
       </c>
       <c r="C23" t="n">
-        <v>1.83135</v>
+        <v>1.84051</v>
       </c>
       <c r="D23" t="n">
-        <v>13.1447</v>
+        <v>13.1895</v>
       </c>
       <c r="E23" t="n">
-        <v>2.08472</v>
+        <v>2.0817</v>
       </c>
       <c r="F23" t="n">
-        <v>2.34648</v>
+        <v>2.32758</v>
       </c>
     </row>
     <row r="24">
@@ -5519,19 +5519,19 @@
         <v>29110</v>
       </c>
       <c r="B24" t="n">
-        <v>2.92787</v>
+        <v>2.90108</v>
       </c>
       <c r="C24" t="n">
-        <v>1.84564</v>
+        <v>1.83407</v>
       </c>
       <c r="D24" t="n">
-        <v>13.6764</v>
+        <v>13.7616</v>
       </c>
       <c r="E24" t="n">
-        <v>2.1091</v>
+        <v>2.11611</v>
       </c>
       <c r="F24" t="n">
-        <v>2.35913</v>
+        <v>2.3572</v>
       </c>
     </row>
     <row r="25">
@@ -5539,19 +5539,19 @@
         <v>30555</v>
       </c>
       <c r="B25" t="n">
-        <v>2.96833</v>
+        <v>2.93287</v>
       </c>
       <c r="C25" t="n">
-        <v>1.88734</v>
+        <v>1.90911</v>
       </c>
       <c r="D25" t="n">
-        <v>14.1877</v>
+        <v>14.2481</v>
       </c>
       <c r="E25" t="n">
-        <v>2.1251</v>
+        <v>2.13865</v>
       </c>
       <c r="F25" t="n">
-        <v>2.41516</v>
+        <v>2.39516</v>
       </c>
     </row>
     <row r="26">
@@ -5559,19 +5559,19 @@
         <v>32072</v>
       </c>
       <c r="B26" t="n">
-        <v>3.01573</v>
+        <v>3.01292</v>
       </c>
       <c r="C26" t="n">
-        <v>1.93233</v>
+        <v>1.93106</v>
       </c>
       <c r="D26" t="n">
-        <v>14.5836</v>
+        <v>14.7073</v>
       </c>
       <c r="E26" t="n">
-        <v>2.15854</v>
+        <v>2.14748</v>
       </c>
       <c r="F26" t="n">
-        <v>2.46042</v>
+        <v>2.43696</v>
       </c>
     </row>
     <row r="27">
@@ -5579,19 +5579,19 @@
         <v>33664</v>
       </c>
       <c r="B27" t="n">
-        <v>3.07578</v>
+        <v>3.09052</v>
       </c>
       <c r="C27" t="n">
-        <v>1.96692</v>
+        <v>1.97558</v>
       </c>
       <c r="D27" t="n">
-        <v>15.1409</v>
+        <v>15.1956</v>
       </c>
       <c r="E27" t="n">
-        <v>2.17791</v>
+        <v>2.17533</v>
       </c>
       <c r="F27" t="n">
-        <v>2.51377</v>
+        <v>2.49906</v>
       </c>
     </row>
     <row r="28">
@@ -5599,19 +5599,19 @@
         <v>35335</v>
       </c>
       <c r="B28" t="n">
-        <v>3.15264</v>
+        <v>3.15686</v>
       </c>
       <c r="C28" t="n">
-        <v>2.03422</v>
+        <v>2.03856</v>
       </c>
       <c r="D28" t="n">
-        <v>15.5653</v>
+        <v>15.6595</v>
       </c>
       <c r="E28" t="n">
-        <v>2.21315</v>
+        <v>2.2235</v>
       </c>
       <c r="F28" t="n">
-        <v>2.5882</v>
+        <v>2.59007</v>
       </c>
     </row>
     <row r="29">
@@ -5619,19 +5619,19 @@
         <v>37089</v>
       </c>
       <c r="B29" t="n">
-        <v>3.27761</v>
+        <v>3.29107</v>
       </c>
       <c r="C29" t="n">
-        <v>2.13802</v>
+        <v>2.13655</v>
       </c>
       <c r="D29" t="n">
-        <v>16.1299</v>
+        <v>16.1758</v>
       </c>
       <c r="E29" t="n">
-        <v>2.26106</v>
+        <v>2.25273</v>
       </c>
       <c r="F29" t="n">
-        <v>2.6563</v>
+        <v>2.65309</v>
       </c>
     </row>
     <row r="30">
@@ -5639,19 +5639,19 @@
         <v>38930</v>
       </c>
       <c r="B30" t="n">
-        <v>3.4344</v>
+        <v>3.45513</v>
       </c>
       <c r="C30" t="n">
-        <v>2.24213</v>
+        <v>2.25387</v>
       </c>
       <c r="D30" t="n">
-        <v>16.6244</v>
+        <v>16.6598</v>
       </c>
       <c r="E30" t="n">
-        <v>2.29718</v>
+        <v>2.29915</v>
       </c>
       <c r="F30" t="n">
-        <v>2.69876</v>
+        <v>2.68101</v>
       </c>
     </row>
     <row r="31">
@@ -5659,19 +5659,19 @@
         <v>40863</v>
       </c>
       <c r="B31" t="n">
-        <v>3.68419</v>
+        <v>3.68895</v>
       </c>
       <c r="C31" t="n">
-        <v>2.41725</v>
+        <v>2.42641</v>
       </c>
       <c r="D31" t="n">
-        <v>17.0602</v>
+        <v>17.0826</v>
       </c>
       <c r="E31" t="n">
-        <v>2.32622</v>
+        <v>2.32088</v>
       </c>
       <c r="F31" t="n">
-        <v>2.76188</v>
+        <v>2.72548</v>
       </c>
     </row>
     <row r="32">
@@ -5679,19 +5679,19 @@
         <v>42892</v>
       </c>
       <c r="B32" t="n">
-        <v>4.04777</v>
+        <v>4.04802</v>
       </c>
       <c r="C32" t="n">
-        <v>2.70273</v>
+        <v>2.71851</v>
       </c>
       <c r="D32" t="n">
-        <v>17.4351</v>
+        <v>17.3993</v>
       </c>
       <c r="E32" t="n">
-        <v>2.41251</v>
+        <v>2.41795</v>
       </c>
       <c r="F32" t="n">
-        <v>2.8529</v>
+        <v>2.85383</v>
       </c>
     </row>
     <row r="33">
@@ -5699,19 +5699,19 @@
         <v>45022</v>
       </c>
       <c r="B33" t="n">
-        <v>4.81436</v>
+        <v>4.69542</v>
       </c>
       <c r="C33" t="n">
-        <v>3.29374</v>
+        <v>3.2954</v>
       </c>
       <c r="D33" t="n">
-        <v>17.9167</v>
+        <v>17.9002</v>
       </c>
       <c r="E33" t="n">
-        <v>2.63879</v>
+        <v>2.64566</v>
       </c>
       <c r="F33" t="n">
-        <v>3.03909</v>
+        <v>3.00913</v>
       </c>
     </row>
     <row r="34">
@@ -5719,19 +5719,19 @@
         <v>47258</v>
       </c>
       <c r="B34" t="n">
-        <v>5.56771</v>
+        <v>5.61942</v>
       </c>
       <c r="C34" t="n">
-        <v>4.13496</v>
+        <v>4.15803</v>
       </c>
       <c r="D34" t="n">
-        <v>18.3392</v>
+        <v>18.3493</v>
       </c>
       <c r="E34" t="n">
-        <v>3.11049</v>
+        <v>3.11519</v>
       </c>
       <c r="F34" t="n">
-        <v>3.44408</v>
+        <v>3.43725</v>
       </c>
     </row>
     <row r="35">
@@ -5739,19 +5739,19 @@
         <v>49605</v>
       </c>
       <c r="B35" t="n">
-        <v>6.99843</v>
+        <v>7.11376</v>
       </c>
       <c r="C35" t="n">
-        <v>5.29847</v>
+        <v>5.30256</v>
       </c>
       <c r="D35" t="n">
-        <v>12.6883</v>
+        <v>12.7256</v>
       </c>
       <c r="E35" t="n">
-        <v>3.90728</v>
+        <v>2.09272</v>
       </c>
       <c r="F35" t="n">
-        <v>4.08013</v>
+        <v>2.39824</v>
       </c>
     </row>
     <row r="36">
@@ -5759,19 +5759,19 @@
         <v>52069</v>
       </c>
       <c r="B36" t="n">
-        <v>9.40817</v>
+        <v>9.303319999999999</v>
       </c>
       <c r="C36" t="n">
-        <v>6.9532</v>
+        <v>6.94398</v>
       </c>
       <c r="D36" t="n">
-        <v>13.1199</v>
+        <v>13.1677</v>
       </c>
       <c r="E36" t="n">
-        <v>4.93986</v>
+        <v>2.11485</v>
       </c>
       <c r="F36" t="n">
-        <v>4.97178</v>
+        <v>2.43569</v>
       </c>
     </row>
     <row r="37">
@@ -5779,19 +5779,19 @@
         <v>54656</v>
       </c>
       <c r="B37" t="n">
-        <v>12.4463</v>
+        <v>12.999</v>
       </c>
       <c r="C37" t="n">
-        <v>1.81817</v>
+        <v>1.89402</v>
       </c>
       <c r="D37" t="n">
-        <v>13.5926</v>
+        <v>13.6739</v>
       </c>
       <c r="E37" t="n">
-        <v>2.15119</v>
+        <v>2.15683</v>
       </c>
       <c r="F37" t="n">
-        <v>2.48894</v>
+        <v>2.4613</v>
       </c>
     </row>
     <row r="38">
@@ -5799,19 +5799,19 @@
         <v>57372</v>
       </c>
       <c r="B38" t="n">
-        <v>2.96067</v>
+        <v>2.97796</v>
       </c>
       <c r="C38" t="n">
-        <v>1.85455</v>
+        <v>1.91818</v>
       </c>
       <c r="D38" t="n">
-        <v>14.1589</v>
+        <v>14.2159</v>
       </c>
       <c r="E38" t="n">
-        <v>2.1706</v>
+        <v>2.16965</v>
       </c>
       <c r="F38" t="n">
-        <v>2.5138</v>
+        <v>2.52477</v>
       </c>
     </row>
     <row r="39">
@@ -5819,19 +5819,19 @@
         <v>60223</v>
       </c>
       <c r="B39" t="n">
-        <v>3.02174</v>
+        <v>3.01132</v>
       </c>
       <c r="C39" t="n">
-        <v>1.89222</v>
+        <v>1.90023</v>
       </c>
       <c r="D39" t="n">
-        <v>14.6706</v>
+        <v>14.731</v>
       </c>
       <c r="E39" t="n">
-        <v>2.2068</v>
+        <v>2.21196</v>
       </c>
       <c r="F39" t="n">
-        <v>2.57602</v>
+        <v>2.5856</v>
       </c>
     </row>
     <row r="40">
@@ -5839,19 +5839,19 @@
         <v>63216</v>
       </c>
       <c r="B40" t="n">
-        <v>3.07973</v>
+        <v>3.07979</v>
       </c>
       <c r="C40" t="n">
-        <v>1.93151</v>
+        <v>1.96741</v>
       </c>
       <c r="D40" t="n">
-        <v>15.1987</v>
+        <v>15.2382</v>
       </c>
       <c r="E40" t="n">
-        <v>2.229</v>
+        <v>2.23051</v>
       </c>
       <c r="F40" t="n">
-        <v>2.63218</v>
+        <v>2.64701</v>
       </c>
     </row>
     <row r="41">
@@ -5859,19 +5859,19 @@
         <v>66358</v>
       </c>
       <c r="B41" t="n">
-        <v>3.14703</v>
+        <v>3.14278</v>
       </c>
       <c r="C41" t="n">
-        <v>2.00526</v>
+        <v>2.03223</v>
       </c>
       <c r="D41" t="n">
-        <v>15.6869</v>
+        <v>15.7079</v>
       </c>
       <c r="E41" t="n">
-        <v>2.25822</v>
+        <v>2.25182</v>
       </c>
       <c r="F41" t="n">
-        <v>2.65202</v>
+        <v>2.69029</v>
       </c>
     </row>
     <row r="42">
@@ -5879,19 +5879,19 @@
         <v>69657</v>
       </c>
       <c r="B42" t="n">
-        <v>3.23134</v>
+        <v>3.20152</v>
       </c>
       <c r="C42" t="n">
-        <v>2.06452</v>
+        <v>2.09369</v>
       </c>
       <c r="D42" t="n">
-        <v>16.1639</v>
+        <v>16.196</v>
       </c>
       <c r="E42" t="n">
-        <v>2.3032</v>
+        <v>2.30521</v>
       </c>
       <c r="F42" t="n">
-        <v>2.73962</v>
+        <v>2.74753</v>
       </c>
     </row>
     <row r="43">
@@ -5899,19 +5899,19 @@
         <v>73120</v>
       </c>
       <c r="B43" t="n">
-        <v>3.35725</v>
+        <v>3.34534</v>
       </c>
       <c r="C43" t="n">
-        <v>2.15361</v>
+        <v>2.1574</v>
       </c>
       <c r="D43" t="n">
-        <v>16.6408</v>
+        <v>16.6595</v>
       </c>
       <c r="E43" t="n">
-        <v>2.35412</v>
+        <v>2.35634</v>
       </c>
       <c r="F43" t="n">
-        <v>2.80767</v>
+        <v>2.82049</v>
       </c>
     </row>
     <row r="44">
@@ -5919,19 +5919,19 @@
         <v>76756</v>
       </c>
       <c r="B44" t="n">
-        <v>3.50776</v>
+        <v>3.50938</v>
       </c>
       <c r="C44" t="n">
-        <v>2.2839</v>
+        <v>2.27574</v>
       </c>
       <c r="D44" t="n">
-        <v>17.0832</v>
+        <v>17.0869</v>
       </c>
       <c r="E44" t="n">
-        <v>2.43814</v>
+        <v>2.4418</v>
       </c>
       <c r="F44" t="n">
-        <v>2.90723</v>
+        <v>2.92168</v>
       </c>
     </row>
     <row r="45">
@@ -5939,19 +5939,19 @@
         <v>80573</v>
       </c>
       <c r="B45" t="n">
-        <v>3.7154</v>
+        <v>3.73701</v>
       </c>
       <c r="C45" t="n">
-        <v>2.54612</v>
+        <v>2.56625</v>
       </c>
       <c r="D45" t="n">
-        <v>17.4755</v>
+        <v>17.4632</v>
       </c>
       <c r="E45" t="n">
-        <v>2.54219</v>
+        <v>2.53981</v>
       </c>
       <c r="F45" t="n">
-        <v>3.03785</v>
+        <v>3.02988</v>
       </c>
     </row>
     <row r="46">
@@ -5959,19 +5959,19 @@
         <v>84580</v>
       </c>
       <c r="B46" t="n">
-        <v>4.09613</v>
+        <v>4.08168</v>
       </c>
       <c r="C46" t="n">
-        <v>2.88261</v>
+        <v>2.88797</v>
       </c>
       <c r="D46" t="n">
-        <v>17.8999</v>
+        <v>17.8933</v>
       </c>
       <c r="E46" t="n">
-        <v>2.70004</v>
+        <v>2.70282</v>
       </c>
       <c r="F46" t="n">
-        <v>3.17542</v>
+        <v>3.19197</v>
       </c>
     </row>
     <row r="47">
@@ -5979,19 +5979,19 @@
         <v>88787</v>
       </c>
       <c r="B47" t="n">
-        <v>4.60384</v>
+        <v>4.64838</v>
       </c>
       <c r="C47" t="n">
-        <v>3.36342</v>
+        <v>3.38476</v>
       </c>
       <c r="D47" t="n">
-        <v>18.3015</v>
+        <v>18.2885</v>
       </c>
       <c r="E47" t="n">
-        <v>2.96801</v>
+        <v>2.96095</v>
       </c>
       <c r="F47" t="n">
-        <v>3.40918</v>
+        <v>3.39945</v>
       </c>
     </row>
     <row r="48">
@@ -5999,19 +5999,19 @@
         <v>93204</v>
       </c>
       <c r="B48" t="n">
-        <v>5.46308</v>
+        <v>5.38555</v>
       </c>
       <c r="C48" t="n">
-        <v>4.04249</v>
+        <v>4.05621</v>
       </c>
       <c r="D48" t="n">
-        <v>18.7624</v>
+        <v>18.7305</v>
       </c>
       <c r="E48" t="n">
-        <v>3.36402</v>
+        <v>3.36209</v>
       </c>
       <c r="F48" t="n">
-        <v>3.70709</v>
+        <v>3.71392</v>
       </c>
     </row>
     <row r="49">
@@ -6019,19 +6019,19 @@
         <v>97841</v>
       </c>
       <c r="B49" t="n">
-        <v>6.43281</v>
+        <v>6.46995</v>
       </c>
       <c r="C49" t="n">
-        <v>5.0169</v>
+        <v>5.02201</v>
       </c>
       <c r="D49" t="n">
-        <v>19.2259</v>
+        <v>19.176</v>
       </c>
       <c r="E49" t="n">
-        <v>3.88719</v>
+        <v>3.88955</v>
       </c>
       <c r="F49" t="n">
-        <v>4.137</v>
+        <v>4.14004</v>
       </c>
     </row>
     <row r="50">
@@ -6039,19 +6039,19 @@
         <v>102709</v>
       </c>
       <c r="B50" t="n">
-        <v>8.446820000000001</v>
+        <v>8.283480000000001</v>
       </c>
       <c r="C50" t="n">
-        <v>6.51529</v>
+        <v>6.47967</v>
       </c>
       <c r="D50" t="n">
-        <v>13.4313</v>
+        <v>13.4506</v>
       </c>
       <c r="E50" t="n">
-        <v>4.749</v>
+        <v>2.27615</v>
       </c>
       <c r="F50" t="n">
-        <v>4.91835</v>
+        <v>2.71011</v>
       </c>
     </row>
     <row r="51">
@@ -6059,19 +6059,19 @@
         <v>107820</v>
       </c>
       <c r="B51" t="n">
-        <v>11.309</v>
+        <v>10.8766</v>
       </c>
       <c r="C51" t="n">
-        <v>1.90909</v>
+        <v>1.91985</v>
       </c>
       <c r="D51" t="n">
-        <v>13.9279</v>
+        <v>13.947</v>
       </c>
       <c r="E51" t="n">
-        <v>2.60006</v>
+        <v>2.29718</v>
       </c>
       <c r="F51" t="n">
-        <v>3.09997</v>
+        <v>2.7356</v>
       </c>
     </row>
     <row r="52">
@@ -6079,19 +6079,19 @@
         <v>113186</v>
       </c>
       <c r="B52" t="n">
-        <v>15.446</v>
+        <v>15.7255</v>
       </c>
       <c r="C52" t="n">
-        <v>2.06046</v>
+        <v>2.39614</v>
       </c>
       <c r="D52" t="n">
-        <v>14.4054</v>
+        <v>14.4271</v>
       </c>
       <c r="E52" t="n">
-        <v>2.63479</v>
+        <v>2.32102</v>
       </c>
       <c r="F52" t="n">
-        <v>2.77788</v>
+        <v>2.87946</v>
       </c>
     </row>
     <row r="53">
@@ -6099,19 +6099,19 @@
         <v>118820</v>
       </c>
       <c r="B53" t="n">
-        <v>3.1379</v>
+        <v>3.08544</v>
       </c>
       <c r="C53" t="n">
-        <v>2.28556</v>
+        <v>2.11235</v>
       </c>
       <c r="D53" t="n">
-        <v>14.8885</v>
+        <v>14.9239</v>
       </c>
       <c r="E53" t="n">
-        <v>2.64721</v>
+        <v>2.35432</v>
       </c>
       <c r="F53" t="n">
-        <v>3.19021</v>
+        <v>2.83317</v>
       </c>
     </row>
     <row r="54">
@@ -6119,19 +6119,19 @@
         <v>124735</v>
       </c>
       <c r="B54" t="n">
-        <v>3.16881</v>
+        <v>3.19398</v>
       </c>
       <c r="C54" t="n">
-        <v>2.35707</v>
+        <v>2.54225</v>
       </c>
       <c r="D54" t="n">
-        <v>15.4043</v>
+        <v>15.4208</v>
       </c>
       <c r="E54" t="n">
-        <v>2.68399</v>
+        <v>2.92254</v>
       </c>
       <c r="F54" t="n">
-        <v>2.89332</v>
+        <v>2.97406</v>
       </c>
     </row>
     <row r="55">
@@ -6139,19 +6139,19 @@
         <v>130945</v>
       </c>
       <c r="B55" t="n">
-        <v>3.27209</v>
+        <v>3.22846</v>
       </c>
       <c r="C55" t="n">
-        <v>2.29031</v>
+        <v>2.54715</v>
       </c>
       <c r="D55" t="n">
-        <v>15.8795</v>
+        <v>15.8872</v>
       </c>
       <c r="E55" t="n">
-        <v>2.50522</v>
+        <v>2.64501</v>
       </c>
       <c r="F55" t="n">
-        <v>2.93875</v>
+        <v>2.92916</v>
       </c>
     </row>
     <row r="56">
@@ -6159,19 +6159,19 @@
         <v>137465</v>
       </c>
       <c r="B56" t="n">
-        <v>3.34883</v>
+        <v>3.35738</v>
       </c>
       <c r="C56" t="n">
-        <v>2.47473</v>
+        <v>2.59964</v>
       </c>
       <c r="D56" t="n">
-        <v>16.3398</v>
+        <v>16.3504</v>
       </c>
       <c r="E56" t="n">
-        <v>2.56065</v>
+        <v>2.70168</v>
       </c>
       <c r="F56" t="n">
-        <v>2.99624</v>
+        <v>2.99591</v>
       </c>
     </row>
     <row r="57">
@@ -6179,19 +6179,19 @@
         <v>144311</v>
       </c>
       <c r="B57" t="n">
-        <v>3.45225</v>
+        <v>3.43397</v>
       </c>
       <c r="C57" t="n">
-        <v>2.56156</v>
+        <v>2.50986</v>
       </c>
       <c r="D57" t="n">
-        <v>16.8084</v>
+        <v>16.8587</v>
       </c>
       <c r="E57" t="n">
-        <v>2.62596</v>
+        <v>3.11296</v>
       </c>
       <c r="F57" t="n">
-        <v>3.11399</v>
+        <v>3.15954</v>
       </c>
     </row>
     <row r="58">
@@ -6199,19 +6199,19 @@
         <v>151499</v>
       </c>
       <c r="B58" t="n">
-        <v>3.62647</v>
+        <v>3.5996</v>
       </c>
       <c r="C58" t="n">
-        <v>2.39841</v>
+        <v>2.57123</v>
       </c>
       <c r="D58" t="n">
-        <v>17.3297</v>
+        <v>17.2717</v>
       </c>
       <c r="E58" t="n">
-        <v>2.69804</v>
+        <v>2.64624</v>
       </c>
       <c r="F58" t="n">
-        <v>3.18747</v>
+        <v>3.59384</v>
       </c>
     </row>
     <row r="59">
@@ -6219,19 +6219,19 @@
         <v>159046</v>
       </c>
       <c r="B59" t="n">
-        <v>4.45492</v>
+        <v>3.89831</v>
       </c>
       <c r="C59" t="n">
-        <v>2.71148</v>
+        <v>3.031</v>
       </c>
       <c r="D59" t="n">
-        <v>17.6959</v>
+        <v>17.7171</v>
       </c>
       <c r="E59" t="n">
-        <v>2.72651</v>
+        <v>3.2775</v>
       </c>
       <c r="F59" t="n">
-        <v>3.49573</v>
+        <v>3.331</v>
       </c>
     </row>
     <row r="60">
@@ -6239,19 +6239,19 @@
         <v>166970</v>
       </c>
       <c r="B60" t="n">
-        <v>4.80893</v>
+        <v>4.23721</v>
       </c>
       <c r="C60" t="n">
-        <v>3.05097</v>
+        <v>3.31403</v>
       </c>
       <c r="D60" t="n">
-        <v>18.2495</v>
+        <v>18.1282</v>
       </c>
       <c r="E60" t="n">
-        <v>3.03064</v>
+        <v>3.40938</v>
       </c>
       <c r="F60" t="n">
-        <v>3.42095</v>
+        <v>3.47811</v>
       </c>
     </row>
     <row r="61">
@@ -6259,19 +6259,19 @@
         <v>175290</v>
       </c>
       <c r="B61" t="n">
-        <v>5.24487</v>
+        <v>4.5301</v>
       </c>
       <c r="C61" t="n">
-        <v>3.40196</v>
+        <v>3.26933</v>
       </c>
       <c r="D61" t="n">
-        <v>18.7131</v>
+        <v>18.5624</v>
       </c>
       <c r="E61" t="n">
-        <v>3.27231</v>
+        <v>3.22173</v>
       </c>
       <c r="F61" t="n">
-        <v>3.58823</v>
+        <v>3.59863</v>
       </c>
     </row>
     <row r="62">
@@ -6279,19 +6279,19 @@
         <v>184026</v>
       </c>
       <c r="B62" t="n">
-        <v>5.28259</v>
+        <v>5.28062</v>
       </c>
       <c r="C62" t="n">
-        <v>3.89063</v>
+        <v>3.88402</v>
       </c>
       <c r="D62" t="n">
-        <v>19.2368</v>
+        <v>18.9681</v>
       </c>
       <c r="E62" t="n">
-        <v>3.54783</v>
+        <v>3.50464</v>
       </c>
       <c r="F62" t="n">
-        <v>3.83626</v>
+        <v>3.84774</v>
       </c>
     </row>
     <row r="63">
@@ -6299,19 +6299,19 @@
         <v>193198</v>
       </c>
       <c r="B63" t="n">
-        <v>6.29563</v>
+        <v>6.37557</v>
       </c>
       <c r="C63" t="n">
-        <v>4.80234</v>
+        <v>4.83213</v>
       </c>
       <c r="D63" t="n">
-        <v>19.7144</v>
+        <v>19.413</v>
       </c>
       <c r="E63" t="n">
-        <v>4.00796</v>
+        <v>3.9646</v>
       </c>
       <c r="F63" t="n">
-        <v>4.23661</v>
+        <v>4.22308</v>
       </c>
     </row>
     <row r="64">
@@ -6319,19 +6319,19 @@
         <v>202828</v>
       </c>
       <c r="B64" t="n">
-        <v>8.02014</v>
+        <v>7.92794</v>
       </c>
       <c r="C64" t="n">
-        <v>6.24856</v>
+        <v>6.42246</v>
       </c>
       <c r="D64" t="n">
-        <v>14.6123</v>
+        <v>17.7894</v>
       </c>
       <c r="E64" t="n">
-        <v>4.68718</v>
+        <v>2.98724</v>
       </c>
       <c r="F64" t="n">
-        <v>4.88106</v>
+        <v>3.40519</v>
       </c>
     </row>
     <row r="65">
@@ -6339,19 +6339,19 @@
         <v>212939</v>
       </c>
       <c r="B65" t="n">
-        <v>10.8179</v>
+        <v>10.5479</v>
       </c>
       <c r="C65" t="n">
-        <v>2.31422</v>
+        <v>2.74238</v>
       </c>
       <c r="D65" t="n">
-        <v>15.3435</v>
+        <v>18.4966</v>
       </c>
       <c r="E65" t="n">
-        <v>5.95693</v>
+        <v>2.76293</v>
       </c>
       <c r="F65" t="n">
-        <v>6.12407</v>
+        <v>3.49434</v>
       </c>
     </row>
     <row r="66">
@@ -6359,19 +6359,19 @@
         <v>223555</v>
       </c>
       <c r="B66" t="n">
-        <v>14.5845</v>
+        <v>14.4813</v>
       </c>
       <c r="C66" t="n">
-        <v>2.46246</v>
+        <v>2.31242</v>
       </c>
       <c r="D66" t="n">
-        <v>15.9855</v>
+        <v>19.2005</v>
       </c>
       <c r="E66" t="n">
-        <v>2.92416</v>
+        <v>2.80183</v>
       </c>
       <c r="F66" t="n">
-        <v>3.36862</v>
+        <v>3.54848</v>
       </c>
     </row>
     <row r="67">
@@ -6379,19 +6379,19 @@
         <v>234701</v>
       </c>
       <c r="B67" t="n">
-        <v>3.54393</v>
+        <v>3.90476</v>
       </c>
       <c r="C67" t="n">
-        <v>2.37642</v>
+        <v>2.35518</v>
       </c>
       <c r="D67" t="n">
-        <v>16.726</v>
+        <v>19.9384</v>
       </c>
       <c r="E67" t="n">
-        <v>2.98873</v>
+        <v>2.82414</v>
       </c>
       <c r="F67" t="n">
-        <v>3.43095</v>
+        <v>3.61192</v>
       </c>
     </row>
     <row r="68">
@@ -6399,19 +6399,19 @@
         <v>246404</v>
       </c>
       <c r="B68" t="n">
-        <v>3.60239</v>
+        <v>3.99047</v>
       </c>
       <c r="C68" t="n">
-        <v>2.41383</v>
+        <v>2.44462</v>
       </c>
       <c r="D68" t="n">
-        <v>17.616</v>
+        <v>20.8282</v>
       </c>
       <c r="E68" t="n">
-        <v>3.03497</v>
+        <v>3.13618</v>
       </c>
       <c r="F68" t="n">
-        <v>3.49058</v>
+        <v>3.68187</v>
       </c>
     </row>
     <row r="69">
@@ -6419,19 +6419,19 @@
         <v>258692</v>
       </c>
       <c r="B69" t="n">
-        <v>3.67482</v>
+        <v>3.66623</v>
       </c>
       <c r="C69" t="n">
-        <v>2.46277</v>
+        <v>2.44623</v>
       </c>
       <c r="D69" t="n">
-        <v>18.3826</v>
+        <v>21.574</v>
       </c>
       <c r="E69" t="n">
-        <v>2.91986</v>
+        <v>3.15141</v>
       </c>
       <c r="F69" t="n">
-        <v>3.55622</v>
+        <v>3.79413</v>
       </c>
     </row>
     <row r="70">
@@ -6439,19 +6439,19 @@
         <v>271594</v>
       </c>
       <c r="B70" t="n">
-        <v>3.78535</v>
+        <v>3.84748</v>
       </c>
       <c r="C70" t="n">
-        <v>2.5057</v>
+        <v>2.84504</v>
       </c>
       <c r="D70" t="n">
-        <v>19.4122</v>
+        <v>22.9215</v>
       </c>
       <c r="E70" t="n">
-        <v>3.12968</v>
+        <v>3.01293</v>
       </c>
       <c r="F70" t="n">
-        <v>3.6258</v>
+        <v>3.91388</v>
       </c>
     </row>
     <row r="71">
@@ -6459,19 +6459,19 @@
         <v>285141</v>
       </c>
       <c r="B71" t="n">
-        <v>3.94474</v>
+        <v>4.05356</v>
       </c>
       <c r="C71" t="n">
-        <v>2.7547</v>
+        <v>2.71035</v>
       </c>
       <c r="D71" t="n">
-        <v>20.2893</v>
+        <v>23.8781</v>
       </c>
       <c r="E71" t="n">
-        <v>2.99796</v>
+        <v>3.28865</v>
       </c>
       <c r="F71" t="n">
-        <v>3.70936</v>
+        <v>3.92156</v>
       </c>
     </row>
     <row r="72">
@@ -6479,19 +6479,19 @@
         <v>299365</v>
       </c>
       <c r="B72" t="n">
-        <v>4.09039</v>
+        <v>4.0918</v>
       </c>
       <c r="C72" t="n">
-        <v>2.89192</v>
+        <v>2.80924</v>
       </c>
       <c r="D72" t="n">
-        <v>21.4584</v>
+        <v>25.3344</v>
       </c>
       <c r="E72" t="n">
-        <v>3.0795</v>
+        <v>3.37161</v>
       </c>
       <c r="F72" t="n">
-        <v>3.8217</v>
+        <v>4.038</v>
       </c>
     </row>
     <row r="73">
@@ -6499,19 +6499,19 @@
         <v>314300</v>
       </c>
       <c r="B73" t="n">
-        <v>4.30059</v>
+        <v>4.24161</v>
       </c>
       <c r="C73" t="n">
-        <v>2.93893</v>
+        <v>3.33618</v>
       </c>
       <c r="D73" t="n">
-        <v>22.3437</v>
+        <v>27.3846</v>
       </c>
       <c r="E73" t="n">
-        <v>3.17521</v>
+        <v>3.4756</v>
       </c>
       <c r="F73" t="n">
-        <v>3.95245</v>
+        <v>4.15818</v>
       </c>
     </row>
     <row r="74">
@@ -6519,19 +6519,19 @@
         <v>329981</v>
       </c>
       <c r="B74" t="n">
-        <v>4.57436</v>
+        <v>4.72058</v>
       </c>
       <c r="C74" t="n">
-        <v>3.14693</v>
+        <v>3.31977</v>
       </c>
       <c r="D74" t="n">
-        <v>23.2821</v>
+        <v>28.5444</v>
       </c>
       <c r="E74" t="n">
-        <v>3.34445</v>
+        <v>3.40063</v>
       </c>
       <c r="F74" t="n">
-        <v>4.13079</v>
+        <v>4.54448</v>
       </c>
     </row>
     <row r="75">
@@ -6539,19 +6539,19 @@
         <v>346446</v>
       </c>
       <c r="B75" t="n">
-        <v>5.15603</v>
+        <v>4.9758</v>
       </c>
       <c r="C75" t="n">
-        <v>3.58656</v>
+        <v>3.70316</v>
       </c>
       <c r="D75" t="n">
-        <v>24.5694</v>
+        <v>29.0649</v>
       </c>
       <c r="E75" t="n">
-        <v>3.55566</v>
+        <v>3.65519</v>
       </c>
       <c r="F75" t="n">
-        <v>4.40858</v>
+        <v>5.17391</v>
       </c>
     </row>
     <row r="76">
@@ -6559,19 +6559,19 @@
         <v>363734</v>
       </c>
       <c r="B76" t="n">
-        <v>5.88241</v>
+        <v>5.59853</v>
       </c>
       <c r="C76" t="n">
-        <v>4.1842</v>
+        <v>4.17524</v>
       </c>
       <c r="D76" t="n">
-        <v>25.9219</v>
+        <v>29.7228</v>
       </c>
       <c r="E76" t="n">
-        <v>3.87367</v>
+        <v>3.77131</v>
       </c>
       <c r="F76" t="n">
-        <v>4.67185</v>
+        <v>4.89972</v>
       </c>
     </row>
     <row r="77">
@@ -6579,19 +6579,19 @@
         <v>381886</v>
       </c>
       <c r="B77" t="n">
-        <v>6.89495</v>
+        <v>6.52798</v>
       </c>
       <c r="C77" t="n">
-        <v>5.13465</v>
+        <v>4.97719</v>
       </c>
       <c r="D77" t="n">
-        <v>27.5858</v>
+        <v>30.6816</v>
       </c>
       <c r="E77" t="n">
-        <v>4.34747</v>
+        <v>4.19556</v>
       </c>
       <c r="F77" t="n">
-        <v>5.22598</v>
+        <v>5.20875</v>
       </c>
     </row>
     <row r="78">
@@ -6599,19 +6599,19 @@
         <v>400945</v>
       </c>
       <c r="B78" t="n">
-        <v>8.515459999999999</v>
+        <v>8.26801</v>
       </c>
       <c r="C78" t="n">
-        <v>6.47266</v>
+        <v>6.36495</v>
       </c>
       <c r="D78" t="n">
-        <v>24.4653</v>
+        <v>24.663</v>
       </c>
       <c r="E78" t="n">
-        <v>5.12816</v>
+        <v>3.13855</v>
       </c>
       <c r="F78" t="n">
-        <v>5.74262</v>
+        <v>3.93959</v>
       </c>
     </row>
     <row r="79">
@@ -6619,19 +6619,19 @@
         <v>420956</v>
       </c>
       <c r="B79" t="n">
-        <v>11.2197</v>
+        <v>10.6062</v>
       </c>
       <c r="C79" t="n">
-        <v>2.65306</v>
+        <v>2.68367</v>
       </c>
       <c r="D79" t="n">
-        <v>25.8814</v>
+        <v>26.3215</v>
       </c>
       <c r="E79" t="n">
-        <v>6.44162</v>
+        <v>3.19193</v>
       </c>
       <c r="F79" t="n">
-        <v>7.23719</v>
+        <v>4.13577</v>
       </c>
     </row>
     <row r="80">
@@ -6639,19 +6639,19 @@
         <v>441967</v>
       </c>
       <c r="B80" t="n">
-        <v>15.5108</v>
+        <v>14.2655</v>
       </c>
       <c r="C80" t="n">
-        <v>2.67329</v>
+        <v>2.75128</v>
       </c>
       <c r="D80" t="n">
-        <v>27.3666</v>
+        <v>27.4338</v>
       </c>
       <c r="E80" t="n">
-        <v>3.24914</v>
+        <v>3.22445</v>
       </c>
       <c r="F80" t="n">
-        <v>4.13875</v>
+        <v>4.22085</v>
       </c>
     </row>
     <row r="81">
@@ -6659,19 +6659,19 @@
         <v>464028</v>
       </c>
       <c r="B81" t="n">
-        <v>4.15208</v>
+        <v>4.1194</v>
       </c>
       <c r="C81" t="n">
-        <v>2.70549</v>
+        <v>2.80767</v>
       </c>
       <c r="D81" t="n">
-        <v>28.5849</v>
+        <v>28.5335</v>
       </c>
       <c r="E81" t="n">
-        <v>3.34666</v>
+        <v>3.33916</v>
       </c>
       <c r="F81" t="n">
-        <v>4.34329</v>
+        <v>4.35134</v>
       </c>
     </row>
     <row r="82">
@@ -6679,19 +6679,19 @@
         <v>487192</v>
       </c>
       <c r="B82" t="n">
-        <v>4.31188</v>
+        <v>4.2371</v>
       </c>
       <c r="C82" t="n">
-        <v>2.9793</v>
+        <v>2.88494</v>
       </c>
       <c r="D82" t="n">
-        <v>29.9159</v>
+        <v>29.7319</v>
       </c>
       <c r="E82" t="n">
-        <v>3.37796</v>
+        <v>3.33546</v>
       </c>
       <c r="F82" t="n">
-        <v>4.5896</v>
+        <v>4.68289</v>
       </c>
     </row>
     <row r="83">
@@ -6699,19 +6699,19 @@
         <v>511514</v>
       </c>
       <c r="B83" t="n">
-        <v>4.56415</v>
+        <v>4.39003</v>
       </c>
       <c r="C83" t="n">
-        <v>2.96195</v>
+        <v>2.99757</v>
       </c>
       <c r="D83" t="n">
-        <v>31.2755</v>
+        <v>31.0961</v>
       </c>
       <c r="E83" t="n">
-        <v>3.48547</v>
+        <v>3.45754</v>
       </c>
       <c r="F83" t="n">
-        <v>4.80822</v>
+        <v>4.88447</v>
       </c>
     </row>
     <row r="84">
@@ -6719,19 +6719,19 @@
         <v>537052</v>
       </c>
       <c r="B84" t="n">
-        <v>4.75759</v>
+        <v>4.58108</v>
       </c>
       <c r="C84" t="n">
-        <v>3.11233</v>
+        <v>3.14564</v>
       </c>
       <c r="D84" t="n">
-        <v>32.9163</v>
+        <v>32.3372</v>
       </c>
       <c r="E84" t="n">
-        <v>3.58626</v>
+        <v>3.45485</v>
       </c>
       <c r="F84" t="n">
-        <v>5.04879</v>
+        <v>5.14688</v>
       </c>
     </row>
     <row r="85">
@@ -6739,19 +6739,19 @@
         <v>563866</v>
       </c>
       <c r="B85" t="n">
-        <v>5.07366</v>
+        <v>4.79689</v>
       </c>
       <c r="C85" t="n">
-        <v>3.30294</v>
+        <v>3.325</v>
       </c>
       <c r="D85" t="n">
-        <v>34.4987</v>
+        <v>33.8523</v>
       </c>
       <c r="E85" t="n">
-        <v>3.72599</v>
+        <v>3.69888</v>
       </c>
       <c r="F85" t="n">
-        <v>5.03351</v>
+        <v>5.03705</v>
       </c>
     </row>
     <row r="86">
@@ -6759,19 +6759,19 @@
         <v>592020</v>
       </c>
       <c r="B86" t="n">
-        <v>5.42191</v>
+        <v>5.17563</v>
       </c>
       <c r="C86" t="n">
-        <v>3.54746</v>
+        <v>3.55912</v>
       </c>
       <c r="D86" t="n">
-        <v>36.1066</v>
+        <v>35.3143</v>
       </c>
       <c r="E86" t="n">
-        <v>3.90975</v>
+        <v>3.85745</v>
       </c>
       <c r="F86" t="n">
-        <v>5.3485</v>
+        <v>5.40901</v>
       </c>
     </row>
     <row r="87">
@@ -6779,19 +6779,19 @@
         <v>621581</v>
       </c>
       <c r="B87" t="n">
-        <v>5.84398</v>
+        <v>5.61573</v>
       </c>
       <c r="C87" t="n">
-        <v>3.82881</v>
+        <v>3.85025</v>
       </c>
       <c r="D87" t="n">
-        <v>37.6948</v>
+        <v>36.9237</v>
       </c>
       <c r="E87" t="n">
-        <v>4.13791</v>
+        <v>4.10896</v>
       </c>
       <c r="F87" t="n">
-        <v>5.73323</v>
+        <v>5.6857</v>
       </c>
     </row>
     <row r="88">
@@ -6799,19 +6799,19 @@
         <v>652620</v>
       </c>
       <c r="B88" t="n">
-        <v>6.23504</v>
+        <v>6.06554</v>
       </c>
       <c r="C88" t="n">
-        <v>4.15666</v>
+        <v>4.21483</v>
       </c>
       <c r="D88" t="n">
-        <v>39.4167</v>
+        <v>37.8348</v>
       </c>
       <c r="E88" t="n">
-        <v>4.38728</v>
+        <v>4.38135</v>
       </c>
       <c r="F88" t="n">
-        <v>6.64115</v>
+        <v>6.83121</v>
       </c>
     </row>
     <row r="89">
@@ -6819,19 +6819,19 @@
         <v>685210</v>
       </c>
       <c r="B89" t="n">
-        <v>6.91587</v>
+        <v>6.83998</v>
       </c>
       <c r="C89" t="n">
-        <v>4.60661</v>
+        <v>4.7942</v>
       </c>
       <c r="D89" t="n">
-        <v>41.174</v>
+        <v>40.9115</v>
       </c>
       <c r="E89" t="n">
-        <v>4.6736</v>
+        <v>4.769</v>
       </c>
       <c r="F89" t="n">
-        <v>7.21176</v>
+        <v>7.51069</v>
       </c>
     </row>
     <row r="90">
@@ -6839,19 +6839,19 @@
         <v>719429</v>
       </c>
       <c r="B90" t="n">
-        <v>7.75466</v>
+        <v>7.68155</v>
       </c>
       <c r="C90" t="n">
-        <v>5.25697</v>
+        <v>5.32623</v>
       </c>
       <c r="D90" t="n">
-        <v>42.9865</v>
+        <v>42.0116</v>
       </c>
       <c r="E90" t="n">
-        <v>5.11928</v>
+        <v>5.18138</v>
       </c>
       <c r="F90" t="n">
-        <v>7.75693</v>
+        <v>7.6627</v>
       </c>
     </row>
     <row r="91">
@@ -6859,19 +6859,19 @@
         <v>755358</v>
       </c>
       <c r="B91" t="n">
-        <v>8.848710000000001</v>
+        <v>8.61314</v>
       </c>
       <c r="C91" t="n">
-        <v>6.13415</v>
+        <v>6.11229</v>
       </c>
       <c r="D91" t="n">
-        <v>44.6192</v>
+        <v>43.704</v>
       </c>
       <c r="E91" t="n">
-        <v>5.69866</v>
+        <v>5.75808</v>
       </c>
       <c r="F91" t="n">
-        <v>8.2211</v>
+        <v>8.104760000000001</v>
       </c>
     </row>
     <row r="92">
@@ -6879,19 +6879,19 @@
         <v>793083</v>
       </c>
       <c r="B92" t="n">
-        <v>10.4545</v>
+        <v>9.991339999999999</v>
       </c>
       <c r="C92" t="n">
-        <v>7.44317</v>
+        <v>7.43483</v>
       </c>
       <c r="D92" t="n">
-        <v>36.6248</v>
+        <v>35.6902</v>
       </c>
       <c r="E92" t="n">
-        <v>6.51912</v>
+        <v>3.92926</v>
       </c>
       <c r="F92" t="n">
-        <v>9.441610000000001</v>
+        <v>5.60599</v>
       </c>
     </row>
     <row r="93">
@@ -6899,19 +6899,19 @@
         <v>832694</v>
       </c>
       <c r="B93" t="n">
-        <v>13.0318</v>
+        <v>12.525</v>
       </c>
       <c r="C93" t="n">
-        <v>9.39035</v>
+        <v>9.356719999999999</v>
       </c>
       <c r="D93" t="n">
-        <v>37.8532</v>
+        <v>36.8652</v>
       </c>
       <c r="E93" t="n">
-        <v>7.83798</v>
+        <v>4.05632</v>
       </c>
       <c r="F93" t="n">
-        <v>10.455</v>
+        <v>5.73609</v>
       </c>
     </row>
     <row r="94">
@@ -6919,19 +6919,19 @@
         <v>874285</v>
       </c>
       <c r="B94" t="n">
-        <v>16.9683</v>
+        <v>16.4285</v>
       </c>
       <c r="C94" t="n">
-        <v>3.79604</v>
+        <v>3.5779</v>
       </c>
       <c r="D94" t="n">
-        <v>39.0203</v>
+        <v>38.21</v>
       </c>
       <c r="E94" t="n">
-        <v>4.32605</v>
+        <v>4.22026</v>
       </c>
       <c r="F94" t="n">
-        <v>6.42106</v>
+        <v>6.13169</v>
       </c>
     </row>
     <row r="95">
@@ -6939,19 +6939,19 @@
         <v>917955</v>
       </c>
       <c r="B95" t="n">
-        <v>5.97929</v>
+        <v>5.77617</v>
       </c>
       <c r="C95" t="n">
-        <v>3.82712</v>
+        <v>3.73846</v>
       </c>
       <c r="D95" t="n">
-        <v>40.3179</v>
+        <v>39.3826</v>
       </c>
       <c r="E95" t="n">
-        <v>4.41118</v>
+        <v>4.35669</v>
       </c>
       <c r="F95" t="n">
-        <v>6.5886</v>
+        <v>6.41157</v>
       </c>
     </row>
     <row r="96">
@@ -6959,19 +6959,19 @@
         <v>963808</v>
       </c>
       <c r="B96" t="n">
-        <v>6.19757</v>
+        <v>6.04145</v>
       </c>
       <c r="C96" t="n">
-        <v>3.985</v>
+        <v>3.90272</v>
       </c>
       <c r="D96" t="n">
-        <v>41.6321</v>
+        <v>40.6681</v>
       </c>
       <c r="E96" t="n">
-        <v>4.57543</v>
+        <v>4.52602</v>
       </c>
       <c r="F96" t="n">
-        <v>7.04836</v>
+        <v>6.81829</v>
       </c>
     </row>
     <row r="97">
@@ -6979,19 +6979,19 @@
         <v>1011953</v>
       </c>
       <c r="B97" t="n">
-        <v>6.52745</v>
+        <v>6.35483</v>
       </c>
       <c r="C97" t="n">
-        <v>4.18786</v>
+        <v>4.08528</v>
       </c>
       <c r="D97" t="n">
-        <v>43.0083</v>
+        <v>41.9828</v>
       </c>
       <c r="E97" t="n">
-        <v>4.79051</v>
+        <v>4.6737</v>
       </c>
       <c r="F97" t="n">
-        <v>7.1672</v>
+        <v>7.02367</v>
       </c>
     </row>
     <row r="98">
@@ -6999,19 +6999,19 @@
         <v>1062505</v>
       </c>
       <c r="B98" t="n">
-        <v>6.83334</v>
+        <v>6.6526</v>
       </c>
       <c r="C98" t="n">
-        <v>4.35588</v>
+        <v>4.22736</v>
       </c>
       <c r="D98" t="n">
-        <v>44.3656</v>
+        <v>43.2769</v>
       </c>
       <c r="E98" t="n">
-        <v>4.98606</v>
+        <v>4.87632</v>
       </c>
       <c r="F98" t="n">
-        <v>7.53592</v>
+        <v>7.32577</v>
       </c>
     </row>
     <row r="99">
@@ -7019,19 +7019,19 @@
         <v>1115584</v>
       </c>
       <c r="B99" t="n">
-        <v>7.14429</v>
+        <v>6.90795</v>
       </c>
       <c r="C99" t="n">
-        <v>4.52309</v>
+        <v>4.44677</v>
       </c>
       <c r="D99" t="n">
-        <v>45.8419</v>
+        <v>44.738</v>
       </c>
       <c r="E99" t="n">
-        <v>5.12876</v>
+        <v>5.10233</v>
       </c>
       <c r="F99" t="n">
-        <v>7.75825</v>
+        <v>7.68532</v>
       </c>
     </row>
     <row r="100">
@@ -7039,19 +7039,19 @@
         <v>1171316</v>
       </c>
       <c r="B100" t="n">
-        <v>7.44742</v>
+        <v>7.25453</v>
       </c>
       <c r="C100" t="n">
-        <v>4.78212</v>
+        <v>4.61995</v>
       </c>
       <c r="D100" t="n">
-        <v>47.3345</v>
+        <v>46.1972</v>
       </c>
       <c r="E100" t="n">
-        <v>5.35452</v>
+        <v>5.23475</v>
       </c>
       <c r="F100" t="n">
-        <v>8.116709999999999</v>
+        <v>8.022040000000001</v>
       </c>
     </row>
     <row r="101">
@@ -7059,19 +7059,19 @@
         <v>1229834</v>
       </c>
       <c r="B101" t="n">
-        <v>7.82241</v>
+        <v>7.54584</v>
       </c>
       <c r="C101" t="n">
-        <v>5.05752</v>
+        <v>4.90244</v>
       </c>
       <c r="D101" t="n">
-        <v>48.5593</v>
+        <v>47.481</v>
       </c>
       <c r="E101" t="n">
-        <v>5.56781</v>
+        <v>5.51283</v>
       </c>
       <c r="F101" t="n">
-        <v>8.477589999999999</v>
+        <v>8.63678</v>
       </c>
     </row>
     <row r="102">
@@ -7079,19 +7079,19 @@
         <v>1291277</v>
       </c>
       <c r="B102" t="n">
-        <v>8.252520000000001</v>
+        <v>7.99291</v>
       </c>
       <c r="C102" t="n">
-        <v>5.42462</v>
+        <v>5.18352</v>
       </c>
       <c r="D102" t="n">
-        <v>50.5695</v>
+        <v>49.2533</v>
       </c>
       <c r="E102" t="n">
-        <v>5.83105</v>
+        <v>5.77269</v>
       </c>
       <c r="F102" t="n">
-        <v>8.996079999999999</v>
+        <v>9.147740000000001</v>
       </c>
     </row>
     <row r="103">
@@ -7099,19 +7099,19 @@
         <v>1355792</v>
       </c>
       <c r="B103" t="n">
-        <v>8.78538</v>
+        <v>8.54358</v>
       </c>
       <c r="C103" t="n">
-        <v>5.8622</v>
+        <v>5.59831</v>
       </c>
       <c r="D103" t="n">
-        <v>52.2364</v>
+        <v>50.6323</v>
       </c>
       <c r="E103" t="n">
-        <v>6.11243</v>
+        <v>6.00769</v>
       </c>
       <c r="F103" t="n">
-        <v>9.78872</v>
+        <v>9.39995</v>
       </c>
     </row>
     <row r="104">
@@ -7119,19 +7119,19 @@
         <v>1423532</v>
       </c>
       <c r="B104" t="n">
-        <v>9.605169999999999</v>
+        <v>9.239549999999999</v>
       </c>
       <c r="C104" t="n">
-        <v>6.46256</v>
+        <v>6.18758</v>
       </c>
       <c r="D104" t="n">
-        <v>54.0579</v>
+        <v>52.5339</v>
       </c>
       <c r="E104" t="n">
-        <v>6.47864</v>
+        <v>6.41229</v>
       </c>
       <c r="F104" t="n">
-        <v>10.5461</v>
+        <v>10.468</v>
       </c>
     </row>
     <row r="105">
@@ -7139,19 +7139,19 @@
         <v>1494659</v>
       </c>
       <c r="B105" t="n">
-        <v>10.6674</v>
+        <v>10.3501</v>
       </c>
       <c r="C105" t="n">
-        <v>7.27452</v>
+        <v>7.01769</v>
       </c>
       <c r="D105" t="n">
-        <v>55.9017</v>
+        <v>54.3232</v>
       </c>
       <c r="E105" t="n">
-        <v>6.98857</v>
+        <v>6.90376</v>
       </c>
       <c r="F105" t="n">
-        <v>11.3734</v>
+        <v>11.1005</v>
       </c>
     </row>
     <row r="106">
@@ -7159,19 +7159,19 @@
         <v>1569342</v>
       </c>
       <c r="B106" t="n">
-        <v>12.3017</v>
+        <v>11.8722</v>
       </c>
       <c r="C106" t="n">
-        <v>8.4084</v>
+        <v>8.231629999999999</v>
       </c>
       <c r="D106" t="n">
-        <v>57.641</v>
+        <v>55.9224</v>
       </c>
       <c r="E106" t="n">
-        <v>7.70552</v>
+        <v>7.68038</v>
       </c>
       <c r="F106" t="n">
-        <v>12.5704</v>
+        <v>12.4933</v>
       </c>
     </row>
     <row r="107">
@@ -7179,19 +7179,19 @@
         <v>1647759</v>
       </c>
       <c r="B107" t="n">
-        <v>14.5836</v>
+        <v>13.987</v>
       </c>
       <c r="C107" t="n">
-        <v>10.1228</v>
+        <v>9.95415</v>
       </c>
       <c r="D107" t="n">
-        <v>44.1483</v>
+        <v>42.4476</v>
       </c>
       <c r="E107" t="n">
-        <v>8.759069999999999</v>
+        <v>4.93967</v>
       </c>
       <c r="F107" t="n">
-        <v>14.3821</v>
+        <v>7.21181</v>
       </c>
     </row>
     <row r="108">
@@ -7199,19 +7199,19 @@
         <v>1730096</v>
       </c>
       <c r="B108" t="n">
-        <v>18.1009</v>
+        <v>17.2485</v>
       </c>
       <c r="C108" t="n">
-        <v>4.50407</v>
+        <v>4.30654</v>
       </c>
       <c r="D108" t="n">
-        <v>45.401</v>
+        <v>43.5569</v>
       </c>
       <c r="E108" t="n">
-        <v>5.09053</v>
+        <v>5.05172</v>
       </c>
       <c r="F108" t="n">
-        <v>7.54699</v>
+        <v>7.58644</v>
       </c>
     </row>
     <row r="109">
@@ -7219,19 +7219,19 @@
         <v>1816549</v>
       </c>
       <c r="B109" t="n">
-        <v>23.0218</v>
+        <v>21.7869</v>
       </c>
       <c r="C109" t="n">
-        <v>4.55524</v>
+        <v>4.5148</v>
       </c>
       <c r="D109" t="n">
-        <v>46.6324</v>
+        <v>44.7665</v>
       </c>
       <c r="E109" t="n">
-        <v>5.21891</v>
+        <v>5.16624</v>
       </c>
       <c r="F109" t="n">
-        <v>8.11139</v>
+        <v>7.8252</v>
       </c>
     </row>
     <row r="110">
@@ -7239,19 +7239,19 @@
         <v>1907324</v>
       </c>
       <c r="B110" t="n">
-        <v>7.55566</v>
+        <v>7.29521</v>
       </c>
       <c r="C110" t="n">
-        <v>4.72712</v>
+        <v>4.59721</v>
       </c>
       <c r="D110" t="n">
-        <v>47.8042</v>
+        <v>45.9682</v>
       </c>
       <c r="E110" t="n">
-        <v>5.32872</v>
+        <v>5.30972</v>
       </c>
       <c r="F110" t="n">
-        <v>8.62032</v>
+        <v>8.414440000000001</v>
       </c>
     </row>
     <row r="111">
@@ -7259,19 +7259,19 @@
         <v>2002637</v>
       </c>
       <c r="B111" t="n">
-        <v>7.82176</v>
+        <v>7.57113</v>
       </c>
       <c r="C111" t="n">
-        <v>4.93665</v>
+        <v>4.80075</v>
       </c>
       <c r="D111" t="n">
-        <v>49.0577</v>
+        <v>47.1663</v>
       </c>
       <c r="E111" t="n">
-        <v>5.49298</v>
+        <v>5.41936</v>
       </c>
       <c r="F111" t="n">
-        <v>9.073180000000001</v>
+        <v>8.83375</v>
       </c>
     </row>
     <row r="112">
@@ -7279,19 +7279,19 @@
         <v>2102715</v>
       </c>
       <c r="B112" t="n">
-        <v>8.134169999999999</v>
+        <v>7.88379</v>
       </c>
       <c r="C112" t="n">
-        <v>5.12665</v>
+        <v>4.95953</v>
       </c>
       <c r="D112" t="n">
-        <v>50.4413</v>
+        <v>48.467</v>
       </c>
       <c r="E112" t="n">
-        <v>5.65097</v>
+        <v>5.57545</v>
       </c>
       <c r="F112" t="n">
-        <v>9.58708</v>
+        <v>9.341469999999999</v>
       </c>
     </row>
     <row r="113">
@@ -7299,19 +7299,19 @@
         <v>2207796</v>
       </c>
       <c r="B113" t="n">
-        <v>8.53209</v>
+        <v>8.25526</v>
       </c>
       <c r="C113" t="n">
-        <v>5.36121</v>
+        <v>5.19495</v>
       </c>
       <c r="D113" t="n">
-        <v>51.8754</v>
+        <v>49.8485</v>
       </c>
       <c r="E113" t="n">
-        <v>5.85529</v>
+        <v>5.75648</v>
       </c>
       <c r="F113" t="n">
-        <v>10.0584</v>
+        <v>9.8581</v>
       </c>
     </row>
     <row r="114">
@@ -7319,19 +7319,19 @@
         <v>2318131</v>
       </c>
       <c r="B114" t="n">
-        <v>8.99084</v>
+        <v>8.66419</v>
       </c>
       <c r="C114" t="n">
-        <v>5.65165</v>
+        <v>5.48595</v>
       </c>
       <c r="D114" t="n">
-        <v>53.327</v>
+        <v>51.2313</v>
       </c>
       <c r="E114" t="n">
-        <v>6.10893</v>
+        <v>5.98917</v>
       </c>
       <c r="F114" t="n">
-        <v>10.6185</v>
+        <v>10.3361</v>
       </c>
     </row>
     <row r="115">
@@ -7339,19 +7339,19 @@
         <v>2433982</v>
       </c>
       <c r="B115" t="n">
-        <v>9.605980000000001</v>
+        <v>9.219049999999999</v>
       </c>
       <c r="C115" t="n">
-        <v>6.04647</v>
+        <v>5.84532</v>
       </c>
       <c r="D115" t="n">
-        <v>54.8603</v>
+        <v>52.7008</v>
       </c>
       <c r="E115" t="n">
-        <v>6.48578</v>
+        <v>6.36126</v>
       </c>
       <c r="F115" t="n">
-        <v>11.2402</v>
+        <v>10.8795</v>
       </c>
     </row>
     <row r="116">
@@ -7359,19 +7359,19 @@
         <v>2555625</v>
       </c>
       <c r="B116" t="n">
-        <v>10.2725</v>
+        <v>9.926450000000001</v>
       </c>
       <c r="C116" t="n">
-        <v>6.53718</v>
+        <v>6.32131</v>
       </c>
       <c r="D116" t="n">
-        <v>56.4355</v>
+        <v>54.2543</v>
       </c>
       <c r="E116" t="n">
-        <v>6.91842</v>
+        <v>6.79005</v>
       </c>
       <c r="F116" t="n">
-        <v>11.7564</v>
+        <v>11.4535</v>
       </c>
     </row>
     <row r="117">
@@ -7379,19 +7379,19 @@
         <v>2683350</v>
       </c>
       <c r="B117" t="n">
-        <v>10.9056</v>
+        <v>10.6021</v>
       </c>
       <c r="C117" t="n">
-        <v>7.05246</v>
+        <v>6.80608</v>
       </c>
       <c r="D117" t="n">
-        <v>58.1129</v>
+        <v>55.822</v>
       </c>
       <c r="E117" t="n">
-        <v>7.38255</v>
+        <v>7.27004</v>
       </c>
       <c r="F117" t="n">
-        <v>12.354</v>
+        <v>12.0494</v>
       </c>
     </row>
     <row r="118">
@@ -7399,19 +7399,19 @@
         <v>2817461</v>
       </c>
       <c r="B118" t="n">
-        <v>11.7301</v>
+        <v>11.3209</v>
       </c>
       <c r="C118" t="n">
-        <v>7.68449</v>
+        <v>7.37132</v>
       </c>
       <c r="D118" t="n">
-        <v>59.9698</v>
+        <v>57.5996</v>
       </c>
       <c r="E118" t="n">
-        <v>7.88616</v>
+        <v>7.74915</v>
       </c>
       <c r="F118" t="n">
-        <v>12.9624</v>
+        <v>12.5731</v>
       </c>
     </row>
     <row r="119">
@@ -7419,19 +7419,19 @@
         <v>2958277</v>
       </c>
       <c r="B119" t="n">
-        <v>12.7487</v>
+        <v>12.2861</v>
       </c>
       <c r="C119" t="n">
-        <v>8.53135</v>
+        <v>8.13007</v>
       </c>
       <c r="D119" t="n">
-        <v>69.0308</v>
+        <v>59.3095</v>
       </c>
       <c r="E119" t="n">
-        <v>8.36694</v>
+        <v>8.360010000000001</v>
       </c>
       <c r="F119" t="n">
-        <v>13.6746</v>
+        <v>13.3793</v>
       </c>
     </row>
     <row r="120">
@@ -7439,19 +7439,19 @@
         <v>3106133</v>
       </c>
       <c r="B120" t="n">
-        <v>13.9294</v>
+        <v>13.4713</v>
       </c>
       <c r="C120" t="n">
-        <v>9.54233</v>
+        <v>9.16503</v>
       </c>
       <c r="D120" t="n">
-        <v>63.3739</v>
+        <v>61.2472</v>
       </c>
       <c r="E120" t="n">
-        <v>9.196580000000001</v>
+        <v>9.08409</v>
       </c>
       <c r="F120" t="n">
-        <v>14.7199</v>
+        <v>14.3893</v>
       </c>
     </row>
     <row r="121">
@@ -7459,19 +7459,19 @@
         <v>3261381</v>
       </c>
       <c r="B121" t="n">
-        <v>15.788</v>
+        <v>15.2393</v>
       </c>
       <c r="C121" t="n">
-        <v>11.049</v>
+        <v>10.6908</v>
       </c>
       <c r="D121" t="n">
-        <v>47.262</v>
+        <v>45.3988</v>
       </c>
       <c r="E121" t="n">
-        <v>10.3087</v>
+        <v>6.99803</v>
       </c>
       <c r="F121" t="n">
-        <v>16.2103</v>
+        <v>9.81793</v>
       </c>
     </row>
     <row r="122">
@@ -7479,19 +7479,19 @@
         <v>3424391</v>
       </c>
       <c r="B122" t="n">
-        <v>18.7345</v>
+        <v>17.8949</v>
       </c>
       <c r="C122" t="n">
-        <v>6.23555</v>
+        <v>6.00091</v>
       </c>
       <c r="D122" t="n">
-        <v>48.2226</v>
+        <v>46.5292</v>
       </c>
       <c r="E122" t="n">
-        <v>12.2049</v>
+        <v>7.10283</v>
       </c>
       <c r="F122" t="n">
-        <v>18.625</v>
+        <v>10.6047</v>
       </c>
     </row>
     <row r="123">
@@ -7499,19 +7499,19 @@
         <v>3595551</v>
       </c>
       <c r="B123" t="n">
-        <v>23.222</v>
+        <v>22.4419</v>
       </c>
       <c r="C123" t="n">
-        <v>6.27062</v>
+        <v>6.07589</v>
       </c>
       <c r="D123" t="n">
-        <v>49.6397</v>
+        <v>47.5258</v>
       </c>
       <c r="E123" t="n">
-        <v>7.35179</v>
+        <v>7.07362</v>
       </c>
       <c r="F123" t="n">
-        <v>11.2952</v>
+        <v>10.3295</v>
       </c>
     </row>
     <row r="124">
@@ -7519,19 +7519,19 @@
         <v>3775269</v>
       </c>
       <c r="B124" t="n">
-        <v>10.2357</v>
+        <v>9.48474</v>
       </c>
       <c r="C124" t="n">
-        <v>6.40474</v>
+        <v>6.22078</v>
       </c>
       <c r="D124" t="n">
-        <v>50.9084</v>
+        <v>48.8772</v>
       </c>
       <c r="E124" t="n">
-        <v>7.5752</v>
+        <v>7.29135</v>
       </c>
       <c r="F124" t="n">
-        <v>11.5159</v>
+        <v>11.1509</v>
       </c>
     </row>
     <row r="125">
@@ -7539,19 +7539,19 @@
         <v>3963972</v>
       </c>
       <c r="B125" t="n">
-        <v>10.2518</v>
+        <v>9.89039</v>
       </c>
       <c r="C125" t="n">
-        <v>6.53681</v>
+        <v>6.26401</v>
       </c>
       <c r="D125" t="n">
-        <v>52.1737</v>
+        <v>50.1317</v>
       </c>
       <c r="E125" t="n">
-        <v>7.74033</v>
+        <v>7.53597</v>
       </c>
       <c r="F125" t="n">
-        <v>12.2036</v>
+        <v>11.38</v>
       </c>
     </row>
     <row r="126">
@@ -7559,19 +7559,19 @@
         <v>4162110</v>
       </c>
       <c r="B126" t="n">
-        <v>10.3427</v>
+        <v>10.2536</v>
       </c>
       <c r="C126" t="n">
-        <v>6.77621</v>
+        <v>6.65375</v>
       </c>
       <c r="D126" t="n">
-        <v>53.5481</v>
+        <v>51.5262</v>
       </c>
       <c r="E126" t="n">
-        <v>8.15236</v>
+        <v>7.90783</v>
       </c>
       <c r="F126" t="n">
-        <v>11.6534</v>
+        <v>12.0936</v>
       </c>
     </row>
     <row r="127">
@@ -7579,19 +7579,19 @@
         <v>4370154</v>
       </c>
       <c r="B127" t="n">
-        <v>10.6861</v>
+        <v>10.4393</v>
       </c>
       <c r="C127" t="n">
-        <v>6.98027</v>
+        <v>6.6993</v>
       </c>
       <c r="D127" t="n">
-        <v>55.0059</v>
+        <v>52.7688</v>
       </c>
       <c r="E127" t="n">
-        <v>8.06887</v>
+        <v>8.223549999999999</v>
       </c>
       <c r="F127" t="n">
-        <v>12.5428</v>
+        <v>12.5706</v>
       </c>
     </row>
     <row r="128">
@@ -7599,19 +7599,19 @@
         <v>4588600</v>
       </c>
       <c r="B128" t="n">
-        <v>10.8594</v>
+        <v>10.6785</v>
       </c>
       <c r="C128" t="n">
-        <v>7.18395</v>
+        <v>7.29174</v>
       </c>
       <c r="D128" t="n">
-        <v>56.4633</v>
+        <v>54.3207</v>
       </c>
       <c r="E128" t="n">
-        <v>8.01432</v>
+        <v>8.259029999999999</v>
       </c>
       <c r="F128" t="n">
-        <v>12.8228</v>
+        <v>12.6839</v>
       </c>
     </row>
     <row r="129">
@@ -7619,19 +7619,19 @@
         <v>4817968</v>
       </c>
       <c r="B129" t="n">
-        <v>11.3492</v>
+        <v>10.773</v>
       </c>
       <c r="C129" t="n">
-        <v>7.60197</v>
+        <v>7.26313</v>
       </c>
       <c r="D129" t="n">
-        <v>57.7761</v>
+        <v>55.7686</v>
       </c>
       <c r="E129" t="n">
-        <v>8.555999999999999</v>
+        <v>8.32996</v>
       </c>
       <c r="F129" t="n">
-        <v>13.3349</v>
+        <v>12.972</v>
       </c>
     </row>
     <row r="130">
@@ -7639,19 +7639,19 @@
         <v>5058804</v>
       </c>
       <c r="B130" t="n">
-        <v>11.6636</v>
+        <v>11.2578</v>
       </c>
       <c r="C130" t="n">
-        <v>7.76331</v>
+        <v>7.36948</v>
       </c>
       <c r="D130" t="n">
-        <v>59.5223</v>
+        <v>57.2285</v>
       </c>
       <c r="E130" t="n">
-        <v>8.85769</v>
+        <v>8.491569999999999</v>
       </c>
       <c r="F130" t="n">
-        <v>13.9113</v>
+        <v>13.2609</v>
       </c>
     </row>
     <row r="131">
@@ -7659,19 +7659,19 @@
         <v>5311681</v>
       </c>
       <c r="B131" t="n">
-        <v>12.266</v>
+        <v>11.9252</v>
       </c>
       <c r="C131" t="n">
-        <v>8.08741</v>
+        <v>7.62056</v>
       </c>
       <c r="D131" t="n">
-        <v>61.1246</v>
+        <v>58.6604</v>
       </c>
       <c r="E131" t="n">
-        <v>9.06377</v>
+        <v>8.85896</v>
       </c>
       <c r="F131" t="n">
-        <v>14.3117</v>
+        <v>13.9396</v>
       </c>
     </row>
     <row r="132">
@@ -7679,19 +7679,19 @@
         <v>5577201</v>
       </c>
       <c r="B132" t="n">
-        <v>12.7979</v>
+        <v>12.4491</v>
       </c>
       <c r="C132" t="n">
-        <v>8.59834</v>
+        <v>8.200889999999999</v>
       </c>
       <c r="D132" t="n">
-        <v>62.7639</v>
+        <v>60.5418</v>
       </c>
       <c r="E132" t="n">
-        <v>9.583410000000001</v>
+        <v>9.39461</v>
       </c>
       <c r="F132" t="n">
-        <v>14.7392</v>
+        <v>14.6235</v>
       </c>
     </row>
     <row r="133">
@@ -7699,19 +7699,19 @@
         <v>5855997</v>
       </c>
       <c r="B133" t="n">
-        <v>13.5821</v>
+        <v>12.834</v>
       </c>
       <c r="C133" t="n">
-        <v>9.36571</v>
+        <v>8.74057</v>
       </c>
       <c r="D133" t="n">
-        <v>64.6987</v>
+        <v>62.1656</v>
       </c>
       <c r="E133" t="n">
-        <v>10.0001</v>
+        <v>9.769550000000001</v>
       </c>
       <c r="F133" t="n">
-        <v>15.7496</v>
+        <v>15.3294</v>
       </c>
     </row>
     <row r="134">
@@ -7719,19 +7719,19 @@
         <v>6148732</v>
       </c>
       <c r="B134" t="n">
-        <v>14.9115</v>
+        <v>14.3191</v>
       </c>
       <c r="C134" t="n">
-        <v>10.2732</v>
+        <v>9.637309999999999</v>
       </c>
       <c r="D134" t="n">
-        <v>66.7625</v>
+        <v>64.0044</v>
       </c>
       <c r="E134" t="n">
-        <v>10.5531</v>
+        <v>10.2901</v>
       </c>
       <c r="F134" t="n">
-        <v>16.5761</v>
+        <v>16.0738</v>
       </c>
     </row>
     <row r="135">
@@ -7739,19 +7739,19 @@
         <v>6456103</v>
       </c>
       <c r="B135" t="n">
-        <v>16.5671</v>
+        <v>16.0298</v>
       </c>
       <c r="C135" t="n">
-        <v>11.6091</v>
+        <v>11.044</v>
       </c>
       <c r="D135" t="n">
-        <v>49.0405</v>
+        <v>47.0992</v>
       </c>
       <c r="E135" t="n">
-        <v>11.552</v>
+        <v>13.4588</v>
       </c>
       <c r="F135" t="n">
-        <v>17.9002</v>
+        <v>17.2774</v>
       </c>
     </row>
     <row r="136">
@@ -7759,19 +7759,19 @@
         <v>6778842</v>
       </c>
       <c r="B136" t="n">
-        <v>19.3174</v>
+        <v>18.3079</v>
       </c>
       <c r="C136" t="n">
-        <v>11.6858</v>
+        <v>11.8419</v>
       </c>
       <c r="D136" t="n">
-        <v>50.1672</v>
+        <v>48.2871</v>
       </c>
       <c r="E136" t="n">
-        <v>13.1823</v>
+        <v>13.6521</v>
       </c>
       <c r="F136" t="n">
-        <v>20.0546</v>
+        <v>17.4516</v>
       </c>
     </row>
     <row r="137">
@@ -7779,19 +7779,19 @@
         <v>7117717</v>
       </c>
       <c r="B137" t="n">
-        <v>23.2425</v>
+        <v>22.187</v>
       </c>
       <c r="C137" t="n">
-        <v>12.0409</v>
+        <v>11.8614</v>
       </c>
       <c r="D137" t="n">
-        <v>51.3716</v>
+        <v>49.5252</v>
       </c>
       <c r="E137" t="n">
-        <v>13.9768</v>
+        <v>13.6261</v>
       </c>
       <c r="F137" t="n">
-        <v>18.04</v>
+        <v>17.0543</v>
       </c>
     </row>
     <row r="138">
@@ -7799,19 +7799,19 @@
         <v>7473535</v>
       </c>
       <c r="B138" t="n">
-        <v>16.7221</v>
+        <v>16.0048</v>
       </c>
       <c r="C138" t="n">
-        <v>12.2164</v>
+        <v>11.9866</v>
       </c>
       <c r="D138" t="n">
-        <v>52.743</v>
+        <v>50.7775</v>
       </c>
       <c r="E138" t="n">
-        <v>13.5278</v>
+        <v>13.753</v>
       </c>
       <c r="F138" t="n">
-        <v>18.424</v>
+        <v>17.3528</v>
       </c>
     </row>
     <row r="139">
@@ -7819,19 +7819,19 @@
         <v>7847143</v>
       </c>
       <c r="B139" t="n">
-        <v>16.6789</v>
+        <v>16.2176</v>
       </c>
       <c r="C139" t="n">
-        <v>12.3493</v>
+        <v>12.0172</v>
       </c>
       <c r="D139" t="n">
-        <v>54.036</v>
+        <v>52.0076</v>
       </c>
       <c r="E139" t="n">
-        <v>14.2644</v>
+        <v>13.8572</v>
       </c>
       <c r="F139" t="n">
-        <v>18.6942</v>
+        <v>17.6594</v>
       </c>
     </row>
     <row r="140">
@@ -7839,19 +7839,19 @@
         <v>8239431</v>
       </c>
       <c r="B140" t="n">
-        <v>16.945</v>
+        <v>16.3962</v>
       </c>
       <c r="C140" t="n">
-        <v>12.3407</v>
+        <v>12.0714</v>
       </c>
       <c r="D140" t="n">
-        <v>55.3345</v>
+        <v>53.3027</v>
       </c>
       <c r="E140" t="n">
-        <v>14.4256</v>
+        <v>14.1525</v>
       </c>
       <c r="F140" t="n">
-        <v>18.4409</v>
+        <v>18.4562</v>
       </c>
     </row>
     <row r="141">
@@ -7859,19 +7859,19 @@
         <v>8651333</v>
       </c>
       <c r="B141" t="n">
-        <v>17.3207</v>
+        <v>16.4133</v>
       </c>
       <c r="C141" t="n">
-        <v>12.6083</v>
+        <v>12.2891</v>
       </c>
       <c r="D141" t="n">
-        <v>56.7504</v>
+        <v>54.7281</v>
       </c>
       <c r="E141" t="n">
-        <v>14.4071</v>
+        <v>14.1254</v>
       </c>
       <c r="F141" t="n">
-        <v>19.1214</v>
+        <v>18.7639</v>
       </c>
     </row>
     <row r="142">
@@ -7879,19 +7879,19 @@
         <v>9083830</v>
       </c>
       <c r="B142" t="n">
-        <v>17.3485</v>
+        <v>16.6115</v>
       </c>
       <c r="C142" t="n">
-        <v>12.6976</v>
+        <v>12.3138</v>
       </c>
       <c r="D142" t="n">
-        <v>58.1577</v>
+        <v>55.9695</v>
       </c>
       <c r="E142" t="n">
-        <v>14.6086</v>
+        <v>14.3606</v>
       </c>
       <c r="F142" t="n">
-        <v>19.7073</v>
+        <v>19.1444</v>
       </c>
     </row>
     <row r="143">
@@ -7899,19 +7899,19 @@
         <v>9537951</v>
       </c>
       <c r="B143" t="n">
-        <v>17.6437</v>
+        <v>17.3885</v>
       </c>
       <c r="C143" t="n">
-        <v>12.859</v>
+        <v>12.5624</v>
       </c>
       <c r="D143" t="n">
-        <v>59.52</v>
+        <v>57.5385</v>
       </c>
       <c r="E143" t="n">
-        <v>14.7526</v>
+        <v>13.7003</v>
       </c>
       <c r="F143" t="n">
-        <v>19.3117</v>
+        <v>19.4934</v>
       </c>
     </row>
   </sheetData>

--- a/gcc-x64/Scattered unsuccessful looukp.xlsx
+++ b/gcc-x64/Scattered unsuccessful looukp.xlsx
@@ -5079,19 +5079,19 @@
         <v>10000</v>
       </c>
       <c r="B2" t="n">
-        <v>2.86993</v>
+        <v>2.85805</v>
       </c>
       <c r="C2" t="n">
-        <v>1.91221</v>
+        <v>1.9131</v>
       </c>
       <c r="D2" t="n">
-        <v>13.4041</v>
+        <v>13.5088</v>
       </c>
       <c r="E2" t="n">
-        <v>1.98911</v>
+        <v>1.91123</v>
       </c>
       <c r="F2" t="n">
-        <v>2.28775</v>
+        <v>2.19815</v>
       </c>
     </row>
     <row r="3">
@@ -5099,19 +5099,19 @@
         <v>10500</v>
       </c>
       <c r="B3" t="n">
-        <v>2.94868</v>
+        <v>2.93976</v>
       </c>
       <c r="C3" t="n">
-        <v>1.98392</v>
+        <v>1.98459</v>
       </c>
       <c r="D3" t="n">
-        <v>14.2215</v>
+        <v>14.1054</v>
       </c>
       <c r="E3" t="n">
-        <v>1.92597</v>
+        <v>1.87887</v>
       </c>
       <c r="F3" t="n">
-        <v>2.14245</v>
+        <v>2.19482</v>
       </c>
     </row>
     <row r="4">
@@ -5119,19 +5119,19 @@
         <v>11025</v>
       </c>
       <c r="B4" t="n">
-        <v>3.05945</v>
+        <v>3.04741</v>
       </c>
       <c r="C4" t="n">
-        <v>2.11661</v>
+        <v>2.11401</v>
       </c>
       <c r="D4" t="n">
-        <v>14.7941</v>
+        <v>14.621</v>
       </c>
       <c r="E4" t="n">
-        <v>1.76087</v>
+        <v>1.69237</v>
       </c>
       <c r="F4" t="n">
-        <v>1.95443</v>
+        <v>2.08237</v>
       </c>
     </row>
     <row r="5">
@@ -5139,19 +5139,19 @@
         <v>11576</v>
       </c>
       <c r="B5" t="n">
-        <v>3.41599</v>
+        <v>3.38481</v>
       </c>
       <c r="C5" t="n">
-        <v>2.25337</v>
+        <v>2.25565</v>
       </c>
       <c r="D5" t="n">
-        <v>15.332</v>
+        <v>15.1062</v>
       </c>
       <c r="E5" t="n">
-        <v>1.77106</v>
+        <v>1.74345</v>
       </c>
       <c r="F5" t="n">
-        <v>2.06225</v>
+        <v>2.17905</v>
       </c>
     </row>
     <row r="6">
@@ -5159,19 +5159,19 @@
         <v>12154</v>
       </c>
       <c r="B6" t="n">
-        <v>4.28394</v>
+        <v>4.26981</v>
       </c>
       <c r="C6" t="n">
-        <v>2.89986</v>
+        <v>2.91004</v>
       </c>
       <c r="D6" t="n">
-        <v>15.9533</v>
+        <v>15.8543</v>
       </c>
       <c r="E6" t="n">
-        <v>1.84047</v>
+        <v>1.78992</v>
       </c>
       <c r="F6" t="n">
-        <v>2.16583</v>
+        <v>2.16885</v>
       </c>
     </row>
     <row r="7">
@@ -5179,19 +5179,19 @@
         <v>12760</v>
       </c>
       <c r="B7" t="n">
-        <v>6.55447</v>
+        <v>6.56207</v>
       </c>
       <c r="C7" t="n">
-        <v>5.03874</v>
+        <v>4.98181</v>
       </c>
       <c r="D7" t="n">
-        <v>10.9289</v>
+        <v>10.9478</v>
       </c>
       <c r="E7" t="n">
-        <v>1.94683</v>
+        <v>1.85369</v>
       </c>
       <c r="F7" t="n">
-        <v>2.06793</v>
+        <v>2.07321</v>
       </c>
     </row>
     <row r="8">
@@ -5199,19 +5199,19 @@
         <v>13396</v>
       </c>
       <c r="B8" t="n">
-        <v>9.38894</v>
+        <v>9.38428</v>
       </c>
       <c r="C8" t="n">
-        <v>1.91746</v>
+        <v>1.76738</v>
       </c>
       <c r="D8" t="n">
-        <v>11.5214</v>
+        <v>11.557</v>
       </c>
       <c r="E8" t="n">
-        <v>1.95855</v>
+        <v>1.87547</v>
       </c>
       <c r="F8" t="n">
-        <v>2.09427</v>
+        <v>2.11091</v>
       </c>
     </row>
     <row r="9">
@@ -5219,19 +5219,19 @@
         <v>14063</v>
       </c>
       <c r="B9" t="n">
-        <v>14.0402</v>
+        <v>13.777</v>
       </c>
       <c r="C9" t="n">
-        <v>1.79742</v>
+        <v>1.96875</v>
       </c>
       <c r="D9" t="n">
-        <v>12.0787</v>
+        <v>12.0052</v>
       </c>
       <c r="E9" t="n">
-        <v>1.96186</v>
+        <v>1.88164</v>
       </c>
       <c r="F9" t="n">
-        <v>2.10523</v>
+        <v>2.10967</v>
       </c>
     </row>
     <row r="10">
@@ -5239,19 +5239,19 @@
         <v>14763</v>
       </c>
       <c r="B10" t="n">
-        <v>2.79144</v>
+        <v>2.80254</v>
       </c>
       <c r="C10" t="n">
-        <v>1.96677</v>
+        <v>2.00391</v>
       </c>
       <c r="D10" t="n">
-        <v>12.8566</v>
+        <v>12.8751</v>
       </c>
       <c r="E10" t="n">
-        <v>1.98879</v>
+        <v>1.8999</v>
       </c>
       <c r="F10" t="n">
-        <v>2.10664</v>
+        <v>2.13379</v>
       </c>
     </row>
     <row r="11">
@@ -5259,19 +5259,19 @@
         <v>15498</v>
       </c>
       <c r="B11" t="n">
-        <v>2.84318</v>
+        <v>2.83636</v>
       </c>
       <c r="C11" t="n">
-        <v>1.93019</v>
+        <v>1.87086</v>
       </c>
       <c r="D11" t="n">
-        <v>13.3633</v>
+        <v>13.314</v>
       </c>
       <c r="E11" t="n">
-        <v>1.9929</v>
+        <v>1.89938</v>
       </c>
       <c r="F11" t="n">
-        <v>2.14956</v>
+        <v>2.16441</v>
       </c>
     </row>
     <row r="12">
@@ -5279,19 +5279,19 @@
         <v>16269</v>
       </c>
       <c r="B12" t="n">
-        <v>2.87194</v>
+        <v>2.88237</v>
       </c>
       <c r="C12" t="n">
-        <v>1.87461</v>
+        <v>1.96771</v>
       </c>
       <c r="D12" t="n">
-        <v>13.8522</v>
+        <v>13.7952</v>
       </c>
       <c r="E12" t="n">
-        <v>2.01317</v>
+        <v>1.92569</v>
       </c>
       <c r="F12" t="n">
-        <v>2.21572</v>
+        <v>2.18551</v>
       </c>
     </row>
     <row r="13">
@@ -5299,19 +5299,19 @@
         <v>17078</v>
       </c>
       <c r="B13" t="n">
-        <v>2.87498</v>
+        <v>2.87698</v>
       </c>
       <c r="C13" t="n">
-        <v>1.90184</v>
+        <v>2.12388</v>
       </c>
       <c r="D13" t="n">
-        <v>14.3866</v>
+        <v>14.3543</v>
       </c>
       <c r="E13" t="n">
-        <v>2.02796</v>
+        <v>1.93423</v>
       </c>
       <c r="F13" t="n">
-        <v>2.2001</v>
+        <v>2.20577</v>
       </c>
     </row>
     <row r="14">
@@ -5319,19 +5319,19 @@
         <v>17927</v>
       </c>
       <c r="B14" t="n">
-        <v>2.95736</v>
+        <v>2.95349</v>
       </c>
       <c r="C14" t="n">
-        <v>1.97726</v>
+        <v>2.09884</v>
       </c>
       <c r="D14" t="n">
-        <v>14.7972</v>
+        <v>14.765</v>
       </c>
       <c r="E14" t="n">
-        <v>2.05052</v>
+        <v>1.9762</v>
       </c>
       <c r="F14" t="n">
-        <v>2.23283</v>
+        <v>2.25808</v>
       </c>
     </row>
     <row r="15">
@@ -5339,19 +5339,19 @@
         <v>18818</v>
       </c>
       <c r="B15" t="n">
-        <v>3.05583</v>
+        <v>3.04764</v>
       </c>
       <c r="C15" t="n">
-        <v>2.00136</v>
+        <v>2.20177</v>
       </c>
       <c r="D15" t="n">
-        <v>15.2089</v>
+        <v>15.2495</v>
       </c>
       <c r="E15" t="n">
-        <v>2.06897</v>
+        <v>1.97831</v>
       </c>
       <c r="F15" t="n">
-        <v>2.27739</v>
+        <v>2.22427</v>
       </c>
     </row>
     <row r="16">
@@ -5359,19 +5359,19 @@
         <v>19753</v>
       </c>
       <c r="B16" t="n">
-        <v>3.0964</v>
+        <v>3.09806</v>
       </c>
       <c r="C16" t="n">
-        <v>2.11706</v>
+        <v>2.20885</v>
       </c>
       <c r="D16" t="n">
-        <v>15.5479</v>
+        <v>15.6852</v>
       </c>
       <c r="E16" t="n">
-        <v>2.10968</v>
+        <v>2.01697</v>
       </c>
       <c r="F16" t="n">
-        <v>2.28261</v>
+        <v>2.29155</v>
       </c>
     </row>
     <row r="17">
@@ -5379,19 +5379,19 @@
         <v>20734</v>
       </c>
       <c r="B17" t="n">
-        <v>3.29122</v>
+        <v>3.27585</v>
       </c>
       <c r="C17" t="n">
-        <v>2.31409</v>
+        <v>2.27666</v>
       </c>
       <c r="D17" t="n">
-        <v>16.1127</v>
+        <v>16.1809</v>
       </c>
       <c r="E17" t="n">
-        <v>2.13968</v>
+        <v>2.05423</v>
       </c>
       <c r="F17" t="n">
-        <v>2.35641</v>
+        <v>2.37028</v>
       </c>
     </row>
     <row r="18">
@@ -5399,19 +5399,19 @@
         <v>21764</v>
       </c>
       <c r="B18" t="n">
-        <v>3.66781</v>
+        <v>3.65871</v>
       </c>
       <c r="C18" t="n">
-        <v>2.51657</v>
+        <v>2.49129</v>
       </c>
       <c r="D18" t="n">
-        <v>16.5091</v>
+        <v>16.5986</v>
       </c>
       <c r="E18" t="n">
-        <v>2.14668</v>
+        <v>2.02779</v>
       </c>
       <c r="F18" t="n">
-        <v>2.42623</v>
+        <v>2.38084</v>
       </c>
     </row>
     <row r="19">
@@ -5419,19 +5419,19 @@
         <v>22845</v>
       </c>
       <c r="B19" t="n">
-        <v>4.21634</v>
+        <v>4.18829</v>
       </c>
       <c r="C19" t="n">
-        <v>3.1316</v>
+        <v>3.17089</v>
       </c>
       <c r="D19" t="n">
-        <v>16.9761</v>
+        <v>17.0186</v>
       </c>
       <c r="E19" t="n">
-        <v>2.1773</v>
+        <v>2.03395</v>
       </c>
       <c r="F19" t="n">
-        <v>2.43475</v>
+        <v>2.52107</v>
       </c>
     </row>
     <row r="20">
@@ -5439,19 +5439,19 @@
         <v>23980</v>
       </c>
       <c r="B20" t="n">
-        <v>5.20072</v>
+        <v>5.19716</v>
       </c>
       <c r="C20" t="n">
-        <v>4.23828</v>
+        <v>4.2765</v>
       </c>
       <c r="D20" t="n">
-        <v>17.3384</v>
+        <v>17.3435</v>
       </c>
       <c r="E20" t="n">
-        <v>2.60138</v>
+        <v>2.46426</v>
       </c>
       <c r="F20" t="n">
-        <v>2.84298</v>
+        <v>2.90528</v>
       </c>
     </row>
     <row r="21">
@@ -5459,19 +5459,19 @@
         <v>25171</v>
       </c>
       <c r="B21" t="n">
-        <v>6.80223</v>
+        <v>6.83902</v>
       </c>
       <c r="C21" t="n">
-        <v>5.53148</v>
+        <v>5.56934</v>
       </c>
       <c r="D21" t="n">
-        <v>12.2414</v>
+        <v>12.2358</v>
       </c>
       <c r="E21" t="n">
-        <v>2.03143</v>
+        <v>1.96734</v>
       </c>
       <c r="F21" t="n">
-        <v>2.21373</v>
+        <v>2.18788</v>
       </c>
     </row>
     <row r="22">
@@ -5479,19 +5479,19 @@
         <v>26421</v>
       </c>
       <c r="B22" t="n">
-        <v>9.066839999999999</v>
+        <v>9.04978</v>
       </c>
       <c r="C22" t="n">
-        <v>1.82336</v>
+        <v>2.04653</v>
       </c>
       <c r="D22" t="n">
-        <v>12.6751</v>
+        <v>12.7068</v>
       </c>
       <c r="E22" t="n">
-        <v>2.07152</v>
+        <v>1.98631</v>
       </c>
       <c r="F22" t="n">
-        <v>2.25743</v>
+        <v>2.21886</v>
       </c>
     </row>
     <row r="23">
@@ -5499,19 +5499,19 @@
         <v>27733</v>
       </c>
       <c r="B23" t="n">
-        <v>12.3841</v>
+        <v>12.3642</v>
       </c>
       <c r="C23" t="n">
-        <v>1.84051</v>
+        <v>1.86508</v>
       </c>
       <c r="D23" t="n">
-        <v>13.1895</v>
+        <v>13.1993</v>
       </c>
       <c r="E23" t="n">
-        <v>2.0817</v>
+        <v>2.01448</v>
       </c>
       <c r="F23" t="n">
-        <v>2.32758</v>
+        <v>2.25764</v>
       </c>
     </row>
     <row r="24">
@@ -5519,19 +5519,19 @@
         <v>29110</v>
       </c>
       <c r="B24" t="n">
-        <v>2.90108</v>
+        <v>2.89462</v>
       </c>
       <c r="C24" t="n">
-        <v>1.83407</v>
+        <v>1.85607</v>
       </c>
       <c r="D24" t="n">
-        <v>13.7616</v>
+        <v>13.7684</v>
       </c>
       <c r="E24" t="n">
-        <v>2.11611</v>
+        <v>2.02814</v>
       </c>
       <c r="F24" t="n">
-        <v>2.3572</v>
+        <v>2.28173</v>
       </c>
     </row>
     <row r="25">
@@ -5539,19 +5539,19 @@
         <v>30555</v>
       </c>
       <c r="B25" t="n">
-        <v>2.93287</v>
+        <v>2.92092</v>
       </c>
       <c r="C25" t="n">
-        <v>1.90911</v>
+        <v>1.89217</v>
       </c>
       <c r="D25" t="n">
-        <v>14.2481</v>
+        <v>14.2503</v>
       </c>
       <c r="E25" t="n">
-        <v>2.13865</v>
+        <v>2.04968</v>
       </c>
       <c r="F25" t="n">
-        <v>2.39516</v>
+        <v>2.31336</v>
       </c>
     </row>
     <row r="26">
@@ -5559,19 +5559,19 @@
         <v>32072</v>
       </c>
       <c r="B26" t="n">
-        <v>3.01292</v>
+        <v>3.00854</v>
       </c>
       <c r="C26" t="n">
-        <v>1.93106</v>
+        <v>1.90649</v>
       </c>
       <c r="D26" t="n">
-        <v>14.7073</v>
+        <v>14.6985</v>
       </c>
       <c r="E26" t="n">
-        <v>2.14748</v>
+        <v>2.07397</v>
       </c>
       <c r="F26" t="n">
-        <v>2.43696</v>
+        <v>2.36215</v>
       </c>
     </row>
     <row r="27">
@@ -5579,19 +5579,19 @@
         <v>33664</v>
       </c>
       <c r="B27" t="n">
-        <v>3.09052</v>
+        <v>3.08245</v>
       </c>
       <c r="C27" t="n">
-        <v>1.97558</v>
+        <v>1.98796</v>
       </c>
       <c r="D27" t="n">
-        <v>15.1956</v>
+        <v>15.2121</v>
       </c>
       <c r="E27" t="n">
-        <v>2.17533</v>
+        <v>2.09307</v>
       </c>
       <c r="F27" t="n">
-        <v>2.49906</v>
+        <v>2.41527</v>
       </c>
     </row>
     <row r="28">
@@ -5599,19 +5599,19 @@
         <v>35335</v>
       </c>
       <c r="B28" t="n">
-        <v>3.15686</v>
+        <v>3.1426</v>
       </c>
       <c r="C28" t="n">
-        <v>2.03856</v>
+        <v>1.99711</v>
       </c>
       <c r="D28" t="n">
-        <v>15.6595</v>
+        <v>15.6545</v>
       </c>
       <c r="E28" t="n">
-        <v>2.2235</v>
+        <v>2.12708</v>
       </c>
       <c r="F28" t="n">
-        <v>2.59007</v>
+        <v>2.44017</v>
       </c>
     </row>
     <row r="29">
@@ -5619,19 +5619,19 @@
         <v>37089</v>
       </c>
       <c r="B29" t="n">
-        <v>3.29107</v>
+        <v>3.28479</v>
       </c>
       <c r="C29" t="n">
-        <v>2.13655</v>
+        <v>2.13781</v>
       </c>
       <c r="D29" t="n">
-        <v>16.1758</v>
+        <v>16.1942</v>
       </c>
       <c r="E29" t="n">
-        <v>2.25273</v>
+        <v>2.18381</v>
       </c>
       <c r="F29" t="n">
-        <v>2.65309</v>
+        <v>2.51882</v>
       </c>
     </row>
     <row r="30">
@@ -5639,19 +5639,19 @@
         <v>38930</v>
       </c>
       <c r="B30" t="n">
-        <v>3.45513</v>
+        <v>3.44698</v>
       </c>
       <c r="C30" t="n">
-        <v>2.25387</v>
+        <v>2.24453</v>
       </c>
       <c r="D30" t="n">
-        <v>16.6598</v>
+        <v>16.6421</v>
       </c>
       <c r="E30" t="n">
-        <v>2.29915</v>
+        <v>2.21863</v>
       </c>
       <c r="F30" t="n">
-        <v>2.68101</v>
+        <v>2.57078</v>
       </c>
     </row>
     <row r="31">
@@ -5659,19 +5659,19 @@
         <v>40863</v>
       </c>
       <c r="B31" t="n">
-        <v>3.68895</v>
+        <v>3.67232</v>
       </c>
       <c r="C31" t="n">
-        <v>2.42641</v>
+        <v>2.43953</v>
       </c>
       <c r="D31" t="n">
-        <v>17.0826</v>
+        <v>17.0691</v>
       </c>
       <c r="E31" t="n">
-        <v>2.32088</v>
+        <v>2.22881</v>
       </c>
       <c r="F31" t="n">
-        <v>2.72548</v>
+        <v>2.6406</v>
       </c>
     </row>
     <row r="32">
@@ -5679,19 +5679,19 @@
         <v>42892</v>
       </c>
       <c r="B32" t="n">
-        <v>4.04802</v>
+        <v>4.0301</v>
       </c>
       <c r="C32" t="n">
-        <v>2.71851</v>
+        <v>2.71481</v>
       </c>
       <c r="D32" t="n">
-        <v>17.3993</v>
+        <v>17.405</v>
       </c>
       <c r="E32" t="n">
-        <v>2.41795</v>
+        <v>2.30705</v>
       </c>
       <c r="F32" t="n">
-        <v>2.85383</v>
+        <v>2.77283</v>
       </c>
     </row>
     <row r="33">
@@ -5699,19 +5699,19 @@
         <v>45022</v>
       </c>
       <c r="B33" t="n">
-        <v>4.69542</v>
+        <v>4.68498</v>
       </c>
       <c r="C33" t="n">
-        <v>3.2954</v>
+        <v>3.29378</v>
       </c>
       <c r="D33" t="n">
-        <v>17.9002</v>
+        <v>17.8409</v>
       </c>
       <c r="E33" t="n">
-        <v>2.64566</v>
+        <v>2.49208</v>
       </c>
       <c r="F33" t="n">
-        <v>3.00913</v>
+        <v>2.97576</v>
       </c>
     </row>
     <row r="34">
@@ -5719,19 +5719,19 @@
         <v>47258</v>
       </c>
       <c r="B34" t="n">
-        <v>5.61942</v>
+        <v>5.61765</v>
       </c>
       <c r="C34" t="n">
-        <v>4.15803</v>
+        <v>4.15225</v>
       </c>
       <c r="D34" t="n">
-        <v>18.3493</v>
+        <v>18.3396</v>
       </c>
       <c r="E34" t="n">
-        <v>3.11519</v>
+        <v>3.01095</v>
       </c>
       <c r="F34" t="n">
-        <v>3.43725</v>
+        <v>3.45284</v>
       </c>
     </row>
     <row r="35">
@@ -5739,19 +5739,19 @@
         <v>49605</v>
       </c>
       <c r="B35" t="n">
-        <v>7.11376</v>
+        <v>7.1033</v>
       </c>
       <c r="C35" t="n">
-        <v>5.30256</v>
+        <v>5.3025</v>
       </c>
       <c r="D35" t="n">
-        <v>12.7256</v>
+        <v>12.7662</v>
       </c>
       <c r="E35" t="n">
-        <v>2.09272</v>
+        <v>2.01094</v>
       </c>
       <c r="F35" t="n">
-        <v>2.39824</v>
+        <v>2.36682</v>
       </c>
     </row>
     <row r="36">
@@ -5759,19 +5759,19 @@
         <v>52069</v>
       </c>
       <c r="B36" t="n">
-        <v>9.303319999999999</v>
+        <v>9.232329999999999</v>
       </c>
       <c r="C36" t="n">
-        <v>6.94398</v>
+        <v>6.94133</v>
       </c>
       <c r="D36" t="n">
-        <v>13.1677</v>
+        <v>13.1898</v>
       </c>
       <c r="E36" t="n">
-        <v>2.11485</v>
+        <v>2.03386</v>
       </c>
       <c r="F36" t="n">
-        <v>2.43569</v>
+        <v>2.39634</v>
       </c>
     </row>
     <row r="37">
@@ -5779,19 +5779,19 @@
         <v>54656</v>
       </c>
       <c r="B37" t="n">
-        <v>12.999</v>
+        <v>12.9994</v>
       </c>
       <c r="C37" t="n">
-        <v>1.89402</v>
+        <v>1.88649</v>
       </c>
       <c r="D37" t="n">
-        <v>13.6739</v>
+        <v>13.6794</v>
       </c>
       <c r="E37" t="n">
-        <v>2.15683</v>
+        <v>2.0567</v>
       </c>
       <c r="F37" t="n">
-        <v>2.4613</v>
+        <v>2.41028</v>
       </c>
     </row>
     <row r="38">
@@ -5799,19 +5799,19 @@
         <v>57372</v>
       </c>
       <c r="B38" t="n">
-        <v>2.97796</v>
+        <v>2.97112</v>
       </c>
       <c r="C38" t="n">
-        <v>1.91818</v>
+        <v>1.94329</v>
       </c>
       <c r="D38" t="n">
-        <v>14.2159</v>
+        <v>14.232</v>
       </c>
       <c r="E38" t="n">
-        <v>2.16965</v>
+        <v>2.0805</v>
       </c>
       <c r="F38" t="n">
-        <v>2.52477</v>
+        <v>2.4691</v>
       </c>
     </row>
     <row r="39">
@@ -5819,19 +5819,19 @@
         <v>60223</v>
       </c>
       <c r="B39" t="n">
-        <v>3.01132</v>
+        <v>2.99038</v>
       </c>
       <c r="C39" t="n">
-        <v>1.90023</v>
+        <v>1.91511</v>
       </c>
       <c r="D39" t="n">
-        <v>14.731</v>
+        <v>14.7283</v>
       </c>
       <c r="E39" t="n">
-        <v>2.21196</v>
+        <v>2.11695</v>
       </c>
       <c r="F39" t="n">
-        <v>2.5856</v>
+        <v>2.52009</v>
       </c>
     </row>
     <row r="40">
@@ -5839,19 +5839,19 @@
         <v>63216</v>
       </c>
       <c r="B40" t="n">
-        <v>3.07979</v>
+        <v>3.06645</v>
       </c>
       <c r="C40" t="n">
-        <v>1.96741</v>
+        <v>1.98065</v>
       </c>
       <c r="D40" t="n">
-        <v>15.2382</v>
+        <v>15.247</v>
       </c>
       <c r="E40" t="n">
-        <v>2.23051</v>
+        <v>2.12972</v>
       </c>
       <c r="F40" t="n">
-        <v>2.64701</v>
+        <v>2.56587</v>
       </c>
     </row>
     <row r="41">
@@ -5859,19 +5859,19 @@
         <v>66358</v>
       </c>
       <c r="B41" t="n">
-        <v>3.14278</v>
+        <v>3.14517</v>
       </c>
       <c r="C41" t="n">
-        <v>2.03223</v>
+        <v>2.04493</v>
       </c>
       <c r="D41" t="n">
-        <v>15.7079</v>
+        <v>15.7212</v>
       </c>
       <c r="E41" t="n">
-        <v>2.25182</v>
+        <v>2.16943</v>
       </c>
       <c r="F41" t="n">
-        <v>2.69029</v>
+        <v>2.62016</v>
       </c>
     </row>
     <row r="42">
@@ -5879,19 +5879,19 @@
         <v>69657</v>
       </c>
       <c r="B42" t="n">
-        <v>3.20152</v>
+        <v>3.19637</v>
       </c>
       <c r="C42" t="n">
-        <v>2.09369</v>
+        <v>2.09403</v>
       </c>
       <c r="D42" t="n">
-        <v>16.196</v>
+        <v>16.1792</v>
       </c>
       <c r="E42" t="n">
-        <v>2.30521</v>
+        <v>2.2136</v>
       </c>
       <c r="F42" t="n">
-        <v>2.74753</v>
+        <v>2.69106</v>
       </c>
     </row>
     <row r="43">
@@ -5899,19 +5899,19 @@
         <v>73120</v>
       </c>
       <c r="B43" t="n">
-        <v>3.34534</v>
+        <v>3.33756</v>
       </c>
       <c r="C43" t="n">
-        <v>2.1574</v>
+        <v>2.18761</v>
       </c>
       <c r="D43" t="n">
-        <v>16.6595</v>
+        <v>16.6596</v>
       </c>
       <c r="E43" t="n">
-        <v>2.35634</v>
+        <v>2.25526</v>
       </c>
       <c r="F43" t="n">
-        <v>2.82049</v>
+        <v>2.75702</v>
       </c>
     </row>
     <row r="44">
@@ -5919,19 +5919,19 @@
         <v>76756</v>
       </c>
       <c r="B44" t="n">
-        <v>3.50938</v>
+        <v>3.50219</v>
       </c>
       <c r="C44" t="n">
-        <v>2.27574</v>
+        <v>2.32236</v>
       </c>
       <c r="D44" t="n">
-        <v>17.0869</v>
+        <v>17.0385</v>
       </c>
       <c r="E44" t="n">
-        <v>2.4418</v>
+        <v>2.33668</v>
       </c>
       <c r="F44" t="n">
-        <v>2.92168</v>
+        <v>2.85428</v>
       </c>
     </row>
     <row r="45">
@@ -5939,19 +5939,19 @@
         <v>80573</v>
       </c>
       <c r="B45" t="n">
-        <v>3.73701</v>
+        <v>3.73762</v>
       </c>
       <c r="C45" t="n">
-        <v>2.56625</v>
+        <v>2.55182</v>
       </c>
       <c r="D45" t="n">
-        <v>17.4632</v>
+        <v>17.4769</v>
       </c>
       <c r="E45" t="n">
-        <v>2.53981</v>
+        <v>2.44703</v>
       </c>
       <c r="F45" t="n">
-        <v>3.02988</v>
+        <v>2.97428</v>
       </c>
     </row>
     <row r="46">
@@ -5959,19 +5959,19 @@
         <v>84580</v>
       </c>
       <c r="B46" t="n">
-        <v>4.08168</v>
+        <v>4.07668</v>
       </c>
       <c r="C46" t="n">
-        <v>2.88797</v>
+        <v>2.88874</v>
       </c>
       <c r="D46" t="n">
-        <v>17.8933</v>
+        <v>17.872</v>
       </c>
       <c r="E46" t="n">
-        <v>2.70282</v>
+        <v>2.60989</v>
       </c>
       <c r="F46" t="n">
-        <v>3.19197</v>
+        <v>3.12263</v>
       </c>
     </row>
     <row r="47">
@@ -5979,19 +5979,19 @@
         <v>88787</v>
       </c>
       <c r="B47" t="n">
-        <v>4.64838</v>
+        <v>4.63613</v>
       </c>
       <c r="C47" t="n">
-        <v>3.38476</v>
+        <v>3.38231</v>
       </c>
       <c r="D47" t="n">
-        <v>18.2885</v>
+        <v>18.3408</v>
       </c>
       <c r="E47" t="n">
-        <v>2.96095</v>
+        <v>2.85319</v>
       </c>
       <c r="F47" t="n">
-        <v>3.39945</v>
+        <v>3.37616</v>
       </c>
     </row>
     <row r="48">
@@ -5999,19 +5999,19 @@
         <v>93204</v>
       </c>
       <c r="B48" t="n">
-        <v>5.38555</v>
+        <v>5.39023</v>
       </c>
       <c r="C48" t="n">
-        <v>4.05621</v>
+        <v>4.04102</v>
       </c>
       <c r="D48" t="n">
-        <v>18.7305</v>
+        <v>18.7361</v>
       </c>
       <c r="E48" t="n">
-        <v>3.36209</v>
+        <v>3.23855</v>
       </c>
       <c r="F48" t="n">
-        <v>3.71392</v>
+        <v>3.74799</v>
       </c>
     </row>
     <row r="49">
@@ -6019,19 +6019,19 @@
         <v>97841</v>
       </c>
       <c r="B49" t="n">
-        <v>6.46995</v>
+        <v>6.46372</v>
       </c>
       <c r="C49" t="n">
-        <v>5.02201</v>
+        <v>5.01431</v>
       </c>
       <c r="D49" t="n">
-        <v>19.176</v>
+        <v>19.2215</v>
       </c>
       <c r="E49" t="n">
-        <v>3.88955</v>
+        <v>3.74313</v>
       </c>
       <c r="F49" t="n">
-        <v>4.14004</v>
+        <v>4.23356</v>
       </c>
     </row>
     <row r="50">
@@ -6039,19 +6039,19 @@
         <v>102709</v>
       </c>
       <c r="B50" t="n">
-        <v>8.283480000000001</v>
+        <v>8.325469999999999</v>
       </c>
       <c r="C50" t="n">
-        <v>6.47967</v>
+        <v>6.481</v>
       </c>
       <c r="D50" t="n">
-        <v>13.4506</v>
+        <v>13.4474</v>
       </c>
       <c r="E50" t="n">
-        <v>2.27615</v>
+        <v>2.16237</v>
       </c>
       <c r="F50" t="n">
-        <v>2.71011</v>
+        <v>2.7392</v>
       </c>
     </row>
     <row r="51">
@@ -6059,19 +6059,19 @@
         <v>107820</v>
       </c>
       <c r="B51" t="n">
-        <v>10.8766</v>
+        <v>10.8793</v>
       </c>
       <c r="C51" t="n">
-        <v>1.91985</v>
+        <v>1.89806</v>
       </c>
       <c r="D51" t="n">
-        <v>13.947</v>
+        <v>13.9514</v>
       </c>
       <c r="E51" t="n">
-        <v>2.29718</v>
+        <v>2.17814</v>
       </c>
       <c r="F51" t="n">
-        <v>2.7356</v>
+        <v>2.75269</v>
       </c>
     </row>
     <row r="52">
@@ -6079,19 +6079,19 @@
         <v>113186</v>
       </c>
       <c r="B52" t="n">
-        <v>15.7255</v>
+        <v>15.3239</v>
       </c>
       <c r="C52" t="n">
-        <v>2.39614</v>
+        <v>2.18614</v>
       </c>
       <c r="D52" t="n">
-        <v>14.4271</v>
+        <v>14.4212</v>
       </c>
       <c r="E52" t="n">
-        <v>2.32102</v>
+        <v>2.20852</v>
       </c>
       <c r="F52" t="n">
-        <v>2.87946</v>
+        <v>2.82928</v>
       </c>
     </row>
     <row r="53">
@@ -6099,19 +6099,19 @@
         <v>118820</v>
       </c>
       <c r="B53" t="n">
-        <v>3.08544</v>
+        <v>3.10359</v>
       </c>
       <c r="C53" t="n">
-        <v>2.11235</v>
+        <v>2.02442</v>
       </c>
       <c r="D53" t="n">
-        <v>14.9239</v>
+        <v>14.9097</v>
       </c>
       <c r="E53" t="n">
-        <v>2.35432</v>
+        <v>2.24132</v>
       </c>
       <c r="F53" t="n">
-        <v>2.83317</v>
+        <v>2.86427</v>
       </c>
     </row>
     <row r="54">
@@ -6119,19 +6119,19 @@
         <v>124735</v>
       </c>
       <c r="B54" t="n">
-        <v>3.19398</v>
+        <v>3.18381</v>
       </c>
       <c r="C54" t="n">
-        <v>2.54225</v>
+        <v>2.11895</v>
       </c>
       <c r="D54" t="n">
-        <v>15.4208</v>
+        <v>15.4228</v>
       </c>
       <c r="E54" t="n">
-        <v>2.92254</v>
+        <v>2.37638</v>
       </c>
       <c r="F54" t="n">
-        <v>2.97406</v>
+        <v>2.91871</v>
       </c>
     </row>
     <row r="55">
@@ -6139,19 +6139,19 @@
         <v>130945</v>
       </c>
       <c r="B55" t="n">
-        <v>3.22846</v>
+        <v>3.25549</v>
       </c>
       <c r="C55" t="n">
-        <v>2.54715</v>
+        <v>2.06465</v>
       </c>
       <c r="D55" t="n">
-        <v>15.8872</v>
+        <v>15.8935</v>
       </c>
       <c r="E55" t="n">
-        <v>2.64501</v>
+        <v>2.45521</v>
       </c>
       <c r="F55" t="n">
-        <v>2.92916</v>
+        <v>2.92702</v>
       </c>
     </row>
     <row r="56">
@@ -6159,19 +6159,19 @@
         <v>137465</v>
       </c>
       <c r="B56" t="n">
-        <v>3.35738</v>
+        <v>3.33362</v>
       </c>
       <c r="C56" t="n">
-        <v>2.59964</v>
+        <v>2.37829</v>
       </c>
       <c r="D56" t="n">
-        <v>16.3504</v>
+        <v>16.361</v>
       </c>
       <c r="E56" t="n">
-        <v>2.70168</v>
+        <v>2.50479</v>
       </c>
       <c r="F56" t="n">
-        <v>2.99591</v>
+        <v>2.98462</v>
       </c>
     </row>
     <row r="57">
@@ -6179,19 +6179,19 @@
         <v>144311</v>
       </c>
       <c r="B57" t="n">
-        <v>3.43397</v>
+        <v>3.47522</v>
       </c>
       <c r="C57" t="n">
-        <v>2.50986</v>
+        <v>2.31285</v>
       </c>
       <c r="D57" t="n">
-        <v>16.8587</v>
+        <v>16.7989</v>
       </c>
       <c r="E57" t="n">
-        <v>3.11296</v>
+        <v>2.5191</v>
       </c>
       <c r="F57" t="n">
-        <v>3.15954</v>
+        <v>3.11328</v>
       </c>
     </row>
     <row r="58">
@@ -6199,19 +6199,19 @@
         <v>151499</v>
       </c>
       <c r="B58" t="n">
-        <v>3.5996</v>
+        <v>3.6175</v>
       </c>
       <c r="C58" t="n">
-        <v>2.57123</v>
+        <v>2.47121</v>
       </c>
       <c r="D58" t="n">
-        <v>17.2717</v>
+        <v>17.2414</v>
       </c>
       <c r="E58" t="n">
-        <v>2.64624</v>
+        <v>2.5936</v>
       </c>
       <c r="F58" t="n">
-        <v>3.59384</v>
+        <v>3.43809</v>
       </c>
     </row>
     <row r="59">
@@ -6219,19 +6219,19 @@
         <v>159046</v>
       </c>
       <c r="B59" t="n">
-        <v>3.89831</v>
+        <v>3.84453</v>
       </c>
       <c r="C59" t="n">
-        <v>3.031</v>
+        <v>2.70442</v>
       </c>
       <c r="D59" t="n">
-        <v>17.7171</v>
+        <v>17.6423</v>
       </c>
       <c r="E59" t="n">
-        <v>3.2775</v>
+        <v>2.76591</v>
       </c>
       <c r="F59" t="n">
-        <v>3.331</v>
+        <v>3.2011</v>
       </c>
     </row>
     <row r="60">
@@ -6239,19 +6239,19 @@
         <v>166970</v>
       </c>
       <c r="B60" t="n">
-        <v>4.23721</v>
+        <v>4.29233</v>
       </c>
       <c r="C60" t="n">
-        <v>3.31403</v>
+        <v>2.98592</v>
       </c>
       <c r="D60" t="n">
-        <v>18.1282</v>
+        <v>18.0714</v>
       </c>
       <c r="E60" t="n">
-        <v>3.40938</v>
+        <v>2.84677</v>
       </c>
       <c r="F60" t="n">
-        <v>3.47811</v>
+        <v>3.37714</v>
       </c>
     </row>
     <row r="61">
@@ -6259,19 +6259,19 @@
         <v>175290</v>
       </c>
       <c r="B61" t="n">
-        <v>4.5301</v>
+        <v>4.56428</v>
       </c>
       <c r="C61" t="n">
-        <v>3.26933</v>
+        <v>3.24358</v>
       </c>
       <c r="D61" t="n">
-        <v>18.5624</v>
+        <v>18.484</v>
       </c>
       <c r="E61" t="n">
-        <v>3.22173</v>
+        <v>3.0126</v>
       </c>
       <c r="F61" t="n">
-        <v>3.59863</v>
+        <v>3.58575</v>
       </c>
     </row>
     <row r="62">
@@ -6279,19 +6279,19 @@
         <v>184026</v>
       </c>
       <c r="B62" t="n">
-        <v>5.28062</v>
+        <v>5.27995</v>
       </c>
       <c r="C62" t="n">
-        <v>3.88402</v>
+        <v>3.86616</v>
       </c>
       <c r="D62" t="n">
-        <v>18.9681</v>
+        <v>18.9433</v>
       </c>
       <c r="E62" t="n">
-        <v>3.50464</v>
+        <v>3.29406</v>
       </c>
       <c r="F62" t="n">
-        <v>3.84774</v>
+        <v>3.84584</v>
       </c>
     </row>
     <row r="63">
@@ -6299,19 +6299,19 @@
         <v>193198</v>
       </c>
       <c r="B63" t="n">
-        <v>6.37557</v>
+        <v>6.37724</v>
       </c>
       <c r="C63" t="n">
-        <v>4.83213</v>
+        <v>4.78795</v>
       </c>
       <c r="D63" t="n">
-        <v>19.413</v>
+        <v>19.4141</v>
       </c>
       <c r="E63" t="n">
-        <v>3.9646</v>
+        <v>3.74069</v>
       </c>
       <c r="F63" t="n">
-        <v>4.22308</v>
+        <v>4.27105</v>
       </c>
     </row>
     <row r="64">
@@ -6319,19 +6319,19 @@
         <v>202828</v>
       </c>
       <c r="B64" t="n">
-        <v>7.92794</v>
+        <v>7.86219</v>
       </c>
       <c r="C64" t="n">
-        <v>6.42246</v>
+        <v>6.26074</v>
       </c>
       <c r="D64" t="n">
-        <v>17.7894</v>
+        <v>14.2384</v>
       </c>
       <c r="E64" t="n">
-        <v>2.98724</v>
+        <v>2.61926</v>
       </c>
       <c r="F64" t="n">
-        <v>3.40519</v>
+        <v>3.21096</v>
       </c>
     </row>
     <row r="65">
@@ -6339,19 +6339,19 @@
         <v>212939</v>
       </c>
       <c r="B65" t="n">
-        <v>10.5479</v>
+        <v>10.4792</v>
       </c>
       <c r="C65" t="n">
-        <v>2.74238</v>
+        <v>2.2782</v>
       </c>
       <c r="D65" t="n">
-        <v>18.4966</v>
+        <v>14.8076</v>
       </c>
       <c r="E65" t="n">
-        <v>2.76293</v>
+        <v>2.70118</v>
       </c>
       <c r="F65" t="n">
-        <v>3.49434</v>
+        <v>3.25998</v>
       </c>
     </row>
     <row r="66">
@@ -6359,19 +6359,19 @@
         <v>223555</v>
       </c>
       <c r="B66" t="n">
-        <v>14.4813</v>
+        <v>14.3842</v>
       </c>
       <c r="C66" t="n">
-        <v>2.31242</v>
+        <v>2.29818</v>
       </c>
       <c r="D66" t="n">
-        <v>19.2005</v>
+        <v>15.5864</v>
       </c>
       <c r="E66" t="n">
-        <v>2.80183</v>
+        <v>2.67624</v>
       </c>
       <c r="F66" t="n">
-        <v>3.54848</v>
+        <v>3.30895</v>
       </c>
     </row>
     <row r="67">
@@ -6379,19 +6379,19 @@
         <v>234701</v>
       </c>
       <c r="B67" t="n">
-        <v>3.90476</v>
+        <v>3.49844</v>
       </c>
       <c r="C67" t="n">
-        <v>2.35518</v>
+        <v>2.32438</v>
       </c>
       <c r="D67" t="n">
-        <v>19.9384</v>
+        <v>16.3161</v>
       </c>
       <c r="E67" t="n">
-        <v>2.82414</v>
+        <v>2.75553</v>
       </c>
       <c r="F67" t="n">
-        <v>3.61192</v>
+        <v>3.36228</v>
       </c>
     </row>
     <row r="68">
@@ -6399,19 +6399,19 @@
         <v>246404</v>
       </c>
       <c r="B68" t="n">
-        <v>3.99047</v>
+        <v>3.58959</v>
       </c>
       <c r="C68" t="n">
-        <v>2.44462</v>
+        <v>2.35273</v>
       </c>
       <c r="D68" t="n">
-        <v>20.8282</v>
+        <v>17.2378</v>
       </c>
       <c r="E68" t="n">
-        <v>3.13618</v>
+        <v>2.75177</v>
       </c>
       <c r="F68" t="n">
-        <v>3.68187</v>
+        <v>3.42765</v>
       </c>
     </row>
     <row r="69">
@@ -6419,19 +6419,19 @@
         <v>258692</v>
       </c>
       <c r="B69" t="n">
-        <v>3.66623</v>
+        <v>3.63583</v>
       </c>
       <c r="C69" t="n">
-        <v>2.44623</v>
+        <v>2.65293</v>
       </c>
       <c r="D69" t="n">
-        <v>21.574</v>
+        <v>17.9832</v>
       </c>
       <c r="E69" t="n">
-        <v>3.15141</v>
+        <v>2.77647</v>
       </c>
       <c r="F69" t="n">
-        <v>3.79413</v>
+        <v>3.5007</v>
       </c>
     </row>
     <row r="70">
@@ -6439,19 +6439,19 @@
         <v>271594</v>
       </c>
       <c r="B70" t="n">
-        <v>3.84748</v>
+        <v>3.7252</v>
       </c>
       <c r="C70" t="n">
-        <v>2.84504</v>
+        <v>2.47922</v>
       </c>
       <c r="D70" t="n">
-        <v>22.9215</v>
+        <v>18.9354</v>
       </c>
       <c r="E70" t="n">
-        <v>3.01293</v>
+        <v>2.81943</v>
       </c>
       <c r="F70" t="n">
-        <v>3.91388</v>
+        <v>3.56418</v>
       </c>
     </row>
     <row r="71">
@@ -6459,19 +6459,19 @@
         <v>285141</v>
       </c>
       <c r="B71" t="n">
-        <v>4.05356</v>
+        <v>3.86965</v>
       </c>
       <c r="C71" t="n">
-        <v>2.71035</v>
+        <v>2.55893</v>
       </c>
       <c r="D71" t="n">
-        <v>23.8781</v>
+        <v>19.8558</v>
       </c>
       <c r="E71" t="n">
-        <v>3.28865</v>
+        <v>2.89536</v>
       </c>
       <c r="F71" t="n">
-        <v>3.92156</v>
+        <v>3.64597</v>
       </c>
     </row>
     <row r="72">
@@ -6479,19 +6479,19 @@
         <v>299365</v>
       </c>
       <c r="B72" t="n">
-        <v>4.0918</v>
+        <v>4.03881</v>
       </c>
       <c r="C72" t="n">
-        <v>2.80924</v>
+        <v>2.86006</v>
       </c>
       <c r="D72" t="n">
-        <v>25.3344</v>
+        <v>20.912</v>
       </c>
       <c r="E72" t="n">
-        <v>3.37161</v>
+        <v>2.98306</v>
       </c>
       <c r="F72" t="n">
-        <v>4.038</v>
+        <v>3.74536</v>
       </c>
     </row>
     <row r="73">
@@ -6499,19 +6499,19 @@
         <v>314300</v>
       </c>
       <c r="B73" t="n">
-        <v>4.24161</v>
+        <v>4.24843</v>
       </c>
       <c r="C73" t="n">
-        <v>3.33618</v>
+        <v>2.88682</v>
       </c>
       <c r="D73" t="n">
-        <v>27.3846</v>
+        <v>21.9696</v>
       </c>
       <c r="E73" t="n">
-        <v>3.4756</v>
+        <v>3.08682</v>
       </c>
       <c r="F73" t="n">
-        <v>4.15818</v>
+        <v>3.87058</v>
       </c>
     </row>
     <row r="74">
@@ -6519,19 +6519,19 @@
         <v>329981</v>
       </c>
       <c r="B74" t="n">
-        <v>4.72058</v>
+        <v>4.51745</v>
       </c>
       <c r="C74" t="n">
-        <v>3.31977</v>
+        <v>3.1331</v>
       </c>
       <c r="D74" t="n">
-        <v>28.5444</v>
+        <v>23.1803</v>
       </c>
       <c r="E74" t="n">
-        <v>3.40063</v>
+        <v>3.43388</v>
       </c>
       <c r="F74" t="n">
-        <v>4.54448</v>
+        <v>4.04167</v>
       </c>
     </row>
     <row r="75">
@@ -6539,19 +6539,19 @@
         <v>346446</v>
       </c>
       <c r="B75" t="n">
-        <v>4.9758</v>
+        <v>5.0393</v>
       </c>
       <c r="C75" t="n">
-        <v>3.70316</v>
+        <v>3.95962</v>
       </c>
       <c r="D75" t="n">
-        <v>29.0649</v>
+        <v>24.6029</v>
       </c>
       <c r="E75" t="n">
-        <v>3.65519</v>
+        <v>3.81609</v>
       </c>
       <c r="F75" t="n">
-        <v>5.17391</v>
+        <v>4.30113</v>
       </c>
     </row>
     <row r="76">
@@ -6559,19 +6559,19 @@
         <v>363734</v>
       </c>
       <c r="B76" t="n">
-        <v>5.59853</v>
+        <v>5.71703</v>
       </c>
       <c r="C76" t="n">
-        <v>4.17524</v>
+        <v>4.50234</v>
       </c>
       <c r="D76" t="n">
-        <v>29.7228</v>
+        <v>25.9798</v>
       </c>
       <c r="E76" t="n">
-        <v>3.77131</v>
+        <v>3.91946</v>
       </c>
       <c r="F76" t="n">
-        <v>4.89972</v>
+        <v>4.70927</v>
       </c>
     </row>
     <row r="77">
@@ -6579,19 +6579,19 @@
         <v>381886</v>
       </c>
       <c r="B77" t="n">
-        <v>6.52798</v>
+        <v>6.7095</v>
       </c>
       <c r="C77" t="n">
-        <v>4.97719</v>
+        <v>5.21657</v>
       </c>
       <c r="D77" t="n">
-        <v>30.6816</v>
+        <v>27.5571</v>
       </c>
       <c r="E77" t="n">
-        <v>4.19556</v>
+        <v>4.39835</v>
       </c>
       <c r="F77" t="n">
-        <v>5.20875</v>
+        <v>5.11964</v>
       </c>
     </row>
     <row r="78">
@@ -6599,19 +6599,19 @@
         <v>400945</v>
       </c>
       <c r="B78" t="n">
-        <v>8.26801</v>
+        <v>8.288819999999999</v>
       </c>
       <c r="C78" t="n">
-        <v>6.36495</v>
+        <v>6.45516</v>
       </c>
       <c r="D78" t="n">
-        <v>24.663</v>
+        <v>24.2614</v>
       </c>
       <c r="E78" t="n">
-        <v>3.13855</v>
+        <v>3.04624</v>
       </c>
       <c r="F78" t="n">
-        <v>3.93959</v>
+        <v>3.82775</v>
       </c>
     </row>
     <row r="79">
@@ -6619,19 +6619,19 @@
         <v>420956</v>
       </c>
       <c r="B79" t="n">
-        <v>10.6062</v>
+        <v>10.9546</v>
       </c>
       <c r="C79" t="n">
-        <v>2.68367</v>
+        <v>2.76871</v>
       </c>
       <c r="D79" t="n">
-        <v>26.3215</v>
+        <v>25.5581</v>
       </c>
       <c r="E79" t="n">
-        <v>3.19193</v>
+        <v>3.17759</v>
       </c>
       <c r="F79" t="n">
-        <v>4.13577</v>
+        <v>3.9334</v>
       </c>
     </row>
     <row r="80">
@@ -6639,19 +6639,19 @@
         <v>441967</v>
       </c>
       <c r="B80" t="n">
-        <v>14.2655</v>
+        <v>14.7562</v>
       </c>
       <c r="C80" t="n">
-        <v>2.75128</v>
+        <v>2.83461</v>
       </c>
       <c r="D80" t="n">
-        <v>27.4338</v>
+        <v>26.6885</v>
       </c>
       <c r="E80" t="n">
-        <v>3.22445</v>
+        <v>3.16644</v>
       </c>
       <c r="F80" t="n">
-        <v>4.22085</v>
+        <v>4.08618</v>
       </c>
     </row>
     <row r="81">
@@ -6659,19 +6659,19 @@
         <v>464028</v>
       </c>
       <c r="B81" t="n">
-        <v>4.1194</v>
+        <v>4.11416</v>
       </c>
       <c r="C81" t="n">
-        <v>2.80767</v>
+        <v>2.88386</v>
       </c>
       <c r="D81" t="n">
-        <v>28.5335</v>
+        <v>27.9869</v>
       </c>
       <c r="E81" t="n">
-        <v>3.33916</v>
+        <v>3.30799</v>
       </c>
       <c r="F81" t="n">
-        <v>4.35134</v>
+        <v>4.47268</v>
       </c>
     </row>
     <row r="82">
@@ -6679,19 +6679,19 @@
         <v>487192</v>
       </c>
       <c r="B82" t="n">
-        <v>4.2371</v>
+        <v>4.22138</v>
       </c>
       <c r="C82" t="n">
-        <v>2.88494</v>
+        <v>2.96189</v>
       </c>
       <c r="D82" t="n">
-        <v>29.7319</v>
+        <v>29.3154</v>
       </c>
       <c r="E82" t="n">
-        <v>3.33546</v>
+        <v>3.30881</v>
       </c>
       <c r="F82" t="n">
-        <v>4.68289</v>
+        <v>4.43195</v>
       </c>
     </row>
     <row r="83">
@@ -6699,19 +6699,19 @@
         <v>511514</v>
       </c>
       <c r="B83" t="n">
-        <v>4.39003</v>
+        <v>4.3671</v>
       </c>
       <c r="C83" t="n">
-        <v>2.99757</v>
+        <v>3.07021</v>
       </c>
       <c r="D83" t="n">
-        <v>31.0961</v>
+        <v>30.6574</v>
       </c>
       <c r="E83" t="n">
-        <v>3.45754</v>
+        <v>3.45311</v>
       </c>
       <c r="F83" t="n">
-        <v>4.88447</v>
+        <v>4.6656</v>
       </c>
     </row>
     <row r="84">
@@ -6719,19 +6719,19 @@
         <v>537052</v>
       </c>
       <c r="B84" t="n">
-        <v>4.58108</v>
+        <v>4.58894</v>
       </c>
       <c r="C84" t="n">
-        <v>3.14564</v>
+        <v>3.20623</v>
       </c>
       <c r="D84" t="n">
-        <v>32.3372</v>
+        <v>32.0695</v>
       </c>
       <c r="E84" t="n">
-        <v>3.45485</v>
+        <v>3.65917</v>
       </c>
       <c r="F84" t="n">
-        <v>5.14688</v>
+        <v>4.95039</v>
       </c>
     </row>
     <row r="85">
@@ -6739,19 +6739,19 @@
         <v>563866</v>
       </c>
       <c r="B85" t="n">
-        <v>4.79689</v>
+        <v>4.80491</v>
       </c>
       <c r="C85" t="n">
-        <v>3.325</v>
+        <v>3.37166</v>
       </c>
       <c r="D85" t="n">
-        <v>33.8523</v>
+        <v>33.5723</v>
       </c>
       <c r="E85" t="n">
-        <v>3.69888</v>
+        <v>3.80171</v>
       </c>
       <c r="F85" t="n">
-        <v>5.03705</v>
+        <v>4.91291</v>
       </c>
     </row>
     <row r="86">
@@ -6759,19 +6759,19 @@
         <v>592020</v>
       </c>
       <c r="B86" t="n">
-        <v>5.17563</v>
+        <v>5.1368</v>
       </c>
       <c r="C86" t="n">
-        <v>3.55912</v>
+        <v>3.60357</v>
       </c>
       <c r="D86" t="n">
-        <v>35.3143</v>
+        <v>35.0508</v>
       </c>
       <c r="E86" t="n">
-        <v>3.85745</v>
+        <v>4.01722</v>
       </c>
       <c r="F86" t="n">
-        <v>5.40901</v>
+        <v>5.26922</v>
       </c>
     </row>
     <row r="87">
@@ -6779,19 +6779,19 @@
         <v>621581</v>
       </c>
       <c r="B87" t="n">
-        <v>5.61573</v>
+        <v>5.54648</v>
       </c>
       <c r="C87" t="n">
-        <v>3.85025</v>
+        <v>3.87842</v>
       </c>
       <c r="D87" t="n">
-        <v>36.9237</v>
+        <v>36.6721</v>
       </c>
       <c r="E87" t="n">
-        <v>4.10896</v>
+        <v>4.27151</v>
       </c>
       <c r="F87" t="n">
-        <v>5.6857</v>
+        <v>5.54259</v>
       </c>
     </row>
     <row r="88">
@@ -6799,19 +6799,19 @@
         <v>652620</v>
       </c>
       <c r="B88" t="n">
-        <v>6.06554</v>
+        <v>6.02107</v>
       </c>
       <c r="C88" t="n">
-        <v>4.21483</v>
+        <v>4.16876</v>
       </c>
       <c r="D88" t="n">
-        <v>37.8348</v>
+        <v>37.7604</v>
       </c>
       <c r="E88" t="n">
-        <v>4.38135</v>
+        <v>4.55925</v>
       </c>
       <c r="F88" t="n">
-        <v>6.83121</v>
+        <v>6.16781</v>
       </c>
     </row>
     <row r="89">
@@ -6819,19 +6819,19 @@
         <v>685210</v>
       </c>
       <c r="B89" t="n">
-        <v>6.83998</v>
+        <v>6.74141</v>
       </c>
       <c r="C89" t="n">
-        <v>4.7942</v>
+        <v>4.73952</v>
       </c>
       <c r="D89" t="n">
-        <v>40.9115</v>
+        <v>39.4963</v>
       </c>
       <c r="E89" t="n">
-        <v>4.769</v>
+        <v>4.91392</v>
       </c>
       <c r="F89" t="n">
-        <v>7.51069</v>
+        <v>6.68443</v>
       </c>
     </row>
     <row r="90">
@@ -6839,19 +6839,19 @@
         <v>719429</v>
       </c>
       <c r="B90" t="n">
-        <v>7.68155</v>
+        <v>7.66512</v>
       </c>
       <c r="C90" t="n">
-        <v>5.32623</v>
+        <v>5.38651</v>
       </c>
       <c r="D90" t="n">
-        <v>42.0116</v>
+        <v>42.0802</v>
       </c>
       <c r="E90" t="n">
-        <v>5.18138</v>
+        <v>5.29769</v>
       </c>
       <c r="F90" t="n">
-        <v>7.6627</v>
+        <v>7.76782</v>
       </c>
     </row>
     <row r="91">
@@ -6859,19 +6859,19 @@
         <v>755358</v>
       </c>
       <c r="B91" t="n">
-        <v>8.61314</v>
+        <v>8.648250000000001</v>
       </c>
       <c r="C91" t="n">
-        <v>6.11229</v>
+        <v>6.1787</v>
       </c>
       <c r="D91" t="n">
-        <v>43.704</v>
+        <v>43.7849</v>
       </c>
       <c r="E91" t="n">
-        <v>5.75808</v>
+        <v>5.8347</v>
       </c>
       <c r="F91" t="n">
-        <v>8.104760000000001</v>
+        <v>8.44943</v>
       </c>
     </row>
     <row r="92">
@@ -6879,19 +6879,19 @@
         <v>793083</v>
       </c>
       <c r="B92" t="n">
-        <v>9.991339999999999</v>
+        <v>10.0139</v>
       </c>
       <c r="C92" t="n">
-        <v>7.43483</v>
+        <v>7.40709</v>
       </c>
       <c r="D92" t="n">
-        <v>35.6902</v>
+        <v>35.5684</v>
       </c>
       <c r="E92" t="n">
-        <v>3.92926</v>
+        <v>3.93713</v>
       </c>
       <c r="F92" t="n">
-        <v>5.60599</v>
+        <v>5.36046</v>
       </c>
     </row>
     <row r="93">
@@ -6899,19 +6899,19 @@
         <v>832694</v>
       </c>
       <c r="B93" t="n">
-        <v>12.525</v>
+        <v>12.3327</v>
       </c>
       <c r="C93" t="n">
-        <v>9.356719999999999</v>
+        <v>9.3285</v>
       </c>
       <c r="D93" t="n">
-        <v>36.8652</v>
+        <v>36.6784</v>
       </c>
       <c r="E93" t="n">
-        <v>4.05632</v>
+        <v>4.0559</v>
       </c>
       <c r="F93" t="n">
-        <v>5.73609</v>
+        <v>5.75514</v>
       </c>
     </row>
     <row r="94">
@@ -6919,19 +6919,19 @@
         <v>874285</v>
       </c>
       <c r="B94" t="n">
-        <v>16.4285</v>
+        <v>16.3087</v>
       </c>
       <c r="C94" t="n">
-        <v>3.5779</v>
+        <v>3.57144</v>
       </c>
       <c r="D94" t="n">
-        <v>38.21</v>
+        <v>37.9868</v>
       </c>
       <c r="E94" t="n">
-        <v>4.22026</v>
+        <v>4.21213</v>
       </c>
       <c r="F94" t="n">
-        <v>6.13169</v>
+        <v>5.99541</v>
       </c>
     </row>
     <row r="95">
@@ -6939,19 +6939,19 @@
         <v>917955</v>
       </c>
       <c r="B95" t="n">
-        <v>5.77617</v>
+        <v>5.79213</v>
       </c>
       <c r="C95" t="n">
-        <v>3.73846</v>
+        <v>3.78307</v>
       </c>
       <c r="D95" t="n">
-        <v>39.3826</v>
+        <v>39.2293</v>
       </c>
       <c r="E95" t="n">
-        <v>4.35669</v>
+        <v>4.40404</v>
       </c>
       <c r="F95" t="n">
-        <v>6.41157</v>
+        <v>6.32611</v>
       </c>
     </row>
     <row r="96">
@@ -6959,19 +6959,19 @@
         <v>963808</v>
       </c>
       <c r="B96" t="n">
-        <v>6.04145</v>
+        <v>6.13552</v>
       </c>
       <c r="C96" t="n">
-        <v>3.90272</v>
+        <v>3.93711</v>
       </c>
       <c r="D96" t="n">
-        <v>40.6681</v>
+        <v>40.5144</v>
       </c>
       <c r="E96" t="n">
-        <v>4.52602</v>
+        <v>4.52865</v>
       </c>
       <c r="F96" t="n">
-        <v>6.81829</v>
+        <v>6.61436</v>
       </c>
     </row>
     <row r="97">
@@ -6979,19 +6979,19 @@
         <v>1011953</v>
       </c>
       <c r="B97" t="n">
-        <v>6.35483</v>
+        <v>6.39519</v>
       </c>
       <c r="C97" t="n">
-        <v>4.08528</v>
+        <v>4.08626</v>
       </c>
       <c r="D97" t="n">
-        <v>41.9828</v>
+        <v>41.8028</v>
       </c>
       <c r="E97" t="n">
-        <v>4.6737</v>
+        <v>4.68686</v>
       </c>
       <c r="F97" t="n">
-        <v>7.02367</v>
+        <v>6.94059</v>
       </c>
     </row>
     <row r="98">
@@ -6999,19 +6999,19 @@
         <v>1062505</v>
       </c>
       <c r="B98" t="n">
-        <v>6.6526</v>
+        <v>6.65937</v>
       </c>
       <c r="C98" t="n">
-        <v>4.22736</v>
+        <v>4.25333</v>
       </c>
       <c r="D98" t="n">
-        <v>43.2769</v>
+        <v>43.1416</v>
       </c>
       <c r="E98" t="n">
-        <v>4.87632</v>
+        <v>4.84011</v>
       </c>
       <c r="F98" t="n">
-        <v>7.32577</v>
+        <v>7.30247</v>
       </c>
     </row>
     <row r="99">
@@ -7019,19 +7019,19 @@
         <v>1115584</v>
       </c>
       <c r="B99" t="n">
-        <v>6.90795</v>
+        <v>6.96612</v>
       </c>
       <c r="C99" t="n">
-        <v>4.44677</v>
+        <v>4.43951</v>
       </c>
       <c r="D99" t="n">
-        <v>44.738</v>
+        <v>44.5274</v>
       </c>
       <c r="E99" t="n">
-        <v>5.10233</v>
+        <v>5.03411</v>
       </c>
       <c r="F99" t="n">
-        <v>7.68532</v>
+        <v>7.59375</v>
       </c>
     </row>
     <row r="100">
@@ -7039,19 +7039,19 @@
         <v>1171316</v>
       </c>
       <c r="B100" t="n">
-        <v>7.25453</v>
+        <v>7.26317</v>
       </c>
       <c r="C100" t="n">
-        <v>4.61995</v>
+        <v>4.63252</v>
       </c>
       <c r="D100" t="n">
-        <v>46.1972</v>
+        <v>46.0127</v>
       </c>
       <c r="E100" t="n">
-        <v>5.23475</v>
+        <v>5.23595</v>
       </c>
       <c r="F100" t="n">
-        <v>8.022040000000001</v>
+        <v>7.91289</v>
       </c>
     </row>
     <row r="101">
@@ -7059,19 +7059,19 @@
         <v>1229834</v>
       </c>
       <c r="B101" t="n">
-        <v>7.54584</v>
+        <v>7.59423</v>
       </c>
       <c r="C101" t="n">
-        <v>4.90244</v>
+        <v>4.92225</v>
       </c>
       <c r="D101" t="n">
-        <v>47.481</v>
+        <v>47.5556</v>
       </c>
       <c r="E101" t="n">
-        <v>5.51283</v>
+        <v>5.51499</v>
       </c>
       <c r="F101" t="n">
-        <v>8.63678</v>
+        <v>8.397690000000001</v>
       </c>
     </row>
     <row r="102">
@@ -7079,19 +7079,19 @@
         <v>1291277</v>
       </c>
       <c r="B102" t="n">
-        <v>7.99291</v>
+        <v>8.0106</v>
       </c>
       <c r="C102" t="n">
-        <v>5.18352</v>
+        <v>5.21107</v>
       </c>
       <c r="D102" t="n">
-        <v>49.2533</v>
+        <v>49.1332</v>
       </c>
       <c r="E102" t="n">
-        <v>5.77269</v>
+        <v>5.78693</v>
       </c>
       <c r="F102" t="n">
-        <v>9.147740000000001</v>
+        <v>8.91736</v>
       </c>
     </row>
     <row r="103">
@@ -7099,19 +7099,19 @@
         <v>1355792</v>
       </c>
       <c r="B103" t="n">
-        <v>8.54358</v>
+        <v>8.53905</v>
       </c>
       <c r="C103" t="n">
-        <v>5.59831</v>
+        <v>5.61546</v>
       </c>
       <c r="D103" t="n">
-        <v>50.6323</v>
+        <v>50.5639</v>
       </c>
       <c r="E103" t="n">
-        <v>6.00769</v>
+        <v>6.10766</v>
       </c>
       <c r="F103" t="n">
-        <v>9.39995</v>
+        <v>9.210150000000001</v>
       </c>
     </row>
     <row r="104">
@@ -7119,19 +7119,19 @@
         <v>1423532</v>
       </c>
       <c r="B104" t="n">
-        <v>9.239549999999999</v>
+        <v>9.22086</v>
       </c>
       <c r="C104" t="n">
-        <v>6.18758</v>
+        <v>6.19104</v>
       </c>
       <c r="D104" t="n">
-        <v>52.5339</v>
+        <v>52.4107</v>
       </c>
       <c r="E104" t="n">
-        <v>6.41229</v>
+        <v>6.54562</v>
       </c>
       <c r="F104" t="n">
-        <v>10.468</v>
+        <v>10.358</v>
       </c>
     </row>
     <row r="105">
@@ -7139,19 +7139,19 @@
         <v>1494659</v>
       </c>
       <c r="B105" t="n">
-        <v>10.3501</v>
+        <v>10.3331</v>
       </c>
       <c r="C105" t="n">
-        <v>7.01769</v>
+        <v>7.03486</v>
       </c>
       <c r="D105" t="n">
-        <v>54.3232</v>
+        <v>54.1569</v>
       </c>
       <c r="E105" t="n">
-        <v>6.90376</v>
+        <v>7.1402</v>
       </c>
       <c r="F105" t="n">
-        <v>11.1005</v>
+        <v>10.6503</v>
       </c>
     </row>
     <row r="106">
@@ -7159,19 +7159,19 @@
         <v>1569342</v>
       </c>
       <c r="B106" t="n">
-        <v>11.8722</v>
+        <v>11.8314</v>
       </c>
       <c r="C106" t="n">
-        <v>8.231629999999999</v>
+        <v>8.21893</v>
       </c>
       <c r="D106" t="n">
-        <v>55.9224</v>
+        <v>55.6658</v>
       </c>
       <c r="E106" t="n">
-        <v>7.68038</v>
+        <v>7.82913</v>
       </c>
       <c r="F106" t="n">
-        <v>12.4933</v>
+        <v>12.417</v>
       </c>
     </row>
     <row r="107">
@@ -7179,19 +7179,19 @@
         <v>1647759</v>
       </c>
       <c r="B107" t="n">
-        <v>13.987</v>
+        <v>13.8904</v>
       </c>
       <c r="C107" t="n">
-        <v>9.95415</v>
+        <v>10.0047</v>
       </c>
       <c r="D107" t="n">
-        <v>42.4476</v>
+        <v>42.4391</v>
       </c>
       <c r="E107" t="n">
-        <v>4.93967</v>
+        <v>4.95528</v>
       </c>
       <c r="F107" t="n">
-        <v>7.21181</v>
+        <v>7.18141</v>
       </c>
     </row>
     <row r="108">
@@ -7199,19 +7199,19 @@
         <v>1730096</v>
       </c>
       <c r="B108" t="n">
-        <v>17.2485</v>
+        <v>17.2889</v>
       </c>
       <c r="C108" t="n">
-        <v>4.30654</v>
+        <v>4.38386</v>
       </c>
       <c r="D108" t="n">
-        <v>43.5569</v>
+        <v>43.58</v>
       </c>
       <c r="E108" t="n">
-        <v>5.05172</v>
+        <v>5.12328</v>
       </c>
       <c r="F108" t="n">
-        <v>7.58644</v>
+        <v>7.51475</v>
       </c>
     </row>
     <row r="109">
@@ -7219,19 +7219,19 @@
         <v>1816549</v>
       </c>
       <c r="B109" t="n">
-        <v>21.7869</v>
+        <v>21.8448</v>
       </c>
       <c r="C109" t="n">
-        <v>4.5148</v>
+        <v>4.51528</v>
       </c>
       <c r="D109" t="n">
-        <v>44.7665</v>
+        <v>44.7325</v>
       </c>
       <c r="E109" t="n">
-        <v>5.16624</v>
+        <v>5.34592</v>
       </c>
       <c r="F109" t="n">
-        <v>7.8252</v>
+        <v>7.81304</v>
       </c>
     </row>
     <row r="110">
@@ -7239,19 +7239,19 @@
         <v>1907324</v>
       </c>
       <c r="B110" t="n">
-        <v>7.29521</v>
+        <v>7.29704</v>
       </c>
       <c r="C110" t="n">
-        <v>4.59721</v>
+        <v>4.59046</v>
       </c>
       <c r="D110" t="n">
-        <v>45.9682</v>
+        <v>45.9529</v>
       </c>
       <c r="E110" t="n">
-        <v>5.30972</v>
+        <v>5.59502</v>
       </c>
       <c r="F110" t="n">
-        <v>8.414440000000001</v>
+        <v>8.242179999999999</v>
       </c>
     </row>
     <row r="111">
@@ -7259,19 +7259,19 @@
         <v>2002637</v>
       </c>
       <c r="B111" t="n">
-        <v>7.57113</v>
+        <v>7.60133</v>
       </c>
       <c r="C111" t="n">
-        <v>4.80075</v>
+        <v>4.76638</v>
       </c>
       <c r="D111" t="n">
-        <v>47.1663</v>
+        <v>47.2761</v>
       </c>
       <c r="E111" t="n">
-        <v>5.41936</v>
+        <v>5.8824</v>
       </c>
       <c r="F111" t="n">
-        <v>8.83375</v>
+        <v>8.77463</v>
       </c>
     </row>
     <row r="112">
@@ -7279,19 +7279,19 @@
         <v>2102715</v>
       </c>
       <c r="B112" t="n">
-        <v>7.88379</v>
+        <v>7.87198</v>
       </c>
       <c r="C112" t="n">
-        <v>4.95953</v>
+        <v>4.92192</v>
       </c>
       <c r="D112" t="n">
-        <v>48.467</v>
+        <v>48.5735</v>
       </c>
       <c r="E112" t="n">
-        <v>5.57545</v>
+        <v>6.04035</v>
       </c>
       <c r="F112" t="n">
-        <v>9.341469999999999</v>
+        <v>9.16065</v>
       </c>
     </row>
     <row r="113">
@@ -7299,19 +7299,19 @@
         <v>2207796</v>
       </c>
       <c r="B113" t="n">
-        <v>8.25526</v>
+        <v>8.282959999999999</v>
       </c>
       <c r="C113" t="n">
-        <v>5.19495</v>
+        <v>5.25801</v>
       </c>
       <c r="D113" t="n">
-        <v>49.8485</v>
+        <v>49.8761</v>
       </c>
       <c r="E113" t="n">
-        <v>5.75648</v>
+        <v>6.27534</v>
       </c>
       <c r="F113" t="n">
-        <v>9.8581</v>
+        <v>9.693390000000001</v>
       </c>
     </row>
     <row r="114">
@@ -7319,19 +7319,19 @@
         <v>2318131</v>
       </c>
       <c r="B114" t="n">
-        <v>8.66419</v>
+        <v>8.68582</v>
       </c>
       <c r="C114" t="n">
-        <v>5.48595</v>
+        <v>5.49565</v>
       </c>
       <c r="D114" t="n">
-        <v>51.2313</v>
+        <v>51.3138</v>
       </c>
       <c r="E114" t="n">
-        <v>5.98917</v>
+        <v>6.51366</v>
       </c>
       <c r="F114" t="n">
-        <v>10.3361</v>
+        <v>10.2333</v>
       </c>
     </row>
     <row r="115">
@@ -7339,19 +7339,19 @@
         <v>2433982</v>
       </c>
       <c r="B115" t="n">
-        <v>9.219049999999999</v>
+        <v>9.28436</v>
       </c>
       <c r="C115" t="n">
-        <v>5.84532</v>
+        <v>5.85189</v>
       </c>
       <c r="D115" t="n">
-        <v>52.7008</v>
+        <v>52.7627</v>
       </c>
       <c r="E115" t="n">
-        <v>6.36126</v>
+        <v>6.75561</v>
       </c>
       <c r="F115" t="n">
-        <v>10.8795</v>
+        <v>10.8533</v>
       </c>
     </row>
     <row r="116">
@@ -7359,19 +7359,19 @@
         <v>2555625</v>
       </c>
       <c r="B116" t="n">
-        <v>9.926450000000001</v>
+        <v>9.93825</v>
       </c>
       <c r="C116" t="n">
-        <v>6.32131</v>
+        <v>6.31637</v>
       </c>
       <c r="D116" t="n">
-        <v>54.2543</v>
+        <v>54.3679</v>
       </c>
       <c r="E116" t="n">
-        <v>6.79005</v>
+        <v>7.05014</v>
       </c>
       <c r="F116" t="n">
-        <v>11.4535</v>
+        <v>11.4702</v>
       </c>
     </row>
     <row r="117">
@@ -7379,19 +7379,19 @@
         <v>2683350</v>
       </c>
       <c r="B117" t="n">
-        <v>10.6021</v>
+        <v>10.5394</v>
       </c>
       <c r="C117" t="n">
-        <v>6.80608</v>
+        <v>6.79376</v>
       </c>
       <c r="D117" t="n">
-        <v>55.822</v>
+        <v>55.9704</v>
       </c>
       <c r="E117" t="n">
-        <v>7.27004</v>
+        <v>7.32668</v>
       </c>
       <c r="F117" t="n">
-        <v>12.0494</v>
+        <v>11.9281</v>
       </c>
     </row>
     <row r="118">
@@ -7399,19 +7399,19 @@
         <v>2817461</v>
       </c>
       <c r="B118" t="n">
-        <v>11.3209</v>
+        <v>11.3049</v>
       </c>
       <c r="C118" t="n">
-        <v>7.37132</v>
+        <v>7.36186</v>
       </c>
       <c r="D118" t="n">
-        <v>57.5996</v>
+        <v>57.5643</v>
       </c>
       <c r="E118" t="n">
-        <v>7.74915</v>
+        <v>7.66911</v>
       </c>
       <c r="F118" t="n">
-        <v>12.5731</v>
+        <v>12.6052</v>
       </c>
     </row>
     <row r="119">
@@ -7419,19 +7419,19 @@
         <v>2958277</v>
       </c>
       <c r="B119" t="n">
-        <v>12.2861</v>
+        <v>12.2475</v>
       </c>
       <c r="C119" t="n">
-        <v>8.13007</v>
+        <v>8.09709</v>
       </c>
       <c r="D119" t="n">
-        <v>59.3095</v>
+        <v>59.3905</v>
       </c>
       <c r="E119" t="n">
-        <v>8.360010000000001</v>
+        <v>8.062340000000001</v>
       </c>
       <c r="F119" t="n">
-        <v>13.3793</v>
+        <v>13.4347</v>
       </c>
     </row>
     <row r="120">
@@ -7439,19 +7439,19 @@
         <v>3106133</v>
       </c>
       <c r="B120" t="n">
-        <v>13.4713</v>
+        <v>13.5004</v>
       </c>
       <c r="C120" t="n">
-        <v>9.16503</v>
+        <v>9.1661</v>
       </c>
       <c r="D120" t="n">
-        <v>61.2472</v>
+        <v>61.296</v>
       </c>
       <c r="E120" t="n">
-        <v>9.08409</v>
+        <v>8.82315</v>
       </c>
       <c r="F120" t="n">
-        <v>14.3893</v>
+        <v>14.247</v>
       </c>
     </row>
     <row r="121">
@@ -7459,19 +7459,19 @@
         <v>3261381</v>
       </c>
       <c r="B121" t="n">
-        <v>15.2393</v>
+        <v>15.2573</v>
       </c>
       <c r="C121" t="n">
-        <v>10.6908</v>
+        <v>10.6936</v>
       </c>
       <c r="D121" t="n">
-        <v>45.3988</v>
+        <v>45.5506</v>
       </c>
       <c r="E121" t="n">
-        <v>6.99803</v>
+        <v>7.23651</v>
       </c>
       <c r="F121" t="n">
-        <v>9.81793</v>
+        <v>10.011</v>
       </c>
     </row>
     <row r="122">
@@ -7479,19 +7479,19 @@
         <v>3424391</v>
       </c>
       <c r="B122" t="n">
-        <v>17.8949</v>
+        <v>17.9208</v>
       </c>
       <c r="C122" t="n">
-        <v>6.00091</v>
+        <v>6.20546</v>
       </c>
       <c r="D122" t="n">
-        <v>46.5292</v>
+        <v>46.3665</v>
       </c>
       <c r="E122" t="n">
-        <v>7.10283</v>
+        <v>7.24231</v>
       </c>
       <c r="F122" t="n">
-        <v>10.6047</v>
+        <v>10.1948</v>
       </c>
     </row>
     <row r="123">
@@ -7499,19 +7499,19 @@
         <v>3595551</v>
       </c>
       <c r="B123" t="n">
-        <v>22.4419</v>
+        <v>22.0891</v>
       </c>
       <c r="C123" t="n">
-        <v>6.07589</v>
+        <v>5.86579</v>
       </c>
       <c r="D123" t="n">
-        <v>47.5258</v>
+        <v>47.7959</v>
       </c>
       <c r="E123" t="n">
-        <v>7.07362</v>
+        <v>7.52114</v>
       </c>
       <c r="F123" t="n">
-        <v>10.3295</v>
+        <v>10.9398</v>
       </c>
     </row>
     <row r="124">
@@ -7519,19 +7519,19 @@
         <v>3775269</v>
       </c>
       <c r="B124" t="n">
-        <v>9.48474</v>
+        <v>9.608359999999999</v>
       </c>
       <c r="C124" t="n">
-        <v>6.22078</v>
+        <v>6.29811</v>
       </c>
       <c r="D124" t="n">
-        <v>48.8772</v>
+        <v>49.0303</v>
       </c>
       <c r="E124" t="n">
-        <v>7.29135</v>
+        <v>8.441179999999999</v>
       </c>
       <c r="F124" t="n">
-        <v>11.1509</v>
+        <v>11.9406</v>
       </c>
     </row>
     <row r="125">
@@ -7539,19 +7539,19 @@
         <v>3963972</v>
       </c>
       <c r="B125" t="n">
-        <v>9.89039</v>
+        <v>9.835089999999999</v>
       </c>
       <c r="C125" t="n">
-        <v>6.26401</v>
+        <v>6.48825</v>
       </c>
       <c r="D125" t="n">
-        <v>50.1317</v>
+        <v>50.2943</v>
       </c>
       <c r="E125" t="n">
-        <v>7.53597</v>
+        <v>7.74917</v>
       </c>
       <c r="F125" t="n">
-        <v>11.38</v>
+        <v>11.3003</v>
       </c>
     </row>
     <row r="126">
@@ -7559,19 +7559,19 @@
         <v>4162110</v>
       </c>
       <c r="B126" t="n">
-        <v>10.2536</v>
+        <v>10.1465</v>
       </c>
       <c r="C126" t="n">
-        <v>6.65375</v>
+        <v>6.71557</v>
       </c>
       <c r="D126" t="n">
-        <v>51.5262</v>
+        <v>51.6641</v>
       </c>
       <c r="E126" t="n">
-        <v>7.90783</v>
+        <v>8.31072</v>
       </c>
       <c r="F126" t="n">
-        <v>12.0936</v>
+        <v>12.0242</v>
       </c>
     </row>
     <row r="127">
@@ -7579,19 +7579,19 @@
         <v>4370154</v>
       </c>
       <c r="B127" t="n">
-        <v>10.4393</v>
+        <v>10.576</v>
       </c>
       <c r="C127" t="n">
-        <v>6.6993</v>
+        <v>6.69033</v>
       </c>
       <c r="D127" t="n">
-        <v>52.7688</v>
+        <v>53.0152</v>
       </c>
       <c r="E127" t="n">
-        <v>8.223549999999999</v>
+        <v>8.318059999999999</v>
       </c>
       <c r="F127" t="n">
-        <v>12.5706</v>
+        <v>11.9588</v>
       </c>
     </row>
     <row r="128">
@@ -7599,19 +7599,19 @@
         <v>4588600</v>
       </c>
       <c r="B128" t="n">
-        <v>10.6785</v>
+        <v>11.0145</v>
       </c>
       <c r="C128" t="n">
-        <v>7.29174</v>
+        <v>7.04007</v>
       </c>
       <c r="D128" t="n">
-        <v>54.3207</v>
+        <v>54.3558</v>
       </c>
       <c r="E128" t="n">
-        <v>8.259029999999999</v>
+        <v>8.722759999999999</v>
       </c>
       <c r="F128" t="n">
-        <v>12.6839</v>
+        <v>12.737</v>
       </c>
     </row>
     <row r="129">
@@ -7619,19 +7619,19 @@
         <v>4817968</v>
       </c>
       <c r="B129" t="n">
-        <v>10.773</v>
+        <v>10.885</v>
       </c>
       <c r="C129" t="n">
-        <v>7.26313</v>
+        <v>7.61917</v>
       </c>
       <c r="D129" t="n">
-        <v>55.7686</v>
+        <v>55.8725</v>
       </c>
       <c r="E129" t="n">
-        <v>8.32996</v>
+        <v>8.677619999999999</v>
       </c>
       <c r="F129" t="n">
-        <v>12.972</v>
+        <v>12.4398</v>
       </c>
     </row>
     <row r="130">
@@ -7639,19 +7639,19 @@
         <v>5058804</v>
       </c>
       <c r="B130" t="n">
-        <v>11.2578</v>
+        <v>11.3157</v>
       </c>
       <c r="C130" t="n">
-        <v>7.36948</v>
+        <v>7.43437</v>
       </c>
       <c r="D130" t="n">
-        <v>57.2285</v>
+        <v>57.4299</v>
       </c>
       <c r="E130" t="n">
-        <v>8.491569999999999</v>
+        <v>9.05429</v>
       </c>
       <c r="F130" t="n">
-        <v>13.2609</v>
+        <v>13.4604</v>
       </c>
     </row>
     <row r="131">
@@ -7659,19 +7659,19 @@
         <v>5311681</v>
       </c>
       <c r="B131" t="n">
-        <v>11.9252</v>
+        <v>11.7489</v>
       </c>
       <c r="C131" t="n">
-        <v>7.62056</v>
+        <v>7.68027</v>
       </c>
       <c r="D131" t="n">
-        <v>58.6604</v>
+        <v>58.7601</v>
       </c>
       <c r="E131" t="n">
-        <v>8.85896</v>
+        <v>9.545529999999999</v>
       </c>
       <c r="F131" t="n">
-        <v>13.9396</v>
+        <v>14.1837</v>
       </c>
     </row>
     <row r="132">
@@ -7679,19 +7679,19 @@
         <v>5577201</v>
       </c>
       <c r="B132" t="n">
-        <v>12.4491</v>
+        <v>12.6125</v>
       </c>
       <c r="C132" t="n">
-        <v>8.200889999999999</v>
+        <v>8.243230000000001</v>
       </c>
       <c r="D132" t="n">
-        <v>60.5418</v>
+        <v>60.6625</v>
       </c>
       <c r="E132" t="n">
-        <v>9.39461</v>
+        <v>9.69552</v>
       </c>
       <c r="F132" t="n">
-        <v>14.6235</v>
+        <v>14.4422</v>
       </c>
     </row>
     <row r="133">
@@ -7699,19 +7699,19 @@
         <v>5855997</v>
       </c>
       <c r="B133" t="n">
-        <v>12.834</v>
+        <v>13.3148</v>
       </c>
       <c r="C133" t="n">
-        <v>8.74057</v>
+        <v>8.85629</v>
       </c>
       <c r="D133" t="n">
-        <v>62.1656</v>
+        <v>62.4482</v>
       </c>
       <c r="E133" t="n">
-        <v>9.769550000000001</v>
+        <v>10.2842</v>
       </c>
       <c r="F133" t="n">
-        <v>15.3294</v>
+        <v>15.3049</v>
       </c>
     </row>
     <row r="134">
@@ -7719,19 +7719,19 @@
         <v>6148732</v>
       </c>
       <c r="B134" t="n">
-        <v>14.3191</v>
+        <v>14.298</v>
       </c>
       <c r="C134" t="n">
-        <v>9.637309999999999</v>
+        <v>9.76854</v>
       </c>
       <c r="D134" t="n">
-        <v>64.0044</v>
+        <v>64.2851</v>
       </c>
       <c r="E134" t="n">
-        <v>10.2901</v>
+        <v>10.7543</v>
       </c>
       <c r="F134" t="n">
-        <v>16.0738</v>
+        <v>16.1823</v>
       </c>
     </row>
     <row r="135">
@@ -7739,19 +7739,19 @@
         <v>6456103</v>
       </c>
       <c r="B135" t="n">
-        <v>16.0298</v>
+        <v>16.044</v>
       </c>
       <c r="C135" t="n">
-        <v>11.044</v>
+        <v>11.0756</v>
       </c>
       <c r="D135" t="n">
-        <v>47.0992</v>
+        <v>47.2192</v>
       </c>
       <c r="E135" t="n">
-        <v>13.4588</v>
+        <v>13.6387</v>
       </c>
       <c r="F135" t="n">
-        <v>17.2774</v>
+        <v>17.0151</v>
       </c>
     </row>
     <row r="136">
@@ -7759,19 +7759,19 @@
         <v>6778842</v>
       </c>
       <c r="B136" t="n">
-        <v>18.3079</v>
+        <v>18.2121</v>
       </c>
       <c r="C136" t="n">
-        <v>11.8419</v>
+        <v>11.8473</v>
       </c>
       <c r="D136" t="n">
-        <v>48.2871</v>
+        <v>48.3527</v>
       </c>
       <c r="E136" t="n">
-        <v>13.6521</v>
+        <v>13.7821</v>
       </c>
       <c r="F136" t="n">
-        <v>17.4516</v>
+        <v>17.3736</v>
       </c>
     </row>
     <row r="137">
@@ -7779,19 +7779,19 @@
         <v>7117717</v>
       </c>
       <c r="B137" t="n">
-        <v>22.187</v>
+        <v>22.2682</v>
       </c>
       <c r="C137" t="n">
-        <v>11.8614</v>
+        <v>11.4909</v>
       </c>
       <c r="D137" t="n">
-        <v>49.5252</v>
+        <v>49.57</v>
       </c>
       <c r="E137" t="n">
-        <v>13.6261</v>
+        <v>13.8694</v>
       </c>
       <c r="F137" t="n">
-        <v>17.0543</v>
+        <v>17.1702</v>
       </c>
     </row>
     <row r="138">
@@ -7799,19 +7799,19 @@
         <v>7473535</v>
       </c>
       <c r="B138" t="n">
-        <v>16.0048</v>
+        <v>15.3173</v>
       </c>
       <c r="C138" t="n">
-        <v>11.9866</v>
+        <v>11.9515</v>
       </c>
       <c r="D138" t="n">
-        <v>50.7775</v>
+        <v>50.6597</v>
       </c>
       <c r="E138" t="n">
-        <v>13.753</v>
+        <v>14.0124</v>
       </c>
       <c r="F138" t="n">
-        <v>17.3528</v>
+        <v>17.3108</v>
       </c>
     </row>
     <row r="139">
@@ -7819,19 +7819,19 @@
         <v>7847143</v>
       </c>
       <c r="B139" t="n">
-        <v>16.2176</v>
+        <v>16.2821</v>
       </c>
       <c r="C139" t="n">
-        <v>12.0172</v>
+        <v>12.0352</v>
       </c>
       <c r="D139" t="n">
-        <v>52.0076</v>
+        <v>51.9395</v>
       </c>
       <c r="E139" t="n">
-        <v>13.8572</v>
+        <v>14.0827</v>
       </c>
       <c r="F139" t="n">
-        <v>17.6594</v>
+        <v>17.408</v>
       </c>
     </row>
     <row r="140">
@@ -7839,19 +7839,19 @@
         <v>8239431</v>
       </c>
       <c r="B140" t="n">
-        <v>16.3962</v>
+        <v>16.2785</v>
       </c>
       <c r="C140" t="n">
-        <v>12.0714</v>
+        <v>12.1552</v>
       </c>
       <c r="D140" t="n">
-        <v>53.3027</v>
+        <v>53.4021</v>
       </c>
       <c r="E140" t="n">
-        <v>14.1525</v>
+        <v>14.2759</v>
       </c>
       <c r="F140" t="n">
-        <v>18.4562</v>
+        <v>17.9274</v>
       </c>
     </row>
     <row r="141">
@@ -7859,19 +7859,19 @@
         <v>8651333</v>
       </c>
       <c r="B141" t="n">
-        <v>16.4133</v>
+        <v>16.6277</v>
       </c>
       <c r="C141" t="n">
-        <v>12.2891</v>
+        <v>12.3691</v>
       </c>
       <c r="D141" t="n">
-        <v>54.7281</v>
+        <v>54.6339</v>
       </c>
       <c r="E141" t="n">
-        <v>14.1254</v>
+        <v>14.5281</v>
       </c>
       <c r="F141" t="n">
-        <v>18.7639</v>
+        <v>18.3251</v>
       </c>
     </row>
     <row r="142">
@@ -7879,19 +7879,19 @@
         <v>9083830</v>
       </c>
       <c r="B142" t="n">
-        <v>16.6115</v>
+        <v>16.6936</v>
       </c>
       <c r="C142" t="n">
-        <v>12.3138</v>
+        <v>12.3571</v>
       </c>
       <c r="D142" t="n">
-        <v>55.9695</v>
+        <v>56.076</v>
       </c>
       <c r="E142" t="n">
-        <v>14.3606</v>
+        <v>14.0536</v>
       </c>
       <c r="F142" t="n">
-        <v>19.1444</v>
+        <v>19.227</v>
       </c>
     </row>
     <row r="143">
@@ -7899,19 +7899,19 @@
         <v>9537951</v>
       </c>
       <c r="B143" t="n">
-        <v>17.3885</v>
+        <v>17.1535</v>
       </c>
       <c r="C143" t="n">
-        <v>12.5624</v>
+        <v>12.5154</v>
       </c>
       <c r="D143" t="n">
-        <v>57.5385</v>
+        <v>57.5753</v>
       </c>
       <c r="E143" t="n">
-        <v>13.7003</v>
+        <v>14.8903</v>
       </c>
       <c r="F143" t="n">
-        <v>19.4934</v>
+        <v>18.885</v>
       </c>
     </row>
   </sheetData>

--- a/gcc-x64/Scattered unsuccessful looukp.xlsx
+++ b/gcc-x64/Scattered unsuccessful looukp.xlsx
@@ -5079,19 +5079,19 @@
         <v>10000</v>
       </c>
       <c r="B2" t="n">
-        <v>2.85805</v>
+        <v>2.86638</v>
       </c>
       <c r="C2" t="n">
-        <v>1.9131</v>
+        <v>1.90975</v>
       </c>
       <c r="D2" t="n">
-        <v>13.5088</v>
+        <v>13.5046</v>
       </c>
       <c r="E2" t="n">
-        <v>1.91123</v>
+        <v>1.90743</v>
       </c>
       <c r="F2" t="n">
-        <v>2.19815</v>
+        <v>2.2774</v>
       </c>
     </row>
     <row r="3">
@@ -5099,19 +5099,19 @@
         <v>10500</v>
       </c>
       <c r="B3" t="n">
-        <v>2.93976</v>
+        <v>2.92867</v>
       </c>
       <c r="C3" t="n">
-        <v>1.98459</v>
+        <v>1.97231</v>
       </c>
       <c r="D3" t="n">
-        <v>14.1054</v>
+        <v>14.6198</v>
       </c>
       <c r="E3" t="n">
-        <v>1.87887</v>
+        <v>1.6896</v>
       </c>
       <c r="F3" t="n">
-        <v>2.19482</v>
+        <v>2.2017</v>
       </c>
     </row>
     <row r="4">
@@ -5119,19 +5119,19 @@
         <v>11025</v>
       </c>
       <c r="B4" t="n">
-        <v>3.04741</v>
+        <v>3.0551</v>
       </c>
       <c r="C4" t="n">
-        <v>2.11401</v>
+        <v>2.11015</v>
       </c>
       <c r="D4" t="n">
-        <v>14.621</v>
+        <v>15.1528</v>
       </c>
       <c r="E4" t="n">
-        <v>1.69237</v>
+        <v>1.71729</v>
       </c>
       <c r="F4" t="n">
-        <v>2.08237</v>
+        <v>2.08846</v>
       </c>
     </row>
     <row r="5">
@@ -5139,19 +5139,19 @@
         <v>11576</v>
       </c>
       <c r="B5" t="n">
-        <v>3.38481</v>
+        <v>3.39846</v>
       </c>
       <c r="C5" t="n">
-        <v>2.25565</v>
+        <v>2.27133</v>
       </c>
       <c r="D5" t="n">
-        <v>15.1062</v>
+        <v>15.6332</v>
       </c>
       <c r="E5" t="n">
-        <v>1.74345</v>
+        <v>1.72986</v>
       </c>
       <c r="F5" t="n">
-        <v>2.17905</v>
+        <v>2.22046</v>
       </c>
     </row>
     <row r="6">
@@ -5159,19 +5159,19 @@
         <v>12154</v>
       </c>
       <c r="B6" t="n">
-        <v>4.26981</v>
+        <v>4.30285</v>
       </c>
       <c r="C6" t="n">
-        <v>2.91004</v>
+        <v>2.88305</v>
       </c>
       <c r="D6" t="n">
-        <v>15.8543</v>
+        <v>16.2875</v>
       </c>
       <c r="E6" t="n">
-        <v>1.78992</v>
+        <v>1.7909</v>
       </c>
       <c r="F6" t="n">
-        <v>2.16885</v>
+        <v>2.35325</v>
       </c>
     </row>
     <row r="7">
@@ -5179,19 +5179,19 @@
         <v>12760</v>
       </c>
       <c r="B7" t="n">
-        <v>6.56207</v>
+        <v>6.54301</v>
       </c>
       <c r="C7" t="n">
-        <v>4.98181</v>
+        <v>5.02181</v>
       </c>
       <c r="D7" t="n">
-        <v>10.9478</v>
+        <v>10.8617</v>
       </c>
       <c r="E7" t="n">
-        <v>1.85369</v>
+        <v>1.87067</v>
       </c>
       <c r="F7" t="n">
-        <v>2.07321</v>
+        <v>2.06586</v>
       </c>
     </row>
     <row r="8">
@@ -5199,19 +5199,19 @@
         <v>13396</v>
       </c>
       <c r="B8" t="n">
-        <v>9.38428</v>
+        <v>9.36591</v>
       </c>
       <c r="C8" t="n">
-        <v>1.76738</v>
+        <v>1.80678</v>
       </c>
       <c r="D8" t="n">
-        <v>11.557</v>
+        <v>11.5408</v>
       </c>
       <c r="E8" t="n">
-        <v>1.87547</v>
+        <v>1.89676</v>
       </c>
       <c r="F8" t="n">
-        <v>2.11091</v>
+        <v>2.10015</v>
       </c>
     </row>
     <row r="9">
@@ -5219,19 +5219,19 @@
         <v>14063</v>
       </c>
       <c r="B9" t="n">
-        <v>13.777</v>
+        <v>13.7354</v>
       </c>
       <c r="C9" t="n">
-        <v>1.96875</v>
+        <v>1.75708</v>
       </c>
       <c r="D9" t="n">
-        <v>12.0052</v>
+        <v>12.0462</v>
       </c>
       <c r="E9" t="n">
-        <v>1.88164</v>
+        <v>1.90602</v>
       </c>
       <c r="F9" t="n">
-        <v>2.10967</v>
+        <v>2.10541</v>
       </c>
     </row>
     <row r="10">
@@ -5239,19 +5239,19 @@
         <v>14763</v>
       </c>
       <c r="B10" t="n">
-        <v>2.80254</v>
+        <v>2.82113</v>
       </c>
       <c r="C10" t="n">
-        <v>2.00391</v>
+        <v>1.78179</v>
       </c>
       <c r="D10" t="n">
-        <v>12.8751</v>
+        <v>12.7965</v>
       </c>
       <c r="E10" t="n">
-        <v>1.8999</v>
+        <v>1.92241</v>
       </c>
       <c r="F10" t="n">
-        <v>2.13379</v>
+        <v>2.11967</v>
       </c>
     </row>
     <row r="11">
@@ -5259,19 +5259,19 @@
         <v>15498</v>
       </c>
       <c r="B11" t="n">
-        <v>2.83636</v>
+        <v>2.84464</v>
       </c>
       <c r="C11" t="n">
-        <v>1.87086</v>
+        <v>1.82451</v>
       </c>
       <c r="D11" t="n">
-        <v>13.314</v>
+        <v>13.2475</v>
       </c>
       <c r="E11" t="n">
-        <v>1.89938</v>
+        <v>1.94522</v>
       </c>
       <c r="F11" t="n">
-        <v>2.16441</v>
+        <v>2.15018</v>
       </c>
     </row>
     <row r="12">
@@ -5279,19 +5279,19 @@
         <v>16269</v>
       </c>
       <c r="B12" t="n">
-        <v>2.88237</v>
+        <v>2.89259</v>
       </c>
       <c r="C12" t="n">
-        <v>1.96771</v>
+        <v>1.85288</v>
       </c>
       <c r="D12" t="n">
-        <v>13.7952</v>
+        <v>13.7749</v>
       </c>
       <c r="E12" t="n">
-        <v>1.92569</v>
+        <v>1.94399</v>
       </c>
       <c r="F12" t="n">
-        <v>2.18551</v>
+        <v>2.19459</v>
       </c>
     </row>
     <row r="13">
@@ -5299,19 +5299,19 @@
         <v>17078</v>
       </c>
       <c r="B13" t="n">
-        <v>2.87698</v>
+        <v>2.8759</v>
       </c>
       <c r="C13" t="n">
-        <v>2.12388</v>
+        <v>1.9571</v>
       </c>
       <c r="D13" t="n">
-        <v>14.3543</v>
+        <v>14.2145</v>
       </c>
       <c r="E13" t="n">
-        <v>1.93423</v>
+        <v>1.94609</v>
       </c>
       <c r="F13" t="n">
-        <v>2.20577</v>
+        <v>2.20193</v>
       </c>
     </row>
     <row r="14">
@@ -5319,19 +5319,19 @@
         <v>17927</v>
       </c>
       <c r="B14" t="n">
-        <v>2.95349</v>
+        <v>2.95423</v>
       </c>
       <c r="C14" t="n">
-        <v>2.09884</v>
+        <v>1.98229</v>
       </c>
       <c r="D14" t="n">
-        <v>14.765</v>
+        <v>14.7003</v>
       </c>
       <c r="E14" t="n">
-        <v>1.9762</v>
+        <v>1.98225</v>
       </c>
       <c r="F14" t="n">
-        <v>2.25808</v>
+        <v>2.2175</v>
       </c>
     </row>
     <row r="15">
@@ -5339,19 +5339,19 @@
         <v>18818</v>
       </c>
       <c r="B15" t="n">
-        <v>3.04764</v>
+        <v>3.05046</v>
       </c>
       <c r="C15" t="n">
-        <v>2.20177</v>
+        <v>2.0724</v>
       </c>
       <c r="D15" t="n">
-        <v>15.2495</v>
+        <v>15.0647</v>
       </c>
       <c r="E15" t="n">
-        <v>1.97831</v>
+        <v>1.99938</v>
       </c>
       <c r="F15" t="n">
-        <v>2.22427</v>
+        <v>2.22366</v>
       </c>
     </row>
     <row r="16">
@@ -5359,19 +5359,19 @@
         <v>19753</v>
       </c>
       <c r="B16" t="n">
-        <v>3.09806</v>
+        <v>3.09498</v>
       </c>
       <c r="C16" t="n">
-        <v>2.20885</v>
+        <v>2.15673</v>
       </c>
       <c r="D16" t="n">
-        <v>15.6852</v>
+        <v>15.5196</v>
       </c>
       <c r="E16" t="n">
-        <v>2.01697</v>
+        <v>2.03492</v>
       </c>
       <c r="F16" t="n">
-        <v>2.29155</v>
+        <v>2.28424</v>
       </c>
     </row>
     <row r="17">
@@ -5379,19 +5379,19 @@
         <v>20734</v>
       </c>
       <c r="B17" t="n">
-        <v>3.27585</v>
+        <v>3.29386</v>
       </c>
       <c r="C17" t="n">
-        <v>2.27666</v>
+        <v>2.29879</v>
       </c>
       <c r="D17" t="n">
-        <v>16.1809</v>
+        <v>15.9741</v>
       </c>
       <c r="E17" t="n">
-        <v>2.05423</v>
+        <v>2.05923</v>
       </c>
       <c r="F17" t="n">
-        <v>2.37028</v>
+        <v>2.36111</v>
       </c>
     </row>
     <row r="18">
@@ -5399,19 +5399,19 @@
         <v>21764</v>
       </c>
       <c r="B18" t="n">
-        <v>3.65871</v>
+        <v>3.66504</v>
       </c>
       <c r="C18" t="n">
-        <v>2.49129</v>
+        <v>2.51968</v>
       </c>
       <c r="D18" t="n">
-        <v>16.5986</v>
+        <v>16.3434</v>
       </c>
       <c r="E18" t="n">
-        <v>2.02779</v>
+        <v>2.02495</v>
       </c>
       <c r="F18" t="n">
-        <v>2.38084</v>
+        <v>2.45057</v>
       </c>
     </row>
     <row r="19">
@@ -5419,19 +5419,19 @@
         <v>22845</v>
       </c>
       <c r="B19" t="n">
-        <v>4.18829</v>
+        <v>4.20317</v>
       </c>
       <c r="C19" t="n">
-        <v>3.17089</v>
+        <v>3.14208</v>
       </c>
       <c r="D19" t="n">
-        <v>17.0186</v>
+        <v>16.899</v>
       </c>
       <c r="E19" t="n">
-        <v>2.03395</v>
+        <v>2.08237</v>
       </c>
       <c r="F19" t="n">
-        <v>2.52107</v>
+        <v>2.56168</v>
       </c>
     </row>
     <row r="20">
@@ -5439,19 +5439,19 @@
         <v>23980</v>
       </c>
       <c r="B20" t="n">
-        <v>5.19716</v>
+        <v>5.18583</v>
       </c>
       <c r="C20" t="n">
-        <v>4.2765</v>
+        <v>4.23885</v>
       </c>
       <c r="D20" t="n">
-        <v>17.3435</v>
+        <v>17.2431</v>
       </c>
       <c r="E20" t="n">
-        <v>2.46426</v>
+        <v>2.48164</v>
       </c>
       <c r="F20" t="n">
-        <v>2.90528</v>
+        <v>2.95889</v>
       </c>
     </row>
     <row r="21">
@@ -5459,19 +5459,19 @@
         <v>25171</v>
       </c>
       <c r="B21" t="n">
-        <v>6.83902</v>
+        <v>6.81488</v>
       </c>
       <c r="C21" t="n">
-        <v>5.56934</v>
+        <v>5.52376</v>
       </c>
       <c r="D21" t="n">
-        <v>12.2358</v>
+        <v>12.1991</v>
       </c>
       <c r="E21" t="n">
-        <v>1.96734</v>
+        <v>1.96729</v>
       </c>
       <c r="F21" t="n">
-        <v>2.18788</v>
+        <v>2.22953</v>
       </c>
     </row>
     <row r="22">
@@ -5479,19 +5479,19 @@
         <v>26421</v>
       </c>
       <c r="B22" t="n">
-        <v>9.04978</v>
+        <v>9.049110000000001</v>
       </c>
       <c r="C22" t="n">
-        <v>2.04653</v>
+        <v>1.83786</v>
       </c>
       <c r="D22" t="n">
-        <v>12.7068</v>
+        <v>12.6571</v>
       </c>
       <c r="E22" t="n">
-        <v>1.98631</v>
+        <v>1.99684</v>
       </c>
       <c r="F22" t="n">
-        <v>2.21886</v>
+        <v>2.26061</v>
       </c>
     </row>
     <row r="23">
@@ -5499,19 +5499,19 @@
         <v>27733</v>
       </c>
       <c r="B23" t="n">
-        <v>12.3642</v>
+        <v>12.4009</v>
       </c>
       <c r="C23" t="n">
-        <v>1.86508</v>
+        <v>1.86588</v>
       </c>
       <c r="D23" t="n">
-        <v>13.1993</v>
+        <v>13.1636</v>
       </c>
       <c r="E23" t="n">
-        <v>2.01448</v>
+        <v>2.00574</v>
       </c>
       <c r="F23" t="n">
-        <v>2.25764</v>
+        <v>2.30373</v>
       </c>
     </row>
     <row r="24">
@@ -5519,19 +5519,19 @@
         <v>29110</v>
       </c>
       <c r="B24" t="n">
-        <v>2.89462</v>
+        <v>2.91145</v>
       </c>
       <c r="C24" t="n">
-        <v>1.85607</v>
+        <v>1.85616</v>
       </c>
       <c r="D24" t="n">
-        <v>13.7684</v>
+        <v>13.7301</v>
       </c>
       <c r="E24" t="n">
-        <v>2.02814</v>
+        <v>2.04901</v>
       </c>
       <c r="F24" t="n">
-        <v>2.28173</v>
+        <v>2.34804</v>
       </c>
     </row>
     <row r="25">
@@ -5539,19 +5539,19 @@
         <v>30555</v>
       </c>
       <c r="B25" t="n">
-        <v>2.92092</v>
+        <v>2.92931</v>
       </c>
       <c r="C25" t="n">
-        <v>1.89217</v>
+        <v>1.91291</v>
       </c>
       <c r="D25" t="n">
-        <v>14.2503</v>
+        <v>14.2266</v>
       </c>
       <c r="E25" t="n">
-        <v>2.04968</v>
+        <v>2.0673</v>
       </c>
       <c r="F25" t="n">
-        <v>2.31336</v>
+        <v>2.367</v>
       </c>
     </row>
     <row r="26">
@@ -5559,19 +5559,19 @@
         <v>32072</v>
       </c>
       <c r="B26" t="n">
-        <v>3.00854</v>
+        <v>3.0215</v>
       </c>
       <c r="C26" t="n">
-        <v>1.90649</v>
+        <v>1.91836</v>
       </c>
       <c r="D26" t="n">
-        <v>14.6985</v>
+        <v>14.6686</v>
       </c>
       <c r="E26" t="n">
-        <v>2.07397</v>
+        <v>2.08059</v>
       </c>
       <c r="F26" t="n">
-        <v>2.36215</v>
+        <v>2.40658</v>
       </c>
     </row>
     <row r="27">
@@ -5579,19 +5579,19 @@
         <v>33664</v>
       </c>
       <c r="B27" t="n">
-        <v>3.08245</v>
+        <v>3.08959</v>
       </c>
       <c r="C27" t="n">
-        <v>1.98796</v>
+        <v>1.99078</v>
       </c>
       <c r="D27" t="n">
-        <v>15.2121</v>
+        <v>15.165</v>
       </c>
       <c r="E27" t="n">
-        <v>2.09307</v>
+        <v>2.11749</v>
       </c>
       <c r="F27" t="n">
-        <v>2.41527</v>
+        <v>2.42516</v>
       </c>
     </row>
     <row r="28">
@@ -5599,19 +5599,19 @@
         <v>35335</v>
       </c>
       <c r="B28" t="n">
-        <v>3.1426</v>
+        <v>3.15384</v>
       </c>
       <c r="C28" t="n">
-        <v>1.99711</v>
+        <v>2.05129</v>
       </c>
       <c r="D28" t="n">
-        <v>15.6545</v>
+        <v>15.6134</v>
       </c>
       <c r="E28" t="n">
-        <v>2.12708</v>
+        <v>2.13748</v>
       </c>
       <c r="F28" t="n">
-        <v>2.44017</v>
+        <v>2.49253</v>
       </c>
     </row>
     <row r="29">
@@ -5619,19 +5619,19 @@
         <v>37089</v>
       </c>
       <c r="B29" t="n">
-        <v>3.28479</v>
+        <v>3.29915</v>
       </c>
       <c r="C29" t="n">
-        <v>2.13781</v>
+        <v>2.15807</v>
       </c>
       <c r="D29" t="n">
-        <v>16.1942</v>
+        <v>16.1341</v>
       </c>
       <c r="E29" t="n">
-        <v>2.18381</v>
+        <v>2.18256</v>
       </c>
       <c r="F29" t="n">
-        <v>2.51882</v>
+        <v>2.54832</v>
       </c>
     </row>
     <row r="30">
@@ -5639,19 +5639,19 @@
         <v>38930</v>
       </c>
       <c r="B30" t="n">
-        <v>3.44698</v>
+        <v>3.45547</v>
       </c>
       <c r="C30" t="n">
-        <v>2.24453</v>
+        <v>2.25205</v>
       </c>
       <c r="D30" t="n">
-        <v>16.6421</v>
+        <v>16.6485</v>
       </c>
       <c r="E30" t="n">
-        <v>2.21863</v>
+        <v>2.23083</v>
       </c>
       <c r="F30" t="n">
-        <v>2.57078</v>
+        <v>2.60007</v>
       </c>
     </row>
     <row r="31">
@@ -5659,19 +5659,19 @@
         <v>40863</v>
       </c>
       <c r="B31" t="n">
-        <v>3.67232</v>
+        <v>3.67626</v>
       </c>
       <c r="C31" t="n">
-        <v>2.43953</v>
+        <v>2.45704</v>
       </c>
       <c r="D31" t="n">
-        <v>17.0691</v>
+        <v>17.0362</v>
       </c>
       <c r="E31" t="n">
-        <v>2.22881</v>
+        <v>2.2555</v>
       </c>
       <c r="F31" t="n">
-        <v>2.6406</v>
+        <v>2.65153</v>
       </c>
     </row>
     <row r="32">
@@ -5679,19 +5679,19 @@
         <v>42892</v>
       </c>
       <c r="B32" t="n">
-        <v>4.0301</v>
+        <v>4.03898</v>
       </c>
       <c r="C32" t="n">
-        <v>2.71481</v>
+        <v>2.7225</v>
       </c>
       <c r="D32" t="n">
-        <v>17.405</v>
+        <v>17.4052</v>
       </c>
       <c r="E32" t="n">
-        <v>2.30705</v>
+        <v>2.32736</v>
       </c>
       <c r="F32" t="n">
-        <v>2.77283</v>
+        <v>2.81752</v>
       </c>
     </row>
     <row r="33">
@@ -5699,19 +5699,19 @@
         <v>45022</v>
       </c>
       <c r="B33" t="n">
-        <v>4.68498</v>
+        <v>4.68842</v>
       </c>
       <c r="C33" t="n">
-        <v>3.29378</v>
+        <v>3.29742</v>
       </c>
       <c r="D33" t="n">
-        <v>17.8409</v>
+        <v>17.8782</v>
       </c>
       <c r="E33" t="n">
-        <v>2.49208</v>
+        <v>2.50001</v>
       </c>
       <c r="F33" t="n">
-        <v>2.97576</v>
+        <v>3.00464</v>
       </c>
     </row>
     <row r="34">
@@ -5719,19 +5719,19 @@
         <v>47258</v>
       </c>
       <c r="B34" t="n">
-        <v>5.61765</v>
+        <v>5.62206</v>
       </c>
       <c r="C34" t="n">
-        <v>4.15225</v>
+        <v>4.15639</v>
       </c>
       <c r="D34" t="n">
-        <v>18.3396</v>
+        <v>18.316</v>
       </c>
       <c r="E34" t="n">
-        <v>3.01095</v>
+        <v>2.99022</v>
       </c>
       <c r="F34" t="n">
-        <v>3.45284</v>
+        <v>3.461</v>
       </c>
     </row>
     <row r="35">
@@ -5739,19 +5739,19 @@
         <v>49605</v>
       </c>
       <c r="B35" t="n">
-        <v>7.1033</v>
+        <v>7.11954</v>
       </c>
       <c r="C35" t="n">
-        <v>5.3025</v>
+        <v>5.31407</v>
       </c>
       <c r="D35" t="n">
-        <v>12.7662</v>
+        <v>12.7111</v>
       </c>
       <c r="E35" t="n">
-        <v>2.01094</v>
+        <v>2.01606</v>
       </c>
       <c r="F35" t="n">
-        <v>2.36682</v>
+        <v>2.35636</v>
       </c>
     </row>
     <row r="36">
@@ -5759,19 +5759,19 @@
         <v>52069</v>
       </c>
       <c r="B36" t="n">
-        <v>9.232329999999999</v>
+        <v>9.24966</v>
       </c>
       <c r="C36" t="n">
-        <v>6.94133</v>
+        <v>6.93132</v>
       </c>
       <c r="D36" t="n">
-        <v>13.1898</v>
+        <v>13.1482</v>
       </c>
       <c r="E36" t="n">
-        <v>2.03386</v>
+        <v>2.04735</v>
       </c>
       <c r="F36" t="n">
-        <v>2.39634</v>
+        <v>2.39607</v>
       </c>
     </row>
     <row r="37">
@@ -5779,19 +5779,19 @@
         <v>54656</v>
       </c>
       <c r="B37" t="n">
-        <v>12.9994</v>
+        <v>12.8395</v>
       </c>
       <c r="C37" t="n">
-        <v>1.88649</v>
+        <v>1.85652</v>
       </c>
       <c r="D37" t="n">
-        <v>13.6794</v>
+        <v>13.6307</v>
       </c>
       <c r="E37" t="n">
-        <v>2.0567</v>
+        <v>2.08165</v>
       </c>
       <c r="F37" t="n">
-        <v>2.41028</v>
+        <v>2.42738</v>
       </c>
     </row>
     <row r="38">
@@ -5799,19 +5799,19 @@
         <v>57372</v>
       </c>
       <c r="B38" t="n">
-        <v>2.97112</v>
+        <v>2.98254</v>
       </c>
       <c r="C38" t="n">
-        <v>1.94329</v>
+        <v>1.93045</v>
       </c>
       <c r="D38" t="n">
-        <v>14.232</v>
+        <v>14.188</v>
       </c>
       <c r="E38" t="n">
-        <v>2.0805</v>
+        <v>2.09815</v>
       </c>
       <c r="F38" t="n">
-        <v>2.4691</v>
+        <v>2.48381</v>
       </c>
     </row>
     <row r="39">
@@ -5819,19 +5819,19 @@
         <v>60223</v>
       </c>
       <c r="B39" t="n">
-        <v>2.99038</v>
+        <v>3.01594</v>
       </c>
       <c r="C39" t="n">
-        <v>1.91511</v>
+        <v>1.90983</v>
       </c>
       <c r="D39" t="n">
-        <v>14.7283</v>
+        <v>14.6891</v>
       </c>
       <c r="E39" t="n">
-        <v>2.11695</v>
+        <v>2.11825</v>
       </c>
       <c r="F39" t="n">
-        <v>2.52009</v>
+        <v>2.51652</v>
       </c>
     </row>
     <row r="40">
@@ -5839,19 +5839,19 @@
         <v>63216</v>
       </c>
       <c r="B40" t="n">
-        <v>3.06645</v>
+        <v>3.08355</v>
       </c>
       <c r="C40" t="n">
-        <v>1.98065</v>
+        <v>1.98962</v>
       </c>
       <c r="D40" t="n">
-        <v>15.247</v>
+        <v>15.208</v>
       </c>
       <c r="E40" t="n">
-        <v>2.12972</v>
+        <v>2.15995</v>
       </c>
       <c r="F40" t="n">
-        <v>2.56587</v>
+        <v>2.59043</v>
       </c>
     </row>
     <row r="41">
@@ -5859,19 +5859,19 @@
         <v>66358</v>
       </c>
       <c r="B41" t="n">
-        <v>3.14517</v>
+        <v>3.1618</v>
       </c>
       <c r="C41" t="n">
-        <v>2.04493</v>
+        <v>2.01837</v>
       </c>
       <c r="D41" t="n">
-        <v>15.7212</v>
+        <v>15.6772</v>
       </c>
       <c r="E41" t="n">
-        <v>2.16943</v>
+        <v>2.18543</v>
       </c>
       <c r="F41" t="n">
-        <v>2.62016</v>
+        <v>2.62766</v>
       </c>
     </row>
     <row r="42">
@@ -5879,19 +5879,19 @@
         <v>69657</v>
       </c>
       <c r="B42" t="n">
-        <v>3.19637</v>
+        <v>3.20413</v>
       </c>
       <c r="C42" t="n">
-        <v>2.09403</v>
+        <v>2.10664</v>
       </c>
       <c r="D42" t="n">
-        <v>16.1792</v>
+        <v>16.1483</v>
       </c>
       <c r="E42" t="n">
-        <v>2.2136</v>
+        <v>2.20405</v>
       </c>
       <c r="F42" t="n">
-        <v>2.69106</v>
+        <v>2.68186</v>
       </c>
     </row>
     <row r="43">
@@ -5899,19 +5899,19 @@
         <v>73120</v>
       </c>
       <c r="B43" t="n">
-        <v>3.33756</v>
+        <v>3.34408</v>
       </c>
       <c r="C43" t="n">
-        <v>2.18761</v>
+        <v>2.15448</v>
       </c>
       <c r="D43" t="n">
-        <v>16.6596</v>
+        <v>16.6354</v>
       </c>
       <c r="E43" t="n">
-        <v>2.25526</v>
+        <v>2.27</v>
       </c>
       <c r="F43" t="n">
-        <v>2.75702</v>
+        <v>2.76205</v>
       </c>
     </row>
     <row r="44">
@@ -5919,19 +5919,19 @@
         <v>76756</v>
       </c>
       <c r="B44" t="n">
-        <v>3.50219</v>
+        <v>3.5113</v>
       </c>
       <c r="C44" t="n">
-        <v>2.32236</v>
+        <v>2.30697</v>
       </c>
       <c r="D44" t="n">
-        <v>17.0385</v>
+        <v>17.0128</v>
       </c>
       <c r="E44" t="n">
-        <v>2.33668</v>
+        <v>2.35591</v>
       </c>
       <c r="F44" t="n">
-        <v>2.85428</v>
+        <v>2.85219</v>
       </c>
     </row>
     <row r="45">
@@ -5939,19 +5939,19 @@
         <v>80573</v>
       </c>
       <c r="B45" t="n">
-        <v>3.73762</v>
+        <v>3.75112</v>
       </c>
       <c r="C45" t="n">
-        <v>2.55182</v>
+        <v>2.56761</v>
       </c>
       <c r="D45" t="n">
-        <v>17.4769</v>
+        <v>17.4295</v>
       </c>
       <c r="E45" t="n">
-        <v>2.44703</v>
+        <v>2.43843</v>
       </c>
       <c r="F45" t="n">
-        <v>2.97428</v>
+        <v>2.96913</v>
       </c>
     </row>
     <row r="46">
@@ -5959,19 +5959,19 @@
         <v>84580</v>
       </c>
       <c r="B46" t="n">
-        <v>4.07668</v>
+        <v>4.09229</v>
       </c>
       <c r="C46" t="n">
-        <v>2.88874</v>
+        <v>2.8731</v>
       </c>
       <c r="D46" t="n">
-        <v>17.872</v>
+        <v>17.8264</v>
       </c>
       <c r="E46" t="n">
-        <v>2.60989</v>
+        <v>2.58511</v>
       </c>
       <c r="F46" t="n">
-        <v>3.12263</v>
+        <v>3.10603</v>
       </c>
     </row>
     <row r="47">
@@ -5979,19 +5979,19 @@
         <v>88787</v>
       </c>
       <c r="B47" t="n">
-        <v>4.63613</v>
+        <v>4.65031</v>
       </c>
       <c r="C47" t="n">
-        <v>3.38231</v>
+        <v>3.36215</v>
       </c>
       <c r="D47" t="n">
-        <v>18.3408</v>
+        <v>18.2258</v>
       </c>
       <c r="E47" t="n">
-        <v>2.85319</v>
+        <v>2.83485</v>
       </c>
       <c r="F47" t="n">
-        <v>3.37616</v>
+        <v>3.37364</v>
       </c>
     </row>
     <row r="48">
@@ -5999,19 +5999,19 @@
         <v>93204</v>
       </c>
       <c r="B48" t="n">
-        <v>5.39023</v>
+        <v>5.38192</v>
       </c>
       <c r="C48" t="n">
-        <v>4.04102</v>
+        <v>4.05093</v>
       </c>
       <c r="D48" t="n">
-        <v>18.7361</v>
+        <v>18.7116</v>
       </c>
       <c r="E48" t="n">
-        <v>3.23855</v>
+        <v>3.23673</v>
       </c>
       <c r="F48" t="n">
-        <v>3.74799</v>
+        <v>3.74325</v>
       </c>
     </row>
     <row r="49">
@@ -6019,19 +6019,19 @@
         <v>97841</v>
       </c>
       <c r="B49" t="n">
-        <v>6.46372</v>
+        <v>6.46965</v>
       </c>
       <c r="C49" t="n">
-        <v>5.01431</v>
+        <v>5.02854</v>
       </c>
       <c r="D49" t="n">
-        <v>19.2215</v>
+        <v>19.1714</v>
       </c>
       <c r="E49" t="n">
-        <v>3.74313</v>
+        <v>3.73812</v>
       </c>
       <c r="F49" t="n">
-        <v>4.23356</v>
+        <v>4.24093</v>
       </c>
     </row>
     <row r="50">
@@ -6039,19 +6039,19 @@
         <v>102709</v>
       </c>
       <c r="B50" t="n">
-        <v>8.325469999999999</v>
+        <v>8.31686</v>
       </c>
       <c r="C50" t="n">
-        <v>6.481</v>
+        <v>6.48365</v>
       </c>
       <c r="D50" t="n">
-        <v>13.4474</v>
+        <v>13.4513</v>
       </c>
       <c r="E50" t="n">
-        <v>2.16237</v>
+        <v>2.21203</v>
       </c>
       <c r="F50" t="n">
-        <v>2.7392</v>
+        <v>2.67285</v>
       </c>
     </row>
     <row r="51">
@@ -6059,19 +6059,19 @@
         <v>107820</v>
       </c>
       <c r="B51" t="n">
-        <v>10.8793</v>
+        <v>10.8707</v>
       </c>
       <c r="C51" t="n">
-        <v>1.89806</v>
+        <v>1.94565</v>
       </c>
       <c r="D51" t="n">
-        <v>13.9514</v>
+        <v>13.9347</v>
       </c>
       <c r="E51" t="n">
-        <v>2.17814</v>
+        <v>2.23265</v>
       </c>
       <c r="F51" t="n">
-        <v>2.75269</v>
+        <v>2.69375</v>
       </c>
     </row>
     <row r="52">
@@ -6079,19 +6079,19 @@
         <v>113186</v>
       </c>
       <c r="B52" t="n">
-        <v>15.3239</v>
+        <v>15.3281</v>
       </c>
       <c r="C52" t="n">
-        <v>2.18614</v>
+        <v>2.01914</v>
       </c>
       <c r="D52" t="n">
-        <v>14.4212</v>
+        <v>14.4196</v>
       </c>
       <c r="E52" t="n">
-        <v>2.20852</v>
+        <v>2.26012</v>
       </c>
       <c r="F52" t="n">
-        <v>2.82928</v>
+        <v>2.7701</v>
       </c>
     </row>
     <row r="53">
@@ -6099,19 +6099,19 @@
         <v>118820</v>
       </c>
       <c r="B53" t="n">
-        <v>3.10359</v>
+        <v>3.12278</v>
       </c>
       <c r="C53" t="n">
-        <v>2.02442</v>
+        <v>2.0871</v>
       </c>
       <c r="D53" t="n">
-        <v>14.9097</v>
+        <v>14.9054</v>
       </c>
       <c r="E53" t="n">
-        <v>2.24132</v>
+        <v>2.29086</v>
       </c>
       <c r="F53" t="n">
-        <v>2.86427</v>
+        <v>2.79841</v>
       </c>
     </row>
     <row r="54">
@@ -6119,19 +6119,19 @@
         <v>124735</v>
       </c>
       <c r="B54" t="n">
-        <v>3.18381</v>
+        <v>3.18366</v>
       </c>
       <c r="C54" t="n">
-        <v>2.11895</v>
+        <v>2.4418</v>
       </c>
       <c r="D54" t="n">
-        <v>15.4228</v>
+        <v>15.4057</v>
       </c>
       <c r="E54" t="n">
-        <v>2.37638</v>
+        <v>2.84385</v>
       </c>
       <c r="F54" t="n">
-        <v>2.91871</v>
+        <v>2.86299</v>
       </c>
     </row>
     <row r="55">
@@ -6139,19 +6139,19 @@
         <v>130945</v>
       </c>
       <c r="B55" t="n">
-        <v>3.25549</v>
+        <v>3.24894</v>
       </c>
       <c r="C55" t="n">
-        <v>2.06465</v>
+        <v>2.59577</v>
       </c>
       <c r="D55" t="n">
-        <v>15.8935</v>
+        <v>15.8769</v>
       </c>
       <c r="E55" t="n">
-        <v>2.45521</v>
+        <v>2.43207</v>
       </c>
       <c r="F55" t="n">
-        <v>2.92702</v>
+        <v>2.96339</v>
       </c>
     </row>
     <row r="56">
@@ -6159,19 +6159,19 @@
         <v>137465</v>
       </c>
       <c r="B56" t="n">
-        <v>3.33362</v>
+        <v>3.35663</v>
       </c>
       <c r="C56" t="n">
-        <v>2.37829</v>
+        <v>2.18978</v>
       </c>
       <c r="D56" t="n">
-        <v>16.361</v>
+        <v>16.3379</v>
       </c>
       <c r="E56" t="n">
-        <v>2.50479</v>
+        <v>2.48169</v>
       </c>
       <c r="F56" t="n">
-        <v>2.98462</v>
+        <v>3.02248</v>
       </c>
     </row>
     <row r="57">
@@ -6179,19 +6179,19 @@
         <v>144311</v>
       </c>
       <c r="B57" t="n">
-        <v>3.47522</v>
+        <v>3.46171</v>
       </c>
       <c r="C57" t="n">
-        <v>2.31285</v>
+        <v>2.49035</v>
       </c>
       <c r="D57" t="n">
-        <v>16.7989</v>
+        <v>16.8027</v>
       </c>
       <c r="E57" t="n">
-        <v>2.5191</v>
+        <v>3.00042</v>
       </c>
       <c r="F57" t="n">
-        <v>3.11328</v>
+        <v>3.02274</v>
       </c>
     </row>
     <row r="58">
@@ -6199,19 +6199,19 @@
         <v>151499</v>
       </c>
       <c r="B58" t="n">
-        <v>3.6175</v>
+        <v>3.6389</v>
       </c>
       <c r="C58" t="n">
-        <v>2.47121</v>
+        <v>2.40216</v>
       </c>
       <c r="D58" t="n">
-        <v>17.2414</v>
+        <v>17.2179</v>
       </c>
       <c r="E58" t="n">
-        <v>2.5936</v>
+        <v>3.01407</v>
       </c>
       <c r="F58" t="n">
-        <v>3.43809</v>
+        <v>3.11198</v>
       </c>
     </row>
     <row r="59">
@@ -6219,19 +6219,19 @@
         <v>159046</v>
       </c>
       <c r="B59" t="n">
-        <v>3.84453</v>
+        <v>3.84817</v>
       </c>
       <c r="C59" t="n">
-        <v>2.70442</v>
+        <v>2.80028</v>
       </c>
       <c r="D59" t="n">
-        <v>17.6423</v>
+        <v>17.643</v>
       </c>
       <c r="E59" t="n">
-        <v>2.76591</v>
+        <v>3.14569</v>
       </c>
       <c r="F59" t="n">
-        <v>3.2011</v>
+        <v>3.22606</v>
       </c>
     </row>
     <row r="60">
@@ -6239,19 +6239,19 @@
         <v>166970</v>
       </c>
       <c r="B60" t="n">
-        <v>4.29233</v>
+        <v>4.21935</v>
       </c>
       <c r="C60" t="n">
-        <v>2.98592</v>
+        <v>3.39407</v>
       </c>
       <c r="D60" t="n">
-        <v>18.0714</v>
+        <v>18.0301</v>
       </c>
       <c r="E60" t="n">
-        <v>2.84677</v>
+        <v>3.26657</v>
       </c>
       <c r="F60" t="n">
-        <v>3.37714</v>
+        <v>3.36713</v>
       </c>
     </row>
     <row r="61">
@@ -6259,19 +6259,19 @@
         <v>175290</v>
       </c>
       <c r="B61" t="n">
-        <v>4.56428</v>
+        <v>4.58273</v>
       </c>
       <c r="C61" t="n">
-        <v>3.24358</v>
+        <v>3.28212</v>
       </c>
       <c r="D61" t="n">
-        <v>18.484</v>
+        <v>18.4575</v>
       </c>
       <c r="E61" t="n">
-        <v>3.0126</v>
+        <v>3.11946</v>
       </c>
       <c r="F61" t="n">
-        <v>3.58575</v>
+        <v>3.54672</v>
       </c>
     </row>
     <row r="62">
@@ -6279,19 +6279,19 @@
         <v>184026</v>
       </c>
       <c r="B62" t="n">
-        <v>5.27995</v>
+        <v>5.24231</v>
       </c>
       <c r="C62" t="n">
-        <v>3.86616</v>
+        <v>3.93103</v>
       </c>
       <c r="D62" t="n">
-        <v>18.9433</v>
+        <v>18.8874</v>
       </c>
       <c r="E62" t="n">
-        <v>3.29406</v>
+        <v>3.39674</v>
       </c>
       <c r="F62" t="n">
-        <v>3.84584</v>
+        <v>3.88994</v>
       </c>
     </row>
     <row r="63">
@@ -6299,19 +6299,19 @@
         <v>193198</v>
       </c>
       <c r="B63" t="n">
-        <v>6.37724</v>
+        <v>6.30964</v>
       </c>
       <c r="C63" t="n">
-        <v>4.78795</v>
+        <v>4.84138</v>
       </c>
       <c r="D63" t="n">
-        <v>19.4141</v>
+        <v>19.3338</v>
       </c>
       <c r="E63" t="n">
-        <v>3.74069</v>
+        <v>3.83657</v>
       </c>
       <c r="F63" t="n">
-        <v>4.27105</v>
+        <v>4.30419</v>
       </c>
     </row>
     <row r="64">
@@ -6319,19 +6319,19 @@
         <v>202828</v>
       </c>
       <c r="B64" t="n">
-        <v>7.86219</v>
+        <v>7.86861</v>
       </c>
       <c r="C64" t="n">
-        <v>6.26074</v>
+        <v>6.13655</v>
       </c>
       <c r="D64" t="n">
-        <v>14.2384</v>
+        <v>14.7269</v>
       </c>
       <c r="E64" t="n">
-        <v>2.61926</v>
+        <v>2.68888</v>
       </c>
       <c r="F64" t="n">
-        <v>3.21096</v>
+        <v>3.39699</v>
       </c>
     </row>
     <row r="65">
@@ -6339,19 +6339,19 @@
         <v>212939</v>
       </c>
       <c r="B65" t="n">
-        <v>10.4792</v>
+        <v>10.5012</v>
       </c>
       <c r="C65" t="n">
-        <v>2.2782</v>
+        <v>2.2951</v>
       </c>
       <c r="D65" t="n">
-        <v>14.8076</v>
+        <v>15.2098</v>
       </c>
       <c r="E65" t="n">
-        <v>2.70118</v>
+        <v>2.71229</v>
       </c>
       <c r="F65" t="n">
-        <v>3.25998</v>
+        <v>3.45298</v>
       </c>
     </row>
     <row r="66">
@@ -6359,19 +6359,19 @@
         <v>223555</v>
       </c>
       <c r="B66" t="n">
-        <v>14.3842</v>
+        <v>14.3979</v>
       </c>
       <c r="C66" t="n">
-        <v>2.29818</v>
+        <v>2.29165</v>
       </c>
       <c r="D66" t="n">
-        <v>15.5864</v>
+        <v>15.9588</v>
       </c>
       <c r="E66" t="n">
-        <v>2.67624</v>
+        <v>2.65531</v>
       </c>
       <c r="F66" t="n">
-        <v>3.30895</v>
+        <v>3.50981</v>
       </c>
     </row>
     <row r="67">
@@ -6379,19 +6379,19 @@
         <v>234701</v>
       </c>
       <c r="B67" t="n">
-        <v>3.49844</v>
+        <v>3.94676</v>
       </c>
       <c r="C67" t="n">
-        <v>2.32438</v>
+        <v>2.31621</v>
       </c>
       <c r="D67" t="n">
-        <v>16.3161</v>
+        <v>16.8297</v>
       </c>
       <c r="E67" t="n">
-        <v>2.75553</v>
+        <v>2.71183</v>
       </c>
       <c r="F67" t="n">
-        <v>3.36228</v>
+        <v>3.57125</v>
       </c>
     </row>
     <row r="68">
@@ -6399,19 +6399,19 @@
         <v>246404</v>
       </c>
       <c r="B68" t="n">
-        <v>3.58959</v>
+        <v>4.01886</v>
       </c>
       <c r="C68" t="n">
-        <v>2.35273</v>
+        <v>2.35053</v>
       </c>
       <c r="D68" t="n">
-        <v>17.2378</v>
+        <v>17.682</v>
       </c>
       <c r="E68" t="n">
-        <v>2.75177</v>
+        <v>2.76169</v>
       </c>
       <c r="F68" t="n">
-        <v>3.42765</v>
+        <v>3.628</v>
       </c>
     </row>
     <row r="69">
@@ -6419,19 +6419,19 @@
         <v>258692</v>
       </c>
       <c r="B69" t="n">
-        <v>3.63583</v>
+        <v>3.78118</v>
       </c>
       <c r="C69" t="n">
-        <v>2.65293</v>
+        <v>2.43806</v>
       </c>
       <c r="D69" t="n">
-        <v>17.9832</v>
+        <v>18.5225</v>
       </c>
       <c r="E69" t="n">
-        <v>2.77647</v>
+        <v>2.7823</v>
       </c>
       <c r="F69" t="n">
-        <v>3.5007</v>
+        <v>3.70297</v>
       </c>
     </row>
     <row r="70">
@@ -6439,19 +6439,19 @@
         <v>271594</v>
       </c>
       <c r="B70" t="n">
-        <v>3.7252</v>
+        <v>4.18934</v>
       </c>
       <c r="C70" t="n">
-        <v>2.47922</v>
+        <v>2.50811</v>
       </c>
       <c r="D70" t="n">
-        <v>18.9354</v>
+        <v>19.7324</v>
       </c>
       <c r="E70" t="n">
-        <v>2.81943</v>
+        <v>2.89094</v>
       </c>
       <c r="F70" t="n">
-        <v>3.56418</v>
+        <v>3.78343</v>
       </c>
     </row>
     <row r="71">
@@ -6459,19 +6459,19 @@
         <v>285141</v>
       </c>
       <c r="B71" t="n">
-        <v>3.86965</v>
+        <v>3.93956</v>
       </c>
       <c r="C71" t="n">
-        <v>2.55893</v>
+        <v>2.64543</v>
       </c>
       <c r="D71" t="n">
-        <v>19.8558</v>
+        <v>21.4593</v>
       </c>
       <c r="E71" t="n">
-        <v>2.89536</v>
+        <v>2.92271</v>
       </c>
       <c r="F71" t="n">
-        <v>3.64597</v>
+        <v>3.77366</v>
       </c>
     </row>
     <row r="72">
@@ -6479,19 +6479,19 @@
         <v>299365</v>
       </c>
       <c r="B72" t="n">
-        <v>4.03881</v>
+        <v>4.14687</v>
       </c>
       <c r="C72" t="n">
-        <v>2.86006</v>
+        <v>2.69165</v>
       </c>
       <c r="D72" t="n">
-        <v>20.912</v>
+        <v>23.2299</v>
       </c>
       <c r="E72" t="n">
-        <v>2.98306</v>
+        <v>3.00203</v>
       </c>
       <c r="F72" t="n">
-        <v>3.74536</v>
+        <v>3.87267</v>
       </c>
     </row>
     <row r="73">
@@ -6499,19 +6499,19 @@
         <v>314300</v>
       </c>
       <c r="B73" t="n">
-        <v>4.24843</v>
+        <v>4.69588</v>
       </c>
       <c r="C73" t="n">
-        <v>2.88682</v>
+        <v>2.91721</v>
       </c>
       <c r="D73" t="n">
-        <v>21.9696</v>
+        <v>25.0733</v>
       </c>
       <c r="E73" t="n">
-        <v>3.08682</v>
+        <v>3.09385</v>
       </c>
       <c r="F73" t="n">
-        <v>3.87058</v>
+        <v>3.9979</v>
       </c>
     </row>
     <row r="74">
@@ -6519,19 +6519,19 @@
         <v>329981</v>
       </c>
       <c r="B74" t="n">
-        <v>4.51745</v>
+        <v>4.65724</v>
       </c>
       <c r="C74" t="n">
-        <v>3.1331</v>
+        <v>3.25376</v>
       </c>
       <c r="D74" t="n">
-        <v>23.1803</v>
+        <v>26.1561</v>
       </c>
       <c r="E74" t="n">
-        <v>3.43388</v>
+        <v>3.19621</v>
       </c>
       <c r="F74" t="n">
-        <v>4.04167</v>
+        <v>4.13114</v>
       </c>
     </row>
     <row r="75">
@@ -6539,19 +6539,19 @@
         <v>346446</v>
       </c>
       <c r="B75" t="n">
-        <v>5.0393</v>
+        <v>4.95577</v>
       </c>
       <c r="C75" t="n">
-        <v>3.95962</v>
+        <v>3.55308</v>
       </c>
       <c r="D75" t="n">
-        <v>24.6029</v>
+        <v>26.8816</v>
       </c>
       <c r="E75" t="n">
-        <v>3.81609</v>
+        <v>3.4121</v>
       </c>
       <c r="F75" t="n">
-        <v>4.30113</v>
+        <v>4.3879</v>
       </c>
     </row>
     <row r="76">
@@ -6559,19 +6559,19 @@
         <v>363734</v>
       </c>
       <c r="B76" t="n">
-        <v>5.71703</v>
+        <v>5.51437</v>
       </c>
       <c r="C76" t="n">
-        <v>4.50234</v>
+        <v>4.1229</v>
       </c>
       <c r="D76" t="n">
-        <v>25.9798</v>
+        <v>28.2916</v>
       </c>
       <c r="E76" t="n">
-        <v>3.91946</v>
+        <v>3.64148</v>
       </c>
       <c r="F76" t="n">
-        <v>4.70927</v>
+        <v>4.58565</v>
       </c>
     </row>
     <row r="77">
@@ -6579,19 +6579,19 @@
         <v>381886</v>
       </c>
       <c r="B77" t="n">
-        <v>6.7095</v>
+        <v>6.5078</v>
       </c>
       <c r="C77" t="n">
-        <v>5.21657</v>
+        <v>5.0073</v>
       </c>
       <c r="D77" t="n">
-        <v>27.5571</v>
+        <v>29.8204</v>
       </c>
       <c r="E77" t="n">
-        <v>4.39835</v>
+        <v>4.04619</v>
       </c>
       <c r="F77" t="n">
-        <v>5.11964</v>
+        <v>5.16269</v>
       </c>
     </row>
     <row r="78">
@@ -6599,19 +6599,19 @@
         <v>400945</v>
       </c>
       <c r="B78" t="n">
-        <v>8.288819999999999</v>
+        <v>8.6013</v>
       </c>
       <c r="C78" t="n">
-        <v>6.45516</v>
+        <v>6.3127</v>
       </c>
       <c r="D78" t="n">
-        <v>24.2614</v>
+        <v>24.1758</v>
       </c>
       <c r="E78" t="n">
-        <v>3.04624</v>
+        <v>2.98092</v>
       </c>
       <c r="F78" t="n">
-        <v>3.82775</v>
+        <v>3.75277</v>
       </c>
     </row>
     <row r="79">
@@ -6619,19 +6619,19 @@
         <v>420956</v>
       </c>
       <c r="B79" t="n">
-        <v>10.9546</v>
+        <v>10.3202</v>
       </c>
       <c r="C79" t="n">
-        <v>2.76871</v>
+        <v>2.58472</v>
       </c>
       <c r="D79" t="n">
-        <v>25.5581</v>
+        <v>25.3882</v>
       </c>
       <c r="E79" t="n">
-        <v>3.17759</v>
+        <v>3.02335</v>
       </c>
       <c r="F79" t="n">
-        <v>3.9334</v>
+        <v>3.83532</v>
       </c>
     </row>
     <row r="80">
@@ -6639,19 +6639,19 @@
         <v>441967</v>
       </c>
       <c r="B80" t="n">
-        <v>14.7562</v>
+        <v>14.3164</v>
       </c>
       <c r="C80" t="n">
-        <v>2.83461</v>
+        <v>2.63088</v>
       </c>
       <c r="D80" t="n">
-        <v>26.6885</v>
+        <v>26.6138</v>
       </c>
       <c r="E80" t="n">
-        <v>3.16644</v>
+        <v>3.0495</v>
       </c>
       <c r="F80" t="n">
-        <v>4.08618</v>
+        <v>3.91258</v>
       </c>
     </row>
     <row r="81">
@@ -6659,19 +6659,19 @@
         <v>464028</v>
       </c>
       <c r="B81" t="n">
-        <v>4.11416</v>
+        <v>4.10459</v>
       </c>
       <c r="C81" t="n">
-        <v>2.88386</v>
+        <v>2.74153</v>
       </c>
       <c r="D81" t="n">
-        <v>27.9869</v>
+        <v>27.7872</v>
       </c>
       <c r="E81" t="n">
-        <v>3.30799</v>
+        <v>3.10546</v>
       </c>
       <c r="F81" t="n">
-        <v>4.47268</v>
+        <v>4.0153</v>
       </c>
     </row>
     <row r="82">
@@ -6679,19 +6679,19 @@
         <v>487192</v>
       </c>
       <c r="B82" t="n">
-        <v>4.22138</v>
+        <v>4.24083</v>
       </c>
       <c r="C82" t="n">
-        <v>2.96189</v>
+        <v>2.8264</v>
       </c>
       <c r="D82" t="n">
-        <v>29.3154</v>
+        <v>29.1113</v>
       </c>
       <c r="E82" t="n">
-        <v>3.30881</v>
+        <v>3.14794</v>
       </c>
       <c r="F82" t="n">
-        <v>4.43195</v>
+        <v>4.16748</v>
       </c>
     </row>
     <row r="83">
@@ -6699,19 +6699,19 @@
         <v>511514</v>
       </c>
       <c r="B83" t="n">
-        <v>4.3671</v>
+        <v>4.41761</v>
       </c>
       <c r="C83" t="n">
-        <v>3.07021</v>
+        <v>2.94142</v>
       </c>
       <c r="D83" t="n">
-        <v>30.6574</v>
+        <v>30.4155</v>
       </c>
       <c r="E83" t="n">
-        <v>3.45311</v>
+        <v>3.25768</v>
       </c>
       <c r="F83" t="n">
-        <v>4.6656</v>
+        <v>4.34106</v>
       </c>
     </row>
     <row r="84">
@@ -6719,19 +6719,19 @@
         <v>537052</v>
       </c>
       <c r="B84" t="n">
-        <v>4.58894</v>
+        <v>4.63506</v>
       </c>
       <c r="C84" t="n">
-        <v>3.20623</v>
+        <v>3.09063</v>
       </c>
       <c r="D84" t="n">
-        <v>32.0695</v>
+        <v>31.7296</v>
       </c>
       <c r="E84" t="n">
-        <v>3.65917</v>
+        <v>3.35748</v>
       </c>
       <c r="F84" t="n">
-        <v>4.95039</v>
+        <v>4.5288</v>
       </c>
     </row>
     <row r="85">
@@ -6739,19 +6739,19 @@
         <v>563866</v>
       </c>
       <c r="B85" t="n">
-        <v>4.80491</v>
+        <v>4.8787</v>
       </c>
       <c r="C85" t="n">
-        <v>3.37166</v>
+        <v>3.31286</v>
       </c>
       <c r="D85" t="n">
-        <v>33.5723</v>
+        <v>33.2317</v>
       </c>
       <c r="E85" t="n">
-        <v>3.80171</v>
+        <v>3.44305</v>
       </c>
       <c r="F85" t="n">
-        <v>4.91291</v>
+        <v>5.32167</v>
       </c>
     </row>
     <row r="86">
@@ -6759,19 +6759,19 @@
         <v>592020</v>
       </c>
       <c r="B86" t="n">
-        <v>5.1368</v>
+        <v>5.27596</v>
       </c>
       <c r="C86" t="n">
-        <v>3.60357</v>
+        <v>3.54017</v>
       </c>
       <c r="D86" t="n">
-        <v>35.0508</v>
+        <v>34.6096</v>
       </c>
       <c r="E86" t="n">
-        <v>4.01722</v>
+        <v>3.61235</v>
       </c>
       <c r="F86" t="n">
-        <v>5.26922</v>
+        <v>5.72451</v>
       </c>
     </row>
     <row r="87">
@@ -6779,19 +6779,19 @@
         <v>621581</v>
       </c>
       <c r="B87" t="n">
-        <v>5.54648</v>
+        <v>5.74323</v>
       </c>
       <c r="C87" t="n">
-        <v>3.87842</v>
+        <v>3.85669</v>
       </c>
       <c r="D87" t="n">
-        <v>36.6721</v>
+        <v>36.2216</v>
       </c>
       <c r="E87" t="n">
-        <v>4.27151</v>
+        <v>3.86608</v>
       </c>
       <c r="F87" t="n">
-        <v>5.54259</v>
+        <v>6.23627</v>
       </c>
     </row>
     <row r="88">
@@ -6799,19 +6799,19 @@
         <v>652620</v>
       </c>
       <c r="B88" t="n">
-        <v>6.02107</v>
+        <v>6.3165</v>
       </c>
       <c r="C88" t="n">
-        <v>4.16876</v>
+        <v>4.22337</v>
       </c>
       <c r="D88" t="n">
-        <v>37.7604</v>
+        <v>37.8117</v>
       </c>
       <c r="E88" t="n">
-        <v>4.55925</v>
+        <v>4.10158</v>
       </c>
       <c r="F88" t="n">
-        <v>6.16781</v>
+        <v>6.18151</v>
       </c>
     </row>
     <row r="89">
@@ -6819,19 +6819,19 @@
         <v>685210</v>
       </c>
       <c r="B89" t="n">
-        <v>6.74141</v>
+        <v>6.86642</v>
       </c>
       <c r="C89" t="n">
-        <v>4.73952</v>
+        <v>4.65659</v>
       </c>
       <c r="D89" t="n">
-        <v>39.4963</v>
+        <v>40.1074</v>
       </c>
       <c r="E89" t="n">
-        <v>4.91392</v>
+        <v>4.47446</v>
       </c>
       <c r="F89" t="n">
-        <v>6.68443</v>
+        <v>7.14713</v>
       </c>
     </row>
     <row r="90">
@@ -6839,19 +6839,19 @@
         <v>719429</v>
       </c>
       <c r="B90" t="n">
-        <v>7.66512</v>
+        <v>7.65188</v>
       </c>
       <c r="C90" t="n">
-        <v>5.38651</v>
+        <v>5.24681</v>
       </c>
       <c r="D90" t="n">
-        <v>42.0802</v>
+        <v>41.411</v>
       </c>
       <c r="E90" t="n">
-        <v>5.29769</v>
+        <v>4.88106</v>
       </c>
       <c r="F90" t="n">
-        <v>7.76782</v>
+        <v>7.39874</v>
       </c>
     </row>
     <row r="91">
@@ -6859,19 +6859,19 @@
         <v>755358</v>
       </c>
       <c r="B91" t="n">
-        <v>8.648250000000001</v>
+        <v>8.73756</v>
       </c>
       <c r="C91" t="n">
-        <v>6.1787</v>
+        <v>6.16135</v>
       </c>
       <c r="D91" t="n">
-        <v>43.7849</v>
+        <v>43.3519</v>
       </c>
       <c r="E91" t="n">
-        <v>5.8347</v>
+        <v>5.45774</v>
       </c>
       <c r="F91" t="n">
-        <v>8.44943</v>
+        <v>8.28861</v>
       </c>
     </row>
     <row r="92">
@@ -6879,19 +6879,19 @@
         <v>793083</v>
       </c>
       <c r="B92" t="n">
-        <v>10.0139</v>
+        <v>10.2427</v>
       </c>
       <c r="C92" t="n">
-        <v>7.40709</v>
+        <v>7.39273</v>
       </c>
       <c r="D92" t="n">
-        <v>35.5684</v>
+        <v>35.1625</v>
       </c>
       <c r="E92" t="n">
-        <v>3.93713</v>
+        <v>3.78328</v>
       </c>
       <c r="F92" t="n">
-        <v>5.36046</v>
+        <v>5.52054</v>
       </c>
     </row>
     <row r="93">
@@ -6899,19 +6899,19 @@
         <v>832694</v>
       </c>
       <c r="B93" t="n">
-        <v>12.3327</v>
+        <v>12.5539</v>
       </c>
       <c r="C93" t="n">
-        <v>9.3285</v>
+        <v>9.171659999999999</v>
       </c>
       <c r="D93" t="n">
-        <v>36.6784</v>
+        <v>36.3963</v>
       </c>
       <c r="E93" t="n">
-        <v>4.0559</v>
+        <v>3.92749</v>
       </c>
       <c r="F93" t="n">
-        <v>5.75514</v>
+        <v>5.64323</v>
       </c>
     </row>
     <row r="94">
@@ -6919,19 +6919,19 @@
         <v>874285</v>
       </c>
       <c r="B94" t="n">
-        <v>16.3087</v>
+        <v>15.7071</v>
       </c>
       <c r="C94" t="n">
-        <v>3.57144</v>
+        <v>3.67543</v>
       </c>
       <c r="D94" t="n">
-        <v>37.9868</v>
+        <v>37.6554</v>
       </c>
       <c r="E94" t="n">
-        <v>4.21213</v>
+        <v>4.0284</v>
       </c>
       <c r="F94" t="n">
-        <v>5.99541</v>
+        <v>6.07826</v>
       </c>
     </row>
     <row r="95">
@@ -6939,19 +6939,19 @@
         <v>917955</v>
       </c>
       <c r="B95" t="n">
-        <v>5.79213</v>
+        <v>5.94247</v>
       </c>
       <c r="C95" t="n">
-        <v>3.78307</v>
+        <v>3.75988</v>
       </c>
       <c r="D95" t="n">
-        <v>39.2293</v>
+        <v>38.9378</v>
       </c>
       <c r="E95" t="n">
-        <v>4.40404</v>
+        <v>4.20077</v>
       </c>
       <c r="F95" t="n">
-        <v>6.32611</v>
+        <v>6.22342</v>
       </c>
     </row>
     <row r="96">
@@ -6959,19 +6959,19 @@
         <v>963808</v>
       </c>
       <c r="B96" t="n">
-        <v>6.13552</v>
+        <v>6.16371</v>
       </c>
       <c r="C96" t="n">
-        <v>3.93711</v>
+        <v>3.91461</v>
       </c>
       <c r="D96" t="n">
-        <v>40.5144</v>
+        <v>40.1522</v>
       </c>
       <c r="E96" t="n">
-        <v>4.52865</v>
+        <v>4.38121</v>
       </c>
       <c r="F96" t="n">
-        <v>6.61436</v>
+        <v>6.65392</v>
       </c>
     </row>
     <row r="97">
@@ -6979,19 +6979,19 @@
         <v>1011953</v>
       </c>
       <c r="B97" t="n">
-        <v>6.39519</v>
+        <v>6.40511</v>
       </c>
       <c r="C97" t="n">
-        <v>4.08626</v>
+        <v>4.13055</v>
       </c>
       <c r="D97" t="n">
-        <v>41.8028</v>
+        <v>41.5396</v>
       </c>
       <c r="E97" t="n">
-        <v>4.68686</v>
+        <v>4.58707</v>
       </c>
       <c r="F97" t="n">
-        <v>6.94059</v>
+        <v>6.91641</v>
       </c>
     </row>
     <row r="98">
@@ -6999,19 +6999,19 @@
         <v>1062505</v>
       </c>
       <c r="B98" t="n">
-        <v>6.65937</v>
+        <v>6.70034</v>
       </c>
       <c r="C98" t="n">
-        <v>4.25333</v>
+        <v>4.28133</v>
       </c>
       <c r="D98" t="n">
-        <v>43.1416</v>
+        <v>42.8342</v>
       </c>
       <c r="E98" t="n">
-        <v>4.84011</v>
+        <v>4.75123</v>
       </c>
       <c r="F98" t="n">
-        <v>7.30247</v>
+        <v>7.23432</v>
       </c>
     </row>
     <row r="99">
@@ -7019,19 +7019,19 @@
         <v>1115584</v>
       </c>
       <c r="B99" t="n">
-        <v>6.96612</v>
+        <v>7.03737</v>
       </c>
       <c r="C99" t="n">
-        <v>4.43951</v>
+        <v>4.46075</v>
       </c>
       <c r="D99" t="n">
-        <v>44.5274</v>
+        <v>44.2617</v>
       </c>
       <c r="E99" t="n">
-        <v>5.03411</v>
+        <v>4.92101</v>
       </c>
       <c r="F99" t="n">
-        <v>7.59375</v>
+        <v>7.61091</v>
       </c>
     </row>
     <row r="100">
@@ -7039,19 +7039,19 @@
         <v>1171316</v>
       </c>
       <c r="B100" t="n">
-        <v>7.26317</v>
+        <v>7.32328</v>
       </c>
       <c r="C100" t="n">
-        <v>4.63252</v>
+        <v>4.68827</v>
       </c>
       <c r="D100" t="n">
-        <v>46.0127</v>
+        <v>45.728</v>
       </c>
       <c r="E100" t="n">
-        <v>5.23595</v>
+        <v>5.12675</v>
       </c>
       <c r="F100" t="n">
-        <v>7.91289</v>
+        <v>7.99698</v>
       </c>
     </row>
     <row r="101">
@@ -7059,19 +7059,19 @@
         <v>1229834</v>
       </c>
       <c r="B101" t="n">
-        <v>7.59423</v>
+        <v>7.67513</v>
       </c>
       <c r="C101" t="n">
-        <v>4.92225</v>
+        <v>4.94275</v>
       </c>
       <c r="D101" t="n">
-        <v>47.5556</v>
+        <v>47.1066</v>
       </c>
       <c r="E101" t="n">
-        <v>5.51499</v>
+        <v>5.34233</v>
       </c>
       <c r="F101" t="n">
-        <v>8.397690000000001</v>
+        <v>8.297280000000001</v>
       </c>
     </row>
     <row r="102">
@@ -7079,19 +7079,19 @@
         <v>1291277</v>
       </c>
       <c r="B102" t="n">
-        <v>8.0106</v>
+        <v>8.08127</v>
       </c>
       <c r="C102" t="n">
-        <v>5.21107</v>
+        <v>5.28428</v>
       </c>
       <c r="D102" t="n">
-        <v>49.1332</v>
+        <v>48.8743</v>
       </c>
       <c r="E102" t="n">
-        <v>5.78693</v>
+        <v>5.57096</v>
       </c>
       <c r="F102" t="n">
-        <v>8.91736</v>
+        <v>8.78424</v>
       </c>
     </row>
     <row r="103">
@@ -7099,19 +7099,19 @@
         <v>1355792</v>
       </c>
       <c r="B103" t="n">
-        <v>8.53905</v>
+        <v>8.6586</v>
       </c>
       <c r="C103" t="n">
-        <v>5.61546</v>
+        <v>5.67941</v>
       </c>
       <c r="D103" t="n">
-        <v>50.5639</v>
+        <v>50.7064</v>
       </c>
       <c r="E103" t="n">
-        <v>6.10766</v>
+        <v>5.82108</v>
       </c>
       <c r="F103" t="n">
-        <v>9.210150000000001</v>
+        <v>9.37973</v>
       </c>
     </row>
     <row r="104">
@@ -7119,19 +7119,19 @@
         <v>1423532</v>
       </c>
       <c r="B104" t="n">
-        <v>9.22086</v>
+        <v>9.391030000000001</v>
       </c>
       <c r="C104" t="n">
-        <v>6.19104</v>
+        <v>6.2574</v>
       </c>
       <c r="D104" t="n">
-        <v>52.4107</v>
+        <v>52.309</v>
       </c>
       <c r="E104" t="n">
-        <v>6.54562</v>
+        <v>6.18888</v>
       </c>
       <c r="F104" t="n">
-        <v>10.358</v>
+        <v>10.1281</v>
       </c>
     </row>
     <row r="105">
@@ -7139,19 +7139,19 @@
         <v>1494659</v>
       </c>
       <c r="B105" t="n">
-        <v>10.3331</v>
+        <v>10.4556</v>
       </c>
       <c r="C105" t="n">
-        <v>7.03486</v>
+        <v>7.07903</v>
       </c>
       <c r="D105" t="n">
-        <v>54.1569</v>
+        <v>54.0902</v>
       </c>
       <c r="E105" t="n">
-        <v>7.1402</v>
+        <v>6.6861</v>
       </c>
       <c r="F105" t="n">
-        <v>10.6503</v>
+        <v>11.0168</v>
       </c>
     </row>
     <row r="106">
@@ -7159,19 +7159,19 @@
         <v>1569342</v>
       </c>
       <c r="B106" t="n">
-        <v>11.8314</v>
+        <v>11.9729</v>
       </c>
       <c r="C106" t="n">
-        <v>8.21893</v>
+        <v>8.26329</v>
       </c>
       <c r="D106" t="n">
-        <v>55.6658</v>
+        <v>56.0963</v>
       </c>
       <c r="E106" t="n">
-        <v>7.82913</v>
+        <v>7.39064</v>
       </c>
       <c r="F106" t="n">
-        <v>12.417</v>
+        <v>12.2622</v>
       </c>
     </row>
     <row r="107">
@@ -7179,19 +7179,19 @@
         <v>1647759</v>
       </c>
       <c r="B107" t="n">
-        <v>13.8904</v>
+        <v>13.9834</v>
       </c>
       <c r="C107" t="n">
-        <v>10.0047</v>
+        <v>9.98019</v>
       </c>
       <c r="D107" t="n">
-        <v>42.4391</v>
+        <v>42.5705</v>
       </c>
       <c r="E107" t="n">
-        <v>4.95528</v>
+        <v>4.78769</v>
       </c>
       <c r="F107" t="n">
-        <v>7.18141</v>
+        <v>7.20561</v>
       </c>
     </row>
     <row r="108">
@@ -7199,19 +7199,19 @@
         <v>1730096</v>
       </c>
       <c r="B108" t="n">
-        <v>17.2889</v>
+        <v>17.1021</v>
       </c>
       <c r="C108" t="n">
-        <v>4.38386</v>
+        <v>4.37325</v>
       </c>
       <c r="D108" t="n">
-        <v>43.58</v>
+        <v>43.7513</v>
       </c>
       <c r="E108" t="n">
-        <v>5.12328</v>
+        <v>4.90648</v>
       </c>
       <c r="F108" t="n">
-        <v>7.51475</v>
+        <v>7.3696</v>
       </c>
     </row>
     <row r="109">
@@ -7219,19 +7219,19 @@
         <v>1816549</v>
       </c>
       <c r="B109" t="n">
-        <v>21.8448</v>
+        <v>21.895</v>
       </c>
       <c r="C109" t="n">
-        <v>4.51528</v>
+        <v>4.53272</v>
       </c>
       <c r="D109" t="n">
-        <v>44.7325</v>
+        <v>44.9346</v>
       </c>
       <c r="E109" t="n">
-        <v>5.34592</v>
+        <v>4.99543</v>
       </c>
       <c r="F109" t="n">
-        <v>7.81304</v>
+        <v>7.66471</v>
       </c>
     </row>
     <row r="110">
@@ -7239,19 +7239,19 @@
         <v>1907324</v>
       </c>
       <c r="B110" t="n">
-        <v>7.29704</v>
+        <v>7.23412</v>
       </c>
       <c r="C110" t="n">
-        <v>4.59046</v>
+        <v>4.6443</v>
       </c>
       <c r="D110" t="n">
-        <v>45.9529</v>
+        <v>46.1713</v>
       </c>
       <c r="E110" t="n">
-        <v>5.59502</v>
+        <v>5.12202</v>
       </c>
       <c r="F110" t="n">
-        <v>8.242179999999999</v>
+        <v>8.27543</v>
       </c>
     </row>
     <row r="111">
@@ -7259,19 +7259,19 @@
         <v>2002637</v>
       </c>
       <c r="B111" t="n">
-        <v>7.60133</v>
+        <v>7.57048</v>
       </c>
       <c r="C111" t="n">
-        <v>4.76638</v>
+        <v>4.82582</v>
       </c>
       <c r="D111" t="n">
-        <v>47.2761</v>
+        <v>47.3924</v>
       </c>
       <c r="E111" t="n">
-        <v>5.8824</v>
+        <v>5.26294</v>
       </c>
       <c r="F111" t="n">
-        <v>8.77463</v>
+        <v>8.77647</v>
       </c>
     </row>
     <row r="112">
@@ -7279,19 +7279,19 @@
         <v>2102715</v>
       </c>
       <c r="B112" t="n">
-        <v>7.87198</v>
+        <v>7.88402</v>
       </c>
       <c r="C112" t="n">
-        <v>4.92192</v>
+        <v>5.04025</v>
       </c>
       <c r="D112" t="n">
-        <v>48.5735</v>
+        <v>48.69</v>
       </c>
       <c r="E112" t="n">
-        <v>6.04035</v>
+        <v>5.36413</v>
       </c>
       <c r="F112" t="n">
-        <v>9.16065</v>
+        <v>9.21725</v>
       </c>
     </row>
     <row r="113">
@@ -7299,19 +7299,19 @@
         <v>2207796</v>
       </c>
       <c r="B113" t="n">
-        <v>8.282959999999999</v>
+        <v>8.279439999999999</v>
       </c>
       <c r="C113" t="n">
-        <v>5.25801</v>
+        <v>5.2281</v>
       </c>
       <c r="D113" t="n">
-        <v>49.8761</v>
+        <v>50.064</v>
       </c>
       <c r="E113" t="n">
-        <v>6.27534</v>
+        <v>5.62153</v>
       </c>
       <c r="F113" t="n">
-        <v>9.693390000000001</v>
+        <v>9.69683</v>
       </c>
     </row>
     <row r="114">
@@ -7319,19 +7319,19 @@
         <v>2318131</v>
       </c>
       <c r="B114" t="n">
-        <v>8.68582</v>
+        <v>8.66755</v>
       </c>
       <c r="C114" t="n">
-        <v>5.49565</v>
+        <v>5.49824</v>
       </c>
       <c r="D114" t="n">
-        <v>51.3138</v>
+        <v>51.4654</v>
       </c>
       <c r="E114" t="n">
-        <v>6.51366</v>
+        <v>5.78377</v>
       </c>
       <c r="F114" t="n">
-        <v>10.2333</v>
+        <v>10.2535</v>
       </c>
     </row>
     <row r="115">
@@ -7339,19 +7339,19 @@
         <v>2433982</v>
       </c>
       <c r="B115" t="n">
-        <v>9.28436</v>
+        <v>9.23335</v>
       </c>
       <c r="C115" t="n">
-        <v>5.85189</v>
+        <v>5.85003</v>
       </c>
       <c r="D115" t="n">
-        <v>52.7627</v>
+        <v>52.9368</v>
       </c>
       <c r="E115" t="n">
-        <v>6.75561</v>
+        <v>6.14348</v>
       </c>
       <c r="F115" t="n">
-        <v>10.8533</v>
+        <v>10.8553</v>
       </c>
     </row>
     <row r="116">
@@ -7359,19 +7359,19 @@
         <v>2555625</v>
       </c>
       <c r="B116" t="n">
-        <v>9.93825</v>
+        <v>9.881880000000001</v>
       </c>
       <c r="C116" t="n">
-        <v>6.31637</v>
+        <v>6.31465</v>
       </c>
       <c r="D116" t="n">
-        <v>54.3679</v>
+        <v>54.4963</v>
       </c>
       <c r="E116" t="n">
-        <v>7.05014</v>
+        <v>6.59475</v>
       </c>
       <c r="F116" t="n">
-        <v>11.4702</v>
+        <v>11.4428</v>
       </c>
     </row>
     <row r="117">
@@ -7379,19 +7379,19 @@
         <v>2683350</v>
       </c>
       <c r="B117" t="n">
-        <v>10.5394</v>
+        <v>10.5581</v>
       </c>
       <c r="C117" t="n">
-        <v>6.79376</v>
+        <v>6.8257</v>
       </c>
       <c r="D117" t="n">
-        <v>55.9704</v>
+        <v>56.1467</v>
       </c>
       <c r="E117" t="n">
-        <v>7.32668</v>
+        <v>7.03622</v>
       </c>
       <c r="F117" t="n">
-        <v>11.9281</v>
+        <v>11.9673</v>
       </c>
     </row>
     <row r="118">
@@ -7399,19 +7399,19 @@
         <v>2817461</v>
       </c>
       <c r="B118" t="n">
-        <v>11.3049</v>
+        <v>11.3072</v>
       </c>
       <c r="C118" t="n">
-        <v>7.36186</v>
+        <v>7.39994</v>
       </c>
       <c r="D118" t="n">
-        <v>57.5643</v>
+        <v>57.8034</v>
       </c>
       <c r="E118" t="n">
-        <v>7.66911</v>
+        <v>7.45525</v>
       </c>
       <c r="F118" t="n">
-        <v>12.6052</v>
+        <v>12.658</v>
       </c>
     </row>
     <row r="119">
@@ -7419,19 +7419,19 @@
         <v>2958277</v>
       </c>
       <c r="B119" t="n">
-        <v>12.2475</v>
+        <v>12.2773</v>
       </c>
       <c r="C119" t="n">
-        <v>8.09709</v>
+        <v>8.15639</v>
       </c>
       <c r="D119" t="n">
-        <v>59.3905</v>
+        <v>59.6345</v>
       </c>
       <c r="E119" t="n">
-        <v>8.062340000000001</v>
+        <v>8.0669</v>
       </c>
       <c r="F119" t="n">
-        <v>13.4347</v>
+        <v>13.4572</v>
       </c>
     </row>
     <row r="120">
@@ -7439,19 +7439,19 @@
         <v>3106133</v>
       </c>
       <c r="B120" t="n">
-        <v>13.5004</v>
+        <v>13.5465</v>
       </c>
       <c r="C120" t="n">
-        <v>9.1661</v>
+        <v>9.20012</v>
       </c>
       <c r="D120" t="n">
-        <v>61.296</v>
+        <v>61.5293</v>
       </c>
       <c r="E120" t="n">
-        <v>8.82315</v>
+        <v>8.75234</v>
       </c>
       <c r="F120" t="n">
-        <v>14.247</v>
+        <v>14.3655</v>
       </c>
     </row>
     <row r="121">
@@ -7459,19 +7459,19 @@
         <v>3261381</v>
       </c>
       <c r="B121" t="n">
-        <v>15.2573</v>
+        <v>15.2728</v>
       </c>
       <c r="C121" t="n">
-        <v>10.6936</v>
+        <v>10.7261</v>
       </c>
       <c r="D121" t="n">
-        <v>45.5506</v>
+        <v>45.7031</v>
       </c>
       <c r="E121" t="n">
-        <v>7.23651</v>
+        <v>6.4558</v>
       </c>
       <c r="F121" t="n">
-        <v>10.011</v>
+        <v>10.6432</v>
       </c>
     </row>
     <row r="122">
@@ -7479,19 +7479,19 @@
         <v>3424391</v>
       </c>
       <c r="B122" t="n">
-        <v>17.9208</v>
+        <v>17.9223</v>
       </c>
       <c r="C122" t="n">
-        <v>6.20546</v>
+        <v>6.20037</v>
       </c>
       <c r="D122" t="n">
-        <v>46.3665</v>
+        <v>46.8216</v>
       </c>
       <c r="E122" t="n">
-        <v>7.24231</v>
+        <v>6.52592</v>
       </c>
       <c r="F122" t="n">
-        <v>10.1948</v>
+        <v>10.8109</v>
       </c>
     </row>
     <row r="123">
@@ -7499,19 +7499,19 @@
         <v>3595551</v>
       </c>
       <c r="B123" t="n">
-        <v>22.0891</v>
+        <v>22.1449</v>
       </c>
       <c r="C123" t="n">
-        <v>5.86579</v>
+        <v>6.4034</v>
       </c>
       <c r="D123" t="n">
-        <v>47.7959</v>
+        <v>48.0334</v>
       </c>
       <c r="E123" t="n">
-        <v>7.52114</v>
+        <v>6.50181</v>
       </c>
       <c r="F123" t="n">
-        <v>10.9398</v>
+        <v>10.5983</v>
       </c>
     </row>
     <row r="124">
@@ -7519,19 +7519,19 @@
         <v>3775269</v>
       </c>
       <c r="B124" t="n">
-        <v>9.608359999999999</v>
+        <v>9.4505</v>
       </c>
       <c r="C124" t="n">
-        <v>6.29811</v>
+        <v>6.38398</v>
       </c>
       <c r="D124" t="n">
-        <v>49.0303</v>
+        <v>49.2687</v>
       </c>
       <c r="E124" t="n">
-        <v>8.441179999999999</v>
+        <v>7.22392</v>
       </c>
       <c r="F124" t="n">
-        <v>11.9406</v>
+        <v>11.2453</v>
       </c>
     </row>
     <row r="125">
@@ -7539,19 +7539,19 @@
         <v>3963972</v>
       </c>
       <c r="B125" t="n">
-        <v>9.835089999999999</v>
+        <v>9.55517</v>
       </c>
       <c r="C125" t="n">
-        <v>6.48825</v>
+        <v>6.34879</v>
       </c>
       <c r="D125" t="n">
-        <v>50.2943</v>
+        <v>50.3389</v>
       </c>
       <c r="E125" t="n">
-        <v>7.74917</v>
+        <v>7.5915</v>
       </c>
       <c r="F125" t="n">
-        <v>11.3003</v>
+        <v>11.4211</v>
       </c>
     </row>
     <row r="126">
@@ -7559,19 +7559,19 @@
         <v>4162110</v>
       </c>
       <c r="B126" t="n">
-        <v>10.1465</v>
+        <v>10.048</v>
       </c>
       <c r="C126" t="n">
-        <v>6.71557</v>
+        <v>6.67343</v>
       </c>
       <c r="D126" t="n">
-        <v>51.6641</v>
+        <v>51.8381</v>
       </c>
       <c r="E126" t="n">
-        <v>8.31072</v>
+        <v>7.67055</v>
       </c>
       <c r="F126" t="n">
-        <v>12.0242</v>
+        <v>11.9983</v>
       </c>
     </row>
     <row r="127">
@@ -7579,19 +7579,19 @@
         <v>4370154</v>
       </c>
       <c r="B127" t="n">
-        <v>10.576</v>
+        <v>10.6291</v>
       </c>
       <c r="C127" t="n">
-        <v>6.69033</v>
+        <v>6.67081</v>
       </c>
       <c r="D127" t="n">
-        <v>53.0152</v>
+        <v>53.187</v>
       </c>
       <c r="E127" t="n">
-        <v>8.318059999999999</v>
+        <v>7.93568</v>
       </c>
       <c r="F127" t="n">
-        <v>11.9588</v>
+        <v>12.1706</v>
       </c>
     </row>
     <row r="128">
@@ -7599,19 +7599,19 @@
         <v>4588600</v>
       </c>
       <c r="B128" t="n">
-        <v>11.0145</v>
+        <v>10.6239</v>
       </c>
       <c r="C128" t="n">
-        <v>7.04007</v>
+        <v>7.05686</v>
       </c>
       <c r="D128" t="n">
-        <v>54.3558</v>
+        <v>54.6052</v>
       </c>
       <c r="E128" t="n">
-        <v>8.722759999999999</v>
+        <v>7.90093</v>
       </c>
       <c r="F128" t="n">
-        <v>12.737</v>
+        <v>12.5345</v>
       </c>
     </row>
     <row r="129">
@@ -7619,19 +7619,19 @@
         <v>4817968</v>
       </c>
       <c r="B129" t="n">
-        <v>10.885</v>
+        <v>11.1709</v>
       </c>
       <c r="C129" t="n">
-        <v>7.61917</v>
+        <v>7.34921</v>
       </c>
       <c r="D129" t="n">
-        <v>55.8725</v>
+        <v>56.0998</v>
       </c>
       <c r="E129" t="n">
-        <v>8.677619999999999</v>
+        <v>8.218680000000001</v>
       </c>
       <c r="F129" t="n">
-        <v>12.4398</v>
+        <v>13.1279</v>
       </c>
     </row>
     <row r="130">
@@ -7639,19 +7639,19 @@
         <v>5058804</v>
       </c>
       <c r="B130" t="n">
-        <v>11.3157</v>
+        <v>11.5048</v>
       </c>
       <c r="C130" t="n">
-        <v>7.43437</v>
+        <v>7.6137</v>
       </c>
       <c r="D130" t="n">
-        <v>57.4299</v>
+        <v>57.5597</v>
       </c>
       <c r="E130" t="n">
-        <v>9.05429</v>
+        <v>8.450290000000001</v>
       </c>
       <c r="F130" t="n">
-        <v>13.4604</v>
+        <v>13.4448</v>
       </c>
     </row>
     <row r="131">
@@ -7659,19 +7659,19 @@
         <v>5311681</v>
       </c>
       <c r="B131" t="n">
-        <v>11.7489</v>
+        <v>11.4144</v>
       </c>
       <c r="C131" t="n">
-        <v>7.68027</v>
+        <v>7.73197</v>
       </c>
       <c r="D131" t="n">
-        <v>58.7601</v>
+        <v>59.1888</v>
       </c>
       <c r="E131" t="n">
-        <v>9.545529999999999</v>
+        <v>8.72292</v>
       </c>
       <c r="F131" t="n">
-        <v>14.1837</v>
+        <v>13.935</v>
       </c>
     </row>
     <row r="132">
@@ -7679,19 +7679,19 @@
         <v>5577201</v>
       </c>
       <c r="B132" t="n">
-        <v>12.6125</v>
+        <v>12.4869</v>
       </c>
       <c r="C132" t="n">
-        <v>8.243230000000001</v>
+        <v>8.31889</v>
       </c>
       <c r="D132" t="n">
-        <v>60.6625</v>
+        <v>60.9081</v>
       </c>
       <c r="E132" t="n">
-        <v>9.69552</v>
+        <v>8.89099</v>
       </c>
       <c r="F132" t="n">
-        <v>14.4422</v>
+        <v>14.5413</v>
       </c>
     </row>
     <row r="133">
@@ -7699,19 +7699,19 @@
         <v>5855997</v>
       </c>
       <c r="B133" t="n">
-        <v>13.3148</v>
+        <v>13.5316</v>
       </c>
       <c r="C133" t="n">
-        <v>8.85629</v>
+        <v>8.88273</v>
       </c>
       <c r="D133" t="n">
-        <v>62.4482</v>
+        <v>62.4934</v>
       </c>
       <c r="E133" t="n">
-        <v>10.2842</v>
+        <v>9.46274</v>
       </c>
       <c r="F133" t="n">
-        <v>15.3049</v>
+        <v>15.3416</v>
       </c>
     </row>
     <row r="134">
@@ -7719,19 +7719,19 @@
         <v>6148732</v>
       </c>
       <c r="B134" t="n">
-        <v>14.298</v>
+        <v>14.35</v>
       </c>
       <c r="C134" t="n">
-        <v>9.76854</v>
+        <v>9.92084</v>
       </c>
       <c r="D134" t="n">
-        <v>64.2851</v>
+        <v>64.37</v>
       </c>
       <c r="E134" t="n">
-        <v>10.7543</v>
+        <v>10.0161</v>
       </c>
       <c r="F134" t="n">
-        <v>16.1823</v>
+        <v>16.2604</v>
       </c>
     </row>
     <row r="135">
@@ -7739,19 +7739,19 @@
         <v>6456103</v>
       </c>
       <c r="B135" t="n">
-        <v>16.044</v>
+        <v>15.9914</v>
       </c>
       <c r="C135" t="n">
-        <v>11.0756</v>
+        <v>11.1209</v>
       </c>
       <c r="D135" t="n">
-        <v>47.2192</v>
+        <v>47.3738</v>
       </c>
       <c r="E135" t="n">
-        <v>13.6387</v>
+        <v>12.6641</v>
       </c>
       <c r="F135" t="n">
-        <v>17.0151</v>
+        <v>17.354</v>
       </c>
     </row>
     <row r="136">
@@ -7759,19 +7759,19 @@
         <v>6778842</v>
       </c>
       <c r="B136" t="n">
-        <v>18.2121</v>
+        <v>17.9669</v>
       </c>
       <c r="C136" t="n">
-        <v>11.8473</v>
+        <v>11.7854</v>
       </c>
       <c r="D136" t="n">
-        <v>48.3527</v>
+        <v>48.5508</v>
       </c>
       <c r="E136" t="n">
-        <v>13.7821</v>
+        <v>13.3344</v>
       </c>
       <c r="F136" t="n">
-        <v>17.3736</v>
+        <v>17.4509</v>
       </c>
     </row>
     <row r="137">
@@ -7779,19 +7779,19 @@
         <v>7117717</v>
       </c>
       <c r="B137" t="n">
-        <v>22.2682</v>
+        <v>21.8829</v>
       </c>
       <c r="C137" t="n">
-        <v>11.4909</v>
+        <v>11.0818</v>
       </c>
       <c r="D137" t="n">
-        <v>49.57</v>
+        <v>49.7606</v>
       </c>
       <c r="E137" t="n">
-        <v>13.8694</v>
+        <v>13.5093</v>
       </c>
       <c r="F137" t="n">
-        <v>17.1702</v>
+        <v>17.5946</v>
       </c>
     </row>
     <row r="138">
@@ -7799,19 +7799,19 @@
         <v>7473535</v>
       </c>
       <c r="B138" t="n">
-        <v>15.3173</v>
+        <v>16.1054</v>
       </c>
       <c r="C138" t="n">
-        <v>11.9515</v>
+        <v>12.0319</v>
       </c>
       <c r="D138" t="n">
-        <v>50.6597</v>
+        <v>51.0046</v>
       </c>
       <c r="E138" t="n">
-        <v>14.0124</v>
+        <v>13.4715</v>
       </c>
       <c r="F138" t="n">
-        <v>17.3108</v>
+        <v>17.9149</v>
       </c>
     </row>
     <row r="139">
@@ -7819,19 +7819,19 @@
         <v>7847143</v>
       </c>
       <c r="B139" t="n">
-        <v>16.2821</v>
+        <v>16.2692</v>
       </c>
       <c r="C139" t="n">
-        <v>12.0352</v>
+        <v>12.2977</v>
       </c>
       <c r="D139" t="n">
-        <v>51.9395</v>
+        <v>52.3371</v>
       </c>
       <c r="E139" t="n">
-        <v>14.0827</v>
+        <v>13.6241</v>
       </c>
       <c r="F139" t="n">
-        <v>17.408</v>
+        <v>18.2989</v>
       </c>
     </row>
     <row r="140">
@@ -7839,19 +7839,19 @@
         <v>8239431</v>
       </c>
       <c r="B140" t="n">
-        <v>16.2785</v>
+        <v>16.3038</v>
       </c>
       <c r="C140" t="n">
-        <v>12.1552</v>
+        <v>12.1181</v>
       </c>
       <c r="D140" t="n">
-        <v>53.4021</v>
+        <v>53.6064</v>
       </c>
       <c r="E140" t="n">
-        <v>14.2759</v>
+        <v>13.7715</v>
       </c>
       <c r="F140" t="n">
-        <v>17.9274</v>
+        <v>18.5731</v>
       </c>
     </row>
     <row r="141">
@@ -7859,19 +7859,19 @@
         <v>8651333</v>
       </c>
       <c r="B141" t="n">
-        <v>16.6277</v>
+        <v>15.8896</v>
       </c>
       <c r="C141" t="n">
-        <v>12.3691</v>
+        <v>12.286</v>
       </c>
       <c r="D141" t="n">
-        <v>54.6339</v>
+        <v>54.9865</v>
       </c>
       <c r="E141" t="n">
-        <v>14.5281</v>
+        <v>13.955</v>
       </c>
       <c r="F141" t="n">
-        <v>18.3251</v>
+        <v>18.9532</v>
       </c>
     </row>
     <row r="142">
@@ -7879,19 +7879,19 @@
         <v>9083830</v>
       </c>
       <c r="B142" t="n">
-        <v>16.6936</v>
+        <v>16.8045</v>
       </c>
       <c r="C142" t="n">
-        <v>12.3571</v>
+        <v>12.411</v>
       </c>
       <c r="D142" t="n">
-        <v>56.076</v>
+        <v>56.2807</v>
       </c>
       <c r="E142" t="n">
-        <v>14.0536</v>
+        <v>13.3779</v>
       </c>
       <c r="F142" t="n">
-        <v>19.227</v>
+        <v>19.2696</v>
       </c>
     </row>
     <row r="143">
@@ -7899,19 +7899,19 @@
         <v>9537951</v>
       </c>
       <c r="B143" t="n">
-        <v>17.1535</v>
+        <v>17.1283</v>
       </c>
       <c r="C143" t="n">
-        <v>12.5154</v>
+        <v>12.6161</v>
       </c>
       <c r="D143" t="n">
-        <v>57.5753</v>
+        <v>57.8263</v>
       </c>
       <c r="E143" t="n">
-        <v>14.8903</v>
+        <v>14.231</v>
       </c>
       <c r="F143" t="n">
-        <v>18.885</v>
+        <v>19.7388</v>
       </c>
     </row>
   </sheetData>

--- a/gcc-x64/Scattered unsuccessful looukp.xlsx
+++ b/gcc-x64/Scattered unsuccessful looukp.xlsx
@@ -5079,19 +5079,19 @@
         <v>10000</v>
       </c>
       <c r="B2" t="n">
-        <v>2.86638</v>
+        <v>2.85902</v>
       </c>
       <c r="C2" t="n">
-        <v>1.90975</v>
+        <v>1.9148</v>
       </c>
       <c r="D2" t="n">
-        <v>13.5046</v>
+        <v>13.5611</v>
       </c>
       <c r="E2" t="n">
-        <v>1.90743</v>
+        <v>1.90636</v>
       </c>
       <c r="F2" t="n">
-        <v>2.2774</v>
+        <v>2.28759</v>
       </c>
     </row>
     <row r="3">
@@ -5099,19 +5099,19 @@
         <v>10500</v>
       </c>
       <c r="B3" t="n">
-        <v>2.92867</v>
+        <v>2.93908</v>
       </c>
       <c r="C3" t="n">
-        <v>1.97231</v>
+        <v>1.97463</v>
       </c>
       <c r="D3" t="n">
-        <v>14.6198</v>
+        <v>14.5136</v>
       </c>
       <c r="E3" t="n">
-        <v>1.6896</v>
+        <v>1.67153</v>
       </c>
       <c r="F3" t="n">
-        <v>2.2017</v>
+        <v>2.20635</v>
       </c>
     </row>
     <row r="4">
@@ -5119,19 +5119,19 @@
         <v>11025</v>
       </c>
       <c r="B4" t="n">
-        <v>3.0551</v>
+        <v>3.06154</v>
       </c>
       <c r="C4" t="n">
-        <v>2.11015</v>
+        <v>2.09949</v>
       </c>
       <c r="D4" t="n">
-        <v>15.1528</v>
+        <v>15.1148</v>
       </c>
       <c r="E4" t="n">
-        <v>1.71729</v>
+        <v>1.66876</v>
       </c>
       <c r="F4" t="n">
-        <v>2.08846</v>
+        <v>2.15927</v>
       </c>
     </row>
     <row r="5">
@@ -5139,19 +5139,19 @@
         <v>11576</v>
       </c>
       <c r="B5" t="n">
-        <v>3.39846</v>
+        <v>3.41637</v>
       </c>
       <c r="C5" t="n">
-        <v>2.27133</v>
+        <v>2.27832</v>
       </c>
       <c r="D5" t="n">
-        <v>15.6332</v>
+        <v>15.6131</v>
       </c>
       <c r="E5" t="n">
-        <v>1.72986</v>
+        <v>1.69177</v>
       </c>
       <c r="F5" t="n">
-        <v>2.22046</v>
+        <v>2.1425</v>
       </c>
     </row>
     <row r="6">
@@ -5159,19 +5159,19 @@
         <v>12154</v>
       </c>
       <c r="B6" t="n">
-        <v>4.30285</v>
+        <v>4.30059</v>
       </c>
       <c r="C6" t="n">
-        <v>2.88305</v>
+        <v>2.87753</v>
       </c>
       <c r="D6" t="n">
-        <v>16.2875</v>
+        <v>16.1434</v>
       </c>
       <c r="E6" t="n">
-        <v>1.7909</v>
+        <v>1.80468</v>
       </c>
       <c r="F6" t="n">
-        <v>2.35325</v>
+        <v>2.26922</v>
       </c>
     </row>
     <row r="7">
@@ -5179,19 +5179,19 @@
         <v>12760</v>
       </c>
       <c r="B7" t="n">
-        <v>6.54301</v>
+        <v>6.55384</v>
       </c>
       <c r="C7" t="n">
-        <v>5.02181</v>
+        <v>5.02472</v>
       </c>
       <c r="D7" t="n">
-        <v>10.8617</v>
+        <v>11.0272</v>
       </c>
       <c r="E7" t="n">
-        <v>1.87067</v>
+        <v>1.88226</v>
       </c>
       <c r="F7" t="n">
-        <v>2.06586</v>
+        <v>2.09571</v>
       </c>
     </row>
     <row r="8">
@@ -5199,19 +5199,19 @@
         <v>13396</v>
       </c>
       <c r="B8" t="n">
-        <v>9.36591</v>
+        <v>9.38223</v>
       </c>
       <c r="C8" t="n">
-        <v>1.80678</v>
+        <v>1.71718</v>
       </c>
       <c r="D8" t="n">
-        <v>11.5408</v>
+        <v>11.6031</v>
       </c>
       <c r="E8" t="n">
-        <v>1.89676</v>
+        <v>1.89865</v>
       </c>
       <c r="F8" t="n">
-        <v>2.10015</v>
+        <v>2.11178</v>
       </c>
     </row>
     <row r="9">
@@ -5219,19 +5219,19 @@
         <v>14063</v>
       </c>
       <c r="B9" t="n">
-        <v>13.7354</v>
+        <v>13.7494</v>
       </c>
       <c r="C9" t="n">
-        <v>1.75708</v>
+        <v>1.74047</v>
       </c>
       <c r="D9" t="n">
-        <v>12.0462</v>
+        <v>12.1725</v>
       </c>
       <c r="E9" t="n">
-        <v>1.90602</v>
+        <v>1.90905</v>
       </c>
       <c r="F9" t="n">
-        <v>2.10541</v>
+        <v>2.12884</v>
       </c>
     </row>
     <row r="10">
@@ -5239,19 +5239,19 @@
         <v>14763</v>
       </c>
       <c r="B10" t="n">
-        <v>2.82113</v>
+        <v>2.80055</v>
       </c>
       <c r="C10" t="n">
-        <v>1.78179</v>
+        <v>1.93351</v>
       </c>
       <c r="D10" t="n">
-        <v>12.7965</v>
+        <v>12.8904</v>
       </c>
       <c r="E10" t="n">
-        <v>1.92241</v>
+        <v>1.92496</v>
       </c>
       <c r="F10" t="n">
-        <v>2.11967</v>
+        <v>2.15998</v>
       </c>
     </row>
     <row r="11">
@@ -5259,19 +5259,19 @@
         <v>15498</v>
       </c>
       <c r="B11" t="n">
-        <v>2.84464</v>
+        <v>2.84071</v>
       </c>
       <c r="C11" t="n">
-        <v>1.82451</v>
+        <v>1.81984</v>
       </c>
       <c r="D11" t="n">
-        <v>13.2475</v>
+        <v>13.3778</v>
       </c>
       <c r="E11" t="n">
-        <v>1.94522</v>
+        <v>1.9273</v>
       </c>
       <c r="F11" t="n">
-        <v>2.15018</v>
+        <v>2.19012</v>
       </c>
     </row>
     <row r="12">
@@ -5279,19 +5279,19 @@
         <v>16269</v>
       </c>
       <c r="B12" t="n">
-        <v>2.89259</v>
+        <v>2.88695</v>
       </c>
       <c r="C12" t="n">
-        <v>1.85288</v>
+        <v>1.84963</v>
       </c>
       <c r="D12" t="n">
-        <v>13.7749</v>
+        <v>13.8966</v>
       </c>
       <c r="E12" t="n">
-        <v>1.94399</v>
+        <v>1.93468</v>
       </c>
       <c r="F12" t="n">
-        <v>2.19459</v>
+        <v>2.20918</v>
       </c>
     </row>
     <row r="13">
@@ -5299,19 +5299,19 @@
         <v>17078</v>
       </c>
       <c r="B13" t="n">
-        <v>2.8759</v>
+        <v>2.88068</v>
       </c>
       <c r="C13" t="n">
-        <v>1.9571</v>
+        <v>1.86884</v>
       </c>
       <c r="D13" t="n">
-        <v>14.2145</v>
+        <v>14.3734</v>
       </c>
       <c r="E13" t="n">
-        <v>1.94609</v>
+        <v>1.93886</v>
       </c>
       <c r="F13" t="n">
-        <v>2.20193</v>
+        <v>2.23738</v>
       </c>
     </row>
     <row r="14">
@@ -5319,19 +5319,19 @@
         <v>17927</v>
       </c>
       <c r="B14" t="n">
-        <v>2.95423</v>
+        <v>2.94266</v>
       </c>
       <c r="C14" t="n">
-        <v>1.98229</v>
+        <v>1.94365</v>
       </c>
       <c r="D14" t="n">
-        <v>14.7003</v>
+        <v>14.8709</v>
       </c>
       <c r="E14" t="n">
-        <v>1.98225</v>
+        <v>1.96989</v>
       </c>
       <c r="F14" t="n">
-        <v>2.2175</v>
+        <v>2.29105</v>
       </c>
     </row>
     <row r="15">
@@ -5339,19 +5339,19 @@
         <v>18818</v>
       </c>
       <c r="B15" t="n">
-        <v>3.05046</v>
+        <v>3.05246</v>
       </c>
       <c r="C15" t="n">
-        <v>2.0724</v>
+        <v>2.00102</v>
       </c>
       <c r="D15" t="n">
-        <v>15.0647</v>
+        <v>15.2623</v>
       </c>
       <c r="E15" t="n">
-        <v>1.99938</v>
+        <v>1.99841</v>
       </c>
       <c r="F15" t="n">
-        <v>2.22366</v>
+        <v>2.31079</v>
       </c>
     </row>
     <row r="16">
@@ -5359,19 +5359,19 @@
         <v>19753</v>
       </c>
       <c r="B16" t="n">
-        <v>3.09498</v>
+        <v>3.0841</v>
       </c>
       <c r="C16" t="n">
-        <v>2.15673</v>
+        <v>2.09514</v>
       </c>
       <c r="D16" t="n">
-        <v>15.5196</v>
+        <v>15.7002</v>
       </c>
       <c r="E16" t="n">
-        <v>2.03492</v>
+        <v>2.0186</v>
       </c>
       <c r="F16" t="n">
-        <v>2.28424</v>
+        <v>2.38324</v>
       </c>
     </row>
     <row r="17">
@@ -5379,19 +5379,19 @@
         <v>20734</v>
       </c>
       <c r="B17" t="n">
-        <v>3.29386</v>
+        <v>3.29557</v>
       </c>
       <c r="C17" t="n">
-        <v>2.29879</v>
+        <v>2.24561</v>
       </c>
       <c r="D17" t="n">
-        <v>15.9741</v>
+        <v>16.0941</v>
       </c>
       <c r="E17" t="n">
-        <v>2.05923</v>
+        <v>2.06039</v>
       </c>
       <c r="F17" t="n">
-        <v>2.36111</v>
+        <v>2.42028</v>
       </c>
     </row>
     <row r="18">
@@ -5399,19 +5399,19 @@
         <v>21764</v>
       </c>
       <c r="B18" t="n">
-        <v>3.66504</v>
+        <v>3.68201</v>
       </c>
       <c r="C18" t="n">
-        <v>2.51968</v>
+        <v>2.46961</v>
       </c>
       <c r="D18" t="n">
-        <v>16.3434</v>
+        <v>16.5652</v>
       </c>
       <c r="E18" t="n">
-        <v>2.02495</v>
+        <v>1.97142</v>
       </c>
       <c r="F18" t="n">
-        <v>2.45057</v>
+        <v>2.46154</v>
       </c>
     </row>
     <row r="19">
@@ -5419,19 +5419,19 @@
         <v>22845</v>
       </c>
       <c r="B19" t="n">
-        <v>4.20317</v>
+        <v>4.20465</v>
       </c>
       <c r="C19" t="n">
-        <v>3.14208</v>
+        <v>3.12129</v>
       </c>
       <c r="D19" t="n">
-        <v>16.899</v>
+        <v>17.0425</v>
       </c>
       <c r="E19" t="n">
-        <v>2.08237</v>
+        <v>2.13963</v>
       </c>
       <c r="F19" t="n">
-        <v>2.56168</v>
+        <v>2.59056</v>
       </c>
     </row>
     <row r="20">
@@ -5439,19 +5439,19 @@
         <v>23980</v>
       </c>
       <c r="B20" t="n">
-        <v>5.18583</v>
+        <v>5.21338</v>
       </c>
       <c r="C20" t="n">
-        <v>4.23885</v>
+        <v>4.23203</v>
       </c>
       <c r="D20" t="n">
-        <v>17.2431</v>
+        <v>17.4892</v>
       </c>
       <c r="E20" t="n">
-        <v>2.48164</v>
+        <v>2.49638</v>
       </c>
       <c r="F20" t="n">
-        <v>2.95889</v>
+        <v>3.00667</v>
       </c>
     </row>
     <row r="21">
@@ -5459,19 +5459,19 @@
         <v>25171</v>
       </c>
       <c r="B21" t="n">
-        <v>6.81488</v>
+        <v>6.85504</v>
       </c>
       <c r="C21" t="n">
-        <v>5.52376</v>
+        <v>5.52991</v>
       </c>
       <c r="D21" t="n">
-        <v>12.1991</v>
+        <v>12.1787</v>
       </c>
       <c r="E21" t="n">
-        <v>1.96729</v>
+        <v>1.97816</v>
       </c>
       <c r="F21" t="n">
-        <v>2.22953</v>
+        <v>2.23879</v>
       </c>
     </row>
     <row r="22">
@@ -5479,19 +5479,19 @@
         <v>26421</v>
       </c>
       <c r="B22" t="n">
-        <v>9.049110000000001</v>
+        <v>9.08522</v>
       </c>
       <c r="C22" t="n">
-        <v>1.83786</v>
+        <v>1.83991</v>
       </c>
       <c r="D22" t="n">
-        <v>12.6571</v>
+        <v>12.6398</v>
       </c>
       <c r="E22" t="n">
-        <v>1.99684</v>
+        <v>1.99364</v>
       </c>
       <c r="F22" t="n">
-        <v>2.26061</v>
+        <v>2.27786</v>
       </c>
     </row>
     <row r="23">
@@ -5499,19 +5499,19 @@
         <v>27733</v>
       </c>
       <c r="B23" t="n">
-        <v>12.4009</v>
+        <v>12.4239</v>
       </c>
       <c r="C23" t="n">
-        <v>1.86588</v>
+        <v>1.80964</v>
       </c>
       <c r="D23" t="n">
-        <v>13.1636</v>
+        <v>13.15</v>
       </c>
       <c r="E23" t="n">
-        <v>2.00574</v>
+        <v>2.00455</v>
       </c>
       <c r="F23" t="n">
-        <v>2.30373</v>
+        <v>2.29184</v>
       </c>
     </row>
     <row r="24">
@@ -5519,19 +5519,19 @@
         <v>29110</v>
       </c>
       <c r="B24" t="n">
-        <v>2.91145</v>
+        <v>2.89787</v>
       </c>
       <c r="C24" t="n">
-        <v>1.85616</v>
+        <v>1.84161</v>
       </c>
       <c r="D24" t="n">
-        <v>13.7301</v>
+        <v>13.6858</v>
       </c>
       <c r="E24" t="n">
-        <v>2.04901</v>
+        <v>2.03054</v>
       </c>
       <c r="F24" t="n">
-        <v>2.34804</v>
+        <v>2.34178</v>
       </c>
     </row>
     <row r="25">
@@ -5539,19 +5539,19 @@
         <v>30555</v>
       </c>
       <c r="B25" t="n">
-        <v>2.92931</v>
+        <v>2.93153</v>
       </c>
       <c r="C25" t="n">
-        <v>1.91291</v>
+        <v>1.86718</v>
       </c>
       <c r="D25" t="n">
-        <v>14.2266</v>
+        <v>14.1831</v>
       </c>
       <c r="E25" t="n">
-        <v>2.0673</v>
+        <v>2.05869</v>
       </c>
       <c r="F25" t="n">
-        <v>2.367</v>
+        <v>2.37553</v>
       </c>
     </row>
     <row r="26">
@@ -5559,19 +5559,19 @@
         <v>32072</v>
       </c>
       <c r="B26" t="n">
-        <v>3.0215</v>
+        <v>3.01358</v>
       </c>
       <c r="C26" t="n">
-        <v>1.91836</v>
+        <v>1.99927</v>
       </c>
       <c r="D26" t="n">
-        <v>14.6686</v>
+        <v>14.612</v>
       </c>
       <c r="E26" t="n">
-        <v>2.08059</v>
+        <v>2.08018</v>
       </c>
       <c r="F26" t="n">
-        <v>2.40658</v>
+        <v>2.42759</v>
       </c>
     </row>
     <row r="27">
@@ -5579,19 +5579,19 @@
         <v>33664</v>
       </c>
       <c r="B27" t="n">
-        <v>3.08959</v>
+        <v>3.08086</v>
       </c>
       <c r="C27" t="n">
-        <v>1.99078</v>
+        <v>1.94096</v>
       </c>
       <c r="D27" t="n">
-        <v>15.165</v>
+        <v>15.1528</v>
       </c>
       <c r="E27" t="n">
-        <v>2.11749</v>
+        <v>2.10547</v>
       </c>
       <c r="F27" t="n">
-        <v>2.42516</v>
+        <v>2.46035</v>
       </c>
     </row>
     <row r="28">
@@ -5599,19 +5599,19 @@
         <v>35335</v>
       </c>
       <c r="B28" t="n">
-        <v>3.15384</v>
+        <v>3.14593</v>
       </c>
       <c r="C28" t="n">
-        <v>2.05129</v>
+        <v>2.00392</v>
       </c>
       <c r="D28" t="n">
-        <v>15.6134</v>
+        <v>15.5931</v>
       </c>
       <c r="E28" t="n">
-        <v>2.13748</v>
+        <v>2.14072</v>
       </c>
       <c r="F28" t="n">
-        <v>2.49253</v>
+        <v>2.5045</v>
       </c>
     </row>
     <row r="29">
@@ -5619,19 +5619,19 @@
         <v>37089</v>
       </c>
       <c r="B29" t="n">
-        <v>3.29915</v>
+        <v>3.29185</v>
       </c>
       <c r="C29" t="n">
-        <v>2.15807</v>
+        <v>2.14988</v>
       </c>
       <c r="D29" t="n">
-        <v>16.1341</v>
+        <v>16.1386</v>
       </c>
       <c r="E29" t="n">
-        <v>2.18256</v>
+        <v>2.17522</v>
       </c>
       <c r="F29" t="n">
-        <v>2.54832</v>
+        <v>2.57884</v>
       </c>
     </row>
     <row r="30">
@@ -5639,19 +5639,19 @@
         <v>38930</v>
       </c>
       <c r="B30" t="n">
-        <v>3.45547</v>
+        <v>3.44219</v>
       </c>
       <c r="C30" t="n">
-        <v>2.25205</v>
+        <v>2.23347</v>
       </c>
       <c r="D30" t="n">
-        <v>16.6485</v>
+        <v>16.6129</v>
       </c>
       <c r="E30" t="n">
-        <v>2.23083</v>
+        <v>2.22082</v>
       </c>
       <c r="F30" t="n">
-        <v>2.60007</v>
+        <v>2.61978</v>
       </c>
     </row>
     <row r="31">
@@ -5659,19 +5659,19 @@
         <v>40863</v>
       </c>
       <c r="B31" t="n">
-        <v>3.67626</v>
+        <v>3.66812</v>
       </c>
       <c r="C31" t="n">
-        <v>2.45704</v>
+        <v>2.40815</v>
       </c>
       <c r="D31" t="n">
-        <v>17.0362</v>
+        <v>17.0358</v>
       </c>
       <c r="E31" t="n">
-        <v>2.2555</v>
+        <v>2.25972</v>
       </c>
       <c r="F31" t="n">
-        <v>2.65153</v>
+        <v>2.67316</v>
       </c>
     </row>
     <row r="32">
@@ -5679,19 +5679,19 @@
         <v>42892</v>
       </c>
       <c r="B32" t="n">
-        <v>4.03898</v>
+        <v>4.03819</v>
       </c>
       <c r="C32" t="n">
-        <v>2.7225</v>
+        <v>2.694</v>
       </c>
       <c r="D32" t="n">
-        <v>17.4052</v>
+        <v>17.3944</v>
       </c>
       <c r="E32" t="n">
-        <v>2.32736</v>
+        <v>2.32573</v>
       </c>
       <c r="F32" t="n">
-        <v>2.81752</v>
+        <v>2.82566</v>
       </c>
     </row>
     <row r="33">
@@ -5699,19 +5699,19 @@
         <v>45022</v>
       </c>
       <c r="B33" t="n">
-        <v>4.68842</v>
+        <v>4.70012</v>
       </c>
       <c r="C33" t="n">
-        <v>3.29742</v>
+        <v>3.29752</v>
       </c>
       <c r="D33" t="n">
-        <v>17.8782</v>
+        <v>17.8818</v>
       </c>
       <c r="E33" t="n">
-        <v>2.50001</v>
+        <v>2.49419</v>
       </c>
       <c r="F33" t="n">
-        <v>3.00464</v>
+        <v>2.99545</v>
       </c>
     </row>
     <row r="34">
@@ -5719,19 +5719,19 @@
         <v>47258</v>
       </c>
       <c r="B34" t="n">
-        <v>5.62206</v>
+        <v>5.64548</v>
       </c>
       <c r="C34" t="n">
-        <v>4.15639</v>
+        <v>4.14793</v>
       </c>
       <c r="D34" t="n">
-        <v>18.316</v>
+        <v>18.2708</v>
       </c>
       <c r="E34" t="n">
-        <v>2.99022</v>
+        <v>2.99119</v>
       </c>
       <c r="F34" t="n">
-        <v>3.461</v>
+        <v>3.46228</v>
       </c>
     </row>
     <row r="35">
@@ -5739,19 +5739,19 @@
         <v>49605</v>
       </c>
       <c r="B35" t="n">
-        <v>7.11954</v>
+        <v>7.11877</v>
       </c>
       <c r="C35" t="n">
-        <v>5.31407</v>
+        <v>5.29861</v>
       </c>
       <c r="D35" t="n">
-        <v>12.7111</v>
+        <v>12.7389</v>
       </c>
       <c r="E35" t="n">
-        <v>2.01606</v>
+        <v>2.02954</v>
       </c>
       <c r="F35" t="n">
-        <v>2.35636</v>
+        <v>2.35467</v>
       </c>
     </row>
     <row r="36">
@@ -5759,19 +5759,19 @@
         <v>52069</v>
       </c>
       <c r="B36" t="n">
-        <v>9.24966</v>
+        <v>9.26243</v>
       </c>
       <c r="C36" t="n">
-        <v>6.93132</v>
+        <v>6.94572</v>
       </c>
       <c r="D36" t="n">
-        <v>13.1482</v>
+        <v>13.1628</v>
       </c>
       <c r="E36" t="n">
-        <v>2.04735</v>
+        <v>2.05071</v>
       </c>
       <c r="F36" t="n">
-        <v>2.39607</v>
+        <v>2.38338</v>
       </c>
     </row>
     <row r="37">
@@ -5779,19 +5779,19 @@
         <v>54656</v>
       </c>
       <c r="B37" t="n">
-        <v>12.8395</v>
+        <v>12.8374</v>
       </c>
       <c r="C37" t="n">
-        <v>1.85652</v>
+        <v>1.82983</v>
       </c>
       <c r="D37" t="n">
-        <v>13.6307</v>
+        <v>13.652</v>
       </c>
       <c r="E37" t="n">
-        <v>2.08165</v>
+        <v>2.07536</v>
       </c>
       <c r="F37" t="n">
-        <v>2.42738</v>
+        <v>2.44696</v>
       </c>
     </row>
     <row r="38">
@@ -5799,19 +5799,19 @@
         <v>57372</v>
       </c>
       <c r="B38" t="n">
-        <v>2.98254</v>
+        <v>2.96976</v>
       </c>
       <c r="C38" t="n">
-        <v>1.93045</v>
+        <v>1.86647</v>
       </c>
       <c r="D38" t="n">
-        <v>14.188</v>
+        <v>14.1997</v>
       </c>
       <c r="E38" t="n">
-        <v>2.09815</v>
+        <v>2.09334</v>
       </c>
       <c r="F38" t="n">
-        <v>2.48381</v>
+        <v>2.46633</v>
       </c>
     </row>
     <row r="39">
@@ -5819,19 +5819,19 @@
         <v>60223</v>
       </c>
       <c r="B39" t="n">
-        <v>3.01594</v>
+        <v>3.00337</v>
       </c>
       <c r="C39" t="n">
-        <v>1.90983</v>
+        <v>1.93394</v>
       </c>
       <c r="D39" t="n">
-        <v>14.6891</v>
+        <v>14.6984</v>
       </c>
       <c r="E39" t="n">
-        <v>2.11825</v>
+        <v>2.12175</v>
       </c>
       <c r="F39" t="n">
-        <v>2.51652</v>
+        <v>2.53954</v>
       </c>
     </row>
     <row r="40">
@@ -5839,19 +5839,19 @@
         <v>63216</v>
       </c>
       <c r="B40" t="n">
-        <v>3.08355</v>
+        <v>3.07137</v>
       </c>
       <c r="C40" t="n">
-        <v>1.98962</v>
+        <v>1.93586</v>
       </c>
       <c r="D40" t="n">
-        <v>15.208</v>
+        <v>15.2098</v>
       </c>
       <c r="E40" t="n">
-        <v>2.15995</v>
+        <v>2.14316</v>
       </c>
       <c r="F40" t="n">
-        <v>2.59043</v>
+        <v>2.58367</v>
       </c>
     </row>
     <row r="41">
@@ -5859,19 +5859,19 @@
         <v>66358</v>
       </c>
       <c r="B41" t="n">
-        <v>3.1618</v>
+        <v>3.13481</v>
       </c>
       <c r="C41" t="n">
-        <v>2.01837</v>
+        <v>2.00343</v>
       </c>
       <c r="D41" t="n">
-        <v>15.6772</v>
+        <v>15.6861</v>
       </c>
       <c r="E41" t="n">
-        <v>2.18543</v>
+        <v>2.18009</v>
       </c>
       <c r="F41" t="n">
-        <v>2.62766</v>
+        <v>2.62732</v>
       </c>
     </row>
     <row r="42">
@@ -5879,19 +5879,19 @@
         <v>69657</v>
       </c>
       <c r="B42" t="n">
-        <v>3.20413</v>
+        <v>3.19631</v>
       </c>
       <c r="C42" t="n">
-        <v>2.10664</v>
+        <v>2.06098</v>
       </c>
       <c r="D42" t="n">
-        <v>16.1483</v>
+        <v>16.1939</v>
       </c>
       <c r="E42" t="n">
-        <v>2.20405</v>
+        <v>2.21809</v>
       </c>
       <c r="F42" t="n">
-        <v>2.68186</v>
+        <v>2.70312</v>
       </c>
     </row>
     <row r="43">
@@ -5899,19 +5899,19 @@
         <v>73120</v>
       </c>
       <c r="B43" t="n">
-        <v>3.34408</v>
+        <v>3.33421</v>
       </c>
       <c r="C43" t="n">
-        <v>2.15448</v>
+        <v>2.15339</v>
       </c>
       <c r="D43" t="n">
-        <v>16.6354</v>
+        <v>16.6277</v>
       </c>
       <c r="E43" t="n">
-        <v>2.27</v>
+        <v>2.26102</v>
       </c>
       <c r="F43" t="n">
-        <v>2.76205</v>
+        <v>2.77208</v>
       </c>
     </row>
     <row r="44">
@@ -5919,19 +5919,19 @@
         <v>76756</v>
       </c>
       <c r="B44" t="n">
-        <v>3.5113</v>
+        <v>3.50387</v>
       </c>
       <c r="C44" t="n">
-        <v>2.30697</v>
+        <v>2.2719</v>
       </c>
       <c r="D44" t="n">
-        <v>17.0128</v>
+        <v>17.0692</v>
       </c>
       <c r="E44" t="n">
-        <v>2.35591</v>
+        <v>2.34</v>
       </c>
       <c r="F44" t="n">
-        <v>2.85219</v>
+        <v>2.85797</v>
       </c>
     </row>
     <row r="45">
@@ -5939,19 +5939,19 @@
         <v>80573</v>
       </c>
       <c r="B45" t="n">
-        <v>3.75112</v>
+        <v>3.73617</v>
       </c>
       <c r="C45" t="n">
-        <v>2.56761</v>
+        <v>2.53629</v>
       </c>
       <c r="D45" t="n">
-        <v>17.4295</v>
+        <v>17.4717</v>
       </c>
       <c r="E45" t="n">
-        <v>2.43843</v>
+        <v>2.43476</v>
       </c>
       <c r="F45" t="n">
-        <v>2.96913</v>
+        <v>2.98303</v>
       </c>
     </row>
     <row r="46">
@@ -5959,19 +5959,19 @@
         <v>84580</v>
       </c>
       <c r="B46" t="n">
-        <v>4.09229</v>
+        <v>4.07445</v>
       </c>
       <c r="C46" t="n">
-        <v>2.8731</v>
+        <v>2.86546</v>
       </c>
       <c r="D46" t="n">
-        <v>17.8264</v>
+        <v>17.8757</v>
       </c>
       <c r="E46" t="n">
-        <v>2.58511</v>
+        <v>2.57434</v>
       </c>
       <c r="F46" t="n">
-        <v>3.10603</v>
+        <v>3.14215</v>
       </c>
     </row>
     <row r="47">
@@ -5979,19 +5979,19 @@
         <v>88787</v>
       </c>
       <c r="B47" t="n">
-        <v>4.65031</v>
+        <v>4.63382</v>
       </c>
       <c r="C47" t="n">
-        <v>3.36215</v>
+        <v>3.35305</v>
       </c>
       <c r="D47" t="n">
-        <v>18.2258</v>
+        <v>18.2978</v>
       </c>
       <c r="E47" t="n">
-        <v>2.83485</v>
+        <v>2.83338</v>
       </c>
       <c r="F47" t="n">
-        <v>3.37364</v>
+        <v>3.36643</v>
       </c>
     </row>
     <row r="48">
@@ -5999,19 +5999,19 @@
         <v>93204</v>
       </c>
       <c r="B48" t="n">
-        <v>5.38192</v>
+        <v>5.39028</v>
       </c>
       <c r="C48" t="n">
-        <v>4.05093</v>
+        <v>4.04503</v>
       </c>
       <c r="D48" t="n">
-        <v>18.7116</v>
+        <v>18.7476</v>
       </c>
       <c r="E48" t="n">
-        <v>3.23673</v>
+        <v>3.22315</v>
       </c>
       <c r="F48" t="n">
-        <v>3.74325</v>
+        <v>3.74048</v>
       </c>
     </row>
     <row r="49">
@@ -6019,19 +6019,19 @@
         <v>97841</v>
       </c>
       <c r="B49" t="n">
-        <v>6.46965</v>
+        <v>6.46784</v>
       </c>
       <c r="C49" t="n">
-        <v>5.02854</v>
+        <v>5.00845</v>
       </c>
       <c r="D49" t="n">
-        <v>19.1714</v>
+        <v>19.1839</v>
       </c>
       <c r="E49" t="n">
-        <v>3.73812</v>
+        <v>3.73042</v>
       </c>
       <c r="F49" t="n">
-        <v>4.24093</v>
+        <v>4.24995</v>
       </c>
     </row>
     <row r="50">
@@ -6039,19 +6039,19 @@
         <v>102709</v>
       </c>
       <c r="B50" t="n">
-        <v>8.31686</v>
+        <v>8.337820000000001</v>
       </c>
       <c r="C50" t="n">
-        <v>6.48365</v>
+        <v>6.47971</v>
       </c>
       <c r="D50" t="n">
-        <v>13.4513</v>
+        <v>13.4275</v>
       </c>
       <c r="E50" t="n">
-        <v>2.21203</v>
+        <v>2.14015</v>
       </c>
       <c r="F50" t="n">
-        <v>2.67285</v>
+        <v>2.6086</v>
       </c>
     </row>
     <row r="51">
@@ -6059,19 +6059,19 @@
         <v>107820</v>
       </c>
       <c r="B51" t="n">
-        <v>10.8707</v>
+        <v>10.8681</v>
       </c>
       <c r="C51" t="n">
-        <v>1.94565</v>
+        <v>1.87269</v>
       </c>
       <c r="D51" t="n">
-        <v>13.9347</v>
+        <v>13.9344</v>
       </c>
       <c r="E51" t="n">
-        <v>2.23265</v>
+        <v>2.15555</v>
       </c>
       <c r="F51" t="n">
-        <v>2.69375</v>
+        <v>2.63709</v>
       </c>
     </row>
     <row r="52">
@@ -6079,19 +6079,19 @@
         <v>113186</v>
       </c>
       <c r="B52" t="n">
-        <v>15.3281</v>
+        <v>15.3413</v>
       </c>
       <c r="C52" t="n">
-        <v>2.01914</v>
+        <v>2.12139</v>
       </c>
       <c r="D52" t="n">
-        <v>14.4196</v>
+        <v>14.4121</v>
       </c>
       <c r="E52" t="n">
-        <v>2.26012</v>
+        <v>2.18674</v>
       </c>
       <c r="F52" t="n">
-        <v>2.7701</v>
+        <v>2.7713</v>
       </c>
     </row>
     <row r="53">
@@ -6099,19 +6099,19 @@
         <v>118820</v>
       </c>
       <c r="B53" t="n">
-        <v>3.12278</v>
+        <v>3.10736</v>
       </c>
       <c r="C53" t="n">
-        <v>2.0871</v>
+        <v>1.98175</v>
       </c>
       <c r="D53" t="n">
-        <v>14.9054</v>
+        <v>14.902</v>
       </c>
       <c r="E53" t="n">
-        <v>2.29086</v>
+        <v>2.21659</v>
       </c>
       <c r="F53" t="n">
-        <v>2.79841</v>
+        <v>2.7341</v>
       </c>
     </row>
     <row r="54">
@@ -6119,19 +6119,19 @@
         <v>124735</v>
       </c>
       <c r="B54" t="n">
-        <v>3.18366</v>
+        <v>3.13618</v>
       </c>
       <c r="C54" t="n">
-        <v>2.4418</v>
+        <v>2.15329</v>
       </c>
       <c r="D54" t="n">
-        <v>15.4057</v>
+        <v>15.4018</v>
       </c>
       <c r="E54" t="n">
-        <v>2.84385</v>
+        <v>2.367</v>
       </c>
       <c r="F54" t="n">
-        <v>2.86299</v>
+        <v>2.86195</v>
       </c>
     </row>
     <row r="55">
@@ -6139,19 +6139,19 @@
         <v>130945</v>
       </c>
       <c r="B55" t="n">
-        <v>3.24894</v>
+        <v>3.22552</v>
       </c>
       <c r="C55" t="n">
-        <v>2.59577</v>
+        <v>2.07765</v>
       </c>
       <c r="D55" t="n">
-        <v>15.8769</v>
+        <v>15.869</v>
       </c>
       <c r="E55" t="n">
-        <v>2.43207</v>
+        <v>2.69306</v>
       </c>
       <c r="F55" t="n">
-        <v>2.96339</v>
+        <v>2.94678</v>
       </c>
     </row>
     <row r="56">
@@ -6159,19 +6159,19 @@
         <v>137465</v>
       </c>
       <c r="B56" t="n">
-        <v>3.35663</v>
+        <v>3.35711</v>
       </c>
       <c r="C56" t="n">
-        <v>2.18978</v>
+        <v>2.31849</v>
       </c>
       <c r="D56" t="n">
-        <v>16.3379</v>
+        <v>16.3376</v>
       </c>
       <c r="E56" t="n">
-        <v>2.48169</v>
+        <v>2.74196</v>
       </c>
       <c r="F56" t="n">
-        <v>3.02248</v>
+        <v>3.01282</v>
       </c>
     </row>
     <row r="57">
@@ -6179,19 +6179,19 @@
         <v>144311</v>
       </c>
       <c r="B57" t="n">
-        <v>3.46171</v>
+        <v>3.46128</v>
       </c>
       <c r="C57" t="n">
-        <v>2.49035</v>
+        <v>2.31614</v>
       </c>
       <c r="D57" t="n">
-        <v>16.8027</v>
+        <v>16.7992</v>
       </c>
       <c r="E57" t="n">
-        <v>3.00042</v>
+        <v>2.51348</v>
       </c>
       <c r="F57" t="n">
-        <v>3.02274</v>
+        <v>3.182</v>
       </c>
     </row>
     <row r="58">
@@ -6199,19 +6199,19 @@
         <v>151499</v>
       </c>
       <c r="B58" t="n">
-        <v>3.6389</v>
+        <v>3.61873</v>
       </c>
       <c r="C58" t="n">
-        <v>2.40216</v>
+        <v>2.4189</v>
       </c>
       <c r="D58" t="n">
-        <v>17.2179</v>
+        <v>17.2225</v>
       </c>
       <c r="E58" t="n">
-        <v>3.01407</v>
+        <v>2.62638</v>
       </c>
       <c r="F58" t="n">
-        <v>3.11198</v>
+        <v>3.19624</v>
       </c>
     </row>
     <row r="59">
@@ -6219,19 +6219,19 @@
         <v>159046</v>
       </c>
       <c r="B59" t="n">
-        <v>3.84817</v>
+        <v>3.78866</v>
       </c>
       <c r="C59" t="n">
-        <v>2.80028</v>
+        <v>2.65709</v>
       </c>
       <c r="D59" t="n">
-        <v>17.643</v>
+        <v>17.6514</v>
       </c>
       <c r="E59" t="n">
-        <v>3.14569</v>
+        <v>2.80117</v>
       </c>
       <c r="F59" t="n">
-        <v>3.22606</v>
+        <v>3.20774</v>
       </c>
     </row>
     <row r="60">
@@ -6239,19 +6239,19 @@
         <v>166970</v>
       </c>
       <c r="B60" t="n">
-        <v>4.21935</v>
+        <v>4.26332</v>
       </c>
       <c r="C60" t="n">
-        <v>3.39407</v>
+        <v>2.99919</v>
       </c>
       <c r="D60" t="n">
-        <v>18.0301</v>
+        <v>18.0313</v>
       </c>
       <c r="E60" t="n">
-        <v>3.26657</v>
+        <v>2.90326</v>
       </c>
       <c r="F60" t="n">
-        <v>3.36713</v>
+        <v>3.30137</v>
       </c>
     </row>
     <row r="61">
@@ -6259,19 +6259,19 @@
         <v>175290</v>
       </c>
       <c r="B61" t="n">
-        <v>4.58273</v>
+        <v>4.61221</v>
       </c>
       <c r="C61" t="n">
-        <v>3.28212</v>
+        <v>3.21195</v>
       </c>
       <c r="D61" t="n">
-        <v>18.4575</v>
+        <v>18.5467</v>
       </c>
       <c r="E61" t="n">
-        <v>3.11946</v>
+        <v>3.14568</v>
       </c>
       <c r="F61" t="n">
-        <v>3.54672</v>
+        <v>3.56755</v>
       </c>
     </row>
     <row r="62">
@@ -6279,19 +6279,19 @@
         <v>184026</v>
       </c>
       <c r="B62" t="n">
-        <v>5.24231</v>
+        <v>5.2539</v>
       </c>
       <c r="C62" t="n">
-        <v>3.93103</v>
+        <v>4.01734</v>
       </c>
       <c r="D62" t="n">
-        <v>18.8874</v>
+        <v>18.8979</v>
       </c>
       <c r="E62" t="n">
-        <v>3.39674</v>
+        <v>3.41481</v>
       </c>
       <c r="F62" t="n">
-        <v>3.88994</v>
+        <v>3.82616</v>
       </c>
     </row>
     <row r="63">
@@ -6299,19 +6299,19 @@
         <v>193198</v>
       </c>
       <c r="B63" t="n">
-        <v>6.30964</v>
+        <v>6.32583</v>
       </c>
       <c r="C63" t="n">
-        <v>4.84138</v>
+        <v>4.93654</v>
       </c>
       <c r="D63" t="n">
-        <v>19.3338</v>
+        <v>19.4515</v>
       </c>
       <c r="E63" t="n">
-        <v>3.83657</v>
+        <v>3.85743</v>
       </c>
       <c r="F63" t="n">
-        <v>4.30419</v>
+        <v>4.31669</v>
       </c>
     </row>
     <row r="64">
@@ -6319,19 +6319,19 @@
         <v>202828</v>
       </c>
       <c r="B64" t="n">
-        <v>7.86861</v>
+        <v>7.83118</v>
       </c>
       <c r="C64" t="n">
-        <v>6.13655</v>
+        <v>6.15207</v>
       </c>
       <c r="D64" t="n">
-        <v>14.7269</v>
+        <v>14.1204</v>
       </c>
       <c r="E64" t="n">
-        <v>2.68888</v>
+        <v>2.83528</v>
       </c>
       <c r="F64" t="n">
-        <v>3.39699</v>
+        <v>3.33187</v>
       </c>
     </row>
     <row r="65">
@@ -6339,19 +6339,19 @@
         <v>212939</v>
       </c>
       <c r="B65" t="n">
-        <v>10.5012</v>
+        <v>10.5243</v>
       </c>
       <c r="C65" t="n">
-        <v>2.2951</v>
+        <v>2.35888</v>
       </c>
       <c r="D65" t="n">
-        <v>15.2098</v>
+        <v>14.7739</v>
       </c>
       <c r="E65" t="n">
-        <v>2.71229</v>
+        <v>2.82965</v>
       </c>
       <c r="F65" t="n">
-        <v>3.45298</v>
+        <v>3.38423</v>
       </c>
     </row>
     <row r="66">
@@ -6359,19 +6359,19 @@
         <v>223555</v>
       </c>
       <c r="B66" t="n">
-        <v>14.3979</v>
+        <v>14.4513</v>
       </c>
       <c r="C66" t="n">
-        <v>2.29165</v>
+        <v>2.441</v>
       </c>
       <c r="D66" t="n">
-        <v>15.9588</v>
+        <v>15.6384</v>
       </c>
       <c r="E66" t="n">
-        <v>2.65531</v>
+        <v>2.81315</v>
       </c>
       <c r="F66" t="n">
-        <v>3.50981</v>
+        <v>3.43461</v>
       </c>
     </row>
     <row r="67">
@@ -6379,19 +6379,19 @@
         <v>234701</v>
       </c>
       <c r="B67" t="n">
-        <v>3.94676</v>
+        <v>3.53067</v>
       </c>
       <c r="C67" t="n">
-        <v>2.31621</v>
+        <v>2.44338</v>
       </c>
       <c r="D67" t="n">
-        <v>16.8297</v>
+        <v>16.3084</v>
       </c>
       <c r="E67" t="n">
-        <v>2.71183</v>
+        <v>2.86263</v>
       </c>
       <c r="F67" t="n">
-        <v>3.57125</v>
+        <v>3.48783</v>
       </c>
     </row>
     <row r="68">
@@ -6399,19 +6399,19 @@
         <v>246404</v>
       </c>
       <c r="B68" t="n">
-        <v>4.01886</v>
+        <v>3.63427</v>
       </c>
       <c r="C68" t="n">
-        <v>2.35053</v>
+        <v>2.48532</v>
       </c>
       <c r="D68" t="n">
-        <v>17.682</v>
+        <v>17.0807</v>
       </c>
       <c r="E68" t="n">
-        <v>2.76169</v>
+        <v>2.74621</v>
       </c>
       <c r="F68" t="n">
-        <v>3.628</v>
+        <v>3.54184</v>
       </c>
     </row>
     <row r="69">
@@ -6419,19 +6419,19 @@
         <v>258692</v>
       </c>
       <c r="B69" t="n">
-        <v>3.78118</v>
+        <v>3.6825</v>
       </c>
       <c r="C69" t="n">
-        <v>2.43806</v>
+        <v>2.50658</v>
       </c>
       <c r="D69" t="n">
-        <v>18.5225</v>
+        <v>17.8468</v>
       </c>
       <c r="E69" t="n">
-        <v>2.7823</v>
+        <v>2.98544</v>
       </c>
       <c r="F69" t="n">
-        <v>3.70297</v>
+        <v>3.60848</v>
       </c>
     </row>
     <row r="70">
@@ -6439,19 +6439,19 @@
         <v>271594</v>
       </c>
       <c r="B70" t="n">
-        <v>4.18934</v>
+        <v>3.83232</v>
       </c>
       <c r="C70" t="n">
-        <v>2.50811</v>
+        <v>2.62516</v>
       </c>
       <c r="D70" t="n">
-        <v>19.7324</v>
+        <v>18.7619</v>
       </c>
       <c r="E70" t="n">
-        <v>2.89094</v>
+        <v>2.96019</v>
       </c>
       <c r="F70" t="n">
-        <v>3.78343</v>
+        <v>3.68199</v>
       </c>
     </row>
     <row r="71">
@@ -6459,19 +6459,19 @@
         <v>285141</v>
       </c>
       <c r="B71" t="n">
-        <v>3.93956</v>
+        <v>3.81373</v>
       </c>
       <c r="C71" t="n">
-        <v>2.64543</v>
+        <v>2.68728</v>
       </c>
       <c r="D71" t="n">
-        <v>21.4593</v>
+        <v>19.8036</v>
       </c>
       <c r="E71" t="n">
-        <v>2.92271</v>
+        <v>2.92563</v>
       </c>
       <c r="F71" t="n">
-        <v>3.77366</v>
+        <v>3.73831</v>
       </c>
     </row>
     <row r="72">
@@ -6479,19 +6479,19 @@
         <v>299365</v>
       </c>
       <c r="B72" t="n">
-        <v>4.14687</v>
+        <v>4.08107</v>
       </c>
       <c r="C72" t="n">
-        <v>2.69165</v>
+        <v>2.7523</v>
       </c>
       <c r="D72" t="n">
-        <v>23.2299</v>
+        <v>20.7096</v>
       </c>
       <c r="E72" t="n">
-        <v>3.00203</v>
+        <v>3.00192</v>
       </c>
       <c r="F72" t="n">
-        <v>3.87267</v>
+        <v>3.83979</v>
       </c>
     </row>
     <row r="73">
@@ -6499,19 +6499,19 @@
         <v>314300</v>
       </c>
       <c r="B73" t="n">
-        <v>4.69588</v>
+        <v>4.35135</v>
       </c>
       <c r="C73" t="n">
-        <v>2.91721</v>
+        <v>2.99462</v>
       </c>
       <c r="D73" t="n">
-        <v>25.0733</v>
+        <v>22.1991</v>
       </c>
       <c r="E73" t="n">
-        <v>3.09385</v>
+        <v>3.08966</v>
       </c>
       <c r="F73" t="n">
-        <v>3.9979</v>
+        <v>3.96635</v>
       </c>
     </row>
     <row r="74">
@@ -6519,19 +6519,19 @@
         <v>329981</v>
       </c>
       <c r="B74" t="n">
-        <v>4.65724</v>
+        <v>4.46562</v>
       </c>
       <c r="C74" t="n">
-        <v>3.25376</v>
+        <v>3.24831</v>
       </c>
       <c r="D74" t="n">
-        <v>26.1561</v>
+        <v>23.8844</v>
       </c>
       <c r="E74" t="n">
-        <v>3.19621</v>
+        <v>3.46205</v>
       </c>
       <c r="F74" t="n">
-        <v>4.13114</v>
+        <v>4.1318</v>
       </c>
     </row>
     <row r="75">
@@ -6539,19 +6539,19 @@
         <v>346446</v>
       </c>
       <c r="B75" t="n">
-        <v>4.95577</v>
+        <v>5.22259</v>
       </c>
       <c r="C75" t="n">
-        <v>3.55308</v>
+        <v>3.90848</v>
       </c>
       <c r="D75" t="n">
-        <v>26.8816</v>
+        <v>24.9108</v>
       </c>
       <c r="E75" t="n">
-        <v>3.4121</v>
+        <v>3.74373</v>
       </c>
       <c r="F75" t="n">
-        <v>4.3879</v>
+        <v>4.31782</v>
       </c>
     </row>
     <row r="76">
@@ -6559,19 +6559,19 @@
         <v>363734</v>
       </c>
       <c r="B76" t="n">
-        <v>5.51437</v>
+        <v>5.86973</v>
       </c>
       <c r="C76" t="n">
-        <v>4.1229</v>
+        <v>4.46921</v>
       </c>
       <c r="D76" t="n">
-        <v>28.2916</v>
+        <v>26.428</v>
       </c>
       <c r="E76" t="n">
-        <v>3.64148</v>
+        <v>3.86862</v>
       </c>
       <c r="F76" t="n">
-        <v>4.58565</v>
+        <v>4.62154</v>
       </c>
     </row>
     <row r="77">
@@ -6579,19 +6579,19 @@
         <v>381886</v>
       </c>
       <c r="B77" t="n">
-        <v>6.5078</v>
+        <v>6.83678</v>
       </c>
       <c r="C77" t="n">
-        <v>5.0073</v>
+        <v>5.19202</v>
       </c>
       <c r="D77" t="n">
-        <v>29.8204</v>
+        <v>27.7495</v>
       </c>
       <c r="E77" t="n">
-        <v>4.04619</v>
+        <v>4.34886</v>
       </c>
       <c r="F77" t="n">
-        <v>5.16269</v>
+        <v>5.0776</v>
       </c>
     </row>
     <row r="78">
@@ -6599,19 +6599,19 @@
         <v>400945</v>
       </c>
       <c r="B78" t="n">
-        <v>8.6013</v>
+        <v>8.31016</v>
       </c>
       <c r="C78" t="n">
-        <v>6.3127</v>
+        <v>6.31446</v>
       </c>
       <c r="D78" t="n">
-        <v>24.1758</v>
+        <v>25.0108</v>
       </c>
       <c r="E78" t="n">
-        <v>2.98092</v>
+        <v>3.07339</v>
       </c>
       <c r="F78" t="n">
-        <v>3.75277</v>
+        <v>3.8269</v>
       </c>
     </row>
     <row r="79">
@@ -6619,19 +6619,19 @@
         <v>420956</v>
       </c>
       <c r="B79" t="n">
-        <v>10.3202</v>
+        <v>11.1786</v>
       </c>
       <c r="C79" t="n">
-        <v>2.58472</v>
+        <v>2.67509</v>
       </c>
       <c r="D79" t="n">
-        <v>25.3882</v>
+        <v>26.2075</v>
       </c>
       <c r="E79" t="n">
-        <v>3.02335</v>
+        <v>3.11157</v>
       </c>
       <c r="F79" t="n">
-        <v>3.83532</v>
+        <v>3.89669</v>
       </c>
     </row>
     <row r="80">
@@ -6639,19 +6639,19 @@
         <v>441967</v>
       </c>
       <c r="B80" t="n">
-        <v>14.3164</v>
+        <v>15.2055</v>
       </c>
       <c r="C80" t="n">
-        <v>2.63088</v>
+        <v>2.73758</v>
       </c>
       <c r="D80" t="n">
-        <v>26.6138</v>
+        <v>27.5279</v>
       </c>
       <c r="E80" t="n">
-        <v>3.0495</v>
+        <v>3.15539</v>
       </c>
       <c r="F80" t="n">
-        <v>3.91258</v>
+        <v>3.99831</v>
       </c>
     </row>
     <row r="81">
@@ -6659,19 +6659,19 @@
         <v>464028</v>
       </c>
       <c r="B81" t="n">
-        <v>4.10459</v>
+        <v>4.25978</v>
       </c>
       <c r="C81" t="n">
-        <v>2.74153</v>
+        <v>2.82649</v>
       </c>
       <c r="D81" t="n">
-        <v>27.7872</v>
+        <v>28.7569</v>
       </c>
       <c r="E81" t="n">
-        <v>3.10546</v>
+        <v>3.18844</v>
       </c>
       <c r="F81" t="n">
-        <v>4.0153</v>
+        <v>4.15283</v>
       </c>
     </row>
     <row r="82">
@@ -6679,19 +6679,19 @@
         <v>487192</v>
       </c>
       <c r="B82" t="n">
-        <v>4.24083</v>
+        <v>4.38736</v>
       </c>
       <c r="C82" t="n">
-        <v>2.8264</v>
+        <v>2.90863</v>
       </c>
       <c r="D82" t="n">
-        <v>29.1113</v>
+        <v>30.1422</v>
       </c>
       <c r="E82" t="n">
-        <v>3.14794</v>
+        <v>3.26146</v>
       </c>
       <c r="F82" t="n">
-        <v>4.16748</v>
+        <v>4.25435</v>
       </c>
     </row>
     <row r="83">
@@ -6699,19 +6699,19 @@
         <v>511514</v>
       </c>
       <c r="B83" t="n">
-        <v>4.41761</v>
+        <v>4.60091</v>
       </c>
       <c r="C83" t="n">
-        <v>2.94142</v>
+        <v>3.02225</v>
       </c>
       <c r="D83" t="n">
-        <v>30.4155</v>
+        <v>31.525</v>
       </c>
       <c r="E83" t="n">
-        <v>3.25768</v>
+        <v>3.30444</v>
       </c>
       <c r="F83" t="n">
-        <v>4.34106</v>
+        <v>4.46243</v>
       </c>
     </row>
     <row r="84">
@@ -6719,19 +6719,19 @@
         <v>537052</v>
       </c>
       <c r="B84" t="n">
-        <v>4.63506</v>
+        <v>4.83165</v>
       </c>
       <c r="C84" t="n">
-        <v>3.09063</v>
+        <v>3.16672</v>
       </c>
       <c r="D84" t="n">
-        <v>31.7296</v>
+        <v>33.0242</v>
       </c>
       <c r="E84" t="n">
-        <v>3.35748</v>
+        <v>3.42318</v>
       </c>
       <c r="F84" t="n">
-        <v>4.5288</v>
+        <v>4.72795</v>
       </c>
     </row>
     <row r="85">
@@ -6739,19 +6739,19 @@
         <v>563866</v>
       </c>
       <c r="B85" t="n">
-        <v>4.8787</v>
+        <v>5.03764</v>
       </c>
       <c r="C85" t="n">
-        <v>3.31286</v>
+        <v>3.28853</v>
       </c>
       <c r="D85" t="n">
-        <v>33.2317</v>
+        <v>34.5861</v>
       </c>
       <c r="E85" t="n">
-        <v>3.44305</v>
+        <v>3.54704</v>
       </c>
       <c r="F85" t="n">
-        <v>5.32167</v>
+        <v>4.86533</v>
       </c>
     </row>
     <row r="86">
@@ -6759,19 +6759,19 @@
         <v>592020</v>
       </c>
       <c r="B86" t="n">
-        <v>5.27596</v>
+        <v>5.46481</v>
       </c>
       <c r="C86" t="n">
-        <v>3.54017</v>
+        <v>3.62338</v>
       </c>
       <c r="D86" t="n">
-        <v>34.6096</v>
+        <v>36.0165</v>
       </c>
       <c r="E86" t="n">
-        <v>3.61235</v>
+        <v>3.75643</v>
       </c>
       <c r="F86" t="n">
-        <v>5.72451</v>
+        <v>5.26209</v>
       </c>
     </row>
     <row r="87">
@@ -6779,19 +6779,19 @@
         <v>621581</v>
       </c>
       <c r="B87" t="n">
-        <v>5.74323</v>
+        <v>5.88117</v>
       </c>
       <c r="C87" t="n">
-        <v>3.85669</v>
+        <v>3.93023</v>
       </c>
       <c r="D87" t="n">
-        <v>36.2216</v>
+        <v>37.6292</v>
       </c>
       <c r="E87" t="n">
-        <v>3.86608</v>
+        <v>3.93118</v>
       </c>
       <c r="F87" t="n">
-        <v>6.23627</v>
+        <v>5.6823</v>
       </c>
     </row>
     <row r="88">
@@ -6799,19 +6799,19 @@
         <v>652620</v>
       </c>
       <c r="B88" t="n">
-        <v>6.3165</v>
+        <v>6.30334</v>
       </c>
       <c r="C88" t="n">
-        <v>4.22337</v>
+        <v>4.16231</v>
       </c>
       <c r="D88" t="n">
-        <v>37.8117</v>
+        <v>38.2522</v>
       </c>
       <c r="E88" t="n">
-        <v>4.10158</v>
+        <v>4.17135</v>
       </c>
       <c r="F88" t="n">
-        <v>6.18151</v>
+        <v>6.12814</v>
       </c>
     </row>
     <row r="89">
@@ -6819,19 +6819,19 @@
         <v>685210</v>
       </c>
       <c r="B89" t="n">
-        <v>6.86642</v>
+        <v>6.95113</v>
       </c>
       <c r="C89" t="n">
-        <v>4.65659</v>
+        <v>4.66083</v>
       </c>
       <c r="D89" t="n">
-        <v>40.1074</v>
+        <v>40.1282</v>
       </c>
       <c r="E89" t="n">
-        <v>4.47446</v>
+        <v>4.48072</v>
       </c>
       <c r="F89" t="n">
-        <v>7.14713</v>
+        <v>6.6399</v>
       </c>
     </row>
     <row r="90">
@@ -6839,19 +6839,19 @@
         <v>719429</v>
       </c>
       <c r="B90" t="n">
-        <v>7.65188</v>
+        <v>7.85811</v>
       </c>
       <c r="C90" t="n">
-        <v>5.24681</v>
+        <v>5.27605</v>
       </c>
       <c r="D90" t="n">
-        <v>41.411</v>
+        <v>42.7893</v>
       </c>
       <c r="E90" t="n">
-        <v>4.88106</v>
+        <v>4.928</v>
       </c>
       <c r="F90" t="n">
-        <v>7.39874</v>
+        <v>7.8006</v>
       </c>
     </row>
     <row r="91">
@@ -6859,19 +6859,19 @@
         <v>755358</v>
       </c>
       <c r="B91" t="n">
-        <v>8.73756</v>
+        <v>9.091810000000001</v>
       </c>
       <c r="C91" t="n">
-        <v>6.16135</v>
+        <v>6.23997</v>
       </c>
       <c r="D91" t="n">
-        <v>43.3519</v>
+        <v>44.9146</v>
       </c>
       <c r="E91" t="n">
-        <v>5.45774</v>
+        <v>5.47278</v>
       </c>
       <c r="F91" t="n">
-        <v>8.28861</v>
+        <v>8.669560000000001</v>
       </c>
     </row>
     <row r="92">
@@ -6879,19 +6879,19 @@
         <v>793083</v>
       </c>
       <c r="B92" t="n">
-        <v>10.2427</v>
+        <v>10.6363</v>
       </c>
       <c r="C92" t="n">
-        <v>7.39273</v>
+        <v>7.49482</v>
       </c>
       <c r="D92" t="n">
-        <v>35.1625</v>
+        <v>36.8217</v>
       </c>
       <c r="E92" t="n">
-        <v>3.78328</v>
+        <v>3.78282</v>
       </c>
       <c r="F92" t="n">
-        <v>5.52054</v>
+        <v>5.48305</v>
       </c>
     </row>
     <row r="93">
@@ -6899,19 +6899,19 @@
         <v>832694</v>
       </c>
       <c r="B93" t="n">
-        <v>12.5539</v>
+        <v>13.0649</v>
       </c>
       <c r="C93" t="n">
-        <v>9.171659999999999</v>
+        <v>9.41093</v>
       </c>
       <c r="D93" t="n">
-        <v>36.3963</v>
+        <v>37.9944</v>
       </c>
       <c r="E93" t="n">
-        <v>3.92749</v>
+        <v>3.92987</v>
       </c>
       <c r="F93" t="n">
-        <v>5.64323</v>
+        <v>5.87433</v>
       </c>
     </row>
     <row r="94">
@@ -6919,19 +6919,19 @@
         <v>874285</v>
       </c>
       <c r="B94" t="n">
-        <v>15.7071</v>
+        <v>16.9748</v>
       </c>
       <c r="C94" t="n">
-        <v>3.67543</v>
+        <v>3.64263</v>
       </c>
       <c r="D94" t="n">
-        <v>37.6554</v>
+        <v>39.1601</v>
       </c>
       <c r="E94" t="n">
-        <v>4.0284</v>
+        <v>4.10004</v>
       </c>
       <c r="F94" t="n">
-        <v>6.07826</v>
+        <v>6.1948</v>
       </c>
     </row>
     <row r="95">
@@ -6939,19 +6939,19 @@
         <v>917955</v>
       </c>
       <c r="B95" t="n">
-        <v>5.94247</v>
+        <v>5.97367</v>
       </c>
       <c r="C95" t="n">
-        <v>3.75988</v>
+        <v>3.83224</v>
       </c>
       <c r="D95" t="n">
-        <v>38.9378</v>
+        <v>40.5085</v>
       </c>
       <c r="E95" t="n">
-        <v>4.20077</v>
+        <v>4.27788</v>
       </c>
       <c r="F95" t="n">
-        <v>6.22342</v>
+        <v>6.45741</v>
       </c>
     </row>
     <row r="96">
@@ -6959,19 +6959,19 @@
         <v>963808</v>
       </c>
       <c r="B96" t="n">
-        <v>6.16371</v>
+        <v>6.26774</v>
       </c>
       <c r="C96" t="n">
-        <v>3.91461</v>
+        <v>4.01356</v>
       </c>
       <c r="D96" t="n">
-        <v>40.1522</v>
+        <v>41.8525</v>
       </c>
       <c r="E96" t="n">
-        <v>4.38121</v>
+        <v>4.45648</v>
       </c>
       <c r="F96" t="n">
-        <v>6.65392</v>
+        <v>6.82398</v>
       </c>
     </row>
     <row r="97">
@@ -6979,19 +6979,19 @@
         <v>1011953</v>
       </c>
       <c r="B97" t="n">
-        <v>6.40511</v>
+        <v>6.52261</v>
       </c>
       <c r="C97" t="n">
-        <v>4.13055</v>
+        <v>4.17434</v>
       </c>
       <c r="D97" t="n">
-        <v>41.5396</v>
+        <v>43.1724</v>
       </c>
       <c r="E97" t="n">
-        <v>4.58707</v>
+        <v>4.64078</v>
       </c>
       <c r="F97" t="n">
-        <v>6.91641</v>
+        <v>7.05211</v>
       </c>
     </row>
     <row r="98">
@@ -6999,19 +6999,19 @@
         <v>1062505</v>
       </c>
       <c r="B98" t="n">
-        <v>6.70034</v>
+        <v>6.84044</v>
       </c>
       <c r="C98" t="n">
-        <v>4.28133</v>
+        <v>4.33485</v>
       </c>
       <c r="D98" t="n">
-        <v>42.8342</v>
+        <v>44.4762</v>
       </c>
       <c r="E98" t="n">
-        <v>4.75123</v>
+        <v>4.82307</v>
       </c>
       <c r="F98" t="n">
-        <v>7.23432</v>
+        <v>7.39064</v>
       </c>
     </row>
     <row r="99">
@@ -7019,19 +7019,19 @@
         <v>1115584</v>
       </c>
       <c r="B99" t="n">
-        <v>7.03737</v>
+        <v>7.12342</v>
       </c>
       <c r="C99" t="n">
-        <v>4.46075</v>
+        <v>4.55796</v>
       </c>
       <c r="D99" t="n">
-        <v>44.2617</v>
+        <v>45.9151</v>
       </c>
       <c r="E99" t="n">
-        <v>4.92101</v>
+        <v>5.00184</v>
       </c>
       <c r="F99" t="n">
-        <v>7.61091</v>
+        <v>7.65379</v>
       </c>
     </row>
     <row r="100">
@@ -7039,19 +7039,19 @@
         <v>1171316</v>
       </c>
       <c r="B100" t="n">
-        <v>7.32328</v>
+        <v>7.49869</v>
       </c>
       <c r="C100" t="n">
-        <v>4.68827</v>
+        <v>4.77789</v>
       </c>
       <c r="D100" t="n">
-        <v>45.728</v>
+        <v>47.439</v>
       </c>
       <c r="E100" t="n">
-        <v>5.12675</v>
+        <v>5.16726</v>
       </c>
       <c r="F100" t="n">
-        <v>7.99698</v>
+        <v>8.0008</v>
       </c>
     </row>
     <row r="101">
@@ -7059,19 +7059,19 @@
         <v>1229834</v>
       </c>
       <c r="B101" t="n">
-        <v>7.67513</v>
+        <v>7.79835</v>
       </c>
       <c r="C101" t="n">
-        <v>4.94275</v>
+        <v>5.06625</v>
       </c>
       <c r="D101" t="n">
-        <v>47.1066</v>
+        <v>48.448</v>
       </c>
       <c r="E101" t="n">
-        <v>5.34233</v>
+        <v>5.37379</v>
       </c>
       <c r="F101" t="n">
-        <v>8.297280000000001</v>
+        <v>8.542920000000001</v>
       </c>
     </row>
     <row r="102">
@@ -7079,19 +7079,19 @@
         <v>1291277</v>
       </c>
       <c r="B102" t="n">
-        <v>8.08127</v>
+        <v>8.26792</v>
       </c>
       <c r="C102" t="n">
-        <v>5.28428</v>
+        <v>5.40882</v>
       </c>
       <c r="D102" t="n">
-        <v>48.8743</v>
+        <v>50.6232</v>
       </c>
       <c r="E102" t="n">
-        <v>5.57096</v>
+        <v>5.60327</v>
       </c>
       <c r="F102" t="n">
-        <v>8.78424</v>
+        <v>9.15432</v>
       </c>
     </row>
     <row r="103">
@@ -7099,19 +7099,19 @@
         <v>1355792</v>
       </c>
       <c r="B103" t="n">
-        <v>8.6586</v>
+        <v>8.852959999999999</v>
       </c>
       <c r="C103" t="n">
-        <v>5.67941</v>
+        <v>5.84569</v>
       </c>
       <c r="D103" t="n">
-        <v>50.7064</v>
+        <v>52.2652</v>
       </c>
       <c r="E103" t="n">
-        <v>5.82108</v>
+        <v>5.88574</v>
       </c>
       <c r="F103" t="n">
-        <v>9.37973</v>
+        <v>9.47448</v>
       </c>
     </row>
     <row r="104">
@@ -7119,19 +7119,19 @@
         <v>1423532</v>
       </c>
       <c r="B104" t="n">
-        <v>9.391030000000001</v>
+        <v>9.62448</v>
       </c>
       <c r="C104" t="n">
-        <v>6.2574</v>
+        <v>6.47503</v>
       </c>
       <c r="D104" t="n">
-        <v>52.309</v>
+        <v>54.0463</v>
       </c>
       <c r="E104" t="n">
-        <v>6.18888</v>
+        <v>6.22928</v>
       </c>
       <c r="F104" t="n">
-        <v>10.1281</v>
+        <v>10.5531</v>
       </c>
     </row>
     <row r="105">
@@ -7139,19 +7139,19 @@
         <v>1494659</v>
       </c>
       <c r="B105" t="n">
-        <v>10.4556</v>
+        <v>10.6612</v>
       </c>
       <c r="C105" t="n">
-        <v>7.07903</v>
+        <v>7.31337</v>
       </c>
       <c r="D105" t="n">
-        <v>54.0902</v>
+        <v>55.9032</v>
       </c>
       <c r="E105" t="n">
-        <v>6.6861</v>
+        <v>6.74706</v>
       </c>
       <c r="F105" t="n">
-        <v>11.0168</v>
+        <v>11.1233</v>
       </c>
     </row>
     <row r="106">
@@ -7159,19 +7159,19 @@
         <v>1569342</v>
       </c>
       <c r="B106" t="n">
-        <v>11.9729</v>
+        <v>12.2637</v>
       </c>
       <c r="C106" t="n">
-        <v>8.26329</v>
+        <v>8.43411</v>
       </c>
       <c r="D106" t="n">
-        <v>56.0963</v>
+        <v>57.3541</v>
       </c>
       <c r="E106" t="n">
-        <v>7.39064</v>
+        <v>7.44114</v>
       </c>
       <c r="F106" t="n">
-        <v>12.2622</v>
+        <v>12.6353</v>
       </c>
     </row>
     <row r="107">
@@ -7179,19 +7179,19 @@
         <v>1647759</v>
       </c>
       <c r="B107" t="n">
-        <v>13.9834</v>
+        <v>14.481</v>
       </c>
       <c r="C107" t="n">
-        <v>9.98019</v>
+        <v>10.1167</v>
       </c>
       <c r="D107" t="n">
-        <v>42.5705</v>
+        <v>43.8137</v>
       </c>
       <c r="E107" t="n">
-        <v>4.78769</v>
+        <v>4.85503</v>
       </c>
       <c r="F107" t="n">
-        <v>7.20561</v>
+        <v>7.28852</v>
       </c>
     </row>
     <row r="108">
@@ -7199,19 +7199,19 @@
         <v>1730096</v>
       </c>
       <c r="B108" t="n">
-        <v>17.1021</v>
+        <v>17.7414</v>
       </c>
       <c r="C108" t="n">
-        <v>4.37325</v>
+        <v>4.43697</v>
       </c>
       <c r="D108" t="n">
-        <v>43.7513</v>
+        <v>44.9385</v>
       </c>
       <c r="E108" t="n">
-        <v>4.90648</v>
+        <v>4.80574</v>
       </c>
       <c r="F108" t="n">
-        <v>7.3696</v>
+        <v>7.5962</v>
       </c>
     </row>
     <row r="109">
@@ -7219,19 +7219,19 @@
         <v>1816549</v>
       </c>
       <c r="B109" t="n">
-        <v>21.895</v>
+        <v>23.002</v>
       </c>
       <c r="C109" t="n">
-        <v>4.53272</v>
+        <v>4.56629</v>
       </c>
       <c r="D109" t="n">
-        <v>44.9346</v>
+        <v>46.2027</v>
       </c>
       <c r="E109" t="n">
-        <v>4.99543</v>
+        <v>5.04337</v>
       </c>
       <c r="F109" t="n">
-        <v>7.66471</v>
+        <v>7.96304</v>
       </c>
     </row>
     <row r="110">
@@ -7239,19 +7239,19 @@
         <v>1907324</v>
       </c>
       <c r="B110" t="n">
-        <v>7.23412</v>
+        <v>7.42654</v>
       </c>
       <c r="C110" t="n">
-        <v>4.6443</v>
+        <v>4.67544</v>
       </c>
       <c r="D110" t="n">
-        <v>46.1713</v>
+        <v>47.3917</v>
       </c>
       <c r="E110" t="n">
-        <v>5.12202</v>
+        <v>5.1825</v>
       </c>
       <c r="F110" t="n">
-        <v>8.27543</v>
+        <v>8.374650000000001</v>
       </c>
     </row>
     <row r="111">
@@ -7259,19 +7259,19 @@
         <v>2002637</v>
       </c>
       <c r="B111" t="n">
-        <v>7.57048</v>
+        <v>7.78837</v>
       </c>
       <c r="C111" t="n">
-        <v>4.82582</v>
+        <v>4.88859</v>
       </c>
       <c r="D111" t="n">
-        <v>47.3924</v>
+        <v>48.8</v>
       </c>
       <c r="E111" t="n">
-        <v>5.26294</v>
+        <v>5.42467</v>
       </c>
       <c r="F111" t="n">
-        <v>8.77647</v>
+        <v>8.90882</v>
       </c>
     </row>
     <row r="112">
@@ -7279,19 +7279,19 @@
         <v>2102715</v>
       </c>
       <c r="B112" t="n">
-        <v>7.88402</v>
+        <v>8.05613</v>
       </c>
       <c r="C112" t="n">
-        <v>5.04025</v>
+        <v>5.06659</v>
       </c>
       <c r="D112" t="n">
-        <v>48.69</v>
+        <v>50.0319</v>
       </c>
       <c r="E112" t="n">
-        <v>5.36413</v>
+        <v>5.49294</v>
       </c>
       <c r="F112" t="n">
-        <v>9.21725</v>
+        <v>9.35999</v>
       </c>
     </row>
     <row r="113">
@@ -7299,19 +7299,19 @@
         <v>2207796</v>
       </c>
       <c r="B113" t="n">
-        <v>8.279439999999999</v>
+        <v>8.48692</v>
       </c>
       <c r="C113" t="n">
-        <v>5.2281</v>
+        <v>5.47469</v>
       </c>
       <c r="D113" t="n">
-        <v>50.064</v>
+        <v>51.4167</v>
       </c>
       <c r="E113" t="n">
-        <v>5.62153</v>
+        <v>5.69987</v>
       </c>
       <c r="F113" t="n">
-        <v>9.69683</v>
+        <v>9.88987</v>
       </c>
     </row>
     <row r="114">
@@ -7319,19 +7319,19 @@
         <v>2318131</v>
       </c>
       <c r="B114" t="n">
-        <v>8.66755</v>
+        <v>8.92717</v>
       </c>
       <c r="C114" t="n">
-        <v>5.49824</v>
+        <v>5.6128</v>
       </c>
       <c r="D114" t="n">
-        <v>51.4654</v>
+        <v>52.831</v>
       </c>
       <c r="E114" t="n">
-        <v>5.78377</v>
+        <v>5.91644</v>
       </c>
       <c r="F114" t="n">
-        <v>10.2535</v>
+        <v>10.4735</v>
       </c>
     </row>
     <row r="115">
@@ -7339,19 +7339,19 @@
         <v>2433982</v>
       </c>
       <c r="B115" t="n">
-        <v>9.23335</v>
+        <v>9.55842</v>
       </c>
       <c r="C115" t="n">
-        <v>5.85003</v>
+        <v>6.00671</v>
       </c>
       <c r="D115" t="n">
-        <v>52.9368</v>
+        <v>54.3372</v>
       </c>
       <c r="E115" t="n">
-        <v>6.14348</v>
+        <v>6.25721</v>
       </c>
       <c r="F115" t="n">
-        <v>10.8553</v>
+        <v>11.0509</v>
       </c>
     </row>
     <row r="116">
@@ -7359,19 +7359,19 @@
         <v>2555625</v>
       </c>
       <c r="B116" t="n">
-        <v>9.881880000000001</v>
+        <v>10.2165</v>
       </c>
       <c r="C116" t="n">
-        <v>6.31465</v>
+        <v>6.50842</v>
       </c>
       <c r="D116" t="n">
-        <v>54.4963</v>
+        <v>55.9479</v>
       </c>
       <c r="E116" t="n">
-        <v>6.59475</v>
+        <v>6.6769</v>
       </c>
       <c r="F116" t="n">
-        <v>11.4428</v>
+        <v>11.6901</v>
       </c>
     </row>
     <row r="117">
@@ -7379,19 +7379,19 @@
         <v>2683350</v>
       </c>
       <c r="B117" t="n">
-        <v>10.5581</v>
+        <v>10.9008</v>
       </c>
       <c r="C117" t="n">
-        <v>6.8257</v>
+        <v>7.05255</v>
       </c>
       <c r="D117" t="n">
-        <v>56.1467</v>
+        <v>57.7046</v>
       </c>
       <c r="E117" t="n">
-        <v>7.03622</v>
+        <v>7.1027</v>
       </c>
       <c r="F117" t="n">
-        <v>11.9673</v>
+        <v>12.2191</v>
       </c>
     </row>
     <row r="118">
@@ -7399,19 +7399,19 @@
         <v>2817461</v>
       </c>
       <c r="B118" t="n">
-        <v>11.3072</v>
+        <v>11.6561</v>
       </c>
       <c r="C118" t="n">
-        <v>7.39994</v>
+        <v>7.68435</v>
       </c>
       <c r="D118" t="n">
-        <v>57.8034</v>
+        <v>59.3289</v>
       </c>
       <c r="E118" t="n">
-        <v>7.45525</v>
+        <v>7.56529</v>
       </c>
       <c r="F118" t="n">
-        <v>12.658</v>
+        <v>12.9276</v>
       </c>
     </row>
     <row r="119">
@@ -7419,19 +7419,19 @@
         <v>2958277</v>
       </c>
       <c r="B119" t="n">
-        <v>12.2773</v>
+        <v>12.6535</v>
       </c>
       <c r="C119" t="n">
-        <v>8.15639</v>
+        <v>8.484640000000001</v>
       </c>
       <c r="D119" t="n">
-        <v>59.6345</v>
+        <v>61.1944</v>
       </c>
       <c r="E119" t="n">
-        <v>8.0669</v>
+        <v>8.14733</v>
       </c>
       <c r="F119" t="n">
-        <v>13.4572</v>
+        <v>13.6032</v>
       </c>
     </row>
     <row r="120">
@@ -7439,19 +7439,19 @@
         <v>3106133</v>
       </c>
       <c r="B120" t="n">
-        <v>13.5465</v>
+        <v>13.9538</v>
       </c>
       <c r="C120" t="n">
-        <v>9.20012</v>
+        <v>9.51498</v>
       </c>
       <c r="D120" t="n">
-        <v>61.5293</v>
+        <v>63.2171</v>
       </c>
       <c r="E120" t="n">
-        <v>8.75234</v>
+        <v>8.88021</v>
       </c>
       <c r="F120" t="n">
-        <v>14.3655</v>
+        <v>14.7072</v>
       </c>
     </row>
     <row r="121">
@@ -7459,19 +7459,19 @@
         <v>3261381</v>
       </c>
       <c r="B121" t="n">
-        <v>15.2728</v>
+        <v>15.7846</v>
       </c>
       <c r="C121" t="n">
-        <v>10.7261</v>
+        <v>11.0743</v>
       </c>
       <c r="D121" t="n">
-        <v>45.7031</v>
+        <v>47.11</v>
       </c>
       <c r="E121" t="n">
-        <v>6.4558</v>
+        <v>6.56617</v>
       </c>
       <c r="F121" t="n">
-        <v>10.6432</v>
+        <v>10.2913</v>
       </c>
     </row>
     <row r="122">
@@ -7479,19 +7479,19 @@
         <v>3424391</v>
       </c>
       <c r="B122" t="n">
-        <v>17.9223</v>
+        <v>18.6817</v>
       </c>
       <c r="C122" t="n">
-        <v>6.20037</v>
+        <v>6.22883</v>
       </c>
       <c r="D122" t="n">
-        <v>46.8216</v>
+        <v>48.4778</v>
       </c>
       <c r="E122" t="n">
-        <v>6.52592</v>
+        <v>7.08016</v>
       </c>
       <c r="F122" t="n">
-        <v>10.8109</v>
+        <v>10.8541</v>
       </c>
     </row>
     <row r="123">
@@ -7499,19 +7499,19 @@
         <v>3595551</v>
       </c>
       <c r="B123" t="n">
-        <v>22.1449</v>
+        <v>23.1118</v>
       </c>
       <c r="C123" t="n">
-        <v>6.4034</v>
+        <v>6.59794</v>
       </c>
       <c r="D123" t="n">
-        <v>48.0334</v>
+        <v>49.6408</v>
       </c>
       <c r="E123" t="n">
-        <v>6.50181</v>
+        <v>7.22012</v>
       </c>
       <c r="F123" t="n">
-        <v>10.5983</v>
+        <v>11.3514</v>
       </c>
     </row>
     <row r="124">
@@ -7519,19 +7519,19 @@
         <v>3775269</v>
       </c>
       <c r="B124" t="n">
-        <v>9.4505</v>
+        <v>9.95715</v>
       </c>
       <c r="C124" t="n">
-        <v>6.38398</v>
+        <v>6.4795</v>
       </c>
       <c r="D124" t="n">
-        <v>49.2687</v>
+        <v>50.8481</v>
       </c>
       <c r="E124" t="n">
-        <v>7.22392</v>
+        <v>7.30055</v>
       </c>
       <c r="F124" t="n">
-        <v>11.2453</v>
+        <v>11.5725</v>
       </c>
     </row>
     <row r="125">
@@ -7539,19 +7539,19 @@
         <v>3963972</v>
       </c>
       <c r="B125" t="n">
-        <v>9.55517</v>
+        <v>10.1521</v>
       </c>
       <c r="C125" t="n">
-        <v>6.34879</v>
+        <v>6.59039</v>
       </c>
       <c r="D125" t="n">
-        <v>50.3389</v>
+        <v>52.2798</v>
       </c>
       <c r="E125" t="n">
-        <v>7.5915</v>
+        <v>7.51573</v>
       </c>
       <c r="F125" t="n">
-        <v>11.4211</v>
+        <v>11.6769</v>
       </c>
     </row>
     <row r="126">
@@ -7559,19 +7559,19 @@
         <v>4162110</v>
       </c>
       <c r="B126" t="n">
-        <v>10.048</v>
+        <v>10.3119</v>
       </c>
       <c r="C126" t="n">
-        <v>6.67343</v>
+        <v>6.90924</v>
       </c>
       <c r="D126" t="n">
-        <v>51.8381</v>
+        <v>53.4251</v>
       </c>
       <c r="E126" t="n">
-        <v>7.67055</v>
+        <v>7.74228</v>
       </c>
       <c r="F126" t="n">
-        <v>11.9983</v>
+        <v>12.1396</v>
       </c>
     </row>
     <row r="127">
@@ -7579,19 +7579,19 @@
         <v>4370154</v>
       </c>
       <c r="B127" t="n">
-        <v>10.6291</v>
+        <v>10.6652</v>
       </c>
       <c r="C127" t="n">
-        <v>6.67081</v>
+        <v>6.9047</v>
       </c>
       <c r="D127" t="n">
-        <v>53.187</v>
+        <v>54.9921</v>
       </c>
       <c r="E127" t="n">
-        <v>7.93568</v>
+        <v>8.233689999999999</v>
       </c>
       <c r="F127" t="n">
-        <v>12.1706</v>
+        <v>12.5147</v>
       </c>
     </row>
     <row r="128">
@@ -7599,19 +7599,19 @@
         <v>4588600</v>
       </c>
       <c r="B128" t="n">
-        <v>10.6239</v>
+        <v>11.0473</v>
       </c>
       <c r="C128" t="n">
-        <v>7.05686</v>
+        <v>7.26824</v>
       </c>
       <c r="D128" t="n">
-        <v>54.6052</v>
+        <v>56.1947</v>
       </c>
       <c r="E128" t="n">
-        <v>7.90093</v>
+        <v>8.079230000000001</v>
       </c>
       <c r="F128" t="n">
-        <v>12.5345</v>
+        <v>12.876</v>
       </c>
     </row>
     <row r="129">
@@ -7619,19 +7619,19 @@
         <v>4817968</v>
       </c>
       <c r="B129" t="n">
-        <v>11.1709</v>
+        <v>11.1976</v>
       </c>
       <c r="C129" t="n">
-        <v>7.34921</v>
+        <v>7.50604</v>
       </c>
       <c r="D129" t="n">
-        <v>56.0998</v>
+        <v>57.7961</v>
       </c>
       <c r="E129" t="n">
-        <v>8.218680000000001</v>
+        <v>8.56166</v>
       </c>
       <c r="F129" t="n">
-        <v>13.1279</v>
+        <v>13.1201</v>
       </c>
     </row>
     <row r="130">
@@ -7639,19 +7639,19 @@
         <v>5058804</v>
       </c>
       <c r="B130" t="n">
-        <v>11.5048</v>
+        <v>11.6962</v>
       </c>
       <c r="C130" t="n">
-        <v>7.6137</v>
+        <v>7.79934</v>
       </c>
       <c r="D130" t="n">
-        <v>57.5597</v>
+        <v>59.1228</v>
       </c>
       <c r="E130" t="n">
-        <v>8.450290000000001</v>
+        <v>8.65024</v>
       </c>
       <c r="F130" t="n">
-        <v>13.4448</v>
+        <v>13.9372</v>
       </c>
     </row>
     <row r="131">
@@ -7659,19 +7659,19 @@
         <v>5311681</v>
       </c>
       <c r="B131" t="n">
-        <v>11.4144</v>
+        <v>12.1964</v>
       </c>
       <c r="C131" t="n">
-        <v>7.73197</v>
+        <v>8.02692</v>
       </c>
       <c r="D131" t="n">
-        <v>59.1888</v>
+        <v>60.8161</v>
       </c>
       <c r="E131" t="n">
-        <v>8.72292</v>
+        <v>8.997159999999999</v>
       </c>
       <c r="F131" t="n">
-        <v>13.935</v>
+        <v>14.3722</v>
       </c>
     </row>
     <row r="132">
@@ -7679,19 +7679,19 @@
         <v>5577201</v>
       </c>
       <c r="B132" t="n">
-        <v>12.4869</v>
+        <v>12.9618</v>
       </c>
       <c r="C132" t="n">
-        <v>8.31889</v>
+        <v>8.646420000000001</v>
       </c>
       <c r="D132" t="n">
-        <v>60.9081</v>
+        <v>62.5874</v>
       </c>
       <c r="E132" t="n">
-        <v>8.89099</v>
+        <v>9.33</v>
       </c>
       <c r="F132" t="n">
-        <v>14.5413</v>
+        <v>15.0583</v>
       </c>
     </row>
     <row r="133">
@@ -7699,19 +7699,19 @@
         <v>5855997</v>
       </c>
       <c r="B133" t="n">
-        <v>13.5316</v>
+        <v>13.7429</v>
       </c>
       <c r="C133" t="n">
-        <v>8.88273</v>
+        <v>9.273820000000001</v>
       </c>
       <c r="D133" t="n">
-        <v>62.4934</v>
+        <v>64.3751</v>
       </c>
       <c r="E133" t="n">
-        <v>9.46274</v>
+        <v>9.612270000000001</v>
       </c>
       <c r="F133" t="n">
-        <v>15.3416</v>
+        <v>15.708</v>
       </c>
     </row>
     <row r="134">
@@ -7719,19 +7719,19 @@
         <v>6148732</v>
       </c>
       <c r="B134" t="n">
-        <v>14.35</v>
+        <v>14.8663</v>
       </c>
       <c r="C134" t="n">
-        <v>9.92084</v>
+        <v>10.2715</v>
       </c>
       <c r="D134" t="n">
-        <v>64.37</v>
+        <v>66.30410000000001</v>
       </c>
       <c r="E134" t="n">
-        <v>10.0161</v>
+        <v>10.0906</v>
       </c>
       <c r="F134" t="n">
-        <v>16.2604</v>
+        <v>16.5279</v>
       </c>
     </row>
     <row r="135">
@@ -7739,19 +7739,19 @@
         <v>6456103</v>
       </c>
       <c r="B135" t="n">
-        <v>15.9914</v>
+        <v>16.4299</v>
       </c>
       <c r="C135" t="n">
-        <v>11.1209</v>
+        <v>11.5568</v>
       </c>
       <c r="D135" t="n">
-        <v>47.3738</v>
+        <v>49.0165</v>
       </c>
       <c r="E135" t="n">
-        <v>12.6641</v>
+        <v>13.1922</v>
       </c>
       <c r="F135" t="n">
-        <v>17.354</v>
+        <v>17.5336</v>
       </c>
     </row>
     <row r="136">
@@ -7759,19 +7759,19 @@
         <v>6778842</v>
       </c>
       <c r="B136" t="n">
-        <v>17.9669</v>
+        <v>18.917</v>
       </c>
       <c r="C136" t="n">
-        <v>11.7854</v>
+        <v>11.9428</v>
       </c>
       <c r="D136" t="n">
-        <v>48.5508</v>
+        <v>50.0063</v>
       </c>
       <c r="E136" t="n">
-        <v>13.3344</v>
+        <v>13.0833</v>
       </c>
       <c r="F136" t="n">
-        <v>17.4509</v>
+        <v>17.8534</v>
       </c>
     </row>
     <row r="137">
@@ -7779,19 +7779,19 @@
         <v>7117717</v>
       </c>
       <c r="B137" t="n">
-        <v>21.8829</v>
+        <v>23.0673</v>
       </c>
       <c r="C137" t="n">
-        <v>11.0818</v>
+        <v>12.0686</v>
       </c>
       <c r="D137" t="n">
-        <v>49.7606</v>
+        <v>51.2237</v>
       </c>
       <c r="E137" t="n">
-        <v>13.5093</v>
+        <v>13.6601</v>
       </c>
       <c r="F137" t="n">
-        <v>17.5946</v>
+        <v>17.9974</v>
       </c>
     </row>
     <row r="138">
@@ -7799,19 +7799,19 @@
         <v>7473535</v>
       </c>
       <c r="B138" t="n">
-        <v>16.1054</v>
+        <v>16.5568</v>
       </c>
       <c r="C138" t="n">
-        <v>12.0319</v>
+        <v>12.0495</v>
       </c>
       <c r="D138" t="n">
-        <v>51.0046</v>
+        <v>52.7346</v>
       </c>
       <c r="E138" t="n">
-        <v>13.4715</v>
+        <v>13.9001</v>
       </c>
       <c r="F138" t="n">
-        <v>17.9149</v>
+        <v>18.4758</v>
       </c>
     </row>
     <row r="139">
@@ -7819,19 +7819,19 @@
         <v>7847143</v>
       </c>
       <c r="B139" t="n">
-        <v>16.2692</v>
+        <v>16.6864</v>
       </c>
       <c r="C139" t="n">
-        <v>12.2977</v>
+        <v>12.3015</v>
       </c>
       <c r="D139" t="n">
-        <v>52.3371</v>
+        <v>53.858</v>
       </c>
       <c r="E139" t="n">
-        <v>13.6241</v>
+        <v>13.8684</v>
       </c>
       <c r="F139" t="n">
-        <v>18.2989</v>
+        <v>18.0392</v>
       </c>
     </row>
     <row r="140">
@@ -7839,19 +7839,19 @@
         <v>8239431</v>
       </c>
       <c r="B140" t="n">
-        <v>16.3038</v>
+        <v>17.0168</v>
       </c>
       <c r="C140" t="n">
-        <v>12.1181</v>
+        <v>12.408</v>
       </c>
       <c r="D140" t="n">
-        <v>53.6064</v>
+        <v>55.1972</v>
       </c>
       <c r="E140" t="n">
-        <v>13.7715</v>
+        <v>13.8942</v>
       </c>
       <c r="F140" t="n">
-        <v>18.5731</v>
+        <v>19.1573</v>
       </c>
     </row>
     <row r="141">
@@ -7859,19 +7859,19 @@
         <v>8651333</v>
       </c>
       <c r="B141" t="n">
-        <v>15.8896</v>
+        <v>17.1053</v>
       </c>
       <c r="C141" t="n">
-        <v>12.286</v>
+        <v>12.4458</v>
       </c>
       <c r="D141" t="n">
-        <v>54.9865</v>
+        <v>56.3302</v>
       </c>
       <c r="E141" t="n">
-        <v>13.955</v>
+        <v>14.2459</v>
       </c>
       <c r="F141" t="n">
-        <v>18.9532</v>
+        <v>18.8207</v>
       </c>
     </row>
     <row r="142">
@@ -7879,19 +7879,19 @@
         <v>9083830</v>
       </c>
       <c r="B142" t="n">
-        <v>16.8045</v>
+        <v>17.3525</v>
       </c>
       <c r="C142" t="n">
-        <v>12.411</v>
+        <v>12.4872</v>
       </c>
       <c r="D142" t="n">
-        <v>56.2807</v>
+        <v>57.8384</v>
       </c>
       <c r="E142" t="n">
-        <v>13.3779</v>
+        <v>14.2547</v>
       </c>
       <c r="F142" t="n">
-        <v>19.2696</v>
+        <v>19.7023</v>
       </c>
     </row>
     <row r="143">
@@ -7899,19 +7899,19 @@
         <v>9537951</v>
       </c>
       <c r="B143" t="n">
-        <v>17.1283</v>
+        <v>17.6349</v>
       </c>
       <c r="C143" t="n">
-        <v>12.6161</v>
+        <v>12.6683</v>
       </c>
       <c r="D143" t="n">
-        <v>57.8263</v>
+        <v>59.6077</v>
       </c>
       <c r="E143" t="n">
-        <v>14.231</v>
+        <v>14.2408</v>
       </c>
       <c r="F143" t="n">
-        <v>19.7388</v>
+        <v>19.6265</v>
       </c>
     </row>
   </sheetData>

--- a/gcc-x64/Scattered unsuccessful looukp.xlsx
+++ b/gcc-x64/Scattered unsuccessful looukp.xlsx
@@ -5079,19 +5079,19 @@
         <v>10000</v>
       </c>
       <c r="B2" t="n">
-        <v>2.85902</v>
+        <v>2.84976</v>
       </c>
       <c r="C2" t="n">
-        <v>1.9148</v>
+        <v>2.29331</v>
       </c>
       <c r="D2" t="n">
-        <v>13.5611</v>
+        <v>13.3546</v>
       </c>
       <c r="E2" t="n">
-        <v>1.90636</v>
+        <v>2.39717</v>
       </c>
       <c r="F2" t="n">
-        <v>2.28759</v>
+        <v>2.62141</v>
       </c>
     </row>
     <row r="3">
@@ -5099,19 +5099,19 @@
         <v>10500</v>
       </c>
       <c r="B3" t="n">
-        <v>2.93908</v>
+        <v>2.96323</v>
       </c>
       <c r="C3" t="n">
-        <v>1.97463</v>
+        <v>2.32521</v>
       </c>
       <c r="D3" t="n">
-        <v>14.5136</v>
+        <v>13.7075</v>
       </c>
       <c r="E3" t="n">
-        <v>1.67153</v>
+        <v>2.4238</v>
       </c>
       <c r="F3" t="n">
-        <v>2.20635</v>
+        <v>2.65403</v>
       </c>
     </row>
     <row r="4">
@@ -5119,19 +5119,19 @@
         <v>11025</v>
       </c>
       <c r="B4" t="n">
-        <v>3.06154</v>
+        <v>3.05475</v>
       </c>
       <c r="C4" t="n">
-        <v>2.09949</v>
+        <v>2.40675</v>
       </c>
       <c r="D4" t="n">
-        <v>15.1148</v>
+        <v>14.2233</v>
       </c>
       <c r="E4" t="n">
-        <v>1.66876</v>
+        <v>2.4311</v>
       </c>
       <c r="F4" t="n">
-        <v>2.15927</v>
+        <v>2.64693</v>
       </c>
     </row>
     <row r="5">
@@ -5139,19 +5139,19 @@
         <v>11576</v>
       </c>
       <c r="B5" t="n">
-        <v>3.41637</v>
+        <v>3.54807</v>
       </c>
       <c r="C5" t="n">
-        <v>2.27832</v>
+        <v>2.61908</v>
       </c>
       <c r="D5" t="n">
-        <v>15.6131</v>
+        <v>15.0297</v>
       </c>
       <c r="E5" t="n">
-        <v>1.69177</v>
+        <v>2.29577</v>
       </c>
       <c r="F5" t="n">
-        <v>2.1425</v>
+        <v>2.63871</v>
       </c>
     </row>
     <row r="6">
@@ -5159,19 +5159,19 @@
         <v>12154</v>
       </c>
       <c r="B6" t="n">
-        <v>4.30059</v>
+        <v>4.74079</v>
       </c>
       <c r="C6" t="n">
-        <v>2.87753</v>
+        <v>3.66963</v>
       </c>
       <c r="D6" t="n">
-        <v>16.1434</v>
+        <v>15.5707</v>
       </c>
       <c r="E6" t="n">
-        <v>1.80468</v>
+        <v>2.33084</v>
       </c>
       <c r="F6" t="n">
-        <v>2.26922</v>
+        <v>2.64503</v>
       </c>
     </row>
     <row r="7">
@@ -5179,19 +5179,19 @@
         <v>12760</v>
       </c>
       <c r="B7" t="n">
-        <v>6.55384</v>
+        <v>6.70184</v>
       </c>
       <c r="C7" t="n">
-        <v>5.02472</v>
+        <v>6.08353</v>
       </c>
       <c r="D7" t="n">
-        <v>11.0272</v>
+        <v>11.1978</v>
       </c>
       <c r="E7" t="n">
-        <v>1.88226</v>
+        <v>2.46864</v>
       </c>
       <c r="F7" t="n">
-        <v>2.09571</v>
+        <v>2.61484</v>
       </c>
     </row>
     <row r="8">
@@ -5199,19 +5199,19 @@
         <v>13396</v>
       </c>
       <c r="B8" t="n">
-        <v>9.38223</v>
+        <v>9.39382</v>
       </c>
       <c r="C8" t="n">
-        <v>1.71718</v>
+        <v>2.1117</v>
       </c>
       <c r="D8" t="n">
-        <v>11.6031</v>
+        <v>11.7621</v>
       </c>
       <c r="E8" t="n">
-        <v>1.89865</v>
+        <v>2.49207</v>
       </c>
       <c r="F8" t="n">
-        <v>2.11178</v>
+        <v>2.61725</v>
       </c>
     </row>
     <row r="9">
@@ -5219,19 +5219,19 @@
         <v>14063</v>
       </c>
       <c r="B9" t="n">
-        <v>13.7494</v>
+        <v>13.7808</v>
       </c>
       <c r="C9" t="n">
-        <v>1.74047</v>
+        <v>2.12353</v>
       </c>
       <c r="D9" t="n">
-        <v>12.1725</v>
+        <v>12.3582</v>
       </c>
       <c r="E9" t="n">
-        <v>1.90905</v>
+        <v>2.50651</v>
       </c>
       <c r="F9" t="n">
-        <v>2.12884</v>
+        <v>2.67277</v>
       </c>
     </row>
     <row r="10">
@@ -5239,19 +5239,19 @@
         <v>14763</v>
       </c>
       <c r="B10" t="n">
-        <v>2.80055</v>
+        <v>2.83408</v>
       </c>
       <c r="C10" t="n">
-        <v>1.93351</v>
+        <v>2.11062</v>
       </c>
       <c r="D10" t="n">
-        <v>12.8904</v>
+        <v>12.9758</v>
       </c>
       <c r="E10" t="n">
-        <v>1.92496</v>
+        <v>2.52632</v>
       </c>
       <c r="F10" t="n">
-        <v>2.15998</v>
+        <v>2.69923</v>
       </c>
     </row>
     <row r="11">
@@ -5259,19 +5259,19 @@
         <v>15498</v>
       </c>
       <c r="B11" t="n">
-        <v>2.84071</v>
+        <v>2.88648</v>
       </c>
       <c r="C11" t="n">
-        <v>1.81984</v>
+        <v>2.13888</v>
       </c>
       <c r="D11" t="n">
-        <v>13.3778</v>
+        <v>13.4216</v>
       </c>
       <c r="E11" t="n">
-        <v>1.9273</v>
+        <v>2.56623</v>
       </c>
       <c r="F11" t="n">
-        <v>2.19012</v>
+        <v>2.76724</v>
       </c>
     </row>
     <row r="12">
@@ -5279,19 +5279,19 @@
         <v>16269</v>
       </c>
       <c r="B12" t="n">
-        <v>2.88695</v>
+        <v>2.90789</v>
       </c>
       <c r="C12" t="n">
-        <v>1.84963</v>
+        <v>2.21287</v>
       </c>
       <c r="D12" t="n">
-        <v>13.8966</v>
+        <v>13.9178</v>
       </c>
       <c r="E12" t="n">
-        <v>1.93468</v>
+        <v>2.56335</v>
       </c>
       <c r="F12" t="n">
-        <v>2.20918</v>
+        <v>2.82109</v>
       </c>
     </row>
     <row r="13">
@@ -5299,19 +5299,19 @@
         <v>17078</v>
       </c>
       <c r="B13" t="n">
-        <v>2.88068</v>
+        <v>3.00103</v>
       </c>
       <c r="C13" t="n">
-        <v>1.86884</v>
+        <v>2.29006</v>
       </c>
       <c r="D13" t="n">
-        <v>14.3734</v>
+        <v>14.5833</v>
       </c>
       <c r="E13" t="n">
-        <v>1.93886</v>
+        <v>2.58246</v>
       </c>
       <c r="F13" t="n">
-        <v>2.23738</v>
+        <v>2.83508</v>
       </c>
     </row>
     <row r="14">
@@ -5319,19 +5319,19 @@
         <v>17927</v>
       </c>
       <c r="B14" t="n">
-        <v>2.94266</v>
+        <v>2.99385</v>
       </c>
       <c r="C14" t="n">
-        <v>1.94365</v>
+        <v>2.31282</v>
       </c>
       <c r="D14" t="n">
-        <v>14.8709</v>
+        <v>15.0127</v>
       </c>
       <c r="E14" t="n">
-        <v>1.96989</v>
+        <v>2.60398</v>
       </c>
       <c r="F14" t="n">
-        <v>2.29105</v>
+        <v>2.88525</v>
       </c>
     </row>
     <row r="15">
@@ -5339,19 +5339,19 @@
         <v>18818</v>
       </c>
       <c r="B15" t="n">
-        <v>3.05246</v>
+        <v>3.05266</v>
       </c>
       <c r="C15" t="n">
-        <v>2.00102</v>
+        <v>2.37954</v>
       </c>
       <c r="D15" t="n">
-        <v>15.2623</v>
+        <v>15.4397</v>
       </c>
       <c r="E15" t="n">
-        <v>1.99841</v>
+        <v>2.6301</v>
       </c>
       <c r="F15" t="n">
-        <v>2.31079</v>
+        <v>2.9372</v>
       </c>
     </row>
     <row r="16">
@@ -5359,19 +5359,19 @@
         <v>19753</v>
       </c>
       <c r="B16" t="n">
-        <v>3.0841</v>
+        <v>3.24238</v>
       </c>
       <c r="C16" t="n">
-        <v>2.09514</v>
+        <v>2.51793</v>
       </c>
       <c r="D16" t="n">
-        <v>15.7002</v>
+        <v>15.7099</v>
       </c>
       <c r="E16" t="n">
-        <v>2.0186</v>
+        <v>2.62288</v>
       </c>
       <c r="F16" t="n">
-        <v>2.38324</v>
+        <v>2.93285</v>
       </c>
     </row>
     <row r="17">
@@ -5379,19 +5379,19 @@
         <v>20734</v>
       </c>
       <c r="B17" t="n">
-        <v>3.29557</v>
+        <v>3.3466</v>
       </c>
       <c r="C17" t="n">
-        <v>2.24561</v>
+        <v>2.59377</v>
       </c>
       <c r="D17" t="n">
-        <v>16.0941</v>
+        <v>16.2317</v>
       </c>
       <c r="E17" t="n">
-        <v>2.06039</v>
+        <v>2.65818</v>
       </c>
       <c r="F17" t="n">
-        <v>2.42028</v>
+        <v>3.01808</v>
       </c>
     </row>
     <row r="18">
@@ -5399,19 +5399,19 @@
         <v>21764</v>
       </c>
       <c r="B18" t="n">
-        <v>3.68201</v>
+        <v>3.75319</v>
       </c>
       <c r="C18" t="n">
-        <v>2.46961</v>
+        <v>2.82194</v>
       </c>
       <c r="D18" t="n">
-        <v>16.5652</v>
+        <v>16.6393</v>
       </c>
       <c r="E18" t="n">
-        <v>1.97142</v>
+        <v>2.64179</v>
       </c>
       <c r="F18" t="n">
-        <v>2.46154</v>
+        <v>2.98326</v>
       </c>
     </row>
     <row r="19">
@@ -5419,19 +5419,19 @@
         <v>22845</v>
       </c>
       <c r="B19" t="n">
-        <v>4.20465</v>
+        <v>4.30401</v>
       </c>
       <c r="C19" t="n">
-        <v>3.12129</v>
+        <v>3.34344</v>
       </c>
       <c r="D19" t="n">
-        <v>17.0425</v>
+        <v>17.1183</v>
       </c>
       <c r="E19" t="n">
-        <v>2.13963</v>
+        <v>2.63721</v>
       </c>
       <c r="F19" t="n">
-        <v>2.59056</v>
+        <v>2.96125</v>
       </c>
     </row>
     <row r="20">
@@ -5439,19 +5439,19 @@
         <v>23980</v>
       </c>
       <c r="B20" t="n">
-        <v>5.21338</v>
+        <v>5.16177</v>
       </c>
       <c r="C20" t="n">
-        <v>4.23203</v>
+        <v>4.48842</v>
       </c>
       <c r="D20" t="n">
-        <v>17.4892</v>
+        <v>17.3991</v>
       </c>
       <c r="E20" t="n">
-        <v>2.49638</v>
+        <v>3.00766</v>
       </c>
       <c r="F20" t="n">
-        <v>3.00667</v>
+        <v>3.27281</v>
       </c>
     </row>
     <row r="21">
@@ -5459,19 +5459,19 @@
         <v>25171</v>
       </c>
       <c r="B21" t="n">
-        <v>6.85504</v>
+        <v>6.62557</v>
       </c>
       <c r="C21" t="n">
-        <v>5.52991</v>
+        <v>6.37394</v>
       </c>
       <c r="D21" t="n">
-        <v>12.1787</v>
+        <v>12.4326</v>
       </c>
       <c r="E21" t="n">
-        <v>1.97816</v>
+        <v>2.58192</v>
       </c>
       <c r="F21" t="n">
-        <v>2.23879</v>
+        <v>2.95384</v>
       </c>
     </row>
     <row r="22">
@@ -5479,19 +5479,19 @@
         <v>26421</v>
       </c>
       <c r="B22" t="n">
-        <v>9.08522</v>
+        <v>8.903840000000001</v>
       </c>
       <c r="C22" t="n">
-        <v>1.83991</v>
+        <v>2.12562</v>
       </c>
       <c r="D22" t="n">
-        <v>12.6398</v>
+        <v>12.9186</v>
       </c>
       <c r="E22" t="n">
-        <v>1.99364</v>
+        <v>2.74583</v>
       </c>
       <c r="F22" t="n">
-        <v>2.27786</v>
+        <v>3.40401</v>
       </c>
     </row>
     <row r="23">
@@ -5499,19 +5499,19 @@
         <v>27733</v>
       </c>
       <c r="B23" t="n">
-        <v>12.4239</v>
+        <v>12.9051</v>
       </c>
       <c r="C23" t="n">
-        <v>1.80964</v>
+        <v>2.21559</v>
       </c>
       <c r="D23" t="n">
-        <v>13.15</v>
+        <v>13.4571</v>
       </c>
       <c r="E23" t="n">
-        <v>2.00455</v>
+        <v>2.61644</v>
       </c>
       <c r="F23" t="n">
-        <v>2.29184</v>
+        <v>3.01823</v>
       </c>
     </row>
     <row r="24">
@@ -5519,19 +5519,19 @@
         <v>29110</v>
       </c>
       <c r="B24" t="n">
-        <v>2.89787</v>
+        <v>3.13546</v>
       </c>
       <c r="C24" t="n">
-        <v>1.84161</v>
+        <v>2.4966</v>
       </c>
       <c r="D24" t="n">
-        <v>13.6858</v>
+        <v>13.9679</v>
       </c>
       <c r="E24" t="n">
-        <v>2.03054</v>
+        <v>2.67906</v>
       </c>
       <c r="F24" t="n">
-        <v>2.34178</v>
+        <v>3.50823</v>
       </c>
     </row>
     <row r="25">
@@ -5539,19 +5539,19 @@
         <v>30555</v>
       </c>
       <c r="B25" t="n">
-        <v>2.93153</v>
+        <v>3.16554</v>
       </c>
       <c r="C25" t="n">
-        <v>1.86718</v>
+        <v>2.4829</v>
       </c>
       <c r="D25" t="n">
-        <v>14.1831</v>
+        <v>14.4759</v>
       </c>
       <c r="E25" t="n">
-        <v>2.05869</v>
+        <v>2.71468</v>
       </c>
       <c r="F25" t="n">
-        <v>2.37553</v>
+        <v>3.52131</v>
       </c>
     </row>
     <row r="26">
@@ -5559,19 +5559,19 @@
         <v>32072</v>
       </c>
       <c r="B26" t="n">
-        <v>3.01358</v>
+        <v>3.21957</v>
       </c>
       <c r="C26" t="n">
-        <v>1.99927</v>
+        <v>2.51443</v>
       </c>
       <c r="D26" t="n">
-        <v>14.612</v>
+        <v>14.9138</v>
       </c>
       <c r="E26" t="n">
-        <v>2.08018</v>
+        <v>2.65731</v>
       </c>
       <c r="F26" t="n">
-        <v>2.42759</v>
+        <v>3.1189</v>
       </c>
     </row>
     <row r="27">
@@ -5579,19 +5579,19 @@
         <v>33664</v>
       </c>
       <c r="B27" t="n">
-        <v>3.08086</v>
+        <v>3.11712</v>
       </c>
       <c r="C27" t="n">
-        <v>1.94096</v>
+        <v>2.36498</v>
       </c>
       <c r="D27" t="n">
-        <v>15.1528</v>
+        <v>15.4583</v>
       </c>
       <c r="E27" t="n">
-        <v>2.10547</v>
+        <v>2.68879</v>
       </c>
       <c r="F27" t="n">
-        <v>2.46035</v>
+        <v>3.1857</v>
       </c>
     </row>
     <row r="28">
@@ -5599,19 +5599,19 @@
         <v>35335</v>
       </c>
       <c r="B28" t="n">
-        <v>3.14593</v>
+        <v>3.3852</v>
       </c>
       <c r="C28" t="n">
-        <v>2.00392</v>
+        <v>2.63986</v>
       </c>
       <c r="D28" t="n">
-        <v>15.5931</v>
+        <v>15.9077</v>
       </c>
       <c r="E28" t="n">
-        <v>2.14072</v>
+        <v>2.72835</v>
       </c>
       <c r="F28" t="n">
-        <v>2.5045</v>
+        <v>3.24744</v>
       </c>
     </row>
     <row r="29">
@@ -5619,19 +5619,19 @@
         <v>37089</v>
       </c>
       <c r="B29" t="n">
-        <v>3.29185</v>
+        <v>3.69881</v>
       </c>
       <c r="C29" t="n">
-        <v>2.14988</v>
+        <v>2.76286</v>
       </c>
       <c r="D29" t="n">
-        <v>16.1386</v>
+        <v>16.4136</v>
       </c>
       <c r="E29" t="n">
-        <v>2.17522</v>
+        <v>2.77099</v>
       </c>
       <c r="F29" t="n">
-        <v>2.57884</v>
+        <v>3.32214</v>
       </c>
     </row>
     <row r="30">
@@ -5639,19 +5639,19 @@
         <v>38930</v>
       </c>
       <c r="B30" t="n">
-        <v>3.44219</v>
+        <v>3.45417</v>
       </c>
       <c r="C30" t="n">
-        <v>2.23347</v>
+        <v>2.84698</v>
       </c>
       <c r="D30" t="n">
-        <v>16.6129</v>
+        <v>16.9602</v>
       </c>
       <c r="E30" t="n">
-        <v>2.22082</v>
+        <v>2.85247</v>
       </c>
       <c r="F30" t="n">
-        <v>2.61978</v>
+        <v>3.78061</v>
       </c>
     </row>
     <row r="31">
@@ -5659,19 +5659,19 @@
         <v>40863</v>
       </c>
       <c r="B31" t="n">
-        <v>3.66812</v>
+        <v>3.67818</v>
       </c>
       <c r="C31" t="n">
-        <v>2.40815</v>
+        <v>3.0135</v>
       </c>
       <c r="D31" t="n">
-        <v>17.0358</v>
+        <v>17.4614</v>
       </c>
       <c r="E31" t="n">
-        <v>2.25972</v>
+        <v>2.85959</v>
       </c>
       <c r="F31" t="n">
-        <v>2.67316</v>
+        <v>3.49581</v>
       </c>
     </row>
     <row r="32">
@@ -5679,19 +5679,19 @@
         <v>42892</v>
       </c>
       <c r="B32" t="n">
-        <v>4.03819</v>
+        <v>4.0148</v>
       </c>
       <c r="C32" t="n">
-        <v>2.694</v>
+        <v>3.30008</v>
       </c>
       <c r="D32" t="n">
-        <v>17.3944</v>
+        <v>17.7708</v>
       </c>
       <c r="E32" t="n">
-        <v>2.32573</v>
+        <v>2.91588</v>
       </c>
       <c r="F32" t="n">
-        <v>2.82566</v>
+        <v>3.60315</v>
       </c>
     </row>
     <row r="33">
@@ -5699,19 +5699,19 @@
         <v>45022</v>
       </c>
       <c r="B33" t="n">
-        <v>4.70012</v>
+        <v>4.67365</v>
       </c>
       <c r="C33" t="n">
-        <v>3.29752</v>
+        <v>3.77757</v>
       </c>
       <c r="D33" t="n">
-        <v>17.8818</v>
+        <v>18.1324</v>
       </c>
       <c r="E33" t="n">
-        <v>2.49419</v>
+        <v>3.00022</v>
       </c>
       <c r="F33" t="n">
-        <v>2.99545</v>
+        <v>3.56824</v>
       </c>
     </row>
     <row r="34">
@@ -5719,19 +5719,19 @@
         <v>47258</v>
       </c>
       <c r="B34" t="n">
-        <v>5.64548</v>
+        <v>5.66473</v>
       </c>
       <c r="C34" t="n">
-        <v>4.14793</v>
+        <v>4.67242</v>
       </c>
       <c r="D34" t="n">
-        <v>18.2708</v>
+        <v>18.6674</v>
       </c>
       <c r="E34" t="n">
-        <v>2.99119</v>
+        <v>3.5009</v>
       </c>
       <c r="F34" t="n">
-        <v>3.46228</v>
+        <v>4.2831</v>
       </c>
     </row>
     <row r="35">
@@ -5739,19 +5739,19 @@
         <v>49605</v>
       </c>
       <c r="B35" t="n">
-        <v>7.11877</v>
+        <v>6.91311</v>
       </c>
       <c r="C35" t="n">
-        <v>5.29861</v>
+        <v>6.19391</v>
       </c>
       <c r="D35" t="n">
-        <v>12.7389</v>
+        <v>12.7419</v>
       </c>
       <c r="E35" t="n">
-        <v>2.02954</v>
+        <v>2.9377</v>
       </c>
       <c r="F35" t="n">
-        <v>2.35467</v>
+        <v>3.44271</v>
       </c>
     </row>
     <row r="36">
@@ -5759,19 +5759,19 @@
         <v>52069</v>
       </c>
       <c r="B36" t="n">
-        <v>9.26243</v>
+        <v>9.1219</v>
       </c>
       <c r="C36" t="n">
-        <v>6.94572</v>
+        <v>8.423120000000001</v>
       </c>
       <c r="D36" t="n">
-        <v>13.1628</v>
+        <v>13.1877</v>
       </c>
       <c r="E36" t="n">
-        <v>2.05071</v>
+        <v>2.95972</v>
       </c>
       <c r="F36" t="n">
-        <v>2.38338</v>
+        <v>3.47443</v>
       </c>
     </row>
     <row r="37">
@@ -5779,19 +5779,19 @@
         <v>54656</v>
       </c>
       <c r="B37" t="n">
-        <v>12.8374</v>
+        <v>12.4896</v>
       </c>
       <c r="C37" t="n">
-        <v>1.82983</v>
+        <v>2.44378</v>
       </c>
       <c r="D37" t="n">
-        <v>13.652</v>
+        <v>13.6902</v>
       </c>
       <c r="E37" t="n">
-        <v>2.07536</v>
+        <v>2.97102</v>
       </c>
       <c r="F37" t="n">
-        <v>2.44696</v>
+        <v>3.0886</v>
       </c>
     </row>
     <row r="38">
@@ -5799,19 +5799,19 @@
         <v>57372</v>
       </c>
       <c r="B38" t="n">
-        <v>2.96976</v>
+        <v>3.15825</v>
       </c>
       <c r="C38" t="n">
-        <v>1.86647</v>
+        <v>2.52746</v>
       </c>
       <c r="D38" t="n">
-        <v>14.1997</v>
+        <v>14.3536</v>
       </c>
       <c r="E38" t="n">
-        <v>2.09334</v>
+        <v>3.07585</v>
       </c>
       <c r="F38" t="n">
-        <v>2.46633</v>
+        <v>3.16073</v>
       </c>
     </row>
     <row r="39">
@@ -5819,19 +5819,19 @@
         <v>60223</v>
       </c>
       <c r="B39" t="n">
-        <v>3.00337</v>
+        <v>3.17814</v>
       </c>
       <c r="C39" t="n">
-        <v>1.93394</v>
+        <v>2.64792</v>
       </c>
       <c r="D39" t="n">
-        <v>14.6984</v>
+        <v>14.8649</v>
       </c>
       <c r="E39" t="n">
-        <v>2.12175</v>
+        <v>3.00659</v>
       </c>
       <c r="F39" t="n">
-        <v>2.53954</v>
+        <v>3.67912</v>
       </c>
     </row>
     <row r="40">
@@ -5839,19 +5839,19 @@
         <v>63216</v>
       </c>
       <c r="B40" t="n">
-        <v>3.07137</v>
+        <v>3.09152</v>
       </c>
       <c r="C40" t="n">
-        <v>1.93586</v>
+        <v>2.52368</v>
       </c>
       <c r="D40" t="n">
-        <v>15.2098</v>
+        <v>15.4868</v>
       </c>
       <c r="E40" t="n">
-        <v>2.14316</v>
+        <v>3.1214</v>
       </c>
       <c r="F40" t="n">
-        <v>2.58367</v>
+        <v>3.27073</v>
       </c>
     </row>
     <row r="41">
@@ -5859,19 +5859,19 @@
         <v>66358</v>
       </c>
       <c r="B41" t="n">
-        <v>3.13481</v>
+        <v>3.33975</v>
       </c>
       <c r="C41" t="n">
-        <v>2.00343</v>
+        <v>2.64593</v>
       </c>
       <c r="D41" t="n">
-        <v>15.6861</v>
+        <v>15.9549</v>
       </c>
       <c r="E41" t="n">
-        <v>2.18009</v>
+        <v>3.14513</v>
       </c>
       <c r="F41" t="n">
-        <v>2.62732</v>
+        <v>3.32688</v>
       </c>
     </row>
     <row r="42">
@@ -5879,19 +5879,19 @@
         <v>69657</v>
       </c>
       <c r="B42" t="n">
-        <v>3.19631</v>
+        <v>3.44402</v>
       </c>
       <c r="C42" t="n">
-        <v>2.06098</v>
+        <v>2.76934</v>
       </c>
       <c r="D42" t="n">
-        <v>16.1939</v>
+        <v>16.4524</v>
       </c>
       <c r="E42" t="n">
-        <v>2.21809</v>
+        <v>3.17658</v>
       </c>
       <c r="F42" t="n">
-        <v>2.70312</v>
+        <v>3.39266</v>
       </c>
     </row>
     <row r="43">
@@ -5899,19 +5899,19 @@
         <v>73120</v>
       </c>
       <c r="B43" t="n">
-        <v>3.33421</v>
+        <v>3.53948</v>
       </c>
       <c r="C43" t="n">
-        <v>2.15339</v>
+        <v>2.87238</v>
       </c>
       <c r="D43" t="n">
-        <v>16.6277</v>
+        <v>16.9248</v>
       </c>
       <c r="E43" t="n">
-        <v>2.26102</v>
+        <v>3.13521</v>
       </c>
       <c r="F43" t="n">
-        <v>2.77208</v>
+        <v>3.8832</v>
       </c>
     </row>
     <row r="44">
@@ -5919,19 +5919,19 @@
         <v>76756</v>
       </c>
       <c r="B44" t="n">
-        <v>3.50387</v>
+        <v>3.72776</v>
       </c>
       <c r="C44" t="n">
-        <v>2.2719</v>
+        <v>2.90264</v>
       </c>
       <c r="D44" t="n">
-        <v>17.0692</v>
+        <v>17.3119</v>
       </c>
       <c r="E44" t="n">
-        <v>2.34</v>
+        <v>3.21238</v>
       </c>
       <c r="F44" t="n">
-        <v>2.85797</v>
+        <v>3.92711</v>
       </c>
     </row>
     <row r="45">
@@ -5939,19 +5939,19 @@
         <v>80573</v>
       </c>
       <c r="B45" t="n">
-        <v>3.73617</v>
+        <v>3.74826</v>
       </c>
       <c r="C45" t="n">
-        <v>2.53629</v>
+        <v>2.984</v>
       </c>
       <c r="D45" t="n">
-        <v>17.4717</v>
+        <v>17.665</v>
       </c>
       <c r="E45" t="n">
-        <v>2.43476</v>
+        <v>2.99205</v>
       </c>
       <c r="F45" t="n">
-        <v>2.98303</v>
+        <v>3.97518</v>
       </c>
     </row>
     <row r="46">
@@ -5959,19 +5959,19 @@
         <v>84580</v>
       </c>
       <c r="B46" t="n">
-        <v>4.07445</v>
+        <v>4.33044</v>
       </c>
       <c r="C46" t="n">
-        <v>2.86546</v>
+        <v>3.46264</v>
       </c>
       <c r="D46" t="n">
-        <v>17.8757</v>
+        <v>18.1232</v>
       </c>
       <c r="E46" t="n">
-        <v>2.57434</v>
+        <v>3.46279</v>
       </c>
       <c r="F46" t="n">
-        <v>3.14215</v>
+        <v>4.06957</v>
       </c>
     </row>
     <row r="47">
@@ -5979,19 +5979,19 @@
         <v>88787</v>
       </c>
       <c r="B47" t="n">
-        <v>4.63382</v>
+        <v>4.9767</v>
       </c>
       <c r="C47" t="n">
-        <v>3.35305</v>
+        <v>3.92402</v>
       </c>
       <c r="D47" t="n">
-        <v>18.2978</v>
+        <v>18.6379</v>
       </c>
       <c r="E47" t="n">
-        <v>2.83338</v>
+        <v>3.65935</v>
       </c>
       <c r="F47" t="n">
-        <v>3.36643</v>
+        <v>4.24104</v>
       </c>
     </row>
     <row r="48">
@@ -5999,19 +5999,19 @@
         <v>93204</v>
       </c>
       <c r="B48" t="n">
-        <v>5.39028</v>
+        <v>5.39562</v>
       </c>
       <c r="C48" t="n">
-        <v>4.04503</v>
+        <v>4.71134</v>
       </c>
       <c r="D48" t="n">
-        <v>18.7476</v>
+        <v>19.176</v>
       </c>
       <c r="E48" t="n">
-        <v>3.22315</v>
+        <v>4.06161</v>
       </c>
       <c r="F48" t="n">
-        <v>3.74048</v>
+        <v>4.65321</v>
       </c>
     </row>
     <row r="49">
@@ -6019,19 +6019,19 @@
         <v>97841</v>
       </c>
       <c r="B49" t="n">
-        <v>6.46784</v>
+        <v>6.48646</v>
       </c>
       <c r="C49" t="n">
-        <v>5.00845</v>
+        <v>5.7783</v>
       </c>
       <c r="D49" t="n">
-        <v>19.1839</v>
+        <v>19.9843</v>
       </c>
       <c r="E49" t="n">
-        <v>3.73042</v>
+        <v>4.56982</v>
       </c>
       <c r="F49" t="n">
-        <v>4.24995</v>
+        <v>4.76528</v>
       </c>
     </row>
     <row r="50">
@@ -6039,19 +6039,19 @@
         <v>102709</v>
       </c>
       <c r="B50" t="n">
-        <v>8.337820000000001</v>
+        <v>8.55702</v>
       </c>
       <c r="C50" t="n">
-        <v>6.47971</v>
+        <v>7.4512</v>
       </c>
       <c r="D50" t="n">
-        <v>13.4275</v>
+        <v>15.5031</v>
       </c>
       <c r="E50" t="n">
-        <v>2.14015</v>
+        <v>3.02363</v>
       </c>
       <c r="F50" t="n">
-        <v>2.6086</v>
+        <v>3.41447</v>
       </c>
     </row>
     <row r="51">
@@ -6059,19 +6059,19 @@
         <v>107820</v>
       </c>
       <c r="B51" t="n">
-        <v>10.8681</v>
+        <v>11.753</v>
       </c>
       <c r="C51" t="n">
-        <v>1.87269</v>
+        <v>2.38985</v>
       </c>
       <c r="D51" t="n">
-        <v>13.9344</v>
+        <v>17.5812</v>
       </c>
       <c r="E51" t="n">
-        <v>2.15555</v>
+        <v>3.04129</v>
       </c>
       <c r="F51" t="n">
-        <v>2.63709</v>
+        <v>3.47463</v>
       </c>
     </row>
     <row r="52">
@@ -6079,19 +6079,19 @@
         <v>113186</v>
       </c>
       <c r="B52" t="n">
-        <v>15.3413</v>
+        <v>15.7103</v>
       </c>
       <c r="C52" t="n">
-        <v>2.12139</v>
+        <v>2.40759</v>
       </c>
       <c r="D52" t="n">
-        <v>14.4121</v>
+        <v>18.7231</v>
       </c>
       <c r="E52" t="n">
-        <v>2.18674</v>
+        <v>3.07246</v>
       </c>
       <c r="F52" t="n">
-        <v>2.7713</v>
+        <v>3.50964</v>
       </c>
     </row>
     <row r="53">
@@ -6099,19 +6099,19 @@
         <v>118820</v>
       </c>
       <c r="B53" t="n">
-        <v>3.10736</v>
+        <v>3.14717</v>
       </c>
       <c r="C53" t="n">
-        <v>1.98175</v>
+        <v>2.45406</v>
       </c>
       <c r="D53" t="n">
-        <v>14.902</v>
+        <v>19.9648</v>
       </c>
       <c r="E53" t="n">
-        <v>2.21659</v>
+        <v>3.48513</v>
       </c>
       <c r="F53" t="n">
-        <v>2.7341</v>
+        <v>3.58016</v>
       </c>
     </row>
     <row r="54">
@@ -6119,19 +6119,19 @@
         <v>124735</v>
       </c>
       <c r="B54" t="n">
-        <v>3.13618</v>
+        <v>3.63032</v>
       </c>
       <c r="C54" t="n">
-        <v>2.15329</v>
+        <v>2.43272</v>
       </c>
       <c r="D54" t="n">
-        <v>15.4018</v>
+        <v>20.2493</v>
       </c>
       <c r="E54" t="n">
-        <v>2.367</v>
+        <v>3.59162</v>
       </c>
       <c r="F54" t="n">
-        <v>2.86195</v>
+        <v>3.59578</v>
       </c>
     </row>
     <row r="55">
@@ -6139,19 +6139,19 @@
         <v>130945</v>
       </c>
       <c r="B55" t="n">
-        <v>3.22552</v>
+        <v>3.66714</v>
       </c>
       <c r="C55" t="n">
-        <v>2.07765</v>
+        <v>2.53866</v>
       </c>
       <c r="D55" t="n">
-        <v>15.869</v>
+        <v>21.7593</v>
       </c>
       <c r="E55" t="n">
-        <v>2.69306</v>
+        <v>2.96938</v>
       </c>
       <c r="F55" t="n">
-        <v>2.94678</v>
+        <v>3.67776</v>
       </c>
     </row>
     <row r="56">
@@ -6159,19 +6159,19 @@
         <v>137465</v>
       </c>
       <c r="B56" t="n">
-        <v>3.35711</v>
+        <v>3.38269</v>
       </c>
       <c r="C56" t="n">
-        <v>2.31849</v>
+        <v>2.63595</v>
       </c>
       <c r="D56" t="n">
-        <v>16.3376</v>
+        <v>22.9767</v>
       </c>
       <c r="E56" t="n">
-        <v>2.74196</v>
+        <v>3.63853</v>
       </c>
       <c r="F56" t="n">
-        <v>3.01282</v>
+        <v>3.76411</v>
       </c>
     </row>
     <row r="57">
@@ -6179,19 +6179,19 @@
         <v>144311</v>
       </c>
       <c r="B57" t="n">
-        <v>3.46128</v>
+        <v>3.48402</v>
       </c>
       <c r="C57" t="n">
-        <v>2.31614</v>
+        <v>2.96084</v>
       </c>
       <c r="D57" t="n">
-        <v>16.7992</v>
+        <v>23.9105</v>
       </c>
       <c r="E57" t="n">
-        <v>2.51348</v>
+        <v>3.78341</v>
       </c>
       <c r="F57" t="n">
-        <v>3.182</v>
+        <v>3.84206</v>
       </c>
     </row>
     <row r="58">
@@ -6199,19 +6199,19 @@
         <v>151499</v>
       </c>
       <c r="B58" t="n">
-        <v>3.61873</v>
+        <v>3.65864</v>
       </c>
       <c r="C58" t="n">
-        <v>2.4189</v>
+        <v>3.09373</v>
       </c>
       <c r="D58" t="n">
-        <v>17.2225</v>
+        <v>24.8918</v>
       </c>
       <c r="E58" t="n">
-        <v>2.62638</v>
+        <v>3.2017</v>
       </c>
       <c r="F58" t="n">
-        <v>3.19624</v>
+        <v>3.97213</v>
       </c>
     </row>
     <row r="59">
@@ -6219,19 +6219,19 @@
         <v>159046</v>
       </c>
       <c r="B59" t="n">
-        <v>3.78866</v>
+        <v>3.85059</v>
       </c>
       <c r="C59" t="n">
-        <v>2.65709</v>
+        <v>3.64119</v>
       </c>
       <c r="D59" t="n">
-        <v>17.6514</v>
+        <v>25.5686</v>
       </c>
       <c r="E59" t="n">
-        <v>2.80117</v>
+        <v>3.3137</v>
       </c>
       <c r="F59" t="n">
-        <v>3.20774</v>
+        <v>4.09498</v>
       </c>
     </row>
     <row r="60">
@@ -6239,19 +6239,19 @@
         <v>166970</v>
       </c>
       <c r="B60" t="n">
-        <v>4.26332</v>
+        <v>4.17445</v>
       </c>
       <c r="C60" t="n">
-        <v>2.99919</v>
+        <v>4.04585</v>
       </c>
       <c r="D60" t="n">
-        <v>18.0313</v>
+        <v>26.1128</v>
       </c>
       <c r="E60" t="n">
-        <v>2.90326</v>
+        <v>3.69769</v>
       </c>
       <c r="F60" t="n">
-        <v>3.30137</v>
+        <v>4.14374</v>
       </c>
     </row>
     <row r="61">
@@ -6259,19 +6259,19 @@
         <v>175290</v>
       </c>
       <c r="B61" t="n">
-        <v>4.61221</v>
+        <v>4.63433</v>
       </c>
       <c r="C61" t="n">
-        <v>3.21195</v>
+        <v>4.03152</v>
       </c>
       <c r="D61" t="n">
-        <v>18.5467</v>
+        <v>27.0792</v>
       </c>
       <c r="E61" t="n">
-        <v>3.14568</v>
+        <v>4.29578</v>
       </c>
       <c r="F61" t="n">
-        <v>3.56755</v>
+        <v>4.73619</v>
       </c>
     </row>
     <row r="62">
@@ -6279,19 +6279,19 @@
         <v>184026</v>
       </c>
       <c r="B62" t="n">
-        <v>5.2539</v>
+        <v>5.31376</v>
       </c>
       <c r="C62" t="n">
-        <v>4.01734</v>
+        <v>5.05898</v>
       </c>
       <c r="D62" t="n">
-        <v>18.8979</v>
+        <v>28.3653</v>
       </c>
       <c r="E62" t="n">
-        <v>3.41481</v>
+        <v>4.58666</v>
       </c>
       <c r="F62" t="n">
-        <v>3.82616</v>
+        <v>4.96481</v>
       </c>
     </row>
     <row r="63">
@@ -6299,19 +6299,19 @@
         <v>193198</v>
       </c>
       <c r="B63" t="n">
-        <v>6.32583</v>
+        <v>6.29505</v>
       </c>
       <c r="C63" t="n">
-        <v>4.93654</v>
+        <v>6.05621</v>
       </c>
       <c r="D63" t="n">
-        <v>19.4515</v>
+        <v>28.3446</v>
       </c>
       <c r="E63" t="n">
-        <v>3.85743</v>
+        <v>5.10781</v>
       </c>
       <c r="F63" t="n">
-        <v>4.31669</v>
+        <v>5.38906</v>
       </c>
     </row>
     <row r="64">
@@ -6319,19 +6319,19 @@
         <v>202828</v>
       </c>
       <c r="B64" t="n">
-        <v>7.83118</v>
+        <v>7.9764</v>
       </c>
       <c r="C64" t="n">
-        <v>6.15207</v>
+        <v>7.5608</v>
       </c>
       <c r="D64" t="n">
-        <v>14.1204</v>
+        <v>19.7621</v>
       </c>
       <c r="E64" t="n">
-        <v>2.83528</v>
+        <v>3.47649</v>
       </c>
       <c r="F64" t="n">
-        <v>3.33187</v>
+        <v>4.17931</v>
       </c>
     </row>
     <row r="65">
@@ -6339,19 +6339,19 @@
         <v>212939</v>
       </c>
       <c r="B65" t="n">
-        <v>10.5243</v>
+        <v>10.4416</v>
       </c>
       <c r="C65" t="n">
-        <v>2.35888</v>
+        <v>2.92289</v>
       </c>
       <c r="D65" t="n">
-        <v>14.7739</v>
+        <v>19.5599</v>
       </c>
       <c r="E65" t="n">
-        <v>2.82965</v>
+        <v>3.61285</v>
       </c>
       <c r="F65" t="n">
-        <v>3.38423</v>
+        <v>4.25982</v>
       </c>
     </row>
     <row r="66">
@@ -6359,19 +6359,19 @@
         <v>223555</v>
       </c>
       <c r="B66" t="n">
-        <v>14.4513</v>
+        <v>14.3274</v>
       </c>
       <c r="C66" t="n">
-        <v>2.441</v>
+        <v>2.96675</v>
       </c>
       <c r="D66" t="n">
-        <v>15.6384</v>
+        <v>20.8636</v>
       </c>
       <c r="E66" t="n">
-        <v>2.81315</v>
+        <v>3.53772</v>
       </c>
       <c r="F66" t="n">
-        <v>3.43461</v>
+        <v>4.30722</v>
       </c>
     </row>
     <row r="67">
@@ -6379,19 +6379,19 @@
         <v>234701</v>
       </c>
       <c r="B67" t="n">
-        <v>3.53067</v>
+        <v>3.72406</v>
       </c>
       <c r="C67" t="n">
-        <v>2.44338</v>
+        <v>3.01591</v>
       </c>
       <c r="D67" t="n">
-        <v>16.3084</v>
+        <v>22.4734</v>
       </c>
       <c r="E67" t="n">
-        <v>2.86263</v>
+        <v>3.57588</v>
       </c>
       <c r="F67" t="n">
-        <v>3.48783</v>
+        <v>4.38313</v>
       </c>
     </row>
     <row r="68">
@@ -6399,19 +6399,19 @@
         <v>246404</v>
       </c>
       <c r="B68" t="n">
-        <v>3.63427</v>
+        <v>3.56644</v>
       </c>
       <c r="C68" t="n">
-        <v>2.48532</v>
+        <v>3.04462</v>
       </c>
       <c r="D68" t="n">
-        <v>17.0807</v>
+        <v>23.939</v>
       </c>
       <c r="E68" t="n">
-        <v>2.74621</v>
+        <v>3.71071</v>
       </c>
       <c r="F68" t="n">
-        <v>3.54184</v>
+        <v>4.47182</v>
       </c>
     </row>
     <row r="69">
@@ -6419,19 +6419,19 @@
         <v>258692</v>
       </c>
       <c r="B69" t="n">
-        <v>3.6825</v>
+        <v>3.63753</v>
       </c>
       <c r="C69" t="n">
-        <v>2.50658</v>
+        <v>3.05521</v>
       </c>
       <c r="D69" t="n">
-        <v>17.8468</v>
+        <v>24.625</v>
       </c>
       <c r="E69" t="n">
-        <v>2.98544</v>
+        <v>3.68028</v>
       </c>
       <c r="F69" t="n">
-        <v>3.60848</v>
+        <v>4.54745</v>
       </c>
     </row>
     <row r="70">
@@ -6439,19 +6439,19 @@
         <v>271594</v>
       </c>
       <c r="B70" t="n">
-        <v>3.83232</v>
+        <v>3.96975</v>
       </c>
       <c r="C70" t="n">
-        <v>2.62516</v>
+        <v>3.18266</v>
       </c>
       <c r="D70" t="n">
-        <v>18.7619</v>
+        <v>25.2376</v>
       </c>
       <c r="E70" t="n">
-        <v>2.96019</v>
+        <v>3.83564</v>
       </c>
       <c r="F70" t="n">
-        <v>3.68199</v>
+        <v>4.64679</v>
       </c>
     </row>
     <row r="71">
@@ -6459,19 +6459,19 @@
         <v>285141</v>
       </c>
       <c r="B71" t="n">
-        <v>3.81373</v>
+        <v>3.8507</v>
       </c>
       <c r="C71" t="n">
-        <v>2.68728</v>
+        <v>3.21605</v>
       </c>
       <c r="D71" t="n">
-        <v>19.8036</v>
+        <v>25.9548</v>
       </c>
       <c r="E71" t="n">
-        <v>2.92563</v>
+        <v>3.77732</v>
       </c>
       <c r="F71" t="n">
-        <v>3.73831</v>
+        <v>4.75204</v>
       </c>
     </row>
     <row r="72">
@@ -6479,19 +6479,19 @@
         <v>299365</v>
       </c>
       <c r="B72" t="n">
-        <v>4.08107</v>
+        <v>4.00258</v>
       </c>
       <c r="C72" t="n">
-        <v>2.7523</v>
+        <v>3.35875</v>
       </c>
       <c r="D72" t="n">
-        <v>20.7096</v>
+        <v>26.8317</v>
       </c>
       <c r="E72" t="n">
-        <v>3.00192</v>
+        <v>3.8573</v>
       </c>
       <c r="F72" t="n">
-        <v>3.83979</v>
+        <v>4.88257</v>
       </c>
     </row>
     <row r="73">
@@ -6499,19 +6499,19 @@
         <v>314300</v>
       </c>
       <c r="B73" t="n">
-        <v>4.35135</v>
+        <v>4.43397</v>
       </c>
       <c r="C73" t="n">
-        <v>2.99462</v>
+        <v>3.59543</v>
       </c>
       <c r="D73" t="n">
-        <v>22.1991</v>
+        <v>27.7873</v>
       </c>
       <c r="E73" t="n">
-        <v>3.08966</v>
+        <v>3.95836</v>
       </c>
       <c r="F73" t="n">
-        <v>3.96635</v>
+        <v>4.98289</v>
       </c>
     </row>
     <row r="74">
@@ -6519,19 +6519,19 @@
         <v>329981</v>
       </c>
       <c r="B74" t="n">
-        <v>4.46562</v>
+        <v>4.60135</v>
       </c>
       <c r="C74" t="n">
-        <v>3.24831</v>
+        <v>3.67798</v>
       </c>
       <c r="D74" t="n">
-        <v>23.8844</v>
+        <v>28.9957</v>
       </c>
       <c r="E74" t="n">
-        <v>3.46205</v>
+        <v>3.88778</v>
       </c>
       <c r="F74" t="n">
-        <v>4.1318</v>
+        <v>5.10676</v>
       </c>
     </row>
     <row r="75">
@@ -6539,19 +6539,19 @@
         <v>346446</v>
       </c>
       <c r="B75" t="n">
-        <v>5.22259</v>
+        <v>5.02266</v>
       </c>
       <c r="C75" t="n">
-        <v>3.90848</v>
+        <v>4.08351</v>
       </c>
       <c r="D75" t="n">
-        <v>24.9108</v>
+        <v>29.5459</v>
       </c>
       <c r="E75" t="n">
-        <v>3.74373</v>
+        <v>4.21278</v>
       </c>
       <c r="F75" t="n">
-        <v>4.31782</v>
+        <v>5.36241</v>
       </c>
     </row>
     <row r="76">
@@ -6559,19 +6559,19 @@
         <v>363734</v>
       </c>
       <c r="B76" t="n">
-        <v>5.86973</v>
+        <v>5.63848</v>
       </c>
       <c r="C76" t="n">
-        <v>4.46921</v>
+        <v>4.70801</v>
       </c>
       <c r="D76" t="n">
-        <v>26.428</v>
+        <v>31.8396</v>
       </c>
       <c r="E76" t="n">
-        <v>3.86862</v>
+        <v>4.31592</v>
       </c>
       <c r="F76" t="n">
-        <v>4.62154</v>
+        <v>6.30395</v>
       </c>
     </row>
     <row r="77">
@@ -6579,19 +6579,19 @@
         <v>381886</v>
       </c>
       <c r="B77" t="n">
-        <v>6.83678</v>
+        <v>6.87139</v>
       </c>
       <c r="C77" t="n">
-        <v>5.19202</v>
+        <v>5.64762</v>
       </c>
       <c r="D77" t="n">
-        <v>27.7495</v>
+        <v>32.8835</v>
       </c>
       <c r="E77" t="n">
-        <v>4.34886</v>
+        <v>4.74853</v>
       </c>
       <c r="F77" t="n">
-        <v>5.0776</v>
+        <v>6.02939</v>
       </c>
     </row>
     <row r="78">
@@ -6599,19 +6599,19 @@
         <v>400945</v>
       </c>
       <c r="B78" t="n">
-        <v>8.31016</v>
+        <v>7.91209</v>
       </c>
       <c r="C78" t="n">
-        <v>6.31446</v>
+        <v>7.21898</v>
       </c>
       <c r="D78" t="n">
-        <v>25.0108</v>
+        <v>24.2115</v>
       </c>
       <c r="E78" t="n">
-        <v>3.07339</v>
+        <v>3.74116</v>
       </c>
       <c r="F78" t="n">
-        <v>3.8269</v>
+        <v>4.5838</v>
       </c>
     </row>
     <row r="79">
@@ -6619,19 +6619,19 @@
         <v>420956</v>
       </c>
       <c r="B79" t="n">
-        <v>11.1786</v>
+        <v>10.0907</v>
       </c>
       <c r="C79" t="n">
-        <v>2.67509</v>
+        <v>3.12807</v>
       </c>
       <c r="D79" t="n">
-        <v>26.2075</v>
+        <v>25.5535</v>
       </c>
       <c r="E79" t="n">
-        <v>3.11157</v>
+        <v>3.77971</v>
       </c>
       <c r="F79" t="n">
-        <v>3.89669</v>
+        <v>4.66627</v>
       </c>
     </row>
     <row r="80">
@@ -6639,19 +6639,19 @@
         <v>441967</v>
       </c>
       <c r="B80" t="n">
-        <v>15.2055</v>
+        <v>13.9522</v>
       </c>
       <c r="C80" t="n">
-        <v>2.73758</v>
+        <v>3.17873</v>
       </c>
       <c r="D80" t="n">
-        <v>27.5279</v>
+        <v>26.7339</v>
       </c>
       <c r="E80" t="n">
-        <v>3.15539</v>
+        <v>3.84168</v>
       </c>
       <c r="F80" t="n">
-        <v>3.99831</v>
+        <v>4.79082</v>
       </c>
     </row>
     <row r="81">
@@ -6659,19 +6659,19 @@
         <v>464028</v>
       </c>
       <c r="B81" t="n">
-        <v>4.25978</v>
+        <v>4.0556</v>
       </c>
       <c r="C81" t="n">
-        <v>2.82649</v>
+        <v>3.23983</v>
       </c>
       <c r="D81" t="n">
-        <v>28.7569</v>
+        <v>28.0235</v>
       </c>
       <c r="E81" t="n">
-        <v>3.18844</v>
+        <v>3.8708</v>
       </c>
       <c r="F81" t="n">
-        <v>4.15283</v>
+        <v>4.85025</v>
       </c>
     </row>
     <row r="82">
@@ -6679,19 +6679,19 @@
         <v>487192</v>
       </c>
       <c r="B82" t="n">
-        <v>4.38736</v>
+        <v>4.13863</v>
       </c>
       <c r="C82" t="n">
-        <v>2.90863</v>
+        <v>3.31276</v>
       </c>
       <c r="D82" t="n">
-        <v>30.1422</v>
+        <v>29.4067</v>
       </c>
       <c r="E82" t="n">
-        <v>3.26146</v>
+        <v>3.94301</v>
       </c>
       <c r="F82" t="n">
-        <v>4.25435</v>
+        <v>5.0341</v>
       </c>
     </row>
     <row r="83">
@@ -6699,19 +6699,19 @@
         <v>511514</v>
       </c>
       <c r="B83" t="n">
-        <v>4.60091</v>
+        <v>4.26974</v>
       </c>
       <c r="C83" t="n">
-        <v>3.02225</v>
+        <v>3.43905</v>
       </c>
       <c r="D83" t="n">
-        <v>31.525</v>
+        <v>30.8686</v>
       </c>
       <c r="E83" t="n">
-        <v>3.30444</v>
+        <v>4.00026</v>
       </c>
       <c r="F83" t="n">
-        <v>4.46243</v>
+        <v>5.18953</v>
       </c>
     </row>
     <row r="84">
@@ -6719,19 +6719,19 @@
         <v>537052</v>
       </c>
       <c r="B84" t="n">
-        <v>4.83165</v>
+        <v>4.45531</v>
       </c>
       <c r="C84" t="n">
-        <v>3.16672</v>
+        <v>3.50773</v>
       </c>
       <c r="D84" t="n">
-        <v>33.0242</v>
+        <v>32.4453</v>
       </c>
       <c r="E84" t="n">
-        <v>3.42318</v>
+        <v>4.08966</v>
       </c>
       <c r="F84" t="n">
-        <v>4.72795</v>
+        <v>5.32533</v>
       </c>
     </row>
     <row r="85">
@@ -6739,19 +6739,19 @@
         <v>563866</v>
       </c>
       <c r="B85" t="n">
-        <v>5.03764</v>
+        <v>4.70182</v>
       </c>
       <c r="C85" t="n">
-        <v>3.28853</v>
+        <v>3.71584</v>
       </c>
       <c r="D85" t="n">
-        <v>34.5861</v>
+        <v>33.9555</v>
       </c>
       <c r="E85" t="n">
-        <v>3.54704</v>
+        <v>4.23136</v>
       </c>
       <c r="F85" t="n">
-        <v>4.86533</v>
+        <v>5.97478</v>
       </c>
     </row>
     <row r="86">
@@ -6759,19 +6759,19 @@
         <v>592020</v>
       </c>
       <c r="B86" t="n">
-        <v>5.46481</v>
+        <v>4.9401</v>
       </c>
       <c r="C86" t="n">
-        <v>3.62338</v>
+        <v>3.92493</v>
       </c>
       <c r="D86" t="n">
-        <v>36.0165</v>
+        <v>35.5063</v>
       </c>
       <c r="E86" t="n">
-        <v>3.75643</v>
+        <v>4.38067</v>
       </c>
       <c r="F86" t="n">
-        <v>5.26209</v>
+        <v>6.36566</v>
       </c>
     </row>
     <row r="87">
@@ -6779,19 +6779,19 @@
         <v>621581</v>
       </c>
       <c r="B87" t="n">
-        <v>5.88117</v>
+        <v>5.33385</v>
       </c>
       <c r="C87" t="n">
-        <v>3.93023</v>
+        <v>4.18998</v>
       </c>
       <c r="D87" t="n">
-        <v>37.6292</v>
+        <v>37.1317</v>
       </c>
       <c r="E87" t="n">
-        <v>3.93118</v>
+        <v>4.62403</v>
       </c>
       <c r="F87" t="n">
-        <v>5.6823</v>
+        <v>6.81783</v>
       </c>
     </row>
     <row r="88">
@@ -6799,19 +6799,19 @@
         <v>652620</v>
       </c>
       <c r="B88" t="n">
-        <v>6.30334</v>
+        <v>5.81518</v>
       </c>
       <c r="C88" t="n">
-        <v>4.16231</v>
+        <v>4.59643</v>
       </c>
       <c r="D88" t="n">
-        <v>38.2522</v>
+        <v>38.8788</v>
       </c>
       <c r="E88" t="n">
-        <v>4.17135</v>
+        <v>4.8558</v>
       </c>
       <c r="F88" t="n">
-        <v>6.12814</v>
+        <v>6.40956</v>
       </c>
     </row>
     <row r="89">
@@ -6819,19 +6819,19 @@
         <v>685210</v>
       </c>
       <c r="B89" t="n">
-        <v>6.95113</v>
+        <v>6.46596</v>
       </c>
       <c r="C89" t="n">
-        <v>4.66083</v>
+        <v>5.11521</v>
       </c>
       <c r="D89" t="n">
-        <v>40.1282</v>
+        <v>40.5929</v>
       </c>
       <c r="E89" t="n">
-        <v>4.48072</v>
+        <v>5.24209</v>
       </c>
       <c r="F89" t="n">
-        <v>6.6399</v>
+        <v>6.81477</v>
       </c>
     </row>
     <row r="90">
@@ -6839,19 +6839,19 @@
         <v>719429</v>
       </c>
       <c r="B90" t="n">
-        <v>7.85811</v>
+        <v>7.23628</v>
       </c>
       <c r="C90" t="n">
-        <v>5.27605</v>
+        <v>5.81271</v>
       </c>
       <c r="D90" t="n">
-        <v>42.7893</v>
+        <v>42.4479</v>
       </c>
       <c r="E90" t="n">
-        <v>4.928</v>
+        <v>5.69734</v>
       </c>
       <c r="F90" t="n">
-        <v>7.8006</v>
+        <v>7.36474</v>
       </c>
     </row>
     <row r="91">
@@ -6859,19 +6859,19 @@
         <v>755358</v>
       </c>
       <c r="B91" t="n">
-        <v>9.091810000000001</v>
+        <v>8.393359999999999</v>
       </c>
       <c r="C91" t="n">
-        <v>6.23997</v>
+        <v>6.78337</v>
       </c>
       <c r="D91" t="n">
-        <v>44.9146</v>
+        <v>44.3081</v>
       </c>
       <c r="E91" t="n">
-        <v>5.47278</v>
+        <v>6.24795</v>
       </c>
       <c r="F91" t="n">
-        <v>8.669560000000001</v>
+        <v>8.141690000000001</v>
       </c>
     </row>
     <row r="92">
@@ -6879,19 +6879,19 @@
         <v>793083</v>
       </c>
       <c r="B92" t="n">
-        <v>10.6363</v>
+        <v>9.79471</v>
       </c>
       <c r="C92" t="n">
-        <v>7.49482</v>
+        <v>8.168939999999999</v>
       </c>
       <c r="D92" t="n">
-        <v>36.8217</v>
+        <v>35.2033</v>
       </c>
       <c r="E92" t="n">
-        <v>3.78282</v>
+        <v>4.63732</v>
       </c>
       <c r="F92" t="n">
-        <v>5.48305</v>
+        <v>6.36712</v>
       </c>
     </row>
     <row r="93">
@@ -6899,19 +6899,19 @@
         <v>832694</v>
       </c>
       <c r="B93" t="n">
-        <v>13.0649</v>
+        <v>11.9586</v>
       </c>
       <c r="C93" t="n">
-        <v>9.41093</v>
+        <v>10.2706</v>
       </c>
       <c r="D93" t="n">
-        <v>37.9944</v>
+        <v>36.6219</v>
       </c>
       <c r="E93" t="n">
-        <v>3.92987</v>
+        <v>4.8326</v>
       </c>
       <c r="F93" t="n">
-        <v>5.87433</v>
+        <v>6.61159</v>
       </c>
     </row>
     <row r="94">
@@ -6919,19 +6919,19 @@
         <v>874285</v>
       </c>
       <c r="B94" t="n">
-        <v>16.9748</v>
+        <v>15.5581</v>
       </c>
       <c r="C94" t="n">
-        <v>3.64263</v>
+        <v>4.28448</v>
       </c>
       <c r="D94" t="n">
-        <v>39.1601</v>
+        <v>37.7069</v>
       </c>
       <c r="E94" t="n">
-        <v>4.10004</v>
+        <v>5.03261</v>
       </c>
       <c r="F94" t="n">
-        <v>6.1948</v>
+        <v>7.23119</v>
       </c>
     </row>
     <row r="95">
@@ -6939,19 +6939,19 @@
         <v>917955</v>
       </c>
       <c r="B95" t="n">
-        <v>5.97367</v>
+        <v>5.88925</v>
       </c>
       <c r="C95" t="n">
-        <v>3.83224</v>
+        <v>4.40563</v>
       </c>
       <c r="D95" t="n">
-        <v>40.5085</v>
+        <v>39.0452</v>
       </c>
       <c r="E95" t="n">
-        <v>4.27788</v>
+        <v>5.20018</v>
       </c>
       <c r="F95" t="n">
-        <v>6.45741</v>
+        <v>7.24365</v>
       </c>
     </row>
     <row r="96">
@@ -6959,19 +6959,19 @@
         <v>963808</v>
       </c>
       <c r="B96" t="n">
-        <v>6.26774</v>
+        <v>6.18194</v>
       </c>
       <c r="C96" t="n">
-        <v>4.01356</v>
+        <v>4.56857</v>
       </c>
       <c r="D96" t="n">
-        <v>41.8525</v>
+        <v>40.3624</v>
       </c>
       <c r="E96" t="n">
-        <v>4.45648</v>
+        <v>5.37263</v>
       </c>
       <c r="F96" t="n">
-        <v>6.82398</v>
+        <v>7.66217</v>
       </c>
     </row>
     <row r="97">
@@ -6979,19 +6979,19 @@
         <v>1011953</v>
       </c>
       <c r="B97" t="n">
-        <v>6.52261</v>
+        <v>6.4347</v>
       </c>
       <c r="C97" t="n">
-        <v>4.17434</v>
+        <v>4.7281</v>
       </c>
       <c r="D97" t="n">
-        <v>43.1724</v>
+        <v>41.7263</v>
       </c>
       <c r="E97" t="n">
-        <v>4.64078</v>
+        <v>5.48614</v>
       </c>
       <c r="F97" t="n">
-        <v>7.05211</v>
+        <v>7.94041</v>
       </c>
     </row>
     <row r="98">
@@ -6999,19 +6999,19 @@
         <v>1062505</v>
       </c>
       <c r="B98" t="n">
-        <v>6.84044</v>
+        <v>6.70296</v>
       </c>
       <c r="C98" t="n">
-        <v>4.33485</v>
+        <v>4.92793</v>
       </c>
       <c r="D98" t="n">
-        <v>44.4762</v>
+        <v>43.0522</v>
       </c>
       <c r="E98" t="n">
-        <v>4.82307</v>
+        <v>5.6885</v>
       </c>
       <c r="F98" t="n">
-        <v>7.39064</v>
+        <v>8.252520000000001</v>
       </c>
     </row>
     <row r="99">
@@ -7019,19 +7019,19 @@
         <v>1115584</v>
       </c>
       <c r="B99" t="n">
-        <v>7.12342</v>
+        <v>7.05168</v>
       </c>
       <c r="C99" t="n">
-        <v>4.55796</v>
+        <v>5.13785</v>
       </c>
       <c r="D99" t="n">
-        <v>45.9151</v>
+        <v>44.4194</v>
       </c>
       <c r="E99" t="n">
-        <v>5.00184</v>
+        <v>5.88334</v>
       </c>
       <c r="F99" t="n">
-        <v>7.65379</v>
+        <v>8.624359999999999</v>
       </c>
     </row>
     <row r="100">
@@ -7039,19 +7039,19 @@
         <v>1171316</v>
       </c>
       <c r="B100" t="n">
-        <v>7.49869</v>
+        <v>7.34266</v>
       </c>
       <c r="C100" t="n">
-        <v>4.77789</v>
+        <v>5.34444</v>
       </c>
       <c r="D100" t="n">
-        <v>47.439</v>
+        <v>46.0252</v>
       </c>
       <c r="E100" t="n">
-        <v>5.16726</v>
+        <v>6.13988</v>
       </c>
       <c r="F100" t="n">
-        <v>8.0008</v>
+        <v>9.06439</v>
       </c>
     </row>
     <row r="101">
@@ -7059,19 +7059,19 @@
         <v>1229834</v>
       </c>
       <c r="B101" t="n">
-        <v>7.79835</v>
+        <v>7.70018</v>
       </c>
       <c r="C101" t="n">
-        <v>5.06625</v>
+        <v>5.62382</v>
       </c>
       <c r="D101" t="n">
-        <v>48.448</v>
+        <v>47.5321</v>
       </c>
       <c r="E101" t="n">
-        <v>5.37379</v>
+        <v>6.35927</v>
       </c>
       <c r="F101" t="n">
-        <v>8.542920000000001</v>
+        <v>9.54102</v>
       </c>
     </row>
     <row r="102">
@@ -7079,19 +7079,19 @@
         <v>1291277</v>
       </c>
       <c r="B102" t="n">
-        <v>8.26792</v>
+        <v>8.105700000000001</v>
       </c>
       <c r="C102" t="n">
-        <v>5.40882</v>
+        <v>5.9755</v>
       </c>
       <c r="D102" t="n">
-        <v>50.6232</v>
+        <v>49.1949</v>
       </c>
       <c r="E102" t="n">
-        <v>5.60327</v>
+        <v>6.60787</v>
       </c>
       <c r="F102" t="n">
-        <v>9.15432</v>
+        <v>9.98743</v>
       </c>
     </row>
     <row r="103">
@@ -7099,19 +7099,19 @@
         <v>1355792</v>
       </c>
       <c r="B103" t="n">
-        <v>8.852959999999999</v>
+        <v>8.67334</v>
       </c>
       <c r="C103" t="n">
-        <v>5.84569</v>
+        <v>6.4266</v>
       </c>
       <c r="D103" t="n">
-        <v>52.2652</v>
+        <v>50.8593</v>
       </c>
       <c r="E103" t="n">
-        <v>5.88574</v>
+        <v>6.93712</v>
       </c>
       <c r="F103" t="n">
-        <v>9.47448</v>
+        <v>10.6402</v>
       </c>
     </row>
     <row r="104">
@@ -7119,19 +7119,19 @@
         <v>1423532</v>
       </c>
       <c r="B104" t="n">
-        <v>9.62448</v>
+        <v>9.40253</v>
       </c>
       <c r="C104" t="n">
-        <v>6.47503</v>
+        <v>7.05896</v>
       </c>
       <c r="D104" t="n">
-        <v>54.0463</v>
+        <v>52.6403</v>
       </c>
       <c r="E104" t="n">
-        <v>6.22928</v>
+        <v>7.32677</v>
       </c>
       <c r="F104" t="n">
-        <v>10.5531</v>
+        <v>11.7145</v>
       </c>
     </row>
     <row r="105">
@@ -7139,19 +7139,19 @@
         <v>1494659</v>
       </c>
       <c r="B105" t="n">
-        <v>10.6612</v>
+        <v>10.4379</v>
       </c>
       <c r="C105" t="n">
-        <v>7.31337</v>
+        <v>8.03285</v>
       </c>
       <c r="D105" t="n">
-        <v>55.9032</v>
+        <v>54.5705</v>
       </c>
       <c r="E105" t="n">
-        <v>6.74706</v>
+        <v>7.92194</v>
       </c>
       <c r="F105" t="n">
-        <v>11.1233</v>
+        <v>12.7393</v>
       </c>
     </row>
     <row r="106">
@@ -7159,19 +7159,19 @@
         <v>1569342</v>
       </c>
       <c r="B106" t="n">
-        <v>12.2637</v>
+        <v>12.0099</v>
       </c>
       <c r="C106" t="n">
-        <v>8.43411</v>
+        <v>9.416980000000001</v>
       </c>
       <c r="D106" t="n">
-        <v>57.3541</v>
+        <v>56.3699</v>
       </c>
       <c r="E106" t="n">
-        <v>7.44114</v>
+        <v>8.77725</v>
       </c>
       <c r="F106" t="n">
-        <v>12.6353</v>
+        <v>13.9492</v>
       </c>
     </row>
     <row r="107">
@@ -7179,19 +7179,19 @@
         <v>1647759</v>
       </c>
       <c r="B107" t="n">
-        <v>14.481</v>
+        <v>14.1146</v>
       </c>
       <c r="C107" t="n">
-        <v>10.1167</v>
+        <v>11.3623</v>
       </c>
       <c r="D107" t="n">
-        <v>43.8137</v>
+        <v>42.8475</v>
       </c>
       <c r="E107" t="n">
-        <v>4.85503</v>
+        <v>5.69049</v>
       </c>
       <c r="F107" t="n">
-        <v>7.28852</v>
+        <v>8.343669999999999</v>
       </c>
     </row>
     <row r="108">
@@ -7199,19 +7199,19 @@
         <v>1730096</v>
       </c>
       <c r="B108" t="n">
-        <v>17.7414</v>
+        <v>17.5689</v>
       </c>
       <c r="C108" t="n">
-        <v>4.43697</v>
+        <v>4.93448</v>
       </c>
       <c r="D108" t="n">
-        <v>44.9385</v>
+        <v>44.0632</v>
       </c>
       <c r="E108" t="n">
-        <v>4.80574</v>
+        <v>5.85425</v>
       </c>
       <c r="F108" t="n">
-        <v>7.5962</v>
+        <v>8.81767</v>
       </c>
     </row>
     <row r="109">
@@ -7219,19 +7219,19 @@
         <v>1816549</v>
       </c>
       <c r="B109" t="n">
-        <v>23.002</v>
+        <v>22.3466</v>
       </c>
       <c r="C109" t="n">
-        <v>4.56629</v>
+        <v>5.09682</v>
       </c>
       <c r="D109" t="n">
-        <v>46.2027</v>
+        <v>45.2466</v>
       </c>
       <c r="E109" t="n">
-        <v>5.04337</v>
+        <v>5.87396</v>
       </c>
       <c r="F109" t="n">
-        <v>7.96304</v>
+        <v>9.21759</v>
       </c>
     </row>
     <row r="110">
@@ -7239,19 +7239,19 @@
         <v>1907324</v>
       </c>
       <c r="B110" t="n">
-        <v>7.42654</v>
+        <v>7.39744</v>
       </c>
       <c r="C110" t="n">
-        <v>4.67544</v>
+        <v>5.2527</v>
       </c>
       <c r="D110" t="n">
-        <v>47.3917</v>
+        <v>46.4915</v>
       </c>
       <c r="E110" t="n">
-        <v>5.1825</v>
+        <v>6.12235</v>
       </c>
       <c r="F110" t="n">
-        <v>8.374650000000001</v>
+        <v>9.43435</v>
       </c>
     </row>
     <row r="111">
@@ -7259,19 +7259,19 @@
         <v>2002637</v>
       </c>
       <c r="B111" t="n">
-        <v>7.78837</v>
+        <v>7.68897</v>
       </c>
       <c r="C111" t="n">
-        <v>4.88859</v>
+        <v>5.42858</v>
       </c>
       <c r="D111" t="n">
-        <v>48.8</v>
+        <v>47.7693</v>
       </c>
       <c r="E111" t="n">
-        <v>5.42467</v>
+        <v>6.3101</v>
       </c>
       <c r="F111" t="n">
-        <v>8.90882</v>
+        <v>9.95294</v>
       </c>
     </row>
     <row r="112">
@@ -7279,19 +7279,19 @@
         <v>2102715</v>
       </c>
       <c r="B112" t="n">
-        <v>8.05613</v>
+        <v>7.98088</v>
       </c>
       <c r="C112" t="n">
-        <v>5.06659</v>
+        <v>5.65327</v>
       </c>
       <c r="D112" t="n">
-        <v>50.0319</v>
+        <v>49.1051</v>
       </c>
       <c r="E112" t="n">
-        <v>5.49294</v>
+        <v>6.51796</v>
       </c>
       <c r="F112" t="n">
-        <v>9.35999</v>
+        <v>10.5072</v>
       </c>
     </row>
     <row r="113">
@@ -7299,19 +7299,19 @@
         <v>2207796</v>
       </c>
       <c r="B113" t="n">
-        <v>8.48692</v>
+        <v>8.5784</v>
       </c>
       <c r="C113" t="n">
-        <v>5.47469</v>
+        <v>6.04606</v>
       </c>
       <c r="D113" t="n">
-        <v>51.4167</v>
+        <v>50.4638</v>
       </c>
       <c r="E113" t="n">
-        <v>5.69987</v>
+        <v>6.79658</v>
       </c>
       <c r="F113" t="n">
-        <v>9.88987</v>
+        <v>11.2094</v>
       </c>
     </row>
     <row r="114">
@@ -7319,19 +7319,19 @@
         <v>2318131</v>
       </c>
       <c r="B114" t="n">
-        <v>8.92717</v>
+        <v>9.189170000000001</v>
       </c>
       <c r="C114" t="n">
-        <v>5.6128</v>
+        <v>6.4902</v>
       </c>
       <c r="D114" t="n">
-        <v>52.831</v>
+        <v>51.8652</v>
       </c>
       <c r="E114" t="n">
-        <v>5.91644</v>
+        <v>7.28856</v>
       </c>
       <c r="F114" t="n">
-        <v>10.4735</v>
+        <v>11.8741</v>
       </c>
     </row>
     <row r="115">
@@ -7339,19 +7339,19 @@
         <v>2433982</v>
       </c>
       <c r="B115" t="n">
-        <v>9.55842</v>
+        <v>9.669230000000001</v>
       </c>
       <c r="C115" t="n">
-        <v>6.00671</v>
+        <v>6.85791</v>
       </c>
       <c r="D115" t="n">
-        <v>54.3372</v>
+        <v>53.376</v>
       </c>
       <c r="E115" t="n">
-        <v>6.25721</v>
+        <v>7.64783</v>
       </c>
       <c r="F115" t="n">
-        <v>11.0509</v>
+        <v>12.3999</v>
       </c>
     </row>
     <row r="116">
@@ -7359,19 +7359,19 @@
         <v>2555625</v>
       </c>
       <c r="B116" t="n">
-        <v>10.2165</v>
+        <v>10.2506</v>
       </c>
       <c r="C116" t="n">
-        <v>6.50842</v>
+        <v>7.30465</v>
       </c>
       <c r="D116" t="n">
-        <v>55.9479</v>
+        <v>54.8952</v>
       </c>
       <c r="E116" t="n">
-        <v>6.6769</v>
+        <v>8.05545</v>
       </c>
       <c r="F116" t="n">
-        <v>11.6901</v>
+        <v>12.9417</v>
       </c>
     </row>
     <row r="117">
@@ -7379,19 +7379,19 @@
         <v>2683350</v>
       </c>
       <c r="B117" t="n">
-        <v>10.9008</v>
+        <v>10.8815</v>
       </c>
       <c r="C117" t="n">
-        <v>7.05255</v>
+        <v>7.83005</v>
       </c>
       <c r="D117" t="n">
-        <v>57.7046</v>
+        <v>56.5195</v>
       </c>
       <c r="E117" t="n">
-        <v>7.1027</v>
+        <v>8.47518</v>
       </c>
       <c r="F117" t="n">
-        <v>12.2191</v>
+        <v>13.5208</v>
       </c>
     </row>
     <row r="118">
@@ -7399,19 +7399,19 @@
         <v>2817461</v>
       </c>
       <c r="B118" t="n">
-        <v>11.6561</v>
+        <v>11.5707</v>
       </c>
       <c r="C118" t="n">
-        <v>7.68435</v>
+        <v>8.4962</v>
       </c>
       <c r="D118" t="n">
-        <v>59.3289</v>
+        <v>58.222</v>
       </c>
       <c r="E118" t="n">
-        <v>7.56529</v>
+        <v>8.981299999999999</v>
       </c>
       <c r="F118" t="n">
-        <v>12.9276</v>
+        <v>14.2501</v>
       </c>
     </row>
     <row r="119">
@@ -7419,19 +7419,19 @@
         <v>2958277</v>
       </c>
       <c r="B119" t="n">
-        <v>12.6535</v>
+        <v>12.4801</v>
       </c>
       <c r="C119" t="n">
-        <v>8.484640000000001</v>
+        <v>9.37907</v>
       </c>
       <c r="D119" t="n">
-        <v>61.1944</v>
+        <v>59.9816</v>
       </c>
       <c r="E119" t="n">
-        <v>8.14733</v>
+        <v>9.524380000000001</v>
       </c>
       <c r="F119" t="n">
-        <v>13.6032</v>
+        <v>15.0516</v>
       </c>
     </row>
     <row r="120">
@@ -7439,19 +7439,19 @@
         <v>3106133</v>
       </c>
       <c r="B120" t="n">
-        <v>13.9538</v>
+        <v>13.6929</v>
       </c>
       <c r="C120" t="n">
-        <v>9.51498</v>
+        <v>10.5534</v>
       </c>
       <c r="D120" t="n">
-        <v>63.2171</v>
+        <v>62.015</v>
       </c>
       <c r="E120" t="n">
-        <v>8.88021</v>
+        <v>10.3078</v>
       </c>
       <c r="F120" t="n">
-        <v>14.7072</v>
+        <v>16.1901</v>
       </c>
     </row>
     <row r="121">
@@ -7459,19 +7459,19 @@
         <v>3261381</v>
       </c>
       <c r="B121" t="n">
-        <v>15.7846</v>
+        <v>15.5248</v>
       </c>
       <c r="C121" t="n">
-        <v>11.0743</v>
+        <v>12.2675</v>
       </c>
       <c r="D121" t="n">
-        <v>47.11</v>
+        <v>45.8663</v>
       </c>
       <c r="E121" t="n">
-        <v>6.56617</v>
+        <v>7.97219</v>
       </c>
       <c r="F121" t="n">
-        <v>10.2913</v>
+        <v>11.1642</v>
       </c>
     </row>
     <row r="122">
@@ -7479,19 +7479,19 @@
         <v>3424391</v>
       </c>
       <c r="B122" t="n">
-        <v>18.6817</v>
+        <v>17.9634</v>
       </c>
       <c r="C122" t="n">
-        <v>6.22883</v>
+        <v>6.81676</v>
       </c>
       <c r="D122" t="n">
-        <v>48.4778</v>
+        <v>47.1113</v>
       </c>
       <c r="E122" t="n">
-        <v>7.08016</v>
+        <v>8.259460000000001</v>
       </c>
       <c r="F122" t="n">
-        <v>10.8541</v>
+        <v>11.9166</v>
       </c>
     </row>
     <row r="123">
@@ -7499,19 +7499,19 @@
         <v>3595551</v>
       </c>
       <c r="B123" t="n">
-        <v>23.1118</v>
+        <v>22.3259</v>
       </c>
       <c r="C123" t="n">
-        <v>6.59794</v>
+        <v>7.26286</v>
       </c>
       <c r="D123" t="n">
-        <v>49.6408</v>
+        <v>48.3539</v>
       </c>
       <c r="E123" t="n">
-        <v>7.22012</v>
+        <v>8.013479999999999</v>
       </c>
       <c r="F123" t="n">
-        <v>11.3514</v>
+        <v>12.055</v>
       </c>
     </row>
     <row r="124">
@@ -7519,19 +7519,19 @@
         <v>3775269</v>
       </c>
       <c r="B124" t="n">
-        <v>9.95715</v>
+        <v>9.729649999999999</v>
       </c>
       <c r="C124" t="n">
-        <v>6.4795</v>
+        <v>7.29027</v>
       </c>
       <c r="D124" t="n">
-        <v>50.8481</v>
+        <v>49.6164</v>
       </c>
       <c r="E124" t="n">
-        <v>7.30055</v>
+        <v>8.327159999999999</v>
       </c>
       <c r="F124" t="n">
-        <v>11.5725</v>
+        <v>12.6151</v>
       </c>
     </row>
     <row r="125">
@@ -7539,19 +7539,19 @@
         <v>3963972</v>
       </c>
       <c r="B125" t="n">
-        <v>10.1521</v>
+        <v>10.1225</v>
       </c>
       <c r="C125" t="n">
-        <v>6.59039</v>
+        <v>7.33811</v>
       </c>
       <c r="D125" t="n">
-        <v>52.2798</v>
+        <v>50.6629</v>
       </c>
       <c r="E125" t="n">
-        <v>7.51573</v>
+        <v>8.48638</v>
       </c>
       <c r="F125" t="n">
-        <v>11.6769</v>
+        <v>12.8097</v>
       </c>
     </row>
     <row r="126">
@@ -7559,19 +7559,19 @@
         <v>4162110</v>
       </c>
       <c r="B126" t="n">
-        <v>10.3119</v>
+        <v>10.0903</v>
       </c>
       <c r="C126" t="n">
-        <v>6.90924</v>
+        <v>7.69197</v>
       </c>
       <c r="D126" t="n">
-        <v>53.4251</v>
+        <v>52.2238</v>
       </c>
       <c r="E126" t="n">
-        <v>7.74228</v>
+        <v>8.618740000000001</v>
       </c>
       <c r="F126" t="n">
-        <v>12.1396</v>
+        <v>13.0487</v>
       </c>
     </row>
     <row r="127">
@@ -7579,19 +7579,19 @@
         <v>4370154</v>
       </c>
       <c r="B127" t="n">
-        <v>10.6652</v>
+        <v>10.545</v>
       </c>
       <c r="C127" t="n">
-        <v>6.9047</v>
+        <v>7.65364</v>
       </c>
       <c r="D127" t="n">
-        <v>54.9921</v>
+        <v>53.5138</v>
       </c>
       <c r="E127" t="n">
-        <v>8.233689999999999</v>
+        <v>9.26008</v>
       </c>
       <c r="F127" t="n">
-        <v>12.5147</v>
+        <v>13.8806</v>
       </c>
     </row>
     <row r="128">
@@ -7599,19 +7599,19 @@
         <v>4588600</v>
       </c>
       <c r="B128" t="n">
-        <v>11.0473</v>
+        <v>10.7042</v>
       </c>
       <c r="C128" t="n">
-        <v>7.26824</v>
+        <v>7.91666</v>
       </c>
       <c r="D128" t="n">
-        <v>56.1947</v>
+        <v>55.083</v>
       </c>
       <c r="E128" t="n">
-        <v>8.079230000000001</v>
+        <v>9.221220000000001</v>
       </c>
       <c r="F128" t="n">
-        <v>12.876</v>
+        <v>13.9827</v>
       </c>
     </row>
     <row r="129">
@@ -7619,19 +7619,19 @@
         <v>4817968</v>
       </c>
       <c r="B129" t="n">
-        <v>11.1976</v>
+        <v>11.1177</v>
       </c>
       <c r="C129" t="n">
-        <v>7.50604</v>
+        <v>8.187430000000001</v>
       </c>
       <c r="D129" t="n">
-        <v>57.7961</v>
+        <v>56.4544</v>
       </c>
       <c r="E129" t="n">
-        <v>8.56166</v>
+        <v>9.57738</v>
       </c>
       <c r="F129" t="n">
-        <v>13.1201</v>
+        <v>14.5279</v>
       </c>
     </row>
     <row r="130">
@@ -7639,19 +7639,19 @@
         <v>5058804</v>
       </c>
       <c r="B130" t="n">
-        <v>11.6962</v>
+        <v>11.6069</v>
       </c>
       <c r="C130" t="n">
-        <v>7.79934</v>
+        <v>8.400919999999999</v>
       </c>
       <c r="D130" t="n">
-        <v>59.1228</v>
+        <v>57.9968</v>
       </c>
       <c r="E130" t="n">
-        <v>8.65024</v>
+        <v>9.95903</v>
       </c>
       <c r="F130" t="n">
-        <v>13.9372</v>
+        <v>14.9939</v>
       </c>
     </row>
     <row r="131">
@@ -7659,19 +7659,19 @@
         <v>5311681</v>
       </c>
       <c r="B131" t="n">
-        <v>12.1964</v>
+        <v>11.9996</v>
       </c>
       <c r="C131" t="n">
-        <v>8.02692</v>
+        <v>8.81134</v>
       </c>
       <c r="D131" t="n">
-        <v>60.8161</v>
+        <v>59.4258</v>
       </c>
       <c r="E131" t="n">
-        <v>8.997159999999999</v>
+        <v>10.0888</v>
       </c>
       <c r="F131" t="n">
-        <v>14.3722</v>
+        <v>15.4657</v>
       </c>
     </row>
     <row r="132">
@@ -7679,19 +7679,19 @@
         <v>5577201</v>
       </c>
       <c r="B132" t="n">
-        <v>12.9618</v>
+        <v>12.6013</v>
       </c>
       <c r="C132" t="n">
-        <v>8.646420000000001</v>
+        <v>9.35144</v>
       </c>
       <c r="D132" t="n">
-        <v>62.5874</v>
+        <v>61.2168</v>
       </c>
       <c r="E132" t="n">
-        <v>9.33</v>
+        <v>10.2638</v>
       </c>
       <c r="F132" t="n">
-        <v>15.0583</v>
+        <v>15.9167</v>
       </c>
     </row>
     <row r="133">
@@ -7699,19 +7699,19 @@
         <v>5855997</v>
       </c>
       <c r="B133" t="n">
-        <v>13.7429</v>
+        <v>13.3941</v>
       </c>
       <c r="C133" t="n">
-        <v>9.273820000000001</v>
+        <v>10.0463</v>
       </c>
       <c r="D133" t="n">
-        <v>64.3751</v>
+        <v>63.0115</v>
       </c>
       <c r="E133" t="n">
-        <v>9.612270000000001</v>
+        <v>10.6983</v>
       </c>
       <c r="F133" t="n">
-        <v>15.708</v>
+        <v>16.7463</v>
       </c>
     </row>
     <row r="134">
@@ -7719,19 +7719,19 @@
         <v>6148732</v>
       </c>
       <c r="B134" t="n">
-        <v>14.8663</v>
+        <v>14.6085</v>
       </c>
       <c r="C134" t="n">
-        <v>10.2715</v>
+        <v>11.2426</v>
       </c>
       <c r="D134" t="n">
-        <v>66.30410000000001</v>
+        <v>64.8914</v>
       </c>
       <c r="E134" t="n">
-        <v>10.0906</v>
+        <v>11.7234</v>
       </c>
       <c r="F134" t="n">
-        <v>16.5279</v>
+        <v>18.2162</v>
       </c>
     </row>
     <row r="135">
@@ -7739,19 +7739,19 @@
         <v>6456103</v>
       </c>
       <c r="B135" t="n">
-        <v>16.4299</v>
+        <v>16.1268</v>
       </c>
       <c r="C135" t="n">
-        <v>11.5568</v>
+        <v>12.6386</v>
       </c>
       <c r="D135" t="n">
-        <v>49.0165</v>
+        <v>47.4904</v>
       </c>
       <c r="E135" t="n">
-        <v>13.1922</v>
+        <v>15.4301</v>
       </c>
       <c r="F135" t="n">
-        <v>17.5336</v>
+        <v>20.0657</v>
       </c>
     </row>
     <row r="136">
@@ -7759,19 +7759,19 @@
         <v>6778842</v>
       </c>
       <c r="B136" t="n">
-        <v>18.917</v>
+        <v>18.4911</v>
       </c>
       <c r="C136" t="n">
-        <v>11.9428</v>
+        <v>13.7102</v>
       </c>
       <c r="D136" t="n">
-        <v>50.0063</v>
+        <v>48.7778</v>
       </c>
       <c r="E136" t="n">
-        <v>13.0833</v>
+        <v>15.5941</v>
       </c>
       <c r="F136" t="n">
-        <v>17.8534</v>
+        <v>19.7461</v>
       </c>
     </row>
     <row r="137">
@@ -7779,19 +7779,19 @@
         <v>7117717</v>
       </c>
       <c r="B137" t="n">
-        <v>23.0673</v>
+        <v>22.2882</v>
       </c>
       <c r="C137" t="n">
-        <v>12.0686</v>
+        <v>14.0285</v>
       </c>
       <c r="D137" t="n">
-        <v>51.2237</v>
+        <v>49.7427</v>
       </c>
       <c r="E137" t="n">
-        <v>13.6601</v>
+        <v>15.6064</v>
       </c>
       <c r="F137" t="n">
-        <v>17.9974</v>
+        <v>20.1239</v>
       </c>
     </row>
     <row r="138">
@@ -7799,19 +7799,19 @@
         <v>7473535</v>
       </c>
       <c r="B138" t="n">
-        <v>16.5568</v>
+        <v>16.2081</v>
       </c>
       <c r="C138" t="n">
-        <v>12.0495</v>
+        <v>14.3687</v>
       </c>
       <c r="D138" t="n">
-        <v>52.7346</v>
+        <v>51.1859</v>
       </c>
       <c r="E138" t="n">
-        <v>13.9001</v>
+        <v>15.6792</v>
       </c>
       <c r="F138" t="n">
-        <v>18.4758</v>
+        <v>20.6171</v>
       </c>
     </row>
     <row r="139">
@@ -7819,19 +7819,19 @@
         <v>7847143</v>
       </c>
       <c r="B139" t="n">
-        <v>16.6864</v>
+        <v>16.2071</v>
       </c>
       <c r="C139" t="n">
-        <v>12.3015</v>
+        <v>14.0958</v>
       </c>
       <c r="D139" t="n">
-        <v>53.858</v>
+        <v>52.5405</v>
       </c>
       <c r="E139" t="n">
-        <v>13.8684</v>
+        <v>15.938</v>
       </c>
       <c r="F139" t="n">
-        <v>18.0392</v>
+        <v>20.9985</v>
       </c>
     </row>
     <row r="140">
@@ -7839,19 +7839,19 @@
         <v>8239431</v>
       </c>
       <c r="B140" t="n">
-        <v>17.0168</v>
+        <v>16.5734</v>
       </c>
       <c r="C140" t="n">
-        <v>12.408</v>
+        <v>14.1886</v>
       </c>
       <c r="D140" t="n">
-        <v>55.1972</v>
+        <v>53.8302</v>
       </c>
       <c r="E140" t="n">
-        <v>13.8942</v>
+        <v>15.9344</v>
       </c>
       <c r="F140" t="n">
-        <v>19.1573</v>
+        <v>21.174</v>
       </c>
     </row>
     <row r="141">
@@ -7859,19 +7859,19 @@
         <v>8651333</v>
       </c>
       <c r="B141" t="n">
-        <v>17.1053</v>
+        <v>16.6724</v>
       </c>
       <c r="C141" t="n">
-        <v>12.4458</v>
+        <v>14.6244</v>
       </c>
       <c r="D141" t="n">
-        <v>56.3302</v>
+        <v>55.1186</v>
       </c>
       <c r="E141" t="n">
-        <v>14.2459</v>
+        <v>16.1325</v>
       </c>
       <c r="F141" t="n">
-        <v>18.8207</v>
+        <v>21.6273</v>
       </c>
     </row>
     <row r="142">
@@ -7879,19 +7879,19 @@
         <v>9083830</v>
       </c>
       <c r="B142" t="n">
-        <v>17.3525</v>
+        <v>16.828</v>
       </c>
       <c r="C142" t="n">
-        <v>12.4872</v>
+        <v>14.4721</v>
       </c>
       <c r="D142" t="n">
-        <v>57.8384</v>
+        <v>56.5239</v>
       </c>
       <c r="E142" t="n">
-        <v>14.2547</v>
+        <v>16.325</v>
       </c>
       <c r="F142" t="n">
-        <v>19.7023</v>
+        <v>22.0327</v>
       </c>
     </row>
     <row r="143">
@@ -7899,19 +7899,19 @@
         <v>9537951</v>
       </c>
       <c r="B143" t="n">
-        <v>17.6349</v>
+        <v>16.7879</v>
       </c>
       <c r="C143" t="n">
-        <v>12.6683</v>
+        <v>14.7711</v>
       </c>
       <c r="D143" t="n">
-        <v>59.6077</v>
+        <v>58.0057</v>
       </c>
       <c r="E143" t="n">
-        <v>14.2408</v>
+        <v>16.4875</v>
       </c>
       <c r="F143" t="n">
-        <v>19.6265</v>
+        <v>22.4541</v>
       </c>
     </row>
   </sheetData>

--- a/gcc-x64/Scattered unsuccessful looukp.xlsx
+++ b/gcc-x64/Scattered unsuccessful looukp.xlsx
@@ -5079,19 +5079,19 @@
         <v>10000</v>
       </c>
       <c r="B2" t="n">
-        <v>2.84976</v>
+        <v>2.93296</v>
       </c>
       <c r="C2" t="n">
-        <v>2.29331</v>
+        <v>1.92244</v>
       </c>
       <c r="D2" t="n">
-        <v>13.3546</v>
+        <v>13.4709</v>
       </c>
       <c r="E2" t="n">
-        <v>2.39717</v>
+        <v>1.85415</v>
       </c>
       <c r="F2" t="n">
-        <v>2.62141</v>
+        <v>2.08544</v>
       </c>
     </row>
     <row r="3">
@@ -5099,19 +5099,19 @@
         <v>10500</v>
       </c>
       <c r="B3" t="n">
-        <v>2.96323</v>
+        <v>3.01709</v>
       </c>
       <c r="C3" t="n">
-        <v>2.32521</v>
+        <v>1.9828</v>
       </c>
       <c r="D3" t="n">
-        <v>13.7075</v>
+        <v>13.7036</v>
       </c>
       <c r="E3" t="n">
-        <v>2.4238</v>
+        <v>1.58057</v>
       </c>
       <c r="F3" t="n">
-        <v>2.65403</v>
+        <v>1.89858</v>
       </c>
     </row>
     <row r="4">
@@ -5119,19 +5119,19 @@
         <v>11025</v>
       </c>
       <c r="B4" t="n">
-        <v>3.05475</v>
+        <v>3.07826</v>
       </c>
       <c r="C4" t="n">
-        <v>2.40675</v>
+        <v>2.06452</v>
       </c>
       <c r="D4" t="n">
-        <v>14.2233</v>
+        <v>14.4756</v>
       </c>
       <c r="E4" t="n">
-        <v>2.4311</v>
+        <v>1.60264</v>
       </c>
       <c r="F4" t="n">
-        <v>2.64693</v>
+        <v>1.80961</v>
       </c>
     </row>
     <row r="5">
@@ -5139,19 +5139,19 @@
         <v>11576</v>
       </c>
       <c r="B5" t="n">
-        <v>3.54807</v>
+        <v>3.51224</v>
       </c>
       <c r="C5" t="n">
-        <v>2.61908</v>
+        <v>2.25355</v>
       </c>
       <c r="D5" t="n">
-        <v>15.0297</v>
+        <v>15.0178</v>
       </c>
       <c r="E5" t="n">
-        <v>2.29577</v>
+        <v>1.75457</v>
       </c>
       <c r="F5" t="n">
-        <v>2.63871</v>
+        <v>1.868</v>
       </c>
     </row>
     <row r="6">
@@ -5159,19 +5159,19 @@
         <v>12154</v>
       </c>
       <c r="B6" t="n">
-        <v>4.74079</v>
+        <v>4.79475</v>
       </c>
       <c r="C6" t="n">
-        <v>3.66963</v>
+        <v>2.98979</v>
       </c>
       <c r="D6" t="n">
-        <v>15.5707</v>
+        <v>15.5595</v>
       </c>
       <c r="E6" t="n">
-        <v>2.33084</v>
+        <v>1.7718</v>
       </c>
       <c r="F6" t="n">
-        <v>2.64503</v>
+        <v>1.87205</v>
       </c>
     </row>
     <row r="7">
@@ -5179,19 +5179,19 @@
         <v>12760</v>
       </c>
       <c r="B7" t="n">
-        <v>6.70184</v>
+        <v>6.209</v>
       </c>
       <c r="C7" t="n">
-        <v>6.08353</v>
+        <v>4.93874</v>
       </c>
       <c r="D7" t="n">
-        <v>11.1978</v>
+        <v>10.6413</v>
       </c>
       <c r="E7" t="n">
-        <v>2.46864</v>
+        <v>1.79225</v>
       </c>
       <c r="F7" t="n">
-        <v>2.61484</v>
+        <v>1.89308</v>
       </c>
     </row>
     <row r="8">
@@ -5199,19 +5199,19 @@
         <v>13396</v>
       </c>
       <c r="B8" t="n">
-        <v>9.39382</v>
+        <v>9.5185</v>
       </c>
       <c r="C8" t="n">
-        <v>2.1117</v>
+        <v>1.73426</v>
       </c>
       <c r="D8" t="n">
-        <v>11.7621</v>
+        <v>11.0569</v>
       </c>
       <c r="E8" t="n">
-        <v>2.49207</v>
+        <v>1.81274</v>
       </c>
       <c r="F8" t="n">
-        <v>2.61725</v>
+        <v>1.92521</v>
       </c>
     </row>
     <row r="9">
@@ -5219,19 +5219,19 @@
         <v>14063</v>
       </c>
       <c r="B9" t="n">
-        <v>13.7808</v>
+        <v>13.9234</v>
       </c>
       <c r="C9" t="n">
-        <v>2.12353</v>
+        <v>1.75359</v>
       </c>
       <c r="D9" t="n">
-        <v>12.3582</v>
+        <v>11.6855</v>
       </c>
       <c r="E9" t="n">
-        <v>2.50651</v>
+        <v>1.80934</v>
       </c>
       <c r="F9" t="n">
-        <v>2.67277</v>
+        <v>1.93077</v>
       </c>
     </row>
     <row r="10">
@@ -5239,19 +5239,19 @@
         <v>14763</v>
       </c>
       <c r="B10" t="n">
-        <v>2.83408</v>
+        <v>2.81432</v>
       </c>
       <c r="C10" t="n">
-        <v>2.11062</v>
+        <v>1.79166</v>
       </c>
       <c r="D10" t="n">
-        <v>12.9758</v>
+        <v>12.2611</v>
       </c>
       <c r="E10" t="n">
-        <v>2.52632</v>
+        <v>1.82592</v>
       </c>
       <c r="F10" t="n">
-        <v>2.69923</v>
+        <v>1.95455</v>
       </c>
     </row>
     <row r="11">
@@ -5259,19 +5259,19 @@
         <v>15498</v>
       </c>
       <c r="B11" t="n">
-        <v>2.88648</v>
+        <v>2.86484</v>
       </c>
       <c r="C11" t="n">
-        <v>2.13888</v>
+        <v>1.9972</v>
       </c>
       <c r="D11" t="n">
-        <v>13.4216</v>
+        <v>12.7119</v>
       </c>
       <c r="E11" t="n">
-        <v>2.56623</v>
+        <v>1.83372</v>
       </c>
       <c r="F11" t="n">
-        <v>2.76724</v>
+        <v>1.9938</v>
       </c>
     </row>
     <row r="12">
@@ -5279,19 +5279,19 @@
         <v>16269</v>
       </c>
       <c r="B12" t="n">
-        <v>2.90789</v>
+        <v>2.89798</v>
       </c>
       <c r="C12" t="n">
-        <v>2.21287</v>
+        <v>2.0459</v>
       </c>
       <c r="D12" t="n">
-        <v>13.9178</v>
+        <v>13.2645</v>
       </c>
       <c r="E12" t="n">
-        <v>2.56335</v>
+        <v>1.85555</v>
       </c>
       <c r="F12" t="n">
-        <v>2.82109</v>
+        <v>2.00323</v>
       </c>
     </row>
     <row r="13">
@@ -5299,19 +5299,19 @@
         <v>17078</v>
       </c>
       <c r="B13" t="n">
-        <v>3.00103</v>
+        <v>2.9259</v>
       </c>
       <c r="C13" t="n">
-        <v>2.29006</v>
+        <v>1.94218</v>
       </c>
       <c r="D13" t="n">
-        <v>14.5833</v>
+        <v>13.7295</v>
       </c>
       <c r="E13" t="n">
-        <v>2.58246</v>
+        <v>1.86428</v>
       </c>
       <c r="F13" t="n">
-        <v>2.83508</v>
+        <v>2.03765</v>
       </c>
     </row>
     <row r="14">
@@ -5319,19 +5319,19 @@
         <v>17927</v>
       </c>
       <c r="B14" t="n">
-        <v>2.99385</v>
+        <v>2.96983</v>
       </c>
       <c r="C14" t="n">
-        <v>2.31282</v>
+        <v>2.06698</v>
       </c>
       <c r="D14" t="n">
-        <v>15.0127</v>
+        <v>14.2572</v>
       </c>
       <c r="E14" t="n">
-        <v>2.60398</v>
+        <v>1.88776</v>
       </c>
       <c r="F14" t="n">
-        <v>2.88525</v>
+        <v>2.0867</v>
       </c>
     </row>
     <row r="15">
@@ -5339,19 +5339,19 @@
         <v>18818</v>
       </c>
       <c r="B15" t="n">
-        <v>3.05266</v>
+        <v>3.0549</v>
       </c>
       <c r="C15" t="n">
-        <v>2.37954</v>
+        <v>2.18093</v>
       </c>
       <c r="D15" t="n">
-        <v>15.4397</v>
+        <v>14.5586</v>
       </c>
       <c r="E15" t="n">
-        <v>2.6301</v>
+        <v>1.90807</v>
       </c>
       <c r="F15" t="n">
-        <v>2.9372</v>
+        <v>2.14097</v>
       </c>
     </row>
     <row r="16">
@@ -5359,19 +5359,19 @@
         <v>19753</v>
       </c>
       <c r="B16" t="n">
-        <v>3.24238</v>
+        <v>3.18072</v>
       </c>
       <c r="C16" t="n">
-        <v>2.51793</v>
+        <v>2.18924</v>
       </c>
       <c r="D16" t="n">
-        <v>15.7099</v>
+        <v>15.0222</v>
       </c>
       <c r="E16" t="n">
-        <v>2.62288</v>
+        <v>1.93065</v>
       </c>
       <c r="F16" t="n">
-        <v>2.93285</v>
+        <v>2.17682</v>
       </c>
     </row>
     <row r="17">
@@ -5379,19 +5379,19 @@
         <v>20734</v>
       </c>
       <c r="B17" t="n">
-        <v>3.3466</v>
+        <v>3.29028</v>
       </c>
       <c r="C17" t="n">
-        <v>2.59377</v>
+        <v>2.33675</v>
       </c>
       <c r="D17" t="n">
-        <v>16.2317</v>
+        <v>15.4309</v>
       </c>
       <c r="E17" t="n">
-        <v>2.65818</v>
+        <v>1.9688</v>
       </c>
       <c r="F17" t="n">
-        <v>3.01808</v>
+        <v>2.2178</v>
       </c>
     </row>
     <row r="18">
@@ -5399,19 +5399,19 @@
         <v>21764</v>
       </c>
       <c r="B18" t="n">
-        <v>3.75319</v>
+        <v>3.66376</v>
       </c>
       <c r="C18" t="n">
-        <v>2.82194</v>
+        <v>2.52532</v>
       </c>
       <c r="D18" t="n">
-        <v>16.6393</v>
+        <v>15.8866</v>
       </c>
       <c r="E18" t="n">
-        <v>2.64179</v>
+        <v>1.87565</v>
       </c>
       <c r="F18" t="n">
-        <v>2.98326</v>
+        <v>2.25422</v>
       </c>
     </row>
     <row r="19">
@@ -5419,19 +5419,19 @@
         <v>22845</v>
       </c>
       <c r="B19" t="n">
-        <v>4.30401</v>
+        <v>4.12529</v>
       </c>
       <c r="C19" t="n">
-        <v>3.34344</v>
+        <v>3.2319</v>
       </c>
       <c r="D19" t="n">
-        <v>17.1183</v>
+        <v>16.3334</v>
       </c>
       <c r="E19" t="n">
-        <v>2.63721</v>
+        <v>1.96876</v>
       </c>
       <c r="F19" t="n">
-        <v>2.96125</v>
+        <v>2.30341</v>
       </c>
     </row>
     <row r="20">
@@ -5439,19 +5439,19 @@
         <v>23980</v>
       </c>
       <c r="B20" t="n">
-        <v>5.16177</v>
+        <v>5.24093</v>
       </c>
       <c r="C20" t="n">
-        <v>4.48842</v>
+        <v>4.26989</v>
       </c>
       <c r="D20" t="n">
-        <v>17.3991</v>
+        <v>16.7195</v>
       </c>
       <c r="E20" t="n">
-        <v>3.00766</v>
+        <v>1.85905</v>
       </c>
       <c r="F20" t="n">
-        <v>3.27281</v>
+        <v>2.00738</v>
       </c>
     </row>
     <row r="21">
@@ -5459,19 +5459,19 @@
         <v>25171</v>
       </c>
       <c r="B21" t="n">
-        <v>6.62557</v>
+        <v>6.66592</v>
       </c>
       <c r="C21" t="n">
-        <v>6.37394</v>
+        <v>5.5906</v>
       </c>
       <c r="D21" t="n">
-        <v>12.4326</v>
+        <v>11.5507</v>
       </c>
       <c r="E21" t="n">
-        <v>2.58192</v>
+        <v>1.88098</v>
       </c>
       <c r="F21" t="n">
-        <v>2.95384</v>
+        <v>2.03909</v>
       </c>
     </row>
     <row r="22">
@@ -5479,19 +5479,19 @@
         <v>26421</v>
       </c>
       <c r="B22" t="n">
-        <v>8.903840000000001</v>
+        <v>9.304959999999999</v>
       </c>
       <c r="C22" t="n">
-        <v>2.12562</v>
+        <v>1.98986</v>
       </c>
       <c r="D22" t="n">
-        <v>12.9186</v>
+        <v>12.0347</v>
       </c>
       <c r="E22" t="n">
-        <v>2.74583</v>
+        <v>1.88911</v>
       </c>
       <c r="F22" t="n">
-        <v>3.40401</v>
+        <v>2.05574</v>
       </c>
     </row>
     <row r="23">
@@ -5499,19 +5499,19 @@
         <v>27733</v>
       </c>
       <c r="B23" t="n">
-        <v>12.9051</v>
+        <v>12.6782</v>
       </c>
       <c r="C23" t="n">
-        <v>2.21559</v>
+        <v>1.9049</v>
       </c>
       <c r="D23" t="n">
-        <v>13.4571</v>
+        <v>12.5374</v>
       </c>
       <c r="E23" t="n">
-        <v>2.61644</v>
+        <v>1.90748</v>
       </c>
       <c r="F23" t="n">
-        <v>3.01823</v>
+        <v>2.09968</v>
       </c>
     </row>
     <row r="24">
@@ -5519,19 +5519,19 @@
         <v>29110</v>
       </c>
       <c r="B24" t="n">
-        <v>3.13546</v>
+        <v>2.90598</v>
       </c>
       <c r="C24" t="n">
-        <v>2.4966</v>
+        <v>1.86088</v>
       </c>
       <c r="D24" t="n">
-        <v>13.9679</v>
+        <v>13.1011</v>
       </c>
       <c r="E24" t="n">
-        <v>2.67906</v>
+        <v>1.92631</v>
       </c>
       <c r="F24" t="n">
-        <v>3.50823</v>
+        <v>2.13645</v>
       </c>
     </row>
     <row r="25">
@@ -5539,19 +5539,19 @@
         <v>30555</v>
       </c>
       <c r="B25" t="n">
-        <v>3.16554</v>
+        <v>2.95361</v>
       </c>
       <c r="C25" t="n">
-        <v>2.4829</v>
+        <v>1.87173</v>
       </c>
       <c r="D25" t="n">
-        <v>14.4759</v>
+        <v>13.594</v>
       </c>
       <c r="E25" t="n">
-        <v>2.71468</v>
+        <v>1.9514</v>
       </c>
       <c r="F25" t="n">
-        <v>3.52131</v>
+        <v>2.18378</v>
       </c>
     </row>
     <row r="26">
@@ -5559,19 +5559,19 @@
         <v>32072</v>
       </c>
       <c r="B26" t="n">
-        <v>3.21957</v>
+        <v>3.00406</v>
       </c>
       <c r="C26" t="n">
-        <v>2.51443</v>
+        <v>1.9412</v>
       </c>
       <c r="D26" t="n">
-        <v>14.9138</v>
+        <v>14.0419</v>
       </c>
       <c r="E26" t="n">
-        <v>2.65731</v>
+        <v>1.98876</v>
       </c>
       <c r="F26" t="n">
-        <v>3.1189</v>
+        <v>2.2175</v>
       </c>
     </row>
     <row r="27">
@@ -5579,19 +5579,19 @@
         <v>33664</v>
       </c>
       <c r="B27" t="n">
-        <v>3.11712</v>
+        <v>3.05075</v>
       </c>
       <c r="C27" t="n">
-        <v>2.36498</v>
+        <v>2.03136</v>
       </c>
       <c r="D27" t="n">
-        <v>15.4583</v>
+        <v>14.5218</v>
       </c>
       <c r="E27" t="n">
-        <v>2.68879</v>
+        <v>2.01622</v>
       </c>
       <c r="F27" t="n">
-        <v>3.1857</v>
+        <v>2.2713</v>
       </c>
     </row>
     <row r="28">
@@ -5599,19 +5599,19 @@
         <v>35335</v>
       </c>
       <c r="B28" t="n">
-        <v>3.3852</v>
+        <v>3.14437</v>
       </c>
       <c r="C28" t="n">
-        <v>2.63986</v>
+        <v>2.02122</v>
       </c>
       <c r="D28" t="n">
-        <v>15.9077</v>
+        <v>14.9609</v>
       </c>
       <c r="E28" t="n">
-        <v>2.72835</v>
+        <v>2.04362</v>
       </c>
       <c r="F28" t="n">
-        <v>3.24744</v>
+        <v>2.30256</v>
       </c>
     </row>
     <row r="29">
@@ -5619,19 +5619,19 @@
         <v>37089</v>
       </c>
       <c r="B29" t="n">
-        <v>3.69881</v>
+        <v>3.30904</v>
       </c>
       <c r="C29" t="n">
-        <v>2.76286</v>
+        <v>2.16282</v>
       </c>
       <c r="D29" t="n">
-        <v>16.4136</v>
+        <v>15.4613</v>
       </c>
       <c r="E29" t="n">
-        <v>2.77099</v>
+        <v>2.08118</v>
       </c>
       <c r="F29" t="n">
-        <v>3.32214</v>
+        <v>2.36526</v>
       </c>
     </row>
     <row r="30">
@@ -5639,19 +5639,19 @@
         <v>38930</v>
       </c>
       <c r="B30" t="n">
-        <v>3.45417</v>
+        <v>3.45592</v>
       </c>
       <c r="C30" t="n">
-        <v>2.84698</v>
+        <v>2.24695</v>
       </c>
       <c r="D30" t="n">
-        <v>16.9602</v>
+        <v>15.9361</v>
       </c>
       <c r="E30" t="n">
-        <v>2.85247</v>
+        <v>2.11489</v>
       </c>
       <c r="F30" t="n">
-        <v>3.78061</v>
+        <v>2.3975</v>
       </c>
     </row>
     <row r="31">
@@ -5659,19 +5659,19 @@
         <v>40863</v>
       </c>
       <c r="B31" t="n">
-        <v>3.67818</v>
+        <v>3.65875</v>
       </c>
       <c r="C31" t="n">
-        <v>3.0135</v>
+        <v>2.45028</v>
       </c>
       <c r="D31" t="n">
-        <v>17.4614</v>
+        <v>16.3999</v>
       </c>
       <c r="E31" t="n">
-        <v>2.85959</v>
+        <v>2.1554</v>
       </c>
       <c r="F31" t="n">
-        <v>3.49581</v>
+        <v>2.46072</v>
       </c>
     </row>
     <row r="32">
@@ -5679,19 +5679,19 @@
         <v>42892</v>
       </c>
       <c r="B32" t="n">
-        <v>4.0148</v>
+        <v>4.09734</v>
       </c>
       <c r="C32" t="n">
-        <v>3.30008</v>
+        <v>2.6991</v>
       </c>
       <c r="D32" t="n">
-        <v>17.7708</v>
+        <v>16.7758</v>
       </c>
       <c r="E32" t="n">
-        <v>2.91588</v>
+        <v>2.24604</v>
       </c>
       <c r="F32" t="n">
-        <v>3.60315</v>
+        <v>2.52309</v>
       </c>
     </row>
     <row r="33">
@@ -5699,19 +5699,19 @@
         <v>45022</v>
       </c>
       <c r="B33" t="n">
-        <v>4.67365</v>
+        <v>4.80659</v>
       </c>
       <c r="C33" t="n">
-        <v>3.77757</v>
+        <v>3.28288</v>
       </c>
       <c r="D33" t="n">
-        <v>18.1324</v>
+        <v>17.2339</v>
       </c>
       <c r="E33" t="n">
-        <v>3.00022</v>
+        <v>2.40249</v>
       </c>
       <c r="F33" t="n">
-        <v>3.56824</v>
+        <v>2.69976</v>
       </c>
     </row>
     <row r="34">
@@ -5719,19 +5719,19 @@
         <v>47258</v>
       </c>
       <c r="B34" t="n">
-        <v>5.66473</v>
+        <v>5.73357</v>
       </c>
       <c r="C34" t="n">
-        <v>4.67242</v>
+        <v>4.1571</v>
       </c>
       <c r="D34" t="n">
-        <v>18.6674</v>
+        <v>17.6919</v>
       </c>
       <c r="E34" t="n">
-        <v>3.5009</v>
+        <v>1.92015</v>
       </c>
       <c r="F34" t="n">
-        <v>4.2831</v>
+        <v>2.1168</v>
       </c>
     </row>
     <row r="35">
@@ -5739,19 +5739,19 @@
         <v>49605</v>
       </c>
       <c r="B35" t="n">
-        <v>6.91311</v>
+        <v>7.20806</v>
       </c>
       <c r="C35" t="n">
-        <v>6.19391</v>
+        <v>5.32848</v>
       </c>
       <c r="D35" t="n">
-        <v>12.7419</v>
+        <v>12.0922</v>
       </c>
       <c r="E35" t="n">
-        <v>2.9377</v>
+        <v>1.93762</v>
       </c>
       <c r="F35" t="n">
-        <v>3.44271</v>
+        <v>2.15382</v>
       </c>
     </row>
     <row r="36">
@@ -5759,19 +5759,19 @@
         <v>52069</v>
       </c>
       <c r="B36" t="n">
-        <v>9.1219</v>
+        <v>9.60144</v>
       </c>
       <c r="C36" t="n">
-        <v>8.423120000000001</v>
+        <v>7.00351</v>
       </c>
       <c r="D36" t="n">
-        <v>13.1877</v>
+        <v>12.5513</v>
       </c>
       <c r="E36" t="n">
-        <v>2.95972</v>
+        <v>1.95566</v>
       </c>
       <c r="F36" t="n">
-        <v>3.47443</v>
+        <v>2.19531</v>
       </c>
     </row>
     <row r="37">
@@ -5779,19 +5779,19 @@
         <v>54656</v>
       </c>
       <c r="B37" t="n">
-        <v>12.4896</v>
+        <v>13.0119</v>
       </c>
       <c r="C37" t="n">
-        <v>2.44378</v>
+        <v>1.84975</v>
       </c>
       <c r="D37" t="n">
-        <v>13.6902</v>
+        <v>13.0178</v>
       </c>
       <c r="E37" t="n">
-        <v>2.97102</v>
+        <v>1.97951</v>
       </c>
       <c r="F37" t="n">
-        <v>3.0886</v>
+        <v>2.22233</v>
       </c>
     </row>
     <row r="38">
@@ -5799,19 +5799,19 @@
         <v>57372</v>
       </c>
       <c r="B38" t="n">
-        <v>3.15825</v>
+        <v>2.95806</v>
       </c>
       <c r="C38" t="n">
-        <v>2.52746</v>
+        <v>1.84466</v>
       </c>
       <c r="D38" t="n">
-        <v>14.3536</v>
+        <v>13.5421</v>
       </c>
       <c r="E38" t="n">
-        <v>3.07585</v>
+        <v>2.00254</v>
       </c>
       <c r="F38" t="n">
-        <v>3.16073</v>
+        <v>2.2363</v>
       </c>
     </row>
     <row r="39">
@@ -5819,19 +5819,19 @@
         <v>60223</v>
       </c>
       <c r="B39" t="n">
-        <v>3.17814</v>
+        <v>3.01241</v>
       </c>
       <c r="C39" t="n">
-        <v>2.64792</v>
+        <v>1.90329</v>
       </c>
       <c r="D39" t="n">
-        <v>14.8649</v>
+        <v>14.049</v>
       </c>
       <c r="E39" t="n">
-        <v>3.00659</v>
+        <v>2.03016</v>
       </c>
       <c r="F39" t="n">
-        <v>3.67912</v>
+        <v>2.28442</v>
       </c>
     </row>
     <row r="40">
@@ -5839,19 +5839,19 @@
         <v>63216</v>
       </c>
       <c r="B40" t="n">
-        <v>3.09152</v>
+        <v>3.06963</v>
       </c>
       <c r="C40" t="n">
-        <v>2.52368</v>
+        <v>1.9305</v>
       </c>
       <c r="D40" t="n">
-        <v>15.4868</v>
+        <v>14.5469</v>
       </c>
       <c r="E40" t="n">
-        <v>3.1214</v>
+        <v>2.04931</v>
       </c>
       <c r="F40" t="n">
-        <v>3.27073</v>
+        <v>2.34935</v>
       </c>
     </row>
     <row r="41">
@@ -5859,19 +5859,19 @@
         <v>66358</v>
       </c>
       <c r="B41" t="n">
-        <v>3.33975</v>
+        <v>3.14001</v>
       </c>
       <c r="C41" t="n">
-        <v>2.64593</v>
+        <v>2.01606</v>
       </c>
       <c r="D41" t="n">
-        <v>15.9549</v>
+        <v>15.0273</v>
       </c>
       <c r="E41" t="n">
-        <v>3.14513</v>
+        <v>2.08941</v>
       </c>
       <c r="F41" t="n">
-        <v>3.32688</v>
+        <v>2.34461</v>
       </c>
     </row>
     <row r="42">
@@ -5879,19 +5879,19 @@
         <v>69657</v>
       </c>
       <c r="B42" t="n">
-        <v>3.44402</v>
+        <v>3.21203</v>
       </c>
       <c r="C42" t="n">
-        <v>2.76934</v>
+        <v>2.04964</v>
       </c>
       <c r="D42" t="n">
-        <v>16.4524</v>
+        <v>15.4661</v>
       </c>
       <c r="E42" t="n">
-        <v>3.17658</v>
+        <v>2.12368</v>
       </c>
       <c r="F42" t="n">
-        <v>3.39266</v>
+        <v>2.4787</v>
       </c>
     </row>
     <row r="43">
@@ -5899,19 +5899,19 @@
         <v>73120</v>
       </c>
       <c r="B43" t="n">
-        <v>3.53948</v>
+        <v>3.32175</v>
       </c>
       <c r="C43" t="n">
-        <v>2.87238</v>
+        <v>2.13372</v>
       </c>
       <c r="D43" t="n">
-        <v>16.9248</v>
+        <v>15.9152</v>
       </c>
       <c r="E43" t="n">
-        <v>3.13521</v>
+        <v>2.18058</v>
       </c>
       <c r="F43" t="n">
-        <v>3.8832</v>
+        <v>2.49667</v>
       </c>
     </row>
     <row r="44">
@@ -5919,19 +5919,19 @@
         <v>76756</v>
       </c>
       <c r="B44" t="n">
-        <v>3.72776</v>
+        <v>3.48748</v>
       </c>
       <c r="C44" t="n">
-        <v>2.90264</v>
+        <v>2.29424</v>
       </c>
       <c r="D44" t="n">
-        <v>17.3119</v>
+        <v>16.3588</v>
       </c>
       <c r="E44" t="n">
-        <v>3.21238</v>
+        <v>2.26851</v>
       </c>
       <c r="F44" t="n">
-        <v>3.92711</v>
+        <v>2.60793</v>
       </c>
     </row>
     <row r="45">
@@ -5939,19 +5939,19 @@
         <v>80573</v>
       </c>
       <c r="B45" t="n">
-        <v>3.74826</v>
+        <v>3.73299</v>
       </c>
       <c r="C45" t="n">
-        <v>2.984</v>
+        <v>2.55313</v>
       </c>
       <c r="D45" t="n">
-        <v>17.665</v>
+        <v>16.6998</v>
       </c>
       <c r="E45" t="n">
-        <v>2.99205</v>
+        <v>2.36009</v>
       </c>
       <c r="F45" t="n">
-        <v>3.97518</v>
+        <v>2.6745</v>
       </c>
     </row>
     <row r="46">
@@ -5959,19 +5959,19 @@
         <v>84580</v>
       </c>
       <c r="B46" t="n">
-        <v>4.33044</v>
+        <v>4.08221</v>
       </c>
       <c r="C46" t="n">
-        <v>3.46264</v>
+        <v>2.90317</v>
       </c>
       <c r="D46" t="n">
-        <v>18.1232</v>
+        <v>17.1677</v>
       </c>
       <c r="E46" t="n">
-        <v>3.46279</v>
+        <v>2.52678</v>
       </c>
       <c r="F46" t="n">
-        <v>4.06957</v>
+        <v>2.82008</v>
       </c>
     </row>
     <row r="47">
@@ -5979,19 +5979,19 @@
         <v>88787</v>
       </c>
       <c r="B47" t="n">
-        <v>4.9767</v>
+        <v>4.62826</v>
       </c>
       <c r="C47" t="n">
-        <v>3.92402</v>
+        <v>3.396</v>
       </c>
       <c r="D47" t="n">
-        <v>18.6379</v>
+        <v>17.5966</v>
       </c>
       <c r="E47" t="n">
-        <v>3.65935</v>
+        <v>2.77406</v>
       </c>
       <c r="F47" t="n">
-        <v>4.24104</v>
+        <v>3.07762</v>
       </c>
     </row>
     <row r="48">
@@ -5999,19 +5999,19 @@
         <v>93204</v>
       </c>
       <c r="B48" t="n">
-        <v>5.39562</v>
+        <v>5.4808</v>
       </c>
       <c r="C48" t="n">
-        <v>4.71134</v>
+        <v>4.05633</v>
       </c>
       <c r="D48" t="n">
-        <v>19.176</v>
+        <v>18.0682</v>
       </c>
       <c r="E48" t="n">
-        <v>4.06161</v>
+        <v>2.09417</v>
       </c>
       <c r="F48" t="n">
-        <v>4.65321</v>
+        <v>2.43785</v>
       </c>
     </row>
     <row r="49">
@@ -6019,19 +6019,19 @@
         <v>97841</v>
       </c>
       <c r="B49" t="n">
-        <v>6.48646</v>
+        <v>6.57975</v>
       </c>
       <c r="C49" t="n">
-        <v>5.7783</v>
+        <v>5.07336</v>
       </c>
       <c r="D49" t="n">
-        <v>19.9843</v>
+        <v>18.5183</v>
       </c>
       <c r="E49" t="n">
-        <v>4.56982</v>
+        <v>2.11057</v>
       </c>
       <c r="F49" t="n">
-        <v>4.76528</v>
+        <v>2.46201</v>
       </c>
     </row>
     <row r="50">
@@ -6039,19 +6039,19 @@
         <v>102709</v>
       </c>
       <c r="B50" t="n">
-        <v>8.55702</v>
+        <v>8.32788</v>
       </c>
       <c r="C50" t="n">
-        <v>7.4512</v>
+        <v>6.6423</v>
       </c>
       <c r="D50" t="n">
-        <v>15.5031</v>
+        <v>12.8783</v>
       </c>
       <c r="E50" t="n">
-        <v>3.02363</v>
+        <v>2.17112</v>
       </c>
       <c r="F50" t="n">
-        <v>3.41447</v>
+        <v>2.52179</v>
       </c>
     </row>
     <row r="51">
@@ -6059,19 +6059,19 @@
         <v>107820</v>
       </c>
       <c r="B51" t="n">
-        <v>11.753</v>
+        <v>11.181</v>
       </c>
       <c r="C51" t="n">
-        <v>2.38985</v>
+        <v>1.95135</v>
       </c>
       <c r="D51" t="n">
-        <v>17.5812</v>
+        <v>13.3587</v>
       </c>
       <c r="E51" t="n">
-        <v>3.04129</v>
+        <v>2.18491</v>
       </c>
       <c r="F51" t="n">
-        <v>3.47463</v>
+        <v>2.55382</v>
       </c>
     </row>
     <row r="52">
@@ -6079,19 +6079,19 @@
         <v>113186</v>
       </c>
       <c r="B52" t="n">
-        <v>15.7103</v>
+        <v>15.4555</v>
       </c>
       <c r="C52" t="n">
-        <v>2.40759</v>
+        <v>1.96969</v>
       </c>
       <c r="D52" t="n">
-        <v>18.7231</v>
+        <v>13.8201</v>
       </c>
       <c r="E52" t="n">
-        <v>3.07246</v>
+        <v>2.21108</v>
       </c>
       <c r="F52" t="n">
-        <v>3.50964</v>
+        <v>2.57424</v>
       </c>
     </row>
     <row r="53">
@@ -6099,19 +6099,19 @@
         <v>118820</v>
       </c>
       <c r="B53" t="n">
-        <v>3.14717</v>
+        <v>3.09185</v>
       </c>
       <c r="C53" t="n">
-        <v>2.45406</v>
+        <v>2.05565</v>
       </c>
       <c r="D53" t="n">
-        <v>19.9648</v>
+        <v>14.2893</v>
       </c>
       <c r="E53" t="n">
-        <v>3.48513</v>
+        <v>2.24381</v>
       </c>
       <c r="F53" t="n">
-        <v>3.58016</v>
+        <v>2.62072</v>
       </c>
     </row>
     <row r="54">
@@ -6119,19 +6119,19 @@
         <v>124735</v>
       </c>
       <c r="B54" t="n">
-        <v>3.63032</v>
+        <v>3.15389</v>
       </c>
       <c r="C54" t="n">
-        <v>2.43272</v>
+        <v>2.07442</v>
       </c>
       <c r="D54" t="n">
-        <v>20.2493</v>
+        <v>14.7849</v>
       </c>
       <c r="E54" t="n">
-        <v>3.59162</v>
+        <v>2.27768</v>
       </c>
       <c r="F54" t="n">
-        <v>3.59578</v>
+        <v>2.67234</v>
       </c>
     </row>
     <row r="55">
@@ -6139,19 +6139,19 @@
         <v>130945</v>
       </c>
       <c r="B55" t="n">
-        <v>3.66714</v>
+        <v>3.20987</v>
       </c>
       <c r="C55" t="n">
-        <v>2.53866</v>
+        <v>2.12556</v>
       </c>
       <c r="D55" t="n">
-        <v>21.7593</v>
+        <v>15.2546</v>
       </c>
       <c r="E55" t="n">
-        <v>2.96938</v>
+        <v>2.39688</v>
       </c>
       <c r="F55" t="n">
-        <v>3.67776</v>
+        <v>2.68299</v>
       </c>
     </row>
     <row r="56">
@@ -6159,19 +6159,19 @@
         <v>137465</v>
       </c>
       <c r="B56" t="n">
-        <v>3.38269</v>
+        <v>3.28361</v>
       </c>
       <c r="C56" t="n">
-        <v>2.63595</v>
+        <v>2.15472</v>
       </c>
       <c r="D56" t="n">
-        <v>22.9767</v>
+        <v>15.721</v>
       </c>
       <c r="E56" t="n">
-        <v>3.63853</v>
+        <v>2.44464</v>
       </c>
       <c r="F56" t="n">
-        <v>3.76411</v>
+        <v>2.73776</v>
       </c>
     </row>
     <row r="57">
@@ -6179,19 +6179,19 @@
         <v>144311</v>
       </c>
       <c r="B57" t="n">
-        <v>3.48402</v>
+        <v>3.4185</v>
       </c>
       <c r="C57" t="n">
-        <v>2.96084</v>
+        <v>2.27658</v>
       </c>
       <c r="D57" t="n">
-        <v>23.9105</v>
+        <v>16.1718</v>
       </c>
       <c r="E57" t="n">
-        <v>3.78341</v>
+        <v>2.50517</v>
       </c>
       <c r="F57" t="n">
-        <v>3.84206</v>
+        <v>2.82178</v>
       </c>
     </row>
     <row r="58">
@@ -6199,19 +6199,19 @@
         <v>151499</v>
       </c>
       <c r="B58" t="n">
-        <v>3.65864</v>
+        <v>3.58407</v>
       </c>
       <c r="C58" t="n">
-        <v>3.09373</v>
+        <v>2.38838</v>
       </c>
       <c r="D58" t="n">
-        <v>24.8918</v>
+        <v>16.5817</v>
       </c>
       <c r="E58" t="n">
-        <v>3.2017</v>
+        <v>2.43603</v>
       </c>
       <c r="F58" t="n">
-        <v>3.97213</v>
+        <v>2.90368</v>
       </c>
     </row>
     <row r="59">
@@ -6219,19 +6219,19 @@
         <v>159046</v>
       </c>
       <c r="B59" t="n">
-        <v>3.85059</v>
+        <v>3.84508</v>
       </c>
       <c r="C59" t="n">
-        <v>3.64119</v>
+        <v>2.60984</v>
       </c>
       <c r="D59" t="n">
-        <v>25.5686</v>
+        <v>16.9973</v>
       </c>
       <c r="E59" t="n">
-        <v>3.3137</v>
+        <v>2.53849</v>
       </c>
       <c r="F59" t="n">
-        <v>4.09498</v>
+        <v>3.04065</v>
       </c>
     </row>
     <row r="60">
@@ -6239,19 +6239,19 @@
         <v>166970</v>
       </c>
       <c r="B60" t="n">
-        <v>4.17445</v>
+        <v>4.15777</v>
       </c>
       <c r="C60" t="n">
-        <v>4.04585</v>
+        <v>2.86476</v>
       </c>
       <c r="D60" t="n">
-        <v>26.1128</v>
+        <v>17.5171</v>
       </c>
       <c r="E60" t="n">
-        <v>3.69769</v>
+        <v>2.68865</v>
       </c>
       <c r="F60" t="n">
-        <v>4.14374</v>
+        <v>3.10182</v>
       </c>
     </row>
     <row r="61">
@@ -6259,19 +6259,19 @@
         <v>175290</v>
       </c>
       <c r="B61" t="n">
-        <v>4.63433</v>
+        <v>4.68413</v>
       </c>
       <c r="C61" t="n">
-        <v>4.03152</v>
+        <v>3.29406</v>
       </c>
       <c r="D61" t="n">
-        <v>27.0792</v>
+        <v>17.9367</v>
       </c>
       <c r="E61" t="n">
-        <v>4.29578</v>
+        <v>2.89971</v>
       </c>
       <c r="F61" t="n">
-        <v>4.73619</v>
+        <v>3.2781</v>
       </c>
     </row>
     <row r="62">
@@ -6279,19 +6279,19 @@
         <v>184026</v>
       </c>
       <c r="B62" t="n">
-        <v>5.31376</v>
+        <v>5.23035</v>
       </c>
       <c r="C62" t="n">
-        <v>5.05898</v>
+        <v>3.90688</v>
       </c>
       <c r="D62" t="n">
-        <v>28.3653</v>
+        <v>18.4634</v>
       </c>
       <c r="E62" t="n">
-        <v>4.58666</v>
+        <v>3.17337</v>
       </c>
       <c r="F62" t="n">
-        <v>4.96481</v>
+        <v>3.57407</v>
       </c>
     </row>
     <row r="63">
@@ -6299,19 +6299,19 @@
         <v>193198</v>
       </c>
       <c r="B63" t="n">
-        <v>6.29505</v>
+        <v>6.2915</v>
       </c>
       <c r="C63" t="n">
-        <v>6.05621</v>
+        <v>4.83892</v>
       </c>
       <c r="D63" t="n">
-        <v>28.3446</v>
+        <v>18.9072</v>
       </c>
       <c r="E63" t="n">
-        <v>5.10781</v>
+        <v>2.47967</v>
       </c>
       <c r="F63" t="n">
-        <v>5.38906</v>
+        <v>2.94178</v>
       </c>
     </row>
     <row r="64">
@@ -6319,19 +6319,19 @@
         <v>202828</v>
       </c>
       <c r="B64" t="n">
-        <v>7.9764</v>
+        <v>7.91829</v>
       </c>
       <c r="C64" t="n">
-        <v>7.5608</v>
+        <v>6.17162</v>
       </c>
       <c r="D64" t="n">
-        <v>19.7621</v>
+        <v>13.6774</v>
       </c>
       <c r="E64" t="n">
-        <v>3.47649</v>
+        <v>2.50526</v>
       </c>
       <c r="F64" t="n">
-        <v>4.17931</v>
+        <v>2.96552</v>
       </c>
     </row>
     <row r="65">
@@ -6339,19 +6339,19 @@
         <v>212939</v>
       </c>
       <c r="B65" t="n">
-        <v>10.4416</v>
+        <v>10.5211</v>
       </c>
       <c r="C65" t="n">
-        <v>2.92289</v>
+        <v>2.32334</v>
       </c>
       <c r="D65" t="n">
-        <v>19.5599</v>
+        <v>14.3383</v>
       </c>
       <c r="E65" t="n">
-        <v>3.61285</v>
+        <v>2.55245</v>
       </c>
       <c r="F65" t="n">
-        <v>4.25982</v>
+        <v>3.00961</v>
       </c>
     </row>
     <row r="66">
@@ -6359,19 +6359,19 @@
         <v>223555</v>
       </c>
       <c r="B66" t="n">
-        <v>14.3274</v>
+        <v>14.7064</v>
       </c>
       <c r="C66" t="n">
-        <v>2.96675</v>
+        <v>2.34169</v>
       </c>
       <c r="D66" t="n">
-        <v>20.8636</v>
+        <v>14.9438</v>
       </c>
       <c r="E66" t="n">
-        <v>3.53772</v>
+        <v>2.58611</v>
       </c>
       <c r="F66" t="n">
-        <v>4.30722</v>
+        <v>3.05099</v>
       </c>
     </row>
     <row r="67">
@@ -6379,19 +6379,19 @@
         <v>234701</v>
       </c>
       <c r="B67" t="n">
-        <v>3.72406</v>
+        <v>3.50456</v>
       </c>
       <c r="C67" t="n">
-        <v>3.01591</v>
+        <v>2.43475</v>
       </c>
       <c r="D67" t="n">
-        <v>22.4734</v>
+        <v>15.753</v>
       </c>
       <c r="E67" t="n">
-        <v>3.57588</v>
+        <v>2.57669</v>
       </c>
       <c r="F67" t="n">
-        <v>4.38313</v>
+        <v>3.10177</v>
       </c>
     </row>
     <row r="68">
@@ -6399,19 +6399,19 @@
         <v>246404</v>
       </c>
       <c r="B68" t="n">
-        <v>3.56644</v>
+        <v>3.57253</v>
       </c>
       <c r="C68" t="n">
-        <v>3.04462</v>
+        <v>2.44791</v>
       </c>
       <c r="D68" t="n">
-        <v>23.939</v>
+        <v>16.5071</v>
       </c>
       <c r="E68" t="n">
-        <v>3.71071</v>
+        <v>2.64106</v>
       </c>
       <c r="F68" t="n">
-        <v>4.47182</v>
+        <v>3.17337</v>
       </c>
     </row>
     <row r="69">
@@ -6419,19 +6419,19 @@
         <v>258692</v>
       </c>
       <c r="B69" t="n">
-        <v>3.63753</v>
+        <v>3.63572</v>
       </c>
       <c r="C69" t="n">
-        <v>3.05521</v>
+        <v>2.54347</v>
       </c>
       <c r="D69" t="n">
-        <v>24.625</v>
+        <v>17.3084</v>
       </c>
       <c r="E69" t="n">
-        <v>3.68028</v>
+        <v>2.65475</v>
       </c>
       <c r="F69" t="n">
-        <v>4.54745</v>
+        <v>3.23741</v>
       </c>
     </row>
     <row r="70">
@@ -6439,19 +6439,19 @@
         <v>271594</v>
       </c>
       <c r="B70" t="n">
-        <v>3.96975</v>
+        <v>3.74819</v>
       </c>
       <c r="C70" t="n">
-        <v>3.18266</v>
+        <v>2.59715</v>
       </c>
       <c r="D70" t="n">
-        <v>25.2376</v>
+        <v>18.3758</v>
       </c>
       <c r="E70" t="n">
-        <v>3.83564</v>
+        <v>2.72418</v>
       </c>
       <c r="F70" t="n">
-        <v>4.64679</v>
+        <v>3.29094</v>
       </c>
     </row>
     <row r="71">
@@ -6459,19 +6459,19 @@
         <v>285141</v>
       </c>
       <c r="B71" t="n">
-        <v>3.8507</v>
+        <v>3.8602</v>
       </c>
       <c r="C71" t="n">
-        <v>3.21605</v>
+        <v>2.67016</v>
       </c>
       <c r="D71" t="n">
-        <v>25.9548</v>
+        <v>19.4108</v>
       </c>
       <c r="E71" t="n">
-        <v>3.77732</v>
+        <v>2.79901</v>
       </c>
       <c r="F71" t="n">
-        <v>4.75204</v>
+        <v>3.39916</v>
       </c>
     </row>
     <row r="72">
@@ -6479,19 +6479,19 @@
         <v>299365</v>
       </c>
       <c r="B72" t="n">
-        <v>4.00258</v>
+        <v>4.00176</v>
       </c>
       <c r="C72" t="n">
-        <v>3.35875</v>
+        <v>2.83716</v>
       </c>
       <c r="D72" t="n">
-        <v>26.8317</v>
+        <v>20.5369</v>
       </c>
       <c r="E72" t="n">
-        <v>3.8573</v>
+        <v>2.87546</v>
       </c>
       <c r="F72" t="n">
-        <v>4.88257</v>
+        <v>3.50986</v>
       </c>
     </row>
     <row r="73">
@@ -6499,19 +6499,19 @@
         <v>314300</v>
       </c>
       <c r="B73" t="n">
-        <v>4.43397</v>
+        <v>4.22897</v>
       </c>
       <c r="C73" t="n">
-        <v>3.59543</v>
+        <v>2.99026</v>
       </c>
       <c r="D73" t="n">
-        <v>27.7873</v>
+        <v>21.807</v>
       </c>
       <c r="E73" t="n">
-        <v>3.95836</v>
+        <v>2.96732</v>
       </c>
       <c r="F73" t="n">
-        <v>4.98289</v>
+        <v>3.62769</v>
       </c>
     </row>
     <row r="74">
@@ -6519,19 +6519,19 @@
         <v>329981</v>
       </c>
       <c r="B74" t="n">
-        <v>4.60135</v>
+        <v>4.54127</v>
       </c>
       <c r="C74" t="n">
-        <v>3.67798</v>
+        <v>3.25383</v>
       </c>
       <c r="D74" t="n">
-        <v>28.9957</v>
+        <v>23.0756</v>
       </c>
       <c r="E74" t="n">
-        <v>3.88778</v>
+        <v>3.04796</v>
       </c>
       <c r="F74" t="n">
-        <v>5.10676</v>
+        <v>3.81072</v>
       </c>
     </row>
     <row r="75">
@@ -6539,19 +6539,19 @@
         <v>346446</v>
       </c>
       <c r="B75" t="n">
-        <v>5.02266</v>
+        <v>4.96891</v>
       </c>
       <c r="C75" t="n">
-        <v>4.08351</v>
+        <v>3.60288</v>
       </c>
       <c r="D75" t="n">
-        <v>29.5459</v>
+        <v>24.6914</v>
       </c>
       <c r="E75" t="n">
-        <v>4.21278</v>
+        <v>3.22323</v>
       </c>
       <c r="F75" t="n">
-        <v>5.36241</v>
+        <v>3.98597</v>
       </c>
     </row>
     <row r="76">
@@ -6559,19 +6559,19 @@
         <v>363734</v>
       </c>
       <c r="B76" t="n">
-        <v>5.63848</v>
+        <v>5.64253</v>
       </c>
       <c r="C76" t="n">
-        <v>4.70801</v>
+        <v>4.16528</v>
       </c>
       <c r="D76" t="n">
-        <v>31.8396</v>
+        <v>26.0847</v>
       </c>
       <c r="E76" t="n">
-        <v>4.31592</v>
+        <v>3.48892</v>
       </c>
       <c r="F76" t="n">
-        <v>6.30395</v>
+        <v>4.24681</v>
       </c>
     </row>
     <row r="77">
@@ -6579,19 +6579,19 @@
         <v>381886</v>
       </c>
       <c r="B77" t="n">
-        <v>6.87139</v>
+        <v>6.52185</v>
       </c>
       <c r="C77" t="n">
-        <v>5.64762</v>
+        <v>5.02864</v>
       </c>
       <c r="D77" t="n">
-        <v>32.8835</v>
+        <v>27.5955</v>
       </c>
       <c r="E77" t="n">
-        <v>4.74853</v>
+        <v>2.87996</v>
       </c>
       <c r="F77" t="n">
-        <v>6.02939</v>
+        <v>3.43779</v>
       </c>
     </row>
     <row r="78">
@@ -6599,19 +6599,19 @@
         <v>400945</v>
       </c>
       <c r="B78" t="n">
-        <v>7.91209</v>
+        <v>7.92556</v>
       </c>
       <c r="C78" t="n">
-        <v>7.21898</v>
+        <v>6.30838</v>
       </c>
       <c r="D78" t="n">
-        <v>24.2115</v>
+        <v>23.0457</v>
       </c>
       <c r="E78" t="n">
-        <v>3.74116</v>
+        <v>2.90317</v>
       </c>
       <c r="F78" t="n">
-        <v>4.5838</v>
+        <v>3.52508</v>
       </c>
     </row>
     <row r="79">
@@ -6619,19 +6619,19 @@
         <v>420956</v>
       </c>
       <c r="B79" t="n">
-        <v>10.0907</v>
+        <v>10.3858</v>
       </c>
       <c r="C79" t="n">
-        <v>3.12807</v>
+        <v>2.74117</v>
       </c>
       <c r="D79" t="n">
-        <v>25.5535</v>
+        <v>24.0939</v>
       </c>
       <c r="E79" t="n">
-        <v>3.77971</v>
+        <v>2.95306</v>
       </c>
       <c r="F79" t="n">
-        <v>4.66627</v>
+        <v>3.55489</v>
       </c>
     </row>
     <row r="80">
@@ -6639,19 +6639,19 @@
         <v>441967</v>
       </c>
       <c r="B80" t="n">
-        <v>13.9522</v>
+        <v>14.0482</v>
       </c>
       <c r="C80" t="n">
-        <v>3.17873</v>
+        <v>2.77872</v>
       </c>
       <c r="D80" t="n">
-        <v>26.7339</v>
+        <v>25.6302</v>
       </c>
       <c r="E80" t="n">
-        <v>3.84168</v>
+        <v>3.03327</v>
       </c>
       <c r="F80" t="n">
-        <v>4.79082</v>
+        <v>3.64308</v>
       </c>
     </row>
     <row r="81">
@@ -6659,19 +6659,19 @@
         <v>464028</v>
       </c>
       <c r="B81" t="n">
-        <v>4.0556</v>
+        <v>4.10816</v>
       </c>
       <c r="C81" t="n">
-        <v>3.23983</v>
+        <v>2.85519</v>
       </c>
       <c r="D81" t="n">
-        <v>28.0235</v>
+        <v>26.9624</v>
       </c>
       <c r="E81" t="n">
-        <v>3.8708</v>
+        <v>3.02967</v>
       </c>
       <c r="F81" t="n">
-        <v>4.85025</v>
+        <v>3.82857</v>
       </c>
     </row>
     <row r="82">
@@ -6679,19 +6679,19 @@
         <v>487192</v>
       </c>
       <c r="B82" t="n">
-        <v>4.13863</v>
+        <v>4.21389</v>
       </c>
       <c r="C82" t="n">
-        <v>3.31276</v>
+        <v>2.91733</v>
       </c>
       <c r="D82" t="n">
-        <v>29.4067</v>
+        <v>28.3881</v>
       </c>
       <c r="E82" t="n">
-        <v>3.94301</v>
+        <v>3.06586</v>
       </c>
       <c r="F82" t="n">
-        <v>5.0341</v>
+        <v>3.9131</v>
       </c>
     </row>
     <row r="83">
@@ -6699,19 +6699,19 @@
         <v>511514</v>
       </c>
       <c r="B83" t="n">
-        <v>4.26974</v>
+        <v>4.38228</v>
       </c>
       <c r="C83" t="n">
-        <v>3.43905</v>
+        <v>3.01146</v>
       </c>
       <c r="D83" t="n">
-        <v>30.8686</v>
+        <v>29.822</v>
       </c>
       <c r="E83" t="n">
-        <v>4.00026</v>
+        <v>3.17063</v>
       </c>
       <c r="F83" t="n">
-        <v>5.18953</v>
+        <v>4.0324</v>
       </c>
     </row>
     <row r="84">
@@ -6719,19 +6719,19 @@
         <v>537052</v>
       </c>
       <c r="B84" t="n">
-        <v>4.45531</v>
+        <v>4.58343</v>
       </c>
       <c r="C84" t="n">
-        <v>3.50773</v>
+        <v>3.19732</v>
       </c>
       <c r="D84" t="n">
-        <v>32.4453</v>
+        <v>31.3489</v>
       </c>
       <c r="E84" t="n">
-        <v>4.08966</v>
+        <v>3.25972</v>
       </c>
       <c r="F84" t="n">
-        <v>5.32533</v>
+        <v>4.2543</v>
       </c>
     </row>
     <row r="85">
@@ -6739,19 +6739,19 @@
         <v>563866</v>
       </c>
       <c r="B85" t="n">
-        <v>4.70182</v>
+        <v>4.79944</v>
       </c>
       <c r="C85" t="n">
-        <v>3.71584</v>
+        <v>3.35736</v>
       </c>
       <c r="D85" t="n">
-        <v>33.9555</v>
+        <v>32.9256</v>
       </c>
       <c r="E85" t="n">
-        <v>4.23136</v>
+        <v>3.32758</v>
       </c>
       <c r="F85" t="n">
-        <v>5.97478</v>
+        <v>4.38296</v>
       </c>
     </row>
     <row r="86">
@@ -6759,19 +6759,19 @@
         <v>592020</v>
       </c>
       <c r="B86" t="n">
-        <v>4.9401</v>
+        <v>5.11822</v>
       </c>
       <c r="C86" t="n">
-        <v>3.92493</v>
+        <v>3.58913</v>
       </c>
       <c r="D86" t="n">
-        <v>35.5063</v>
+        <v>34.5155</v>
       </c>
       <c r="E86" t="n">
-        <v>4.38067</v>
+        <v>3.4787</v>
       </c>
       <c r="F86" t="n">
-        <v>6.36566</v>
+        <v>4.68994</v>
       </c>
     </row>
     <row r="87">
@@ -6779,19 +6779,19 @@
         <v>621581</v>
       </c>
       <c r="B87" t="n">
-        <v>5.33385</v>
+        <v>5.51979</v>
       </c>
       <c r="C87" t="n">
-        <v>4.18998</v>
+        <v>3.85493</v>
       </c>
       <c r="D87" t="n">
-        <v>37.1317</v>
+        <v>36.1585</v>
       </c>
       <c r="E87" t="n">
-        <v>4.62403</v>
+        <v>3.73964</v>
       </c>
       <c r="F87" t="n">
-        <v>6.81783</v>
+        <v>5.22022</v>
       </c>
     </row>
     <row r="88">
@@ -6799,19 +6799,19 @@
         <v>652620</v>
       </c>
       <c r="B88" t="n">
-        <v>5.81518</v>
+        <v>6.04471</v>
       </c>
       <c r="C88" t="n">
-        <v>4.59643</v>
+        <v>4.15963</v>
       </c>
       <c r="D88" t="n">
-        <v>38.8788</v>
+        <v>37.7407</v>
       </c>
       <c r="E88" t="n">
-        <v>4.8558</v>
+        <v>3.91475</v>
       </c>
       <c r="F88" t="n">
-        <v>6.40956</v>
+        <v>5.62457</v>
       </c>
     </row>
     <row r="89">
@@ -6819,19 +6819,19 @@
         <v>685210</v>
       </c>
       <c r="B89" t="n">
-        <v>6.46596</v>
+        <v>6.63766</v>
       </c>
       <c r="C89" t="n">
-        <v>5.11521</v>
+        <v>4.64765</v>
       </c>
       <c r="D89" t="n">
-        <v>40.5929</v>
+        <v>39.5953</v>
       </c>
       <c r="E89" t="n">
-        <v>5.24209</v>
+        <v>4.25104</v>
       </c>
       <c r="F89" t="n">
-        <v>6.81477</v>
+        <v>6.18339</v>
       </c>
     </row>
     <row r="90">
@@ -6839,19 +6839,19 @@
         <v>719429</v>
       </c>
       <c r="B90" t="n">
-        <v>7.23628</v>
+        <v>7.38072</v>
       </c>
       <c r="C90" t="n">
-        <v>5.81271</v>
+        <v>5.22968</v>
       </c>
       <c r="D90" t="n">
-        <v>42.4479</v>
+        <v>41.4514</v>
       </c>
       <c r="E90" t="n">
-        <v>5.69734</v>
+        <v>4.64194</v>
       </c>
       <c r="F90" t="n">
-        <v>7.36474</v>
+        <v>6.75601</v>
       </c>
     </row>
     <row r="91">
@@ -6859,19 +6859,19 @@
         <v>755358</v>
       </c>
       <c r="B91" t="n">
-        <v>8.393359999999999</v>
+        <v>8.51628</v>
       </c>
       <c r="C91" t="n">
-        <v>6.78337</v>
+        <v>6.11894</v>
       </c>
       <c r="D91" t="n">
-        <v>44.3081</v>
+        <v>43.4228</v>
       </c>
       <c r="E91" t="n">
-        <v>6.24795</v>
+        <v>3.31009</v>
       </c>
       <c r="F91" t="n">
-        <v>8.141690000000001</v>
+        <v>4.64578</v>
       </c>
     </row>
     <row r="92">
@@ -6879,19 +6879,19 @@
         <v>793083</v>
       </c>
       <c r="B92" t="n">
-        <v>9.79471</v>
+        <v>9.990119999999999</v>
       </c>
       <c r="C92" t="n">
-        <v>8.168939999999999</v>
+        <v>7.31434</v>
       </c>
       <c r="D92" t="n">
-        <v>35.2033</v>
+        <v>35.6025</v>
       </c>
       <c r="E92" t="n">
-        <v>4.63732</v>
+        <v>3.54263</v>
       </c>
       <c r="F92" t="n">
-        <v>6.36712</v>
+        <v>4.96324</v>
       </c>
     </row>
     <row r="93">
@@ -6899,19 +6899,19 @@
         <v>832694</v>
       </c>
       <c r="B93" t="n">
-        <v>11.9586</v>
+        <v>12.4518</v>
       </c>
       <c r="C93" t="n">
-        <v>10.2706</v>
+        <v>9.2105</v>
       </c>
       <c r="D93" t="n">
-        <v>36.6219</v>
+        <v>36.7985</v>
       </c>
       <c r="E93" t="n">
-        <v>4.8326</v>
+        <v>3.76308</v>
       </c>
       <c r="F93" t="n">
-        <v>6.61159</v>
+        <v>5.26186</v>
       </c>
     </row>
     <row r="94">
@@ -6919,19 +6919,19 @@
         <v>874285</v>
       </c>
       <c r="B94" t="n">
-        <v>15.5581</v>
+        <v>15.802</v>
       </c>
       <c r="C94" t="n">
-        <v>4.28448</v>
+        <v>3.77486</v>
       </c>
       <c r="D94" t="n">
-        <v>37.7069</v>
+        <v>38.0456</v>
       </c>
       <c r="E94" t="n">
-        <v>5.03261</v>
+        <v>3.90217</v>
       </c>
       <c r="F94" t="n">
-        <v>7.23119</v>
+        <v>5.62264</v>
       </c>
     </row>
     <row r="95">
@@ -6939,19 +6939,19 @@
         <v>917955</v>
       </c>
       <c r="B95" t="n">
-        <v>5.88925</v>
+        <v>5.93881</v>
       </c>
       <c r="C95" t="n">
-        <v>4.40563</v>
+        <v>3.98382</v>
       </c>
       <c r="D95" t="n">
-        <v>39.0452</v>
+        <v>39.2782</v>
       </c>
       <c r="E95" t="n">
-        <v>5.20018</v>
+        <v>4.15201</v>
       </c>
       <c r="F95" t="n">
-        <v>7.24365</v>
+        <v>6.01889</v>
       </c>
     </row>
     <row r="96">
@@ -6959,19 +6959,19 @@
         <v>963808</v>
       </c>
       <c r="B96" t="n">
-        <v>6.18194</v>
+        <v>6.2548</v>
       </c>
       <c r="C96" t="n">
-        <v>4.56857</v>
+        <v>4.13774</v>
       </c>
       <c r="D96" t="n">
-        <v>40.3624</v>
+        <v>40.6082</v>
       </c>
       <c r="E96" t="n">
-        <v>5.37263</v>
+        <v>4.30566</v>
       </c>
       <c r="F96" t="n">
-        <v>7.66217</v>
+        <v>6.37994</v>
       </c>
     </row>
     <row r="97">
@@ -6979,19 +6979,19 @@
         <v>1011953</v>
       </c>
       <c r="B97" t="n">
-        <v>6.4347</v>
+        <v>6.47284</v>
       </c>
       <c r="C97" t="n">
-        <v>4.7281</v>
+        <v>4.27039</v>
       </c>
       <c r="D97" t="n">
-        <v>41.7263</v>
+        <v>41.9832</v>
       </c>
       <c r="E97" t="n">
-        <v>5.48614</v>
+        <v>4.4697</v>
       </c>
       <c r="F97" t="n">
-        <v>7.94041</v>
+        <v>6.69895</v>
       </c>
     </row>
     <row r="98">
@@ -6999,19 +6999,19 @@
         <v>1062505</v>
       </c>
       <c r="B98" t="n">
-        <v>6.70296</v>
+        <v>6.73628</v>
       </c>
       <c r="C98" t="n">
-        <v>4.92793</v>
+        <v>4.45559</v>
       </c>
       <c r="D98" t="n">
-        <v>43.0522</v>
+        <v>43.3374</v>
       </c>
       <c r="E98" t="n">
-        <v>5.6885</v>
+        <v>4.62885</v>
       </c>
       <c r="F98" t="n">
-        <v>8.252520000000001</v>
+        <v>6.84635</v>
       </c>
     </row>
     <row r="99">
@@ -7019,19 +7019,19 @@
         <v>1115584</v>
       </c>
       <c r="B99" t="n">
-        <v>7.05168</v>
+        <v>6.94892</v>
       </c>
       <c r="C99" t="n">
-        <v>5.13785</v>
+        <v>4.64163</v>
       </c>
       <c r="D99" t="n">
-        <v>44.4194</v>
+        <v>44.7912</v>
       </c>
       <c r="E99" t="n">
-        <v>5.88334</v>
+        <v>4.74577</v>
       </c>
       <c r="F99" t="n">
-        <v>8.624359999999999</v>
+        <v>7.04907</v>
       </c>
     </row>
     <row r="100">
@@ -7039,19 +7039,19 @@
         <v>1171316</v>
       </c>
       <c r="B100" t="n">
-        <v>7.34266</v>
+        <v>7.25896</v>
       </c>
       <c r="C100" t="n">
-        <v>5.34444</v>
+        <v>4.84852</v>
       </c>
       <c r="D100" t="n">
-        <v>46.0252</v>
+        <v>46.2481</v>
       </c>
       <c r="E100" t="n">
-        <v>6.13988</v>
+        <v>4.9743</v>
       </c>
       <c r="F100" t="n">
-        <v>9.06439</v>
+        <v>7.37737</v>
       </c>
     </row>
     <row r="101">
@@ -7059,19 +7059,19 @@
         <v>1229834</v>
       </c>
       <c r="B101" t="n">
-        <v>7.70018</v>
+        <v>7.62397</v>
       </c>
       <c r="C101" t="n">
-        <v>5.62382</v>
+        <v>5.06724</v>
       </c>
       <c r="D101" t="n">
-        <v>47.5321</v>
+        <v>47.7999</v>
       </c>
       <c r="E101" t="n">
-        <v>6.35927</v>
+        <v>5.15036</v>
       </c>
       <c r="F101" t="n">
-        <v>9.54102</v>
+        <v>8.07888</v>
       </c>
     </row>
     <row r="102">
@@ -7079,19 +7079,19 @@
         <v>1291277</v>
       </c>
       <c r="B102" t="n">
-        <v>8.105700000000001</v>
+        <v>8.064539999999999</v>
       </c>
       <c r="C102" t="n">
-        <v>5.9755</v>
+        <v>5.40262</v>
       </c>
       <c r="D102" t="n">
-        <v>49.1949</v>
+        <v>49.4446</v>
       </c>
       <c r="E102" t="n">
-        <v>6.60787</v>
+        <v>5.37916</v>
       </c>
       <c r="F102" t="n">
-        <v>9.98743</v>
+        <v>8.409890000000001</v>
       </c>
     </row>
     <row r="103">
@@ -7099,19 +7099,19 @@
         <v>1355792</v>
       </c>
       <c r="B103" t="n">
-        <v>8.67334</v>
+        <v>8.65949</v>
       </c>
       <c r="C103" t="n">
-        <v>6.4266</v>
+        <v>5.86074</v>
       </c>
       <c r="D103" t="n">
-        <v>50.8593</v>
+        <v>51.1349</v>
       </c>
       <c r="E103" t="n">
-        <v>6.93712</v>
+        <v>5.7045</v>
       </c>
       <c r="F103" t="n">
-        <v>10.6402</v>
+        <v>8.92268</v>
       </c>
     </row>
     <row r="104">
@@ -7119,19 +7119,19 @@
         <v>1423532</v>
       </c>
       <c r="B104" t="n">
-        <v>9.40253</v>
+        <v>9.39644</v>
       </c>
       <c r="C104" t="n">
-        <v>7.05896</v>
+        <v>6.42717</v>
       </c>
       <c r="D104" t="n">
-        <v>52.6403</v>
+        <v>52.6911</v>
       </c>
       <c r="E104" t="n">
-        <v>7.32677</v>
+        <v>6.00964</v>
       </c>
       <c r="F104" t="n">
-        <v>11.7145</v>
+        <v>9.73659</v>
       </c>
     </row>
     <row r="105">
@@ -7139,19 +7139,19 @@
         <v>1494659</v>
       </c>
       <c r="B105" t="n">
-        <v>10.4379</v>
+        <v>10.5135</v>
       </c>
       <c r="C105" t="n">
-        <v>8.03285</v>
+        <v>7.28653</v>
       </c>
       <c r="D105" t="n">
-        <v>54.5705</v>
+        <v>54.5201</v>
       </c>
       <c r="E105" t="n">
-        <v>7.92194</v>
+        <v>4.44754</v>
       </c>
       <c r="F105" t="n">
-        <v>12.7393</v>
+        <v>6.4198</v>
       </c>
     </row>
     <row r="106">
@@ -7159,19 +7159,19 @@
         <v>1569342</v>
       </c>
       <c r="B106" t="n">
-        <v>12.0099</v>
+        <v>11.9832</v>
       </c>
       <c r="C106" t="n">
-        <v>9.416980000000001</v>
+        <v>8.42535</v>
       </c>
       <c r="D106" t="n">
-        <v>56.3699</v>
+        <v>56.4614</v>
       </c>
       <c r="E106" t="n">
-        <v>8.77725</v>
+        <v>4.55985</v>
       </c>
       <c r="F106" t="n">
-        <v>13.9492</v>
+        <v>6.73155</v>
       </c>
     </row>
     <row r="107">
@@ -7179,19 +7179,19 @@
         <v>1647759</v>
       </c>
       <c r="B107" t="n">
-        <v>14.1146</v>
+        <v>14.2873</v>
       </c>
       <c r="C107" t="n">
-        <v>11.3623</v>
+        <v>10.2728</v>
       </c>
       <c r="D107" t="n">
-        <v>42.8475</v>
+        <v>42.8553</v>
       </c>
       <c r="E107" t="n">
-        <v>5.69049</v>
+        <v>4.5079</v>
       </c>
       <c r="F107" t="n">
-        <v>8.343669999999999</v>
+        <v>7.0375</v>
       </c>
     </row>
     <row r="108">
@@ -7199,19 +7199,19 @@
         <v>1730096</v>
       </c>
       <c r="B108" t="n">
-        <v>17.5689</v>
+        <v>17.221</v>
       </c>
       <c r="C108" t="n">
-        <v>4.93448</v>
+        <v>4.52918</v>
       </c>
       <c r="D108" t="n">
-        <v>44.0632</v>
+        <v>44.0955</v>
       </c>
       <c r="E108" t="n">
-        <v>5.85425</v>
+        <v>4.77771</v>
       </c>
       <c r="F108" t="n">
-        <v>8.81767</v>
+        <v>7.37835</v>
       </c>
     </row>
     <row r="109">
@@ -7219,19 +7219,19 @@
         <v>1816549</v>
       </c>
       <c r="B109" t="n">
-        <v>22.3466</v>
+        <v>22.0377</v>
       </c>
       <c r="C109" t="n">
-        <v>5.09682</v>
+        <v>4.74841</v>
       </c>
       <c r="D109" t="n">
-        <v>45.2466</v>
+        <v>45.314</v>
       </c>
       <c r="E109" t="n">
-        <v>5.87396</v>
+        <v>4.91241</v>
       </c>
       <c r="F109" t="n">
-        <v>9.21759</v>
+        <v>7.77031</v>
       </c>
     </row>
     <row r="110">
@@ -7239,19 +7239,19 @@
         <v>1907324</v>
       </c>
       <c r="B110" t="n">
-        <v>7.39744</v>
+        <v>7.55634</v>
       </c>
       <c r="C110" t="n">
-        <v>5.2527</v>
+        <v>4.8821</v>
       </c>
       <c r="D110" t="n">
-        <v>46.4915</v>
+        <v>46.59</v>
       </c>
       <c r="E110" t="n">
-        <v>6.12235</v>
+        <v>5.05718</v>
       </c>
       <c r="F110" t="n">
-        <v>9.43435</v>
+        <v>8.29059</v>
       </c>
     </row>
     <row r="111">
@@ -7259,19 +7259,19 @@
         <v>2002637</v>
       </c>
       <c r="B111" t="n">
-        <v>7.68897</v>
+        <v>8.05837</v>
       </c>
       <c r="C111" t="n">
-        <v>5.42858</v>
+        <v>5.20996</v>
       </c>
       <c r="D111" t="n">
-        <v>47.7693</v>
+        <v>47.8536</v>
       </c>
       <c r="E111" t="n">
-        <v>6.3101</v>
+        <v>5.28339</v>
       </c>
       <c r="F111" t="n">
-        <v>9.95294</v>
+        <v>8.96504</v>
       </c>
     </row>
     <row r="112">
@@ -7279,19 +7279,19 @@
         <v>2102715</v>
       </c>
       <c r="B112" t="n">
-        <v>7.98088</v>
+        <v>8.630839999999999</v>
       </c>
       <c r="C112" t="n">
-        <v>5.65327</v>
+        <v>5.55469</v>
       </c>
       <c r="D112" t="n">
-        <v>49.1051</v>
+        <v>49.1413</v>
       </c>
       <c r="E112" t="n">
-        <v>6.51796</v>
+        <v>5.6424</v>
       </c>
       <c r="F112" t="n">
-        <v>10.5072</v>
+        <v>9.527139999999999</v>
       </c>
     </row>
     <row r="113">
@@ -7299,19 +7299,19 @@
         <v>2207796</v>
       </c>
       <c r="B113" t="n">
-        <v>8.5784</v>
+        <v>9.11758</v>
       </c>
       <c r="C113" t="n">
-        <v>6.04606</v>
+        <v>5.87843</v>
       </c>
       <c r="D113" t="n">
-        <v>50.4638</v>
+        <v>50.5533</v>
       </c>
       <c r="E113" t="n">
-        <v>6.79658</v>
+        <v>5.99747</v>
       </c>
       <c r="F113" t="n">
-        <v>11.2094</v>
+        <v>10.0496</v>
       </c>
     </row>
     <row r="114">
@@ -7319,19 +7319,19 @@
         <v>2318131</v>
       </c>
       <c r="B114" t="n">
-        <v>9.189170000000001</v>
+        <v>9.516299999999999</v>
       </c>
       <c r="C114" t="n">
-        <v>6.4902</v>
+        <v>6.18519</v>
       </c>
       <c r="D114" t="n">
-        <v>51.8652</v>
+        <v>51.9444</v>
       </c>
       <c r="E114" t="n">
-        <v>7.28856</v>
+        <v>6.30674</v>
       </c>
       <c r="F114" t="n">
-        <v>11.8741</v>
+        <v>10.4529</v>
       </c>
     </row>
     <row r="115">
@@ -7339,19 +7339,19 @@
         <v>2433982</v>
       </c>
       <c r="B115" t="n">
-        <v>9.669230000000001</v>
+        <v>9.9337</v>
       </c>
       <c r="C115" t="n">
-        <v>6.85791</v>
+        <v>6.47222</v>
       </c>
       <c r="D115" t="n">
-        <v>53.376</v>
+        <v>53.4331</v>
       </c>
       <c r="E115" t="n">
-        <v>7.64783</v>
+        <v>6.58809</v>
       </c>
       <c r="F115" t="n">
-        <v>12.3999</v>
+        <v>10.8705</v>
       </c>
     </row>
     <row r="116">
@@ -7359,19 +7359,19 @@
         <v>2555625</v>
       </c>
       <c r="B116" t="n">
-        <v>10.2506</v>
+        <v>10.4136</v>
       </c>
       <c r="C116" t="n">
-        <v>7.30465</v>
+        <v>6.83482</v>
       </c>
       <c r="D116" t="n">
-        <v>54.8952</v>
+        <v>55.0165</v>
       </c>
       <c r="E116" t="n">
-        <v>8.05545</v>
+        <v>6.90686</v>
       </c>
       <c r="F116" t="n">
-        <v>12.9417</v>
+        <v>11.317</v>
       </c>
     </row>
     <row r="117">
@@ -7379,19 +7379,19 @@
         <v>2683350</v>
       </c>
       <c r="B117" t="n">
-        <v>10.8815</v>
+        <v>10.9533</v>
       </c>
       <c r="C117" t="n">
-        <v>7.83005</v>
+        <v>7.25709</v>
       </c>
       <c r="D117" t="n">
-        <v>56.5195</v>
+        <v>56.6626</v>
       </c>
       <c r="E117" t="n">
-        <v>8.47518</v>
+        <v>7.23548</v>
       </c>
       <c r="F117" t="n">
-        <v>13.5208</v>
+        <v>11.8083</v>
       </c>
     </row>
     <row r="118">
@@ -7399,19 +7399,19 @@
         <v>2817461</v>
       </c>
       <c r="B118" t="n">
-        <v>11.5707</v>
+        <v>11.6161</v>
       </c>
       <c r="C118" t="n">
-        <v>8.4962</v>
+        <v>7.80291</v>
       </c>
       <c r="D118" t="n">
-        <v>58.222</v>
+        <v>58.2893</v>
       </c>
       <c r="E118" t="n">
-        <v>8.981299999999999</v>
+        <v>7.62996</v>
       </c>
       <c r="F118" t="n">
-        <v>14.2501</v>
+        <v>12.4018</v>
       </c>
     </row>
     <row r="119">
@@ -7419,19 +7419,19 @@
         <v>2958277</v>
       </c>
       <c r="B119" t="n">
-        <v>12.4801</v>
+        <v>12.5193</v>
       </c>
       <c r="C119" t="n">
-        <v>9.37907</v>
+        <v>8.53308</v>
       </c>
       <c r="D119" t="n">
-        <v>59.9816</v>
+        <v>60.104</v>
       </c>
       <c r="E119" t="n">
-        <v>9.524380000000001</v>
+        <v>6.39563</v>
       </c>
       <c r="F119" t="n">
-        <v>15.0516</v>
+        <v>8.893190000000001</v>
       </c>
     </row>
     <row r="120">
@@ -7439,19 +7439,19 @@
         <v>3106133</v>
       </c>
       <c r="B120" t="n">
-        <v>13.6929</v>
+        <v>13.7543</v>
       </c>
       <c r="C120" t="n">
-        <v>10.5534</v>
+        <v>9.559559999999999</v>
       </c>
       <c r="D120" t="n">
-        <v>62.015</v>
+        <v>62.0305</v>
       </c>
       <c r="E120" t="n">
-        <v>10.3078</v>
+        <v>6.74417</v>
       </c>
       <c r="F120" t="n">
-        <v>16.1901</v>
+        <v>9.597020000000001</v>
       </c>
     </row>
     <row r="121">
@@ -7459,19 +7459,19 @@
         <v>3261381</v>
       </c>
       <c r="B121" t="n">
-        <v>15.5248</v>
+        <v>15.5187</v>
       </c>
       <c r="C121" t="n">
-        <v>12.2675</v>
+        <v>11.0729</v>
       </c>
       <c r="D121" t="n">
-        <v>45.8663</v>
+        <v>45.9864</v>
       </c>
       <c r="E121" t="n">
-        <v>7.97219</v>
+        <v>6.84287</v>
       </c>
       <c r="F121" t="n">
-        <v>11.1642</v>
+        <v>10.3859</v>
       </c>
     </row>
     <row r="122">
@@ -7479,19 +7479,19 @@
         <v>3424391</v>
       </c>
       <c r="B122" t="n">
-        <v>17.9634</v>
+        <v>18.201</v>
       </c>
       <c r="C122" t="n">
-        <v>6.81676</v>
+        <v>6.38264</v>
       </c>
       <c r="D122" t="n">
-        <v>47.1113</v>
+        <v>47.1829</v>
       </c>
       <c r="E122" t="n">
-        <v>8.259460000000001</v>
+        <v>6.86994</v>
       </c>
       <c r="F122" t="n">
-        <v>11.9166</v>
+        <v>10.3691</v>
       </c>
     </row>
     <row r="123">
@@ -7499,19 +7499,19 @@
         <v>3595551</v>
       </c>
       <c r="B123" t="n">
-        <v>22.3259</v>
+        <v>22.2919</v>
       </c>
       <c r="C123" t="n">
-        <v>7.26286</v>
+        <v>6.53982</v>
       </c>
       <c r="D123" t="n">
-        <v>48.3539</v>
+        <v>48.1535</v>
       </c>
       <c r="E123" t="n">
-        <v>8.013479999999999</v>
+        <v>7.13205</v>
       </c>
       <c r="F123" t="n">
-        <v>12.055</v>
+        <v>10.4086</v>
       </c>
     </row>
     <row r="124">
@@ -7519,19 +7519,19 @@
         <v>3775269</v>
       </c>
       <c r="B124" t="n">
-        <v>9.729649999999999</v>
+        <v>9.300509999999999</v>
       </c>
       <c r="C124" t="n">
-        <v>7.29027</v>
+        <v>6.48788</v>
       </c>
       <c r="D124" t="n">
-        <v>49.6164</v>
+        <v>49.6896</v>
       </c>
       <c r="E124" t="n">
-        <v>8.327159999999999</v>
+        <v>7.15297</v>
       </c>
       <c r="F124" t="n">
-        <v>12.6151</v>
+        <v>10.8788</v>
       </c>
     </row>
     <row r="125">
@@ -7539,19 +7539,19 @@
         <v>3963972</v>
       </c>
       <c r="B125" t="n">
-        <v>10.1225</v>
+        <v>10.0697</v>
       </c>
       <c r="C125" t="n">
-        <v>7.33811</v>
+        <v>6.98539</v>
       </c>
       <c r="D125" t="n">
-        <v>50.6629</v>
+        <v>50.9614</v>
       </c>
       <c r="E125" t="n">
-        <v>8.48638</v>
+        <v>7.17325</v>
       </c>
       <c r="F125" t="n">
-        <v>12.8097</v>
+        <v>11.0873</v>
       </c>
     </row>
     <row r="126">
@@ -7559,19 +7559,19 @@
         <v>4162110</v>
       </c>
       <c r="B126" t="n">
-        <v>10.0903</v>
+        <v>10.2085</v>
       </c>
       <c r="C126" t="n">
-        <v>7.69197</v>
+        <v>6.93299</v>
       </c>
       <c r="D126" t="n">
-        <v>52.2238</v>
+        <v>52.3438</v>
       </c>
       <c r="E126" t="n">
-        <v>8.618740000000001</v>
+        <v>7.44948</v>
       </c>
       <c r="F126" t="n">
-        <v>13.0487</v>
+        <v>11.5256</v>
       </c>
     </row>
     <row r="127">
@@ -7579,19 +7579,19 @@
         <v>4370154</v>
       </c>
       <c r="B127" t="n">
-        <v>10.545</v>
+        <v>10.6477</v>
       </c>
       <c r="C127" t="n">
-        <v>7.65364</v>
+        <v>6.84692</v>
       </c>
       <c r="D127" t="n">
-        <v>53.5138</v>
+        <v>53.6989</v>
       </c>
       <c r="E127" t="n">
-        <v>9.26008</v>
+        <v>7.55281</v>
       </c>
       <c r="F127" t="n">
-        <v>13.8806</v>
+        <v>11.7205</v>
       </c>
     </row>
     <row r="128">
@@ -7599,19 +7599,19 @@
         <v>4588600</v>
       </c>
       <c r="B128" t="n">
-        <v>10.7042</v>
+        <v>10.7654</v>
       </c>
       <c r="C128" t="n">
-        <v>7.91666</v>
+        <v>7.21672</v>
       </c>
       <c r="D128" t="n">
-        <v>55.083</v>
+        <v>55.0849</v>
       </c>
       <c r="E128" t="n">
-        <v>9.221220000000001</v>
+        <v>7.83366</v>
       </c>
       <c r="F128" t="n">
-        <v>13.9827</v>
+        <v>12.2474</v>
       </c>
     </row>
     <row r="129">
@@ -7619,19 +7619,19 @@
         <v>4817968</v>
       </c>
       <c r="B129" t="n">
-        <v>11.1177</v>
+        <v>11.2327</v>
       </c>
       <c r="C129" t="n">
-        <v>8.187430000000001</v>
+        <v>7.35734</v>
       </c>
       <c r="D129" t="n">
-        <v>56.4544</v>
+        <v>56.5918</v>
       </c>
       <c r="E129" t="n">
-        <v>9.57738</v>
+        <v>7.96014</v>
       </c>
       <c r="F129" t="n">
-        <v>14.5279</v>
+        <v>12.5561</v>
       </c>
     </row>
     <row r="130">
@@ -7639,19 +7639,19 @@
         <v>5058804</v>
       </c>
       <c r="B130" t="n">
-        <v>11.6069</v>
+        <v>11.5886</v>
       </c>
       <c r="C130" t="n">
-        <v>8.400919999999999</v>
+        <v>7.67289</v>
       </c>
       <c r="D130" t="n">
-        <v>57.9968</v>
+        <v>57.9435</v>
       </c>
       <c r="E130" t="n">
-        <v>9.95903</v>
+        <v>8.17784</v>
       </c>
       <c r="F130" t="n">
-        <v>14.9939</v>
+        <v>12.9954</v>
       </c>
     </row>
     <row r="131">
@@ -7659,19 +7659,19 @@
         <v>5311681</v>
       </c>
       <c r="B131" t="n">
-        <v>11.9996</v>
+        <v>12.0547</v>
       </c>
       <c r="C131" t="n">
-        <v>8.81134</v>
+        <v>8.16807</v>
       </c>
       <c r="D131" t="n">
-        <v>59.4258</v>
+        <v>59.7596</v>
       </c>
       <c r="E131" t="n">
-        <v>10.0888</v>
+        <v>8.415229999999999</v>
       </c>
       <c r="F131" t="n">
-        <v>15.4657</v>
+        <v>13.3687</v>
       </c>
     </row>
     <row r="132">
@@ -7679,19 +7679,19 @@
         <v>5577201</v>
       </c>
       <c r="B132" t="n">
-        <v>12.6013</v>
+        <v>12.5026</v>
       </c>
       <c r="C132" t="n">
-        <v>9.35144</v>
+        <v>8.48597</v>
       </c>
       <c r="D132" t="n">
-        <v>61.2168</v>
+        <v>61.44</v>
       </c>
       <c r="E132" t="n">
-        <v>10.2638</v>
+        <v>8.66023</v>
       </c>
       <c r="F132" t="n">
-        <v>15.9167</v>
+        <v>13.8812</v>
       </c>
     </row>
     <row r="133">
@@ -7699,19 +7699,19 @@
         <v>5855997</v>
       </c>
       <c r="B133" t="n">
-        <v>13.3941</v>
+        <v>13.3417</v>
       </c>
       <c r="C133" t="n">
-        <v>10.0463</v>
+        <v>9.10514</v>
       </c>
       <c r="D133" t="n">
-        <v>63.0115</v>
+        <v>63.2431</v>
       </c>
       <c r="E133" t="n">
-        <v>10.6983</v>
+        <v>9.17961</v>
       </c>
       <c r="F133" t="n">
-        <v>16.7463</v>
+        <v>15.163</v>
       </c>
     </row>
     <row r="134">
@@ -7719,19 +7719,19 @@
         <v>6148732</v>
       </c>
       <c r="B134" t="n">
-        <v>14.6085</v>
+        <v>14.6569</v>
       </c>
       <c r="C134" t="n">
-        <v>11.2426</v>
+        <v>10.0551</v>
       </c>
       <c r="D134" t="n">
-        <v>64.8914</v>
+        <v>65.21169999999999</v>
       </c>
       <c r="E134" t="n">
-        <v>11.7234</v>
+        <v>12.34</v>
       </c>
       <c r="F134" t="n">
-        <v>18.2162</v>
+        <v>16.3947</v>
       </c>
     </row>
     <row r="135">
@@ -7739,19 +7739,19 @@
         <v>6456103</v>
       </c>
       <c r="B135" t="n">
-        <v>16.1268</v>
+        <v>16.1247</v>
       </c>
       <c r="C135" t="n">
-        <v>12.6386</v>
+        <v>11.4468</v>
       </c>
       <c r="D135" t="n">
-        <v>47.4904</v>
+        <v>47.7591</v>
       </c>
       <c r="E135" t="n">
-        <v>15.4301</v>
+        <v>12.7357</v>
       </c>
       <c r="F135" t="n">
-        <v>20.0657</v>
+        <v>16.3531</v>
       </c>
     </row>
     <row r="136">
@@ -7759,19 +7759,19 @@
         <v>6778842</v>
       </c>
       <c r="B136" t="n">
-        <v>18.4911</v>
+        <v>18.9694</v>
       </c>
       <c r="C136" t="n">
-        <v>13.7102</v>
+        <v>12.5341</v>
       </c>
       <c r="D136" t="n">
-        <v>48.7778</v>
+        <v>48.9695</v>
       </c>
       <c r="E136" t="n">
-        <v>15.5941</v>
+        <v>12.37</v>
       </c>
       <c r="F136" t="n">
-        <v>19.7461</v>
+        <v>16.5708</v>
       </c>
     </row>
     <row r="137">
@@ -7779,19 +7779,19 @@
         <v>7117717</v>
       </c>
       <c r="B137" t="n">
-        <v>22.2882</v>
+        <v>22.1481</v>
       </c>
       <c r="C137" t="n">
-        <v>14.0285</v>
+        <v>12.5342</v>
       </c>
       <c r="D137" t="n">
-        <v>49.7427</v>
+        <v>50.0077</v>
       </c>
       <c r="E137" t="n">
-        <v>15.6064</v>
+        <v>12.9247</v>
       </c>
       <c r="F137" t="n">
-        <v>20.1239</v>
+        <v>16.7849</v>
       </c>
     </row>
     <row r="138">
@@ -7799,19 +7799,19 @@
         <v>7473535</v>
       </c>
       <c r="B138" t="n">
-        <v>16.2081</v>
+        <v>16.1684</v>
       </c>
       <c r="C138" t="n">
-        <v>14.3687</v>
+        <v>12.4161</v>
       </c>
       <c r="D138" t="n">
-        <v>51.1859</v>
+        <v>51.3171</v>
       </c>
       <c r="E138" t="n">
-        <v>15.6792</v>
+        <v>13.0404</v>
       </c>
       <c r="F138" t="n">
-        <v>20.6171</v>
+        <v>16.9823</v>
       </c>
     </row>
     <row r="139">
@@ -7819,19 +7819,19 @@
         <v>7847143</v>
       </c>
       <c r="B139" t="n">
-        <v>16.2071</v>
+        <v>15.6421</v>
       </c>
       <c r="C139" t="n">
-        <v>14.0958</v>
+        <v>12.685</v>
       </c>
       <c r="D139" t="n">
-        <v>52.5405</v>
+        <v>52.7906</v>
       </c>
       <c r="E139" t="n">
-        <v>15.938</v>
+        <v>13.2874</v>
       </c>
       <c r="F139" t="n">
-        <v>20.9985</v>
+        <v>17.471</v>
       </c>
     </row>
     <row r="140">
@@ -7839,19 +7839,19 @@
         <v>8239431</v>
       </c>
       <c r="B140" t="n">
-        <v>16.5734</v>
+        <v>16.5641</v>
       </c>
       <c r="C140" t="n">
-        <v>14.1886</v>
+        <v>12.747</v>
       </c>
       <c r="D140" t="n">
-        <v>53.8302</v>
+        <v>54.1195</v>
       </c>
       <c r="E140" t="n">
-        <v>15.9344</v>
+        <v>13.4308</v>
       </c>
       <c r="F140" t="n">
-        <v>21.174</v>
+        <v>17.7738</v>
       </c>
     </row>
     <row r="141">
@@ -7859,19 +7859,19 @@
         <v>8651333</v>
       </c>
       <c r="B141" t="n">
-        <v>16.6724</v>
+        <v>16.7148</v>
       </c>
       <c r="C141" t="n">
-        <v>14.6244</v>
+        <v>12.9069</v>
       </c>
       <c r="D141" t="n">
-        <v>55.1186</v>
+        <v>55.3415</v>
       </c>
       <c r="E141" t="n">
-        <v>16.1325</v>
+        <v>13.4509</v>
       </c>
       <c r="F141" t="n">
-        <v>21.6273</v>
+        <v>17.9141</v>
       </c>
     </row>
     <row r="142">
@@ -7879,19 +7879,19 @@
         <v>9083830</v>
       </c>
       <c r="B142" t="n">
-        <v>16.828</v>
+        <v>17.0695</v>
       </c>
       <c r="C142" t="n">
-        <v>14.4721</v>
+        <v>13.0538</v>
       </c>
       <c r="D142" t="n">
-        <v>56.5239</v>
+        <v>56.781</v>
       </c>
       <c r="E142" t="n">
-        <v>16.325</v>
+        <v>13.4066</v>
       </c>
       <c r="F142" t="n">
-        <v>22.0327</v>
+        <v>17.5497</v>
       </c>
     </row>
     <row r="143">
@@ -7899,19 +7899,19 @@
         <v>9537951</v>
       </c>
       <c r="B143" t="n">
-        <v>16.7879</v>
+        <v>17.2464</v>
       </c>
       <c r="C143" t="n">
-        <v>14.7711</v>
+        <v>13.1144</v>
       </c>
       <c r="D143" t="n">
-        <v>58.0057</v>
+        <v>58.4119</v>
       </c>
       <c r="E143" t="n">
-        <v>16.4875</v>
+        <v>13.8534</v>
       </c>
       <c r="F143" t="n">
-        <v>22.4541</v>
+        <v>18.0245</v>
       </c>
     </row>
   </sheetData>

--- a/gcc-x64/Scattered unsuccessful looukp.xlsx
+++ b/gcc-x64/Scattered unsuccessful looukp.xlsx
@@ -5079,19 +5079,19 @@
         <v>10000</v>
       </c>
       <c r="B2" t="n">
-        <v>2.93296</v>
+        <v>2.77856</v>
       </c>
       <c r="C2" t="n">
-        <v>1.92244</v>
+        <v>1.9456</v>
       </c>
       <c r="D2" t="n">
-        <v>13.4709</v>
+        <v>12.5926</v>
       </c>
       <c r="E2" t="n">
-        <v>1.85415</v>
+        <v>1.8628</v>
       </c>
       <c r="F2" t="n">
-        <v>2.08544</v>
+        <v>2.06968</v>
       </c>
     </row>
     <row r="3">
@@ -5099,19 +5099,19 @@
         <v>10500</v>
       </c>
       <c r="B3" t="n">
-        <v>3.01709</v>
+        <v>2.96491</v>
       </c>
       <c r="C3" t="n">
-        <v>1.9828</v>
+        <v>2.02484</v>
       </c>
       <c r="D3" t="n">
-        <v>13.7036</v>
+        <v>12.9839</v>
       </c>
       <c r="E3" t="n">
-        <v>1.58057</v>
+        <v>1.85677</v>
       </c>
       <c r="F3" t="n">
-        <v>1.89858</v>
+        <v>1.99282</v>
       </c>
     </row>
     <row r="4">
@@ -5119,19 +5119,19 @@
         <v>11025</v>
       </c>
       <c r="B4" t="n">
-        <v>3.07826</v>
+        <v>3.22207</v>
       </c>
       <c r="C4" t="n">
-        <v>2.06452</v>
+        <v>2.14543</v>
       </c>
       <c r="D4" t="n">
-        <v>14.4756</v>
+        <v>13.4442</v>
       </c>
       <c r="E4" t="n">
-        <v>1.60264</v>
+        <v>1.78182</v>
       </c>
       <c r="F4" t="n">
-        <v>1.80961</v>
+        <v>1.9142</v>
       </c>
     </row>
     <row r="5">
@@ -5139,19 +5139,19 @@
         <v>11576</v>
       </c>
       <c r="B5" t="n">
-        <v>3.51224</v>
+        <v>3.72414</v>
       </c>
       <c r="C5" t="n">
-        <v>2.25355</v>
+        <v>2.3927</v>
       </c>
       <c r="D5" t="n">
-        <v>15.0178</v>
+        <v>13.9543</v>
       </c>
       <c r="E5" t="n">
-        <v>1.75457</v>
+        <v>1.75181</v>
       </c>
       <c r="F5" t="n">
-        <v>1.868</v>
+        <v>1.8288</v>
       </c>
     </row>
     <row r="6">
@@ -5159,19 +5159,19 @@
         <v>12154</v>
       </c>
       <c r="B6" t="n">
-        <v>4.79475</v>
+        <v>4.76229</v>
       </c>
       <c r="C6" t="n">
-        <v>2.98979</v>
+        <v>3.64181</v>
       </c>
       <c r="D6" t="n">
-        <v>15.5595</v>
+        <v>14.41</v>
       </c>
       <c r="E6" t="n">
-        <v>1.7718</v>
+        <v>1.77457</v>
       </c>
       <c r="F6" t="n">
-        <v>1.87205</v>
+        <v>1.85327</v>
       </c>
     </row>
     <row r="7">
@@ -5179,19 +5179,19 @@
         <v>12760</v>
       </c>
       <c r="B7" t="n">
-        <v>6.209</v>
+        <v>6.36596</v>
       </c>
       <c r="C7" t="n">
-        <v>4.93874</v>
+        <v>6.05866</v>
       </c>
       <c r="D7" t="n">
-        <v>10.6413</v>
+        <v>9.832800000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>1.79225</v>
+        <v>1.80463</v>
       </c>
       <c r="F7" t="n">
-        <v>1.89308</v>
+        <v>1.88225</v>
       </c>
     </row>
     <row r="8">
@@ -5199,19 +5199,19 @@
         <v>13396</v>
       </c>
       <c r="B8" t="n">
-        <v>9.5185</v>
+        <v>8.37917</v>
       </c>
       <c r="C8" t="n">
-        <v>1.73426</v>
+        <v>1.72018</v>
       </c>
       <c r="D8" t="n">
-        <v>11.0569</v>
+        <v>10.555</v>
       </c>
       <c r="E8" t="n">
-        <v>1.81274</v>
+        <v>1.80594</v>
       </c>
       <c r="F8" t="n">
-        <v>1.92521</v>
+        <v>1.90739</v>
       </c>
     </row>
     <row r="9">
@@ -5219,19 +5219,19 @@
         <v>14063</v>
       </c>
       <c r="B9" t="n">
-        <v>13.9234</v>
+        <v>12.4203</v>
       </c>
       <c r="C9" t="n">
-        <v>1.75359</v>
+        <v>1.73732</v>
       </c>
       <c r="D9" t="n">
-        <v>11.6855</v>
+        <v>11.1277</v>
       </c>
       <c r="E9" t="n">
-        <v>1.80934</v>
+        <v>1.81525</v>
       </c>
       <c r="F9" t="n">
-        <v>1.93077</v>
+        <v>1.90003</v>
       </c>
     </row>
     <row r="10">
@@ -5239,19 +5239,19 @@
         <v>14763</v>
       </c>
       <c r="B10" t="n">
-        <v>2.81432</v>
+        <v>2.49846</v>
       </c>
       <c r="C10" t="n">
-        <v>1.79166</v>
+        <v>1.74488</v>
       </c>
       <c r="D10" t="n">
-        <v>12.2611</v>
+        <v>11.9379</v>
       </c>
       <c r="E10" t="n">
-        <v>1.82592</v>
+        <v>1.8258</v>
       </c>
       <c r="F10" t="n">
-        <v>1.95455</v>
+        <v>1.92032</v>
       </c>
     </row>
     <row r="11">
@@ -5259,19 +5259,19 @@
         <v>15498</v>
       </c>
       <c r="B11" t="n">
-        <v>2.86484</v>
+        <v>2.56371</v>
       </c>
       <c r="C11" t="n">
-        <v>1.9972</v>
+        <v>1.77959</v>
       </c>
       <c r="D11" t="n">
-        <v>12.7119</v>
+        <v>12.4373</v>
       </c>
       <c r="E11" t="n">
-        <v>1.83372</v>
+        <v>1.84437</v>
       </c>
       <c r="F11" t="n">
-        <v>1.9938</v>
+        <v>1.93694</v>
       </c>
     </row>
     <row r="12">
@@ -5279,19 +5279,19 @@
         <v>16269</v>
       </c>
       <c r="B12" t="n">
-        <v>2.89798</v>
+        <v>2.60583</v>
       </c>
       <c r="C12" t="n">
-        <v>2.0459</v>
+        <v>1.81442</v>
       </c>
       <c r="D12" t="n">
-        <v>13.2645</v>
+        <v>12.9673</v>
       </c>
       <c r="E12" t="n">
-        <v>1.85555</v>
+        <v>1.86069</v>
       </c>
       <c r="F12" t="n">
-        <v>2.00323</v>
+        <v>1.95662</v>
       </c>
     </row>
     <row r="13">
@@ -5299,19 +5299,19 @@
         <v>17078</v>
       </c>
       <c r="B13" t="n">
-        <v>2.9259</v>
+        <v>2.68672</v>
       </c>
       <c r="C13" t="n">
-        <v>1.94218</v>
+        <v>1.85804</v>
       </c>
       <c r="D13" t="n">
-        <v>13.7295</v>
+        <v>13.4965</v>
       </c>
       <c r="E13" t="n">
-        <v>1.86428</v>
+        <v>1.88422</v>
       </c>
       <c r="F13" t="n">
-        <v>2.03765</v>
+        <v>1.99306</v>
       </c>
     </row>
     <row r="14">
@@ -5319,19 +5319,19 @@
         <v>17927</v>
       </c>
       <c r="B14" t="n">
-        <v>2.96983</v>
+        <v>2.73835</v>
       </c>
       <c r="C14" t="n">
-        <v>2.06698</v>
+        <v>1.9055</v>
       </c>
       <c r="D14" t="n">
-        <v>14.2572</v>
+        <v>14.0662</v>
       </c>
       <c r="E14" t="n">
-        <v>1.88776</v>
+        <v>1.88496</v>
       </c>
       <c r="F14" t="n">
-        <v>2.0867</v>
+        <v>2.01798</v>
       </c>
     </row>
     <row r="15">
@@ -5339,19 +5339,19 @@
         <v>18818</v>
       </c>
       <c r="B15" t="n">
-        <v>3.0549</v>
+        <v>2.86363</v>
       </c>
       <c r="C15" t="n">
-        <v>2.18093</v>
+        <v>1.9811</v>
       </c>
       <c r="D15" t="n">
-        <v>14.5586</v>
+        <v>14.4801</v>
       </c>
       <c r="E15" t="n">
-        <v>1.90807</v>
+        <v>1.9187</v>
       </c>
       <c r="F15" t="n">
-        <v>2.14097</v>
+        <v>2.04172</v>
       </c>
     </row>
     <row r="16">
@@ -5359,19 +5359,19 @@
         <v>19753</v>
       </c>
       <c r="B16" t="n">
-        <v>3.18072</v>
+        <v>3.031</v>
       </c>
       <c r="C16" t="n">
-        <v>2.18924</v>
+        <v>2.05646</v>
       </c>
       <c r="D16" t="n">
-        <v>15.0222</v>
+        <v>14.9159</v>
       </c>
       <c r="E16" t="n">
-        <v>1.93065</v>
+        <v>1.93579</v>
       </c>
       <c r="F16" t="n">
-        <v>2.17682</v>
+        <v>2.05558</v>
       </c>
     </row>
     <row r="17">
@@ -5379,19 +5379,19 @@
         <v>20734</v>
       </c>
       <c r="B17" t="n">
-        <v>3.29028</v>
+        <v>3.26775</v>
       </c>
       <c r="C17" t="n">
-        <v>2.33675</v>
+        <v>2.2166</v>
       </c>
       <c r="D17" t="n">
-        <v>15.4309</v>
+        <v>15.439</v>
       </c>
       <c r="E17" t="n">
-        <v>1.9688</v>
+        <v>1.95759</v>
       </c>
       <c r="F17" t="n">
-        <v>2.2178</v>
+        <v>2.10564</v>
       </c>
     </row>
     <row r="18">
@@ -5399,19 +5399,19 @@
         <v>21764</v>
       </c>
       <c r="B18" t="n">
-        <v>3.66376</v>
+        <v>3.61363</v>
       </c>
       <c r="C18" t="n">
-        <v>2.52532</v>
+        <v>2.54231</v>
       </c>
       <c r="D18" t="n">
-        <v>15.8866</v>
+        <v>15.8152</v>
       </c>
       <c r="E18" t="n">
-        <v>1.87565</v>
+        <v>1.95776</v>
       </c>
       <c r="F18" t="n">
-        <v>2.25422</v>
+        <v>2.12118</v>
       </c>
     </row>
     <row r="19">
@@ -5419,19 +5419,19 @@
         <v>22845</v>
       </c>
       <c r="B19" t="n">
-        <v>4.12529</v>
+        <v>4.16956</v>
       </c>
       <c r="C19" t="n">
-        <v>3.2319</v>
+        <v>3.33242</v>
       </c>
       <c r="D19" t="n">
-        <v>16.3334</v>
+        <v>16.4262</v>
       </c>
       <c r="E19" t="n">
-        <v>1.96876</v>
+        <v>1.94234</v>
       </c>
       <c r="F19" t="n">
-        <v>2.30341</v>
+        <v>2.19763</v>
       </c>
     </row>
     <row r="20">
@@ -5439,19 +5439,19 @@
         <v>23980</v>
       </c>
       <c r="B20" t="n">
-        <v>5.24093</v>
+        <v>5.47949</v>
       </c>
       <c r="C20" t="n">
-        <v>4.26989</v>
+        <v>4.52922</v>
       </c>
       <c r="D20" t="n">
-        <v>16.7195</v>
+        <v>16.8524</v>
       </c>
       <c r="E20" t="n">
-        <v>1.85905</v>
+        <v>1.83835</v>
       </c>
       <c r="F20" t="n">
-        <v>2.00738</v>
+        <v>1.95066</v>
       </c>
     </row>
     <row r="21">
@@ -5459,19 +5459,19 @@
         <v>25171</v>
       </c>
       <c r="B21" t="n">
-        <v>6.66592</v>
+        <v>7.13401</v>
       </c>
       <c r="C21" t="n">
-        <v>5.5906</v>
+        <v>6.19774</v>
       </c>
       <c r="D21" t="n">
-        <v>11.5507</v>
+        <v>11.5859</v>
       </c>
       <c r="E21" t="n">
-        <v>1.88098</v>
+        <v>1.85614</v>
       </c>
       <c r="F21" t="n">
-        <v>2.03909</v>
+        <v>2.09451</v>
       </c>
     </row>
     <row r="22">
@@ -5479,19 +5479,19 @@
         <v>26421</v>
       </c>
       <c r="B22" t="n">
-        <v>9.304959999999999</v>
+        <v>9.281000000000001</v>
       </c>
       <c r="C22" t="n">
-        <v>1.98986</v>
+        <v>1.75724</v>
       </c>
       <c r="D22" t="n">
-        <v>12.0347</v>
+        <v>12.13</v>
       </c>
       <c r="E22" t="n">
-        <v>1.88911</v>
+        <v>1.8804</v>
       </c>
       <c r="F22" t="n">
-        <v>2.05574</v>
+        <v>2.00429</v>
       </c>
     </row>
     <row r="23">
@@ -5499,19 +5499,19 @@
         <v>27733</v>
       </c>
       <c r="B23" t="n">
-        <v>12.6782</v>
+        <v>12.703</v>
       </c>
       <c r="C23" t="n">
-        <v>1.9049</v>
+        <v>1.77444</v>
       </c>
       <c r="D23" t="n">
-        <v>12.5374</v>
+        <v>12.6411</v>
       </c>
       <c r="E23" t="n">
-        <v>1.90748</v>
+        <v>1.89684</v>
       </c>
       <c r="F23" t="n">
-        <v>2.09968</v>
+        <v>2.03865</v>
       </c>
     </row>
     <row r="24">
@@ -5519,19 +5519,19 @@
         <v>29110</v>
       </c>
       <c r="B24" t="n">
-        <v>2.90598</v>
+        <v>2.67929</v>
       </c>
       <c r="C24" t="n">
-        <v>1.86088</v>
+        <v>1.80782</v>
       </c>
       <c r="D24" t="n">
-        <v>13.1011</v>
+        <v>13.1448</v>
       </c>
       <c r="E24" t="n">
-        <v>1.92631</v>
+        <v>1.92849</v>
       </c>
       <c r="F24" t="n">
-        <v>2.13645</v>
+        <v>2.06786</v>
       </c>
     </row>
     <row r="25">
@@ -5539,19 +5539,19 @@
         <v>30555</v>
       </c>
       <c r="B25" t="n">
-        <v>2.95361</v>
+        <v>2.72203</v>
       </c>
       <c r="C25" t="n">
-        <v>1.87173</v>
+        <v>1.83298</v>
       </c>
       <c r="D25" t="n">
-        <v>13.594</v>
+        <v>13.5607</v>
       </c>
       <c r="E25" t="n">
-        <v>1.9514</v>
+        <v>1.94385</v>
       </c>
       <c r="F25" t="n">
-        <v>2.18378</v>
+        <v>2.10868</v>
       </c>
     </row>
     <row r="26">
@@ -5559,19 +5559,19 @@
         <v>32072</v>
       </c>
       <c r="B26" t="n">
-        <v>3.00406</v>
+        <v>2.78252</v>
       </c>
       <c r="C26" t="n">
-        <v>1.9412</v>
+        <v>1.88312</v>
       </c>
       <c r="D26" t="n">
-        <v>14.0419</v>
+        <v>14.1262</v>
       </c>
       <c r="E26" t="n">
-        <v>1.98876</v>
+        <v>1.98489</v>
       </c>
       <c r="F26" t="n">
-        <v>2.2175</v>
+        <v>2.22207</v>
       </c>
     </row>
     <row r="27">
@@ -5579,19 +5579,19 @@
         <v>33664</v>
       </c>
       <c r="B27" t="n">
-        <v>3.05075</v>
+        <v>2.79323</v>
       </c>
       <c r="C27" t="n">
-        <v>2.03136</v>
+        <v>1.94342</v>
       </c>
       <c r="D27" t="n">
-        <v>14.5218</v>
+        <v>14.6336</v>
       </c>
       <c r="E27" t="n">
-        <v>2.01622</v>
+        <v>2.00934</v>
       </c>
       <c r="F27" t="n">
-        <v>2.2713</v>
+        <v>2.18355</v>
       </c>
     </row>
     <row r="28">
@@ -5599,19 +5599,19 @@
         <v>35335</v>
       </c>
       <c r="B28" t="n">
-        <v>3.14437</v>
+        <v>2.96546</v>
       </c>
       <c r="C28" t="n">
-        <v>2.02122</v>
+        <v>2.00038</v>
       </c>
       <c r="D28" t="n">
-        <v>14.9609</v>
+        <v>15.1034</v>
       </c>
       <c r="E28" t="n">
-        <v>2.04362</v>
+        <v>2.04876</v>
       </c>
       <c r="F28" t="n">
-        <v>2.30256</v>
+        <v>2.25885</v>
       </c>
     </row>
     <row r="29">
@@ -5619,19 +5619,19 @@
         <v>37089</v>
       </c>
       <c r="B29" t="n">
-        <v>3.30904</v>
+        <v>3.11343</v>
       </c>
       <c r="C29" t="n">
-        <v>2.16282</v>
+        <v>2.07653</v>
       </c>
       <c r="D29" t="n">
-        <v>15.4613</v>
+        <v>15.5941</v>
       </c>
       <c r="E29" t="n">
-        <v>2.08118</v>
+        <v>2.06123</v>
       </c>
       <c r="F29" t="n">
-        <v>2.36526</v>
+        <v>2.31648</v>
       </c>
     </row>
     <row r="30">
@@ -5639,19 +5639,19 @@
         <v>38930</v>
       </c>
       <c r="B30" t="n">
-        <v>3.45592</v>
+        <v>3.21232</v>
       </c>
       <c r="C30" t="n">
-        <v>2.24695</v>
+        <v>2.21598</v>
       </c>
       <c r="D30" t="n">
-        <v>15.9361</v>
+        <v>15.9638</v>
       </c>
       <c r="E30" t="n">
-        <v>2.11489</v>
+        <v>2.11199</v>
       </c>
       <c r="F30" t="n">
-        <v>2.3975</v>
+        <v>2.39601</v>
       </c>
     </row>
     <row r="31">
@@ -5659,19 +5659,19 @@
         <v>40863</v>
       </c>
       <c r="B31" t="n">
-        <v>3.65875</v>
+        <v>3.51315</v>
       </c>
       <c r="C31" t="n">
-        <v>2.45028</v>
+        <v>2.4326</v>
       </c>
       <c r="D31" t="n">
-        <v>16.3999</v>
+        <v>16.4261</v>
       </c>
       <c r="E31" t="n">
-        <v>2.1554</v>
+        <v>2.17832</v>
       </c>
       <c r="F31" t="n">
-        <v>2.46072</v>
+        <v>2.47092</v>
       </c>
     </row>
     <row r="32">
@@ -5679,19 +5679,19 @@
         <v>42892</v>
       </c>
       <c r="B32" t="n">
-        <v>4.09734</v>
+        <v>3.90131</v>
       </c>
       <c r="C32" t="n">
-        <v>2.6991</v>
+        <v>2.92338</v>
       </c>
       <c r="D32" t="n">
-        <v>16.7758</v>
+        <v>16.9141</v>
       </c>
       <c r="E32" t="n">
-        <v>2.24604</v>
+        <v>2.26882</v>
       </c>
       <c r="F32" t="n">
-        <v>2.52309</v>
+        <v>2.58997</v>
       </c>
     </row>
     <row r="33">
@@ -5699,19 +5699,19 @@
         <v>45022</v>
       </c>
       <c r="B33" t="n">
-        <v>4.80659</v>
+        <v>4.55428</v>
       </c>
       <c r="C33" t="n">
-        <v>3.28288</v>
+        <v>3.65523</v>
       </c>
       <c r="D33" t="n">
-        <v>17.2339</v>
+        <v>17.3695</v>
       </c>
       <c r="E33" t="n">
-        <v>2.40249</v>
+        <v>2.42976</v>
       </c>
       <c r="F33" t="n">
-        <v>2.69976</v>
+        <v>2.77044</v>
       </c>
     </row>
     <row r="34">
@@ -5719,19 +5719,19 @@
         <v>47258</v>
       </c>
       <c r="B34" t="n">
-        <v>5.73357</v>
+        <v>5.52645</v>
       </c>
       <c r="C34" t="n">
-        <v>4.1571</v>
+        <v>4.73108</v>
       </c>
       <c r="D34" t="n">
-        <v>17.6919</v>
+        <v>17.7546</v>
       </c>
       <c r="E34" t="n">
-        <v>1.92015</v>
+        <v>1.92985</v>
       </c>
       <c r="F34" t="n">
-        <v>2.1168</v>
+        <v>2.16688</v>
       </c>
     </row>
     <row r="35">
@@ -5739,19 +5739,19 @@
         <v>49605</v>
       </c>
       <c r="B35" t="n">
-        <v>7.20806</v>
+        <v>6.62149</v>
       </c>
       <c r="C35" t="n">
-        <v>5.32848</v>
+        <v>6.28144</v>
       </c>
       <c r="D35" t="n">
-        <v>12.0922</v>
+        <v>12.0773</v>
       </c>
       <c r="E35" t="n">
-        <v>1.93762</v>
+        <v>1.95237</v>
       </c>
       <c r="F35" t="n">
-        <v>2.15382</v>
+        <v>2.21151</v>
       </c>
     </row>
     <row r="36">
@@ -5759,19 +5759,19 @@
         <v>52069</v>
       </c>
       <c r="B36" t="n">
-        <v>9.60144</v>
+        <v>8.45335</v>
       </c>
       <c r="C36" t="n">
-        <v>7.00351</v>
+        <v>8.11321</v>
       </c>
       <c r="D36" t="n">
-        <v>12.5513</v>
+        <v>12.5131</v>
       </c>
       <c r="E36" t="n">
-        <v>1.95566</v>
+        <v>1.97733</v>
       </c>
       <c r="F36" t="n">
-        <v>2.19531</v>
+        <v>2.24317</v>
       </c>
     </row>
     <row r="37">
@@ -5779,19 +5779,19 @@
         <v>54656</v>
       </c>
       <c r="B37" t="n">
-        <v>13.0119</v>
+        <v>11.9162</v>
       </c>
       <c r="C37" t="n">
-        <v>1.84975</v>
+        <v>1.8328</v>
       </c>
       <c r="D37" t="n">
-        <v>13.0178</v>
+        <v>13.021</v>
       </c>
       <c r="E37" t="n">
-        <v>1.97951</v>
+        <v>1.9954</v>
       </c>
       <c r="F37" t="n">
-        <v>2.22233</v>
+        <v>2.27707</v>
       </c>
     </row>
     <row r="38">
@@ -5799,19 +5799,19 @@
         <v>57372</v>
       </c>
       <c r="B38" t="n">
-        <v>2.95806</v>
+        <v>2.76484</v>
       </c>
       <c r="C38" t="n">
-        <v>1.84466</v>
+        <v>1.8672</v>
       </c>
       <c r="D38" t="n">
-        <v>13.5421</v>
+        <v>13.5478</v>
       </c>
       <c r="E38" t="n">
-        <v>2.00254</v>
+        <v>2.02652</v>
       </c>
       <c r="F38" t="n">
-        <v>2.2363</v>
+        <v>2.34516</v>
       </c>
     </row>
     <row r="39">
@@ -5819,19 +5819,19 @@
         <v>60223</v>
       </c>
       <c r="B39" t="n">
-        <v>3.01241</v>
+        <v>2.81085</v>
       </c>
       <c r="C39" t="n">
-        <v>1.90329</v>
+        <v>1.90124</v>
       </c>
       <c r="D39" t="n">
-        <v>14.049</v>
+        <v>14.0532</v>
       </c>
       <c r="E39" t="n">
-        <v>2.03016</v>
+        <v>2.05234</v>
       </c>
       <c r="F39" t="n">
-        <v>2.28442</v>
+        <v>2.35356</v>
       </c>
     </row>
     <row r="40">
@@ -5839,19 +5839,19 @@
         <v>63216</v>
       </c>
       <c r="B40" t="n">
-        <v>3.06963</v>
+        <v>2.88709</v>
       </c>
       <c r="C40" t="n">
-        <v>1.9305</v>
+        <v>1.9376</v>
       </c>
       <c r="D40" t="n">
-        <v>14.5469</v>
+        <v>14.5532</v>
       </c>
       <c r="E40" t="n">
-        <v>2.04931</v>
+        <v>2.07529</v>
       </c>
       <c r="F40" t="n">
-        <v>2.34935</v>
+        <v>2.3987</v>
       </c>
     </row>
     <row r="41">
@@ -5859,19 +5859,19 @@
         <v>66358</v>
       </c>
       <c r="B41" t="n">
-        <v>3.14001</v>
+        <v>2.95482</v>
       </c>
       <c r="C41" t="n">
-        <v>2.01606</v>
+        <v>1.99798</v>
       </c>
       <c r="D41" t="n">
-        <v>15.0273</v>
+        <v>14.9974</v>
       </c>
       <c r="E41" t="n">
-        <v>2.08941</v>
+        <v>2.10859</v>
       </c>
       <c r="F41" t="n">
-        <v>2.34461</v>
+        <v>2.43747</v>
       </c>
     </row>
     <row r="42">
@@ -5879,19 +5879,19 @@
         <v>69657</v>
       </c>
       <c r="B42" t="n">
-        <v>3.21203</v>
+        <v>3.03236</v>
       </c>
       <c r="C42" t="n">
-        <v>2.04964</v>
+        <v>2.05302</v>
       </c>
       <c r="D42" t="n">
-        <v>15.4661</v>
+        <v>15.4958</v>
       </c>
       <c r="E42" t="n">
-        <v>2.12368</v>
+        <v>2.14515</v>
       </c>
       <c r="F42" t="n">
-        <v>2.4787</v>
+        <v>2.48267</v>
       </c>
     </row>
     <row r="43">
@@ -5899,19 +5899,19 @@
         <v>73120</v>
       </c>
       <c r="B43" t="n">
-        <v>3.32175</v>
+        <v>3.19071</v>
       </c>
       <c r="C43" t="n">
-        <v>2.13372</v>
+        <v>2.16283</v>
       </c>
       <c r="D43" t="n">
-        <v>15.9152</v>
+        <v>15.9732</v>
       </c>
       <c r="E43" t="n">
-        <v>2.18058</v>
+        <v>2.18562</v>
       </c>
       <c r="F43" t="n">
-        <v>2.49667</v>
+        <v>2.53416</v>
       </c>
     </row>
     <row r="44">
@@ -5919,19 +5919,19 @@
         <v>76756</v>
       </c>
       <c r="B44" t="n">
-        <v>3.48748</v>
+        <v>3.30585</v>
       </c>
       <c r="C44" t="n">
-        <v>2.29424</v>
+        <v>2.31797</v>
       </c>
       <c r="D44" t="n">
-        <v>16.3588</v>
+        <v>16.3891</v>
       </c>
       <c r="E44" t="n">
-        <v>2.26851</v>
+        <v>2.25735</v>
       </c>
       <c r="F44" t="n">
-        <v>2.60793</v>
+        <v>2.60743</v>
       </c>
     </row>
     <row r="45">
@@ -5939,19 +5939,19 @@
         <v>80573</v>
       </c>
       <c r="B45" t="n">
-        <v>3.73299</v>
+        <v>3.6095</v>
       </c>
       <c r="C45" t="n">
-        <v>2.55313</v>
+        <v>2.55925</v>
       </c>
       <c r="D45" t="n">
-        <v>16.6998</v>
+        <v>16.7911</v>
       </c>
       <c r="E45" t="n">
-        <v>2.36009</v>
+        <v>2.35288</v>
       </c>
       <c r="F45" t="n">
-        <v>2.6745</v>
+        <v>2.7125</v>
       </c>
     </row>
     <row r="46">
@@ -5959,19 +5959,19 @@
         <v>84580</v>
       </c>
       <c r="B46" t="n">
-        <v>4.08221</v>
+        <v>3.94223</v>
       </c>
       <c r="C46" t="n">
-        <v>2.90317</v>
+        <v>2.9213</v>
       </c>
       <c r="D46" t="n">
-        <v>17.1677</v>
+        <v>17.2272</v>
       </c>
       <c r="E46" t="n">
-        <v>2.52678</v>
+        <v>2.47377</v>
       </c>
       <c r="F46" t="n">
-        <v>2.82008</v>
+        <v>2.83718</v>
       </c>
     </row>
     <row r="47">
@@ -5979,19 +5979,19 @@
         <v>88787</v>
       </c>
       <c r="B47" t="n">
-        <v>4.62826</v>
+        <v>4.47071</v>
       </c>
       <c r="C47" t="n">
-        <v>3.396</v>
+        <v>3.62546</v>
       </c>
       <c r="D47" t="n">
-        <v>17.5966</v>
+        <v>17.6667</v>
       </c>
       <c r="E47" t="n">
-        <v>2.77406</v>
+        <v>2.70851</v>
       </c>
       <c r="F47" t="n">
-        <v>3.07762</v>
+        <v>3.06099</v>
       </c>
     </row>
     <row r="48">
@@ -5999,19 +5999,19 @@
         <v>93204</v>
       </c>
       <c r="B48" t="n">
-        <v>5.4808</v>
+        <v>5.32882</v>
       </c>
       <c r="C48" t="n">
-        <v>4.05633</v>
+        <v>4.481</v>
       </c>
       <c r="D48" t="n">
-        <v>18.0682</v>
+        <v>18.1163</v>
       </c>
       <c r="E48" t="n">
-        <v>2.09417</v>
+        <v>1.95393</v>
       </c>
       <c r="F48" t="n">
-        <v>2.43785</v>
+        <v>2.3476</v>
       </c>
     </row>
     <row r="49">
@@ -6019,19 +6019,19 @@
         <v>97841</v>
       </c>
       <c r="B49" t="n">
-        <v>6.57975</v>
+        <v>6.51209</v>
       </c>
       <c r="C49" t="n">
-        <v>5.07336</v>
+        <v>5.66892</v>
       </c>
       <c r="D49" t="n">
-        <v>18.5183</v>
+        <v>18.6977</v>
       </c>
       <c r="E49" t="n">
-        <v>2.11057</v>
+        <v>2.06915</v>
       </c>
       <c r="F49" t="n">
-        <v>2.46201</v>
+        <v>2.41908</v>
       </c>
     </row>
     <row r="50">
@@ -6039,19 +6039,19 @@
         <v>102709</v>
       </c>
       <c r="B50" t="n">
-        <v>8.32788</v>
+        <v>8.428140000000001</v>
       </c>
       <c r="C50" t="n">
-        <v>6.6423</v>
+        <v>7.46636</v>
       </c>
       <c r="D50" t="n">
-        <v>12.8783</v>
+        <v>12.8086</v>
       </c>
       <c r="E50" t="n">
-        <v>2.17112</v>
+        <v>2.1123</v>
       </c>
       <c r="F50" t="n">
-        <v>2.52179</v>
+        <v>2.45689</v>
       </c>
     </row>
     <row r="51">
@@ -6059,19 +6059,19 @@
         <v>107820</v>
       </c>
       <c r="B51" t="n">
-        <v>11.181</v>
+        <v>11.5599</v>
       </c>
       <c r="C51" t="n">
-        <v>1.95135</v>
+        <v>2.05122</v>
       </c>
       <c r="D51" t="n">
-        <v>13.3587</v>
+        <v>13.2797</v>
       </c>
       <c r="E51" t="n">
-        <v>2.18491</v>
+        <v>2.21597</v>
       </c>
       <c r="F51" t="n">
-        <v>2.55382</v>
+        <v>2.51787</v>
       </c>
     </row>
     <row r="52">
@@ -6079,19 +6079,19 @@
         <v>113186</v>
       </c>
       <c r="B52" t="n">
-        <v>15.4555</v>
+        <v>16.1599</v>
       </c>
       <c r="C52" t="n">
-        <v>1.96969</v>
+        <v>1.93669</v>
       </c>
       <c r="D52" t="n">
-        <v>13.8201</v>
+        <v>13.7479</v>
       </c>
       <c r="E52" t="n">
-        <v>2.21108</v>
+        <v>2.24382</v>
       </c>
       <c r="F52" t="n">
-        <v>2.57424</v>
+        <v>2.54826</v>
       </c>
     </row>
     <row r="53">
@@ -6099,19 +6099,19 @@
         <v>118820</v>
       </c>
       <c r="B53" t="n">
-        <v>3.09185</v>
+        <v>2.88488</v>
       </c>
       <c r="C53" t="n">
-        <v>2.05565</v>
+        <v>1.99166</v>
       </c>
       <c r="D53" t="n">
-        <v>14.2893</v>
+        <v>14.2591</v>
       </c>
       <c r="E53" t="n">
-        <v>2.24381</v>
+        <v>2.26909</v>
       </c>
       <c r="F53" t="n">
-        <v>2.62072</v>
+        <v>2.58728</v>
       </c>
     </row>
     <row r="54">
@@ -6119,19 +6119,19 @@
         <v>124735</v>
       </c>
       <c r="B54" t="n">
-        <v>3.15389</v>
+        <v>2.90618</v>
       </c>
       <c r="C54" t="n">
-        <v>2.07442</v>
+        <v>2.02213</v>
       </c>
       <c r="D54" t="n">
-        <v>14.7849</v>
+        <v>14.7308</v>
       </c>
       <c r="E54" t="n">
-        <v>2.27768</v>
+        <v>2.24613</v>
       </c>
       <c r="F54" t="n">
-        <v>2.67234</v>
+        <v>2.58961</v>
       </c>
     </row>
     <row r="55">
@@ -6139,19 +6139,19 @@
         <v>130945</v>
       </c>
       <c r="B55" t="n">
-        <v>3.20987</v>
+        <v>2.99362</v>
       </c>
       <c r="C55" t="n">
-        <v>2.12556</v>
+        <v>2.11474</v>
       </c>
       <c r="D55" t="n">
-        <v>15.2546</v>
+        <v>15.2046</v>
       </c>
       <c r="E55" t="n">
-        <v>2.39688</v>
+        <v>2.34227</v>
       </c>
       <c r="F55" t="n">
-        <v>2.68299</v>
+        <v>2.64875</v>
       </c>
     </row>
     <row r="56">
@@ -6159,19 +6159,19 @@
         <v>137465</v>
       </c>
       <c r="B56" t="n">
-        <v>3.28361</v>
+        <v>3.10812</v>
       </c>
       <c r="C56" t="n">
-        <v>2.15472</v>
+        <v>2.17724</v>
       </c>
       <c r="D56" t="n">
-        <v>15.721</v>
+        <v>15.6448</v>
       </c>
       <c r="E56" t="n">
-        <v>2.44464</v>
+        <v>2.32627</v>
       </c>
       <c r="F56" t="n">
-        <v>2.73776</v>
+        <v>2.76289</v>
       </c>
     </row>
     <row r="57">
@@ -6179,19 +6179,19 @@
         <v>144311</v>
       </c>
       <c r="B57" t="n">
-        <v>3.4185</v>
+        <v>3.20344</v>
       </c>
       <c r="C57" t="n">
-        <v>2.27658</v>
+        <v>2.23558</v>
       </c>
       <c r="D57" t="n">
-        <v>16.1718</v>
+        <v>16.1129</v>
       </c>
       <c r="E57" t="n">
-        <v>2.50517</v>
+        <v>2.37028</v>
       </c>
       <c r="F57" t="n">
-        <v>2.82178</v>
+        <v>2.82348</v>
       </c>
     </row>
     <row r="58">
@@ -6199,19 +6199,19 @@
         <v>151499</v>
       </c>
       <c r="B58" t="n">
-        <v>3.58407</v>
+        <v>3.46146</v>
       </c>
       <c r="C58" t="n">
-        <v>2.38838</v>
+        <v>2.39471</v>
       </c>
       <c r="D58" t="n">
-        <v>16.5817</v>
+        <v>16.573</v>
       </c>
       <c r="E58" t="n">
-        <v>2.43603</v>
+        <v>2.49751</v>
       </c>
       <c r="F58" t="n">
-        <v>2.90368</v>
+        <v>2.84541</v>
       </c>
     </row>
     <row r="59">
@@ -6219,19 +6219,19 @@
         <v>159046</v>
       </c>
       <c r="B59" t="n">
-        <v>3.84508</v>
+        <v>3.71313</v>
       </c>
       <c r="C59" t="n">
-        <v>2.60984</v>
+        <v>2.60534</v>
       </c>
       <c r="D59" t="n">
-        <v>16.9973</v>
+        <v>16.9436</v>
       </c>
       <c r="E59" t="n">
-        <v>2.53849</v>
+        <v>2.55651</v>
       </c>
       <c r="F59" t="n">
-        <v>3.04065</v>
+        <v>2.96346</v>
       </c>
     </row>
     <row r="60">
@@ -6239,19 +6239,19 @@
         <v>166970</v>
       </c>
       <c r="B60" t="n">
-        <v>4.15777</v>
+        <v>4.03268</v>
       </c>
       <c r="C60" t="n">
-        <v>2.86476</v>
+        <v>3.0241</v>
       </c>
       <c r="D60" t="n">
-        <v>17.5171</v>
+        <v>17.4381</v>
       </c>
       <c r="E60" t="n">
-        <v>2.68865</v>
+        <v>2.73077</v>
       </c>
       <c r="F60" t="n">
-        <v>3.10182</v>
+        <v>3.0317</v>
       </c>
     </row>
     <row r="61">
@@ -6259,19 +6259,19 @@
         <v>175290</v>
       </c>
       <c r="B61" t="n">
-        <v>4.68413</v>
+        <v>4.46623</v>
       </c>
       <c r="C61" t="n">
-        <v>3.29406</v>
+        <v>3.4809</v>
       </c>
       <c r="D61" t="n">
-        <v>17.9367</v>
+        <v>17.8576</v>
       </c>
       <c r="E61" t="n">
-        <v>2.89971</v>
+        <v>2.91259</v>
       </c>
       <c r="F61" t="n">
-        <v>3.2781</v>
+        <v>3.21502</v>
       </c>
     </row>
     <row r="62">
@@ -6279,19 +6279,19 @@
         <v>184026</v>
       </c>
       <c r="B62" t="n">
-        <v>5.23035</v>
+        <v>5.15797</v>
       </c>
       <c r="C62" t="n">
-        <v>3.90688</v>
+        <v>4.3485</v>
       </c>
       <c r="D62" t="n">
-        <v>18.4634</v>
+        <v>18.3906</v>
       </c>
       <c r="E62" t="n">
-        <v>3.17337</v>
+        <v>3.23551</v>
       </c>
       <c r="F62" t="n">
-        <v>3.57407</v>
+        <v>3.48993</v>
       </c>
     </row>
     <row r="63">
@@ -6299,19 +6299,19 @@
         <v>193198</v>
       </c>
       <c r="B63" t="n">
-        <v>6.2915</v>
+        <v>6.19771</v>
       </c>
       <c r="C63" t="n">
-        <v>4.83892</v>
+        <v>5.41054</v>
       </c>
       <c r="D63" t="n">
-        <v>18.9072</v>
+        <v>18.9488</v>
       </c>
       <c r="E63" t="n">
-        <v>2.47967</v>
+        <v>2.53296</v>
       </c>
       <c r="F63" t="n">
-        <v>2.94178</v>
+        <v>2.92682</v>
       </c>
     </row>
     <row r="64">
@@ -6319,19 +6319,19 @@
         <v>202828</v>
       </c>
       <c r="B64" t="n">
-        <v>7.91829</v>
+        <v>7.78486</v>
       </c>
       <c r="C64" t="n">
-        <v>6.17162</v>
+        <v>7.00308</v>
       </c>
       <c r="D64" t="n">
-        <v>13.6774</v>
+        <v>13.1196</v>
       </c>
       <c r="E64" t="n">
-        <v>2.50526</v>
+        <v>2.54229</v>
       </c>
       <c r="F64" t="n">
-        <v>2.96552</v>
+        <v>2.99451</v>
       </c>
     </row>
     <row r="65">
@@ -6339,19 +6339,19 @@
         <v>212939</v>
       </c>
       <c r="B65" t="n">
-        <v>10.5211</v>
+        <v>10.5868</v>
       </c>
       <c r="C65" t="n">
-        <v>2.32334</v>
+        <v>2.32414</v>
       </c>
       <c r="D65" t="n">
-        <v>14.3383</v>
+        <v>13.6353</v>
       </c>
       <c r="E65" t="n">
-        <v>2.55245</v>
+        <v>2.55552</v>
       </c>
       <c r="F65" t="n">
-        <v>3.00961</v>
+        <v>3.03529</v>
       </c>
     </row>
     <row r="66">
@@ -6359,19 +6359,19 @@
         <v>223555</v>
       </c>
       <c r="B66" t="n">
-        <v>14.7064</v>
+        <v>14.8647</v>
       </c>
       <c r="C66" t="n">
-        <v>2.34169</v>
+        <v>2.35643</v>
       </c>
       <c r="D66" t="n">
-        <v>14.9438</v>
+        <v>14.3694</v>
       </c>
       <c r="E66" t="n">
-        <v>2.58611</v>
+        <v>2.58993</v>
       </c>
       <c r="F66" t="n">
-        <v>3.05099</v>
+        <v>3.08324</v>
       </c>
     </row>
     <row r="67">
@@ -6379,19 +6379,19 @@
         <v>234701</v>
       </c>
       <c r="B67" t="n">
-        <v>3.50456</v>
+        <v>3.41818</v>
       </c>
       <c r="C67" t="n">
-        <v>2.43475</v>
+        <v>2.38778</v>
       </c>
       <c r="D67" t="n">
-        <v>15.753</v>
+        <v>15.0483</v>
       </c>
       <c r="E67" t="n">
-        <v>2.57669</v>
+        <v>2.6322</v>
       </c>
       <c r="F67" t="n">
-        <v>3.10177</v>
+        <v>3.13929</v>
       </c>
     </row>
     <row r="68">
@@ -6399,19 +6399,19 @@
         <v>246404</v>
       </c>
       <c r="B68" t="n">
-        <v>3.57253</v>
+        <v>3.48337</v>
       </c>
       <c r="C68" t="n">
-        <v>2.44791</v>
+        <v>2.42869</v>
       </c>
       <c r="D68" t="n">
-        <v>16.5071</v>
+        <v>15.717</v>
       </c>
       <c r="E68" t="n">
-        <v>2.64106</v>
+        <v>2.66246</v>
       </c>
       <c r="F68" t="n">
-        <v>3.17337</v>
+        <v>3.19115</v>
       </c>
     </row>
     <row r="69">
@@ -6419,19 +6419,19 @@
         <v>258692</v>
       </c>
       <c r="B69" t="n">
-        <v>3.63572</v>
+        <v>3.55042</v>
       </c>
       <c r="C69" t="n">
-        <v>2.54347</v>
+        <v>2.4707</v>
       </c>
       <c r="D69" t="n">
-        <v>17.3084</v>
+        <v>16.52</v>
       </c>
       <c r="E69" t="n">
-        <v>2.65475</v>
+        <v>2.72583</v>
       </c>
       <c r="F69" t="n">
-        <v>3.23741</v>
+        <v>3.25809</v>
       </c>
     </row>
     <row r="70">
@@ -6439,19 +6439,19 @@
         <v>271594</v>
       </c>
       <c r="B70" t="n">
-        <v>3.74819</v>
+        <v>3.60149</v>
       </c>
       <c r="C70" t="n">
-        <v>2.59715</v>
+        <v>2.55174</v>
       </c>
       <c r="D70" t="n">
-        <v>18.3758</v>
+        <v>17.4477</v>
       </c>
       <c r="E70" t="n">
-        <v>2.72418</v>
+        <v>2.7699</v>
       </c>
       <c r="F70" t="n">
-        <v>3.29094</v>
+        <v>3.30701</v>
       </c>
     </row>
     <row r="71">
@@ -6459,19 +6459,19 @@
         <v>285141</v>
       </c>
       <c r="B71" t="n">
-        <v>3.8602</v>
+        <v>3.74756</v>
       </c>
       <c r="C71" t="n">
-        <v>2.67016</v>
+        <v>2.63824</v>
       </c>
       <c r="D71" t="n">
-        <v>19.4108</v>
+        <v>18.3708</v>
       </c>
       <c r="E71" t="n">
-        <v>2.79901</v>
+        <v>2.79443</v>
       </c>
       <c r="F71" t="n">
-        <v>3.39916</v>
+        <v>3.40548</v>
       </c>
     </row>
     <row r="72">
@@ -6479,19 +6479,19 @@
         <v>299365</v>
       </c>
       <c r="B72" t="n">
-        <v>4.00176</v>
+        <v>3.90648</v>
       </c>
       <c r="C72" t="n">
-        <v>2.83716</v>
+        <v>2.76083</v>
       </c>
       <c r="D72" t="n">
-        <v>20.5369</v>
+        <v>19.3222</v>
       </c>
       <c r="E72" t="n">
-        <v>2.87546</v>
+        <v>2.85893</v>
       </c>
       <c r="F72" t="n">
-        <v>3.50986</v>
+        <v>3.49773</v>
       </c>
     </row>
     <row r="73">
@@ -6499,19 +6499,19 @@
         <v>314300</v>
       </c>
       <c r="B73" t="n">
-        <v>4.22897</v>
+        <v>4.09136</v>
       </c>
       <c r="C73" t="n">
-        <v>2.99026</v>
+        <v>2.97836</v>
       </c>
       <c r="D73" t="n">
-        <v>21.807</v>
+        <v>20.5736</v>
       </c>
       <c r="E73" t="n">
-        <v>2.96732</v>
+        <v>2.95996</v>
       </c>
       <c r="F73" t="n">
-        <v>3.62769</v>
+        <v>3.60393</v>
       </c>
     </row>
     <row r="74">
@@ -6519,19 +6519,19 @@
         <v>329981</v>
       </c>
       <c r="B74" t="n">
-        <v>4.54127</v>
+        <v>4.38809</v>
       </c>
       <c r="C74" t="n">
-        <v>3.25383</v>
+        <v>3.26722</v>
       </c>
       <c r="D74" t="n">
-        <v>23.0756</v>
+        <v>21.8152</v>
       </c>
       <c r="E74" t="n">
-        <v>3.04796</v>
+        <v>3.06206</v>
       </c>
       <c r="F74" t="n">
-        <v>3.81072</v>
+        <v>3.74899</v>
       </c>
     </row>
     <row r="75">
@@ -6539,19 +6539,19 @@
         <v>346446</v>
       </c>
       <c r="B75" t="n">
-        <v>4.96891</v>
+        <v>4.85769</v>
       </c>
       <c r="C75" t="n">
-        <v>3.60288</v>
+        <v>3.73365</v>
       </c>
       <c r="D75" t="n">
-        <v>24.6914</v>
+        <v>23.3119</v>
       </c>
       <c r="E75" t="n">
-        <v>3.22323</v>
+        <v>3.24768</v>
       </c>
       <c r="F75" t="n">
-        <v>3.98597</v>
+        <v>3.88644</v>
       </c>
     </row>
     <row r="76">
@@ -6559,19 +6559,19 @@
         <v>363734</v>
       </c>
       <c r="B76" t="n">
-        <v>5.64253</v>
+        <v>5.45954</v>
       </c>
       <c r="C76" t="n">
-        <v>4.16528</v>
+        <v>4.48406</v>
       </c>
       <c r="D76" t="n">
-        <v>26.0847</v>
+        <v>24.5481</v>
       </c>
       <c r="E76" t="n">
-        <v>3.48892</v>
+        <v>3.53396</v>
       </c>
       <c r="F76" t="n">
-        <v>4.24681</v>
+        <v>4.11327</v>
       </c>
     </row>
     <row r="77">
@@ -6579,19 +6579,19 @@
         <v>381886</v>
       </c>
       <c r="B77" t="n">
-        <v>6.52185</v>
+        <v>6.40242</v>
       </c>
       <c r="C77" t="n">
-        <v>5.02864</v>
+        <v>5.58315</v>
       </c>
       <c r="D77" t="n">
-        <v>27.5955</v>
+        <v>26.1356</v>
       </c>
       <c r="E77" t="n">
-        <v>2.87996</v>
+        <v>2.84232</v>
       </c>
       <c r="F77" t="n">
-        <v>3.43779</v>
+        <v>3.36636</v>
       </c>
     </row>
     <row r="78">
@@ -6599,19 +6599,19 @@
         <v>400945</v>
       </c>
       <c r="B78" t="n">
-        <v>7.92556</v>
+        <v>7.82244</v>
       </c>
       <c r="C78" t="n">
-        <v>6.30838</v>
+        <v>7.03882</v>
       </c>
       <c r="D78" t="n">
-        <v>23.0457</v>
+        <v>23.1564</v>
       </c>
       <c r="E78" t="n">
-        <v>2.90317</v>
+        <v>2.92297</v>
       </c>
       <c r="F78" t="n">
-        <v>3.52508</v>
+        <v>3.40362</v>
       </c>
     </row>
     <row r="79">
@@ -6619,19 +6619,19 @@
         <v>420956</v>
       </c>
       <c r="B79" t="n">
-        <v>10.3858</v>
+        <v>10.2989</v>
       </c>
       <c r="C79" t="n">
-        <v>2.74117</v>
+        <v>2.65217</v>
       </c>
       <c r="D79" t="n">
-        <v>24.0939</v>
+        <v>24.5164</v>
       </c>
       <c r="E79" t="n">
-        <v>2.95306</v>
+        <v>2.95896</v>
       </c>
       <c r="F79" t="n">
-        <v>3.55489</v>
+        <v>3.47858</v>
       </c>
     </row>
     <row r="80">
@@ -6639,19 +6639,19 @@
         <v>441967</v>
       </c>
       <c r="B80" t="n">
-        <v>14.0482</v>
+        <v>14.39</v>
       </c>
       <c r="C80" t="n">
-        <v>2.77872</v>
+        <v>2.70476</v>
       </c>
       <c r="D80" t="n">
-        <v>25.6302</v>
+        <v>25.8852</v>
       </c>
       <c r="E80" t="n">
-        <v>3.03327</v>
+        <v>2.99693</v>
       </c>
       <c r="F80" t="n">
-        <v>3.64308</v>
+        <v>3.54964</v>
       </c>
     </row>
     <row r="81">
@@ -6659,19 +6659,19 @@
         <v>464028</v>
       </c>
       <c r="B81" t="n">
-        <v>4.10816</v>
+        <v>3.90838</v>
       </c>
       <c r="C81" t="n">
-        <v>2.85519</v>
+        <v>2.71639</v>
       </c>
       <c r="D81" t="n">
-        <v>26.9624</v>
+        <v>27.267</v>
       </c>
       <c r="E81" t="n">
-        <v>3.02967</v>
+        <v>3.00063</v>
       </c>
       <c r="F81" t="n">
-        <v>3.82857</v>
+        <v>3.59174</v>
       </c>
     </row>
     <row r="82">
@@ -6679,19 +6679,19 @@
         <v>487192</v>
       </c>
       <c r="B82" t="n">
-        <v>4.21389</v>
+        <v>3.97918</v>
       </c>
       <c r="C82" t="n">
-        <v>2.91733</v>
+        <v>2.79716</v>
       </c>
       <c r="D82" t="n">
-        <v>28.3881</v>
+        <v>28.6697</v>
       </c>
       <c r="E82" t="n">
-        <v>3.06586</v>
+        <v>3.0518</v>
       </c>
       <c r="F82" t="n">
-        <v>3.9131</v>
+        <v>3.67081</v>
       </c>
     </row>
     <row r="83">
@@ -6699,19 +6699,19 @@
         <v>511514</v>
       </c>
       <c r="B83" t="n">
-        <v>4.38228</v>
+        <v>4.06547</v>
       </c>
       <c r="C83" t="n">
-        <v>3.01146</v>
+        <v>2.85922</v>
       </c>
       <c r="D83" t="n">
-        <v>29.822</v>
+        <v>30.1204</v>
       </c>
       <c r="E83" t="n">
-        <v>3.17063</v>
+        <v>3.09441</v>
       </c>
       <c r="F83" t="n">
-        <v>4.0324</v>
+        <v>3.77008</v>
       </c>
     </row>
     <row r="84">
@@ -6719,19 +6719,19 @@
         <v>537052</v>
       </c>
       <c r="B84" t="n">
-        <v>4.58343</v>
+        <v>4.16968</v>
       </c>
       <c r="C84" t="n">
-        <v>3.19732</v>
+        <v>2.93993</v>
       </c>
       <c r="D84" t="n">
-        <v>31.3489</v>
+        <v>31.6366</v>
       </c>
       <c r="E84" t="n">
-        <v>3.25972</v>
+        <v>3.13941</v>
       </c>
       <c r="F84" t="n">
-        <v>4.2543</v>
+        <v>3.85974</v>
       </c>
     </row>
     <row r="85">
@@ -6739,19 +6739,19 @@
         <v>563866</v>
       </c>
       <c r="B85" t="n">
-        <v>4.79944</v>
+        <v>4.32619</v>
       </c>
       <c r="C85" t="n">
-        <v>3.35736</v>
+        <v>3.05513</v>
       </c>
       <c r="D85" t="n">
-        <v>32.9256</v>
+        <v>33.1696</v>
       </c>
       <c r="E85" t="n">
-        <v>3.32758</v>
+        <v>3.18663</v>
       </c>
       <c r="F85" t="n">
-        <v>4.38296</v>
+        <v>4.00119</v>
       </c>
     </row>
     <row r="86">
@@ -6759,19 +6759,19 @@
         <v>592020</v>
       </c>
       <c r="B86" t="n">
-        <v>5.11822</v>
+        <v>4.49286</v>
       </c>
       <c r="C86" t="n">
-        <v>3.58913</v>
+        <v>3.2823</v>
       </c>
       <c r="D86" t="n">
-        <v>34.5155</v>
+        <v>34.6815</v>
       </c>
       <c r="E86" t="n">
-        <v>3.4787</v>
+        <v>3.25136</v>
       </c>
       <c r="F86" t="n">
-        <v>4.68994</v>
+        <v>4.21198</v>
       </c>
     </row>
     <row r="87">
@@ -6779,19 +6779,19 @@
         <v>621581</v>
       </c>
       <c r="B87" t="n">
-        <v>5.51979</v>
+        <v>4.84441</v>
       </c>
       <c r="C87" t="n">
-        <v>3.85493</v>
+        <v>3.45831</v>
       </c>
       <c r="D87" t="n">
-        <v>36.1585</v>
+        <v>36.275</v>
       </c>
       <c r="E87" t="n">
-        <v>3.73964</v>
+        <v>3.34566</v>
       </c>
       <c r="F87" t="n">
-        <v>5.22022</v>
+        <v>4.40804</v>
       </c>
     </row>
     <row r="88">
@@ -6799,19 +6799,19 @@
         <v>652620</v>
       </c>
       <c r="B88" t="n">
-        <v>6.04471</v>
+        <v>5.22392</v>
       </c>
       <c r="C88" t="n">
-        <v>4.15963</v>
+        <v>3.86943</v>
       </c>
       <c r="D88" t="n">
-        <v>37.7407</v>
+        <v>38.0129</v>
       </c>
       <c r="E88" t="n">
-        <v>3.91475</v>
+        <v>3.57552</v>
       </c>
       <c r="F88" t="n">
-        <v>5.62457</v>
+        <v>4.73179</v>
       </c>
     </row>
     <row r="89">
@@ -6819,19 +6819,19 @@
         <v>685210</v>
       </c>
       <c r="B89" t="n">
-        <v>6.63766</v>
+        <v>5.76769</v>
       </c>
       <c r="C89" t="n">
-        <v>4.64765</v>
+        <v>4.34818</v>
       </c>
       <c r="D89" t="n">
-        <v>39.5953</v>
+        <v>39.7818</v>
       </c>
       <c r="E89" t="n">
-        <v>4.25104</v>
+        <v>3.79813</v>
       </c>
       <c r="F89" t="n">
-        <v>6.18339</v>
+        <v>5.09136</v>
       </c>
     </row>
     <row r="90">
@@ -6839,19 +6839,19 @@
         <v>719429</v>
       </c>
       <c r="B90" t="n">
-        <v>7.38072</v>
+        <v>6.53636</v>
       </c>
       <c r="C90" t="n">
-        <v>5.22968</v>
+        <v>5.10245</v>
       </c>
       <c r="D90" t="n">
-        <v>41.4514</v>
+        <v>41.4809</v>
       </c>
       <c r="E90" t="n">
-        <v>4.64194</v>
+        <v>4.0882</v>
       </c>
       <c r="F90" t="n">
-        <v>6.75601</v>
+        <v>5.79073</v>
       </c>
     </row>
     <row r="91">
@@ -6859,19 +6859,19 @@
         <v>755358</v>
       </c>
       <c r="B91" t="n">
-        <v>8.51628</v>
+        <v>7.6104</v>
       </c>
       <c r="C91" t="n">
-        <v>6.11894</v>
+        <v>6.20288</v>
       </c>
       <c r="D91" t="n">
-        <v>43.4228</v>
+        <v>43.3725</v>
       </c>
       <c r="E91" t="n">
-        <v>3.31009</v>
+        <v>3.10686</v>
       </c>
       <c r="F91" t="n">
-        <v>4.64578</v>
+        <v>4.02873</v>
       </c>
     </row>
     <row r="92">
@@ -6879,19 +6879,19 @@
         <v>793083</v>
       </c>
       <c r="B92" t="n">
-        <v>9.990119999999999</v>
+        <v>9.10337</v>
       </c>
       <c r="C92" t="n">
-        <v>7.31434</v>
+        <v>7.73459</v>
       </c>
       <c r="D92" t="n">
-        <v>35.6025</v>
+        <v>35.616</v>
       </c>
       <c r="E92" t="n">
-        <v>3.54263</v>
+        <v>3.16896</v>
       </c>
       <c r="F92" t="n">
-        <v>4.96324</v>
+        <v>4.23298</v>
       </c>
     </row>
     <row r="93">
@@ -6899,19 +6899,19 @@
         <v>832694</v>
       </c>
       <c r="B93" t="n">
-        <v>12.4518</v>
+        <v>11.492</v>
       </c>
       <c r="C93" t="n">
-        <v>9.2105</v>
+        <v>9.88874</v>
       </c>
       <c r="D93" t="n">
-        <v>36.7985</v>
+        <v>36.8452</v>
       </c>
       <c r="E93" t="n">
-        <v>3.76308</v>
+        <v>3.26199</v>
       </c>
       <c r="F93" t="n">
-        <v>5.26186</v>
+        <v>4.49182</v>
       </c>
     </row>
     <row r="94">
@@ -6919,19 +6919,19 @@
         <v>874285</v>
       </c>
       <c r="B94" t="n">
-        <v>15.802</v>
+        <v>15.1691</v>
       </c>
       <c r="C94" t="n">
-        <v>3.77486</v>
+        <v>3.21387</v>
       </c>
       <c r="D94" t="n">
-        <v>38.0456</v>
+        <v>38.054</v>
       </c>
       <c r="E94" t="n">
-        <v>3.90217</v>
+        <v>3.35055</v>
       </c>
       <c r="F94" t="n">
-        <v>5.62264</v>
+        <v>4.85069</v>
       </c>
     </row>
     <row r="95">
@@ -6939,19 +6939,19 @@
         <v>917955</v>
       </c>
       <c r="B95" t="n">
-        <v>5.93881</v>
+        <v>5.0482</v>
       </c>
       <c r="C95" t="n">
-        <v>3.98382</v>
+        <v>3.42882</v>
       </c>
       <c r="D95" t="n">
-        <v>39.2782</v>
+        <v>39.3243</v>
       </c>
       <c r="E95" t="n">
-        <v>4.15201</v>
+        <v>3.5004</v>
       </c>
       <c r="F95" t="n">
-        <v>6.01889</v>
+        <v>5.25099</v>
       </c>
     </row>
     <row r="96">
@@ -6959,19 +6959,19 @@
         <v>963808</v>
       </c>
       <c r="B96" t="n">
-        <v>6.2548</v>
+        <v>5.43355</v>
       </c>
       <c r="C96" t="n">
-        <v>4.13774</v>
+        <v>3.59994</v>
       </c>
       <c r="D96" t="n">
-        <v>40.6082</v>
+        <v>40.5962</v>
       </c>
       <c r="E96" t="n">
-        <v>4.30566</v>
+        <v>3.65844</v>
       </c>
       <c r="F96" t="n">
-        <v>6.37994</v>
+        <v>5.68092</v>
       </c>
     </row>
     <row r="97">
@@ -6979,19 +6979,19 @@
         <v>1011953</v>
       </c>
       <c r="B97" t="n">
-        <v>6.47284</v>
+        <v>5.79575</v>
       </c>
       <c r="C97" t="n">
-        <v>4.27039</v>
+        <v>3.82449</v>
       </c>
       <c r="D97" t="n">
-        <v>41.9832</v>
+        <v>41.9257</v>
       </c>
       <c r="E97" t="n">
-        <v>4.4697</v>
+        <v>3.80407</v>
       </c>
       <c r="F97" t="n">
-        <v>6.69895</v>
+        <v>6.17021</v>
       </c>
     </row>
     <row r="98">
@@ -6999,19 +6999,19 @@
         <v>1062505</v>
       </c>
       <c r="B98" t="n">
-        <v>6.73628</v>
+        <v>6.1569</v>
       </c>
       <c r="C98" t="n">
-        <v>4.45559</v>
+        <v>4.11042</v>
       </c>
       <c r="D98" t="n">
-        <v>43.3374</v>
+        <v>43.3045</v>
       </c>
       <c r="E98" t="n">
-        <v>4.62885</v>
+        <v>4.05163</v>
       </c>
       <c r="F98" t="n">
-        <v>6.84635</v>
+        <v>6.74748</v>
       </c>
     </row>
     <row r="99">
@@ -7019,19 +7019,19 @@
         <v>1115584</v>
       </c>
       <c r="B99" t="n">
-        <v>6.94892</v>
+        <v>6.7221</v>
       </c>
       <c r="C99" t="n">
-        <v>4.64163</v>
+        <v>4.44415</v>
       </c>
       <c r="D99" t="n">
-        <v>44.7912</v>
+        <v>44.6924</v>
       </c>
       <c r="E99" t="n">
-        <v>4.74577</v>
+        <v>4.36933</v>
       </c>
       <c r="F99" t="n">
-        <v>7.04907</v>
+        <v>7.4075</v>
       </c>
     </row>
     <row r="100">
@@ -7039,19 +7039,19 @@
         <v>1171316</v>
       </c>
       <c r="B100" t="n">
-        <v>7.25896</v>
+        <v>7.19741</v>
       </c>
       <c r="C100" t="n">
-        <v>4.84852</v>
+        <v>4.80186</v>
       </c>
       <c r="D100" t="n">
-        <v>46.2481</v>
+        <v>46.2039</v>
       </c>
       <c r="E100" t="n">
-        <v>4.9743</v>
+        <v>4.64752</v>
       </c>
       <c r="F100" t="n">
-        <v>7.37737</v>
+        <v>8.08536</v>
       </c>
     </row>
     <row r="101">
@@ -7059,19 +7059,19 @@
         <v>1229834</v>
       </c>
       <c r="B101" t="n">
-        <v>7.62397</v>
+        <v>7.8024</v>
       </c>
       <c r="C101" t="n">
-        <v>5.06724</v>
+        <v>5.21099</v>
       </c>
       <c r="D101" t="n">
-        <v>47.7999</v>
+        <v>47.6392</v>
       </c>
       <c r="E101" t="n">
-        <v>5.15036</v>
+        <v>5.01045</v>
       </c>
       <c r="F101" t="n">
-        <v>8.07888</v>
+        <v>8.77928</v>
       </c>
     </row>
     <row r="102">
@@ -7079,19 +7079,19 @@
         <v>1291277</v>
       </c>
       <c r="B102" t="n">
-        <v>8.064539999999999</v>
+        <v>8.503740000000001</v>
       </c>
       <c r="C102" t="n">
-        <v>5.40262</v>
+        <v>5.74309</v>
       </c>
       <c r="D102" t="n">
-        <v>49.4446</v>
+        <v>49.2457</v>
       </c>
       <c r="E102" t="n">
-        <v>5.37916</v>
+        <v>5.41434</v>
       </c>
       <c r="F102" t="n">
-        <v>8.409890000000001</v>
+        <v>9.49296</v>
       </c>
     </row>
     <row r="103">
@@ -7099,19 +7099,19 @@
         <v>1355792</v>
       </c>
       <c r="B103" t="n">
-        <v>8.65949</v>
+        <v>9.301869999999999</v>
       </c>
       <c r="C103" t="n">
-        <v>5.86074</v>
+        <v>6.34984</v>
       </c>
       <c r="D103" t="n">
-        <v>51.1349</v>
+        <v>50.9721</v>
       </c>
       <c r="E103" t="n">
-        <v>5.7045</v>
+        <v>5.92378</v>
       </c>
       <c r="F103" t="n">
-        <v>8.92268</v>
+        <v>10.1694</v>
       </c>
     </row>
     <row r="104">
@@ -7119,19 +7119,19 @@
         <v>1423532</v>
       </c>
       <c r="B104" t="n">
-        <v>9.39644</v>
+        <v>10.1622</v>
       </c>
       <c r="C104" t="n">
-        <v>6.42717</v>
+        <v>7.10594</v>
       </c>
       <c r="D104" t="n">
-        <v>52.6911</v>
+        <v>52.6964</v>
       </c>
       <c r="E104" t="n">
-        <v>6.00964</v>
+        <v>6.399</v>
       </c>
       <c r="F104" t="n">
-        <v>9.73659</v>
+        <v>10.8859</v>
       </c>
     </row>
     <row r="105">
@@ -7139,19 +7139,19 @@
         <v>1494659</v>
       </c>
       <c r="B105" t="n">
-        <v>10.5135</v>
+        <v>11.2358</v>
       </c>
       <c r="C105" t="n">
-        <v>7.28653</v>
+        <v>8.08835</v>
       </c>
       <c r="D105" t="n">
-        <v>54.5201</v>
+        <v>54.4304</v>
       </c>
       <c r="E105" t="n">
-        <v>4.44754</v>
+        <v>4.58901</v>
       </c>
       <c r="F105" t="n">
-        <v>6.4198</v>
+        <v>7.29496</v>
       </c>
     </row>
     <row r="106">
@@ -7159,19 +7159,19 @@
         <v>1569342</v>
       </c>
       <c r="B106" t="n">
-        <v>11.9832</v>
+        <v>12.5435</v>
       </c>
       <c r="C106" t="n">
-        <v>8.42535</v>
+        <v>9.458740000000001</v>
       </c>
       <c r="D106" t="n">
-        <v>56.4614</v>
+        <v>56.2687</v>
       </c>
       <c r="E106" t="n">
-        <v>4.55985</v>
+        <v>4.83878</v>
       </c>
       <c r="F106" t="n">
-        <v>6.73155</v>
+        <v>7.79979</v>
       </c>
     </row>
     <row r="107">
@@ -7179,19 +7179,19 @@
         <v>1647759</v>
       </c>
       <c r="B107" t="n">
-        <v>14.2873</v>
+        <v>14.4488</v>
       </c>
       <c r="C107" t="n">
-        <v>10.2728</v>
+        <v>11.3193</v>
       </c>
       <c r="D107" t="n">
-        <v>42.8553</v>
+        <v>42.9809</v>
       </c>
       <c r="E107" t="n">
-        <v>4.5079</v>
+        <v>5.04841</v>
       </c>
       <c r="F107" t="n">
-        <v>7.0375</v>
+        <v>8.16901</v>
       </c>
     </row>
     <row r="108">
@@ -7199,19 +7199,19 @@
         <v>1730096</v>
       </c>
       <c r="B108" t="n">
-        <v>17.221</v>
+        <v>17.421</v>
       </c>
       <c r="C108" t="n">
-        <v>4.52918</v>
+        <v>5.09913</v>
       </c>
       <c r="D108" t="n">
-        <v>44.0955</v>
+        <v>44.1362</v>
       </c>
       <c r="E108" t="n">
-        <v>4.77771</v>
+        <v>5.25619</v>
       </c>
       <c r="F108" t="n">
-        <v>7.37835</v>
+        <v>8.538919999999999</v>
       </c>
     </row>
     <row r="109">
@@ -7219,19 +7219,19 @@
         <v>1816549</v>
       </c>
       <c r="B109" t="n">
-        <v>22.0377</v>
+        <v>22.1876</v>
       </c>
       <c r="C109" t="n">
-        <v>4.74841</v>
+        <v>5.28007</v>
       </c>
       <c r="D109" t="n">
-        <v>45.314</v>
+        <v>45.341</v>
       </c>
       <c r="E109" t="n">
-        <v>4.91241</v>
+        <v>5.49826</v>
       </c>
       <c r="F109" t="n">
-        <v>7.77031</v>
+        <v>8.862439999999999</v>
       </c>
     </row>
     <row r="110">
@@ -7239,19 +7239,19 @@
         <v>1907324</v>
       </c>
       <c r="B110" t="n">
-        <v>7.55634</v>
+        <v>8.48645</v>
       </c>
       <c r="C110" t="n">
-        <v>4.8821</v>
+        <v>5.47467</v>
       </c>
       <c r="D110" t="n">
-        <v>46.59</v>
+        <v>46.5874</v>
       </c>
       <c r="E110" t="n">
-        <v>5.05718</v>
+        <v>5.70495</v>
       </c>
       <c r="F110" t="n">
-        <v>8.29059</v>
+        <v>9.18797</v>
       </c>
     </row>
     <row r="111">
@@ -7259,19 +7259,19 @@
         <v>2002637</v>
       </c>
       <c r="B111" t="n">
-        <v>8.05837</v>
+        <v>8.79965</v>
       </c>
       <c r="C111" t="n">
-        <v>5.20996</v>
+        <v>5.64747</v>
       </c>
       <c r="D111" t="n">
-        <v>47.8536</v>
+        <v>47.8604</v>
       </c>
       <c r="E111" t="n">
-        <v>5.28339</v>
+        <v>5.88584</v>
       </c>
       <c r="F111" t="n">
-        <v>8.96504</v>
+        <v>9.51346</v>
       </c>
     </row>
     <row r="112">
@@ -7279,19 +7279,19 @@
         <v>2102715</v>
       </c>
       <c r="B112" t="n">
-        <v>8.630839999999999</v>
+        <v>9.07748</v>
       </c>
       <c r="C112" t="n">
-        <v>5.55469</v>
+        <v>5.84766</v>
       </c>
       <c r="D112" t="n">
-        <v>49.1413</v>
+        <v>49.179</v>
       </c>
       <c r="E112" t="n">
-        <v>5.6424</v>
+        <v>6.15968</v>
       </c>
       <c r="F112" t="n">
-        <v>9.527139999999999</v>
+        <v>9.820320000000001</v>
       </c>
     </row>
     <row r="113">
@@ -7299,19 +7299,19 @@
         <v>2207796</v>
       </c>
       <c r="B113" t="n">
-        <v>9.11758</v>
+        <v>9.347009999999999</v>
       </c>
       <c r="C113" t="n">
-        <v>5.87843</v>
+        <v>6.05466</v>
       </c>
       <c r="D113" t="n">
-        <v>50.5533</v>
+        <v>50.4965</v>
       </c>
       <c r="E113" t="n">
-        <v>5.99747</v>
+        <v>6.32197</v>
       </c>
       <c r="F113" t="n">
-        <v>10.0496</v>
+        <v>10.1552</v>
       </c>
     </row>
     <row r="114">
@@ -7319,19 +7319,19 @@
         <v>2318131</v>
       </c>
       <c r="B114" t="n">
-        <v>9.516299999999999</v>
+        <v>9.67088</v>
       </c>
       <c r="C114" t="n">
-        <v>6.18519</v>
+        <v>6.28102</v>
       </c>
       <c r="D114" t="n">
-        <v>51.9444</v>
+        <v>51.911</v>
       </c>
       <c r="E114" t="n">
-        <v>6.30674</v>
+        <v>6.52627</v>
       </c>
       <c r="F114" t="n">
-        <v>10.4529</v>
+        <v>10.4928</v>
       </c>
     </row>
     <row r="115">
@@ -7339,19 +7339,19 @@
         <v>2433982</v>
       </c>
       <c r="B115" t="n">
-        <v>9.9337</v>
+        <v>10.03</v>
       </c>
       <c r="C115" t="n">
-        <v>6.47222</v>
+        <v>6.54596</v>
       </c>
       <c r="D115" t="n">
-        <v>53.4331</v>
+        <v>53.3551</v>
       </c>
       <c r="E115" t="n">
-        <v>6.58809</v>
+        <v>6.76611</v>
       </c>
       <c r="F115" t="n">
-        <v>10.8705</v>
+        <v>10.8341</v>
       </c>
     </row>
     <row r="116">
@@ -7359,19 +7359,19 @@
         <v>2555625</v>
       </c>
       <c r="B116" t="n">
-        <v>10.4136</v>
+        <v>10.473</v>
       </c>
       <c r="C116" t="n">
-        <v>6.83482</v>
+        <v>6.89318</v>
       </c>
       <c r="D116" t="n">
-        <v>55.0165</v>
+        <v>54.8943</v>
       </c>
       <c r="E116" t="n">
-        <v>6.90686</v>
+        <v>6.99571</v>
       </c>
       <c r="F116" t="n">
-        <v>11.317</v>
+        <v>11.3266</v>
       </c>
     </row>
     <row r="117">
@@ -7379,19 +7379,19 @@
         <v>2683350</v>
       </c>
       <c r="B117" t="n">
-        <v>10.9533</v>
+        <v>10.9741</v>
       </c>
       <c r="C117" t="n">
-        <v>7.25709</v>
+        <v>7.32654</v>
       </c>
       <c r="D117" t="n">
-        <v>56.6626</v>
+        <v>56.5386</v>
       </c>
       <c r="E117" t="n">
-        <v>7.23548</v>
+        <v>7.28864</v>
       </c>
       <c r="F117" t="n">
-        <v>11.8083</v>
+        <v>11.7699</v>
       </c>
     </row>
     <row r="118">
@@ -7399,19 +7399,19 @@
         <v>2817461</v>
       </c>
       <c r="B118" t="n">
-        <v>11.6161</v>
+        <v>11.6019</v>
       </c>
       <c r="C118" t="n">
-        <v>7.80291</v>
+        <v>7.92195</v>
       </c>
       <c r="D118" t="n">
-        <v>58.2893</v>
+        <v>58.2105</v>
       </c>
       <c r="E118" t="n">
-        <v>7.62996</v>
+        <v>7.63175</v>
       </c>
       <c r="F118" t="n">
-        <v>12.4018</v>
+        <v>12.3353</v>
       </c>
     </row>
     <row r="119">
@@ -7419,19 +7419,19 @@
         <v>2958277</v>
       </c>
       <c r="B119" t="n">
-        <v>12.5193</v>
+        <v>12.4909</v>
       </c>
       <c r="C119" t="n">
-        <v>8.53308</v>
+        <v>8.758839999999999</v>
       </c>
       <c r="D119" t="n">
-        <v>60.104</v>
+        <v>60.0187</v>
       </c>
       <c r="E119" t="n">
-        <v>6.39563</v>
+        <v>6.26765</v>
       </c>
       <c r="F119" t="n">
-        <v>8.893190000000001</v>
+        <v>9.42792</v>
       </c>
     </row>
     <row r="120">
@@ -7439,19 +7439,19 @@
         <v>3106133</v>
       </c>
       <c r="B120" t="n">
-        <v>13.7543</v>
+        <v>13.6892</v>
       </c>
       <c r="C120" t="n">
-        <v>9.559559999999999</v>
+        <v>9.968590000000001</v>
       </c>
       <c r="D120" t="n">
-        <v>62.0305</v>
+        <v>61.9227</v>
       </c>
       <c r="E120" t="n">
-        <v>6.74417</v>
+        <v>6.79125</v>
       </c>
       <c r="F120" t="n">
-        <v>9.597020000000001</v>
+        <v>10.1841</v>
       </c>
     </row>
     <row r="121">
@@ -7459,19 +7459,19 @@
         <v>3261381</v>
       </c>
       <c r="B121" t="n">
-        <v>15.5187</v>
+        <v>15.3856</v>
       </c>
       <c r="C121" t="n">
-        <v>11.0729</v>
+        <v>11.7073</v>
       </c>
       <c r="D121" t="n">
-        <v>45.9864</v>
+        <v>46.1019</v>
       </c>
       <c r="E121" t="n">
-        <v>6.84287</v>
+        <v>6.61597</v>
       </c>
       <c r="F121" t="n">
-        <v>10.3859</v>
+        <v>10.0644</v>
       </c>
     </row>
     <row r="122">
@@ -7479,19 +7479,19 @@
         <v>3424391</v>
       </c>
       <c r="B122" t="n">
-        <v>18.201</v>
+        <v>18.1387</v>
       </c>
       <c r="C122" t="n">
-        <v>6.38264</v>
+        <v>6.20435</v>
       </c>
       <c r="D122" t="n">
-        <v>47.1829</v>
+        <v>47.341</v>
       </c>
       <c r="E122" t="n">
-        <v>6.86994</v>
+        <v>6.4473</v>
       </c>
       <c r="F122" t="n">
-        <v>10.3691</v>
+        <v>9.856999999999999</v>
       </c>
     </row>
     <row r="123">
@@ -7499,19 +7499,19 @@
         <v>3595551</v>
       </c>
       <c r="B123" t="n">
-        <v>22.2919</v>
+        <v>22.1339</v>
       </c>
       <c r="C123" t="n">
-        <v>6.53982</v>
+        <v>6.35743</v>
       </c>
       <c r="D123" t="n">
-        <v>48.1535</v>
+        <v>48.5764</v>
       </c>
       <c r="E123" t="n">
-        <v>7.13205</v>
+        <v>6.73308</v>
       </c>
       <c r="F123" t="n">
-        <v>10.4086</v>
+        <v>10.4174</v>
       </c>
     </row>
     <row r="124">
@@ -7519,19 +7519,19 @@
         <v>3775269</v>
       </c>
       <c r="B124" t="n">
-        <v>9.300509999999999</v>
+        <v>9.781560000000001</v>
       </c>
       <c r="C124" t="n">
-        <v>6.48788</v>
+        <v>6.33439</v>
       </c>
       <c r="D124" t="n">
-        <v>49.6896</v>
+        <v>49.7127</v>
       </c>
       <c r="E124" t="n">
-        <v>7.15297</v>
+        <v>6.93258</v>
       </c>
       <c r="F124" t="n">
-        <v>10.8788</v>
+        <v>10.8008</v>
       </c>
     </row>
     <row r="125">
@@ -7539,19 +7539,19 @@
         <v>3963972</v>
       </c>
       <c r="B125" t="n">
-        <v>10.0697</v>
+        <v>9.984109999999999</v>
       </c>
       <c r="C125" t="n">
-        <v>6.98539</v>
+        <v>6.64715</v>
       </c>
       <c r="D125" t="n">
-        <v>50.9614</v>
+        <v>51.0004</v>
       </c>
       <c r="E125" t="n">
-        <v>7.17325</v>
+        <v>7.28425</v>
       </c>
       <c r="F125" t="n">
-        <v>11.0873</v>
+        <v>11.2769</v>
       </c>
     </row>
     <row r="126">
@@ -7559,19 +7559,19 @@
         <v>4162110</v>
       </c>
       <c r="B126" t="n">
-        <v>10.2085</v>
+        <v>10.1893</v>
       </c>
       <c r="C126" t="n">
-        <v>6.93299</v>
+        <v>7.13778</v>
       </c>
       <c r="D126" t="n">
-        <v>52.3438</v>
+        <v>52.3613</v>
       </c>
       <c r="E126" t="n">
-        <v>7.44948</v>
+        <v>7.36366</v>
       </c>
       <c r="F126" t="n">
-        <v>11.5256</v>
+        <v>11.4449</v>
       </c>
     </row>
     <row r="127">
@@ -7579,19 +7579,19 @@
         <v>4370154</v>
       </c>
       <c r="B127" t="n">
-        <v>10.6477</v>
+        <v>10.3937</v>
       </c>
       <c r="C127" t="n">
-        <v>6.84692</v>
+        <v>6.82203</v>
       </c>
       <c r="D127" t="n">
-        <v>53.6989</v>
+        <v>53.7176</v>
       </c>
       <c r="E127" t="n">
-        <v>7.55281</v>
+        <v>7.47209</v>
       </c>
       <c r="F127" t="n">
-        <v>11.7205</v>
+        <v>11.8059</v>
       </c>
     </row>
     <row r="128">
@@ -7599,19 +7599,19 @@
         <v>4588600</v>
       </c>
       <c r="B128" t="n">
-        <v>10.7654</v>
+        <v>10.608</v>
       </c>
       <c r="C128" t="n">
-        <v>7.21672</v>
+        <v>7.09963</v>
       </c>
       <c r="D128" t="n">
-        <v>55.0849</v>
+        <v>55.1459</v>
       </c>
       <c r="E128" t="n">
-        <v>7.83366</v>
+        <v>7.58399</v>
       </c>
       <c r="F128" t="n">
-        <v>12.2474</v>
+        <v>12.0154</v>
       </c>
     </row>
     <row r="129">
@@ -7619,19 +7619,19 @@
         <v>4817968</v>
       </c>
       <c r="B129" t="n">
-        <v>11.2327</v>
+        <v>10.928</v>
       </c>
       <c r="C129" t="n">
-        <v>7.35734</v>
+        <v>7.22601</v>
       </c>
       <c r="D129" t="n">
-        <v>56.5918</v>
+        <v>56.6474</v>
       </c>
       <c r="E129" t="n">
-        <v>7.96014</v>
+        <v>7.82924</v>
       </c>
       <c r="F129" t="n">
-        <v>12.5561</v>
+        <v>12.411</v>
       </c>
     </row>
     <row r="130">
@@ -7639,19 +7639,19 @@
         <v>5058804</v>
       </c>
       <c r="B130" t="n">
-        <v>11.5886</v>
+        <v>11.4088</v>
       </c>
       <c r="C130" t="n">
-        <v>7.67289</v>
+        <v>7.77323</v>
       </c>
       <c r="D130" t="n">
-        <v>57.9435</v>
+        <v>58.133</v>
       </c>
       <c r="E130" t="n">
-        <v>8.17784</v>
+        <v>8.05838</v>
       </c>
       <c r="F130" t="n">
-        <v>12.9954</v>
+        <v>12.78</v>
       </c>
     </row>
     <row r="131">
@@ -7659,19 +7659,19 @@
         <v>5311681</v>
       </c>
       <c r="B131" t="n">
-        <v>12.0547</v>
+        <v>11.4793</v>
       </c>
       <c r="C131" t="n">
-        <v>8.16807</v>
+        <v>8.01839</v>
       </c>
       <c r="D131" t="n">
-        <v>59.7596</v>
+        <v>59.7671</v>
       </c>
       <c r="E131" t="n">
-        <v>8.415229999999999</v>
+        <v>8.390129999999999</v>
       </c>
       <c r="F131" t="n">
-        <v>13.3687</v>
+        <v>13.1452</v>
       </c>
     </row>
     <row r="132">
@@ -7679,19 +7679,19 @@
         <v>5577201</v>
       </c>
       <c r="B132" t="n">
-        <v>12.5026</v>
+        <v>12.4329</v>
       </c>
       <c r="C132" t="n">
-        <v>8.48597</v>
+        <v>8.425520000000001</v>
       </c>
       <c r="D132" t="n">
-        <v>61.44</v>
+        <v>61.4554</v>
       </c>
       <c r="E132" t="n">
-        <v>8.66023</v>
+        <v>8.85754</v>
       </c>
       <c r="F132" t="n">
-        <v>13.8812</v>
+        <v>14.055</v>
       </c>
     </row>
     <row r="133">
@@ -7699,19 +7699,19 @@
         <v>5855997</v>
       </c>
       <c r="B133" t="n">
-        <v>13.3417</v>
+        <v>13.3346</v>
       </c>
       <c r="C133" t="n">
-        <v>9.10514</v>
+        <v>9.2262</v>
       </c>
       <c r="D133" t="n">
-        <v>63.2431</v>
+        <v>63.2107</v>
       </c>
       <c r="E133" t="n">
-        <v>9.17961</v>
+        <v>9.254910000000001</v>
       </c>
       <c r="F133" t="n">
-        <v>15.163</v>
+        <v>14.7106</v>
       </c>
     </row>
     <row r="134">
@@ -7719,19 +7719,19 @@
         <v>6148732</v>
       </c>
       <c r="B134" t="n">
-        <v>14.6569</v>
+        <v>14.4313</v>
       </c>
       <c r="C134" t="n">
-        <v>10.0551</v>
+        <v>10.438</v>
       </c>
       <c r="D134" t="n">
-        <v>65.21169999999999</v>
+        <v>64.95180000000001</v>
       </c>
       <c r="E134" t="n">
-        <v>12.34</v>
+        <v>12.6439</v>
       </c>
       <c r="F134" t="n">
-        <v>16.3947</v>
+        <v>16.0597</v>
       </c>
     </row>
     <row r="135">
@@ -7739,19 +7739,19 @@
         <v>6456103</v>
       </c>
       <c r="B135" t="n">
-        <v>16.1247</v>
+        <v>16.0911</v>
       </c>
       <c r="C135" t="n">
-        <v>11.4468</v>
+        <v>11.9887</v>
       </c>
       <c r="D135" t="n">
-        <v>47.7591</v>
+        <v>47.8869</v>
       </c>
       <c r="E135" t="n">
-        <v>12.7357</v>
+        <v>12.7639</v>
       </c>
       <c r="F135" t="n">
-        <v>16.3531</v>
+        <v>16.4921</v>
       </c>
     </row>
     <row r="136">
@@ -7759,19 +7759,19 @@
         <v>6778842</v>
       </c>
       <c r="B136" t="n">
-        <v>18.9694</v>
+        <v>18.3464</v>
       </c>
       <c r="C136" t="n">
-        <v>12.5341</v>
+        <v>12.3524</v>
       </c>
       <c r="D136" t="n">
-        <v>48.9695</v>
+        <v>49.0545</v>
       </c>
       <c r="E136" t="n">
-        <v>12.37</v>
+        <v>12.8133</v>
       </c>
       <c r="F136" t="n">
-        <v>16.5708</v>
+        <v>16.4824</v>
       </c>
     </row>
     <row r="137">
@@ -7779,19 +7779,19 @@
         <v>7117717</v>
       </c>
       <c r="B137" t="n">
-        <v>22.1481</v>
+        <v>22.3465</v>
       </c>
       <c r="C137" t="n">
-        <v>12.5342</v>
+        <v>12.4733</v>
       </c>
       <c r="D137" t="n">
-        <v>50.0077</v>
+        <v>50.2802</v>
       </c>
       <c r="E137" t="n">
-        <v>12.9247</v>
+        <v>12.9458</v>
       </c>
       <c r="F137" t="n">
-        <v>16.7849</v>
+        <v>16.799</v>
       </c>
     </row>
     <row r="138">
@@ -7799,19 +7799,19 @@
         <v>7473535</v>
       </c>
       <c r="B138" t="n">
-        <v>16.1684</v>
+        <v>16.2345</v>
       </c>
       <c r="C138" t="n">
-        <v>12.4161</v>
+        <v>12.4407</v>
       </c>
       <c r="D138" t="n">
-        <v>51.3171</v>
+        <v>51.5161</v>
       </c>
       <c r="E138" t="n">
-        <v>13.0404</v>
+        <v>13.0738</v>
       </c>
       <c r="F138" t="n">
-        <v>16.9823</v>
+        <v>16.9869</v>
       </c>
     </row>
     <row r="139">
@@ -7819,19 +7819,19 @@
         <v>7847143</v>
       </c>
       <c r="B139" t="n">
-        <v>15.6421</v>
+        <v>16.356</v>
       </c>
       <c r="C139" t="n">
-        <v>12.685</v>
+        <v>12.6322</v>
       </c>
       <c r="D139" t="n">
-        <v>52.7906</v>
+        <v>52.8037</v>
       </c>
       <c r="E139" t="n">
-        <v>13.2874</v>
+        <v>13.1684</v>
       </c>
       <c r="F139" t="n">
-        <v>17.471</v>
+        <v>17.461</v>
       </c>
     </row>
     <row r="140">
@@ -7839,19 +7839,19 @@
         <v>8239431</v>
       </c>
       <c r="B140" t="n">
-        <v>16.5641</v>
+        <v>16.5624</v>
       </c>
       <c r="C140" t="n">
-        <v>12.747</v>
+        <v>12.7963</v>
       </c>
       <c r="D140" t="n">
-        <v>54.1195</v>
+        <v>54.1246</v>
       </c>
       <c r="E140" t="n">
-        <v>13.4308</v>
+        <v>13.2283</v>
       </c>
       <c r="F140" t="n">
-        <v>17.7738</v>
+        <v>17.6621</v>
       </c>
     </row>
     <row r="141">
@@ -7859,19 +7859,19 @@
         <v>8651333</v>
       </c>
       <c r="B141" t="n">
-        <v>16.7148</v>
+        <v>16.6487</v>
       </c>
       <c r="C141" t="n">
-        <v>12.9069</v>
+        <v>12.8331</v>
       </c>
       <c r="D141" t="n">
-        <v>55.3415</v>
+        <v>55.5239</v>
       </c>
       <c r="E141" t="n">
-        <v>13.4509</v>
+        <v>12.9707</v>
       </c>
       <c r="F141" t="n">
-        <v>17.9141</v>
+        <v>17.0659</v>
       </c>
     </row>
     <row r="142">
@@ -7879,19 +7879,19 @@
         <v>9083830</v>
       </c>
       <c r="B142" t="n">
-        <v>17.0695</v>
+        <v>16.7895</v>
       </c>
       <c r="C142" t="n">
-        <v>13.0538</v>
+        <v>12.9504</v>
       </c>
       <c r="D142" t="n">
-        <v>56.781</v>
+        <v>56.9236</v>
       </c>
       <c r="E142" t="n">
-        <v>13.4066</v>
+        <v>12.7097</v>
       </c>
       <c r="F142" t="n">
-        <v>17.5497</v>
+        <v>18.234</v>
       </c>
     </row>
     <row r="143">
@@ -7899,19 +7899,19 @@
         <v>9537951</v>
       </c>
       <c r="B143" t="n">
-        <v>17.2464</v>
+        <v>16.2367</v>
       </c>
       <c r="C143" t="n">
-        <v>13.1144</v>
+        <v>13.1603</v>
       </c>
       <c r="D143" t="n">
-        <v>58.4119</v>
+        <v>58.4003</v>
       </c>
       <c r="E143" t="n">
-        <v>13.8534</v>
+        <v>13.71</v>
       </c>
       <c r="F143" t="n">
-        <v>18.0245</v>
+        <v>18.6603</v>
       </c>
     </row>
   </sheetData>
